--- a/Gear_Picker.xlsx
+++ b/Gear_Picker.xlsx
@@ -12524,7 +12524,7 @@
       </c>
       <c r="I3" s="41" t="inlineStr">
         <is>
-          <t>https://www.rei.com/product/199425/rei-co-op-flash-55-pack</t>
+          <t>https://www.rei.com/product/236975/rei-co-op-flash-55-pack-mens</t>
         </is>
       </c>
       <c r="J3" s="38" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="I21" s="41" t="inlineStr">
         <is>
-          <t>https://www.rei.com/product/106323/sea-to-summit-ultra-sil-dry-sack</t>
+          <t>https://www.rei.com/product/205635/sea-to-summit-ultra-sil-dry-sack-set-of-3</t>
         </is>
       </c>
       <c r="J21" s="38" t="inlineStr">
@@ -15035,7 +15035,7 @@
       </c>
       <c r="I30" s="41" t="inlineStr">
         <is>
-          <t>https://www.toakoutdoors.com/products/toaks-titanium-750ml-pot-with-bail-handle</t>
+          <t>https://www.toaksoutdoor.com/products/pot-750-bh</t>
         </is>
       </c>
       <c r="J30" s="38" t="inlineStr">
@@ -15314,7 +15314,7 @@
       </c>
       <c r="I33" s="41" t="inlineStr">
         <is>
-          <t>https://www.rei.com/product/807823/msr-isopro-fuel</t>
+          <t>https://www.rei.com/product/651555/msr-isopro-fuel-canister-8-oz-227-g</t>
         </is>
       </c>
       <c r="J33" s="38" t="inlineStr">
@@ -15593,7 +15593,7 @@
       </c>
       <c r="I36" s="41" t="inlineStr">
         <is>
-          <t>https://www.seatosummit.com/products/alpha-light-long-spoon</t>
+          <t>https://seatosummit.com/products/alpha-light-utensil-long-spoon</t>
         </is>
       </c>
       <c r="J36" s="38" t="inlineStr">
@@ -15868,7 +15868,7 @@
       </c>
       <c r="I39" s="41" t="inlineStr">
         <is>
-          <t>https://www.katadyn.com/us/us/8018648-befree-1-0l</t>
+          <t>https://www.rei.com/product/116364/katadyn-befree-10-l-water-filter-bottle-338-fl-oz</t>
         </is>
       </c>
       <c r="J39" s="38" t="inlineStr">
@@ -16147,7 +16147,7 @@
       </c>
       <c r="I42" s="41" t="inlineStr">
         <is>
-          <t>https://hydrapak.com/products/stow</t>
+          <t>https://www.hydrapak.com/products/stow-1-l-2021</t>
         </is>
       </c>
       <c r="J42" s="38" t="inlineStr">
@@ -16422,7 +16422,7 @@
       </c>
       <c r="I45" s="41" t="inlineStr">
         <is>
-          <t>https://ursack.com/products/ursack-major</t>
+          <t>https://ursack.com/products/ursack-major-xl-opsak</t>
         </is>
       </c>
       <c r="J45" s="38" t="inlineStr">
@@ -16697,7 +16697,7 @@
       </c>
       <c r="I48" s="41" t="inlineStr">
         <is>
-          <t>https://www.blackdiamondequipment.com/en_US/spot-400-headlamp-BD6206.html</t>
+          <t>https://blackdiamondequipment.com/products/spot-400-headlamp</t>
         </is>
       </c>
       <c r="J48" s="38" t="inlineStr">
@@ -16968,7 +16968,7 @@
       </c>
       <c r="I51" s="41" t="inlineStr">
         <is>
-          <t>https://flashlight.nitecore.com/product/nb10000-gen3</t>
+          <t>https://www.nitecore.com/product/nb10000gen3</t>
         </is>
       </c>
       <c r="J51" s="38" t="inlineStr">
@@ -17243,7 +17243,7 @@
       </c>
       <c r="I54" s="41" t="inlineStr">
         <is>
-          <t>https://www.zoleo.com/products/zoleo-satellite-communicator</t>
+          <t>https://www.zoleo.com/en-us/product/zoleo-global-satellite-communicator</t>
         </is>
       </c>
       <c r="J54" s="38" t="inlineStr">
@@ -17797,7 +17797,7 @@
       </c>
       <c r="I60" s="41" t="inlineStr">
         <is>
-          <t>https://www.leatherman.com/wingman-832524.html</t>
+          <t>https://www.leatherman.com/products/wingman</t>
         </is>
       </c>
       <c r="J60" s="38" t="inlineStr">
@@ -18068,7 +18068,7 @@
       </c>
       <c r="I63" s="41" t="inlineStr">
         <is>
-          <t>https://adventuremedicalkits.com/products/ultralight-watertight-7</t>
+          <t>https://adventuremedicalkits.com/products/ultralight-watertight-medical-kit-7</t>
         </is>
       </c>
       <c r="J63" s="38" t="inlineStr">
@@ -18343,7 +18343,7 @@
       </c>
       <c r="I66" s="41" t="inlineStr">
         <is>
-          <t>https://www.gsioutdoors.com/cathole-trowel</t>
+          <t>https://gsioutdoors.com/products/cathole-trowel</t>
         </is>
       </c>
       <c r="J66" s="38" t="inlineStr">
@@ -18610,7 +18610,7 @@
       </c>
       <c r="I69" s="41" t="inlineStr">
         <is>
-          <t>https://www.cleverhiker.com/backpacking/cascade-mountain-tech-carbon-fiber-quick-lock-review/</t>
+          <t>https://www.amazon.com/Cascade-Mountain-Tech-Carbon-Trekking/dp/B07RH3P6MT</t>
         </is>
       </c>
       <c r="J69" s="38" t="inlineStr">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="I72" s="41" t="inlineStr">
         <is>
-          <t>https://www.thermarest.com/sleeping-pads/accessories/z-seat/09632.html</t>
+          <t>https://www.rei.com/product/734520/therm-a-rest-z-seat</t>
         </is>
       </c>
       <c r="J72" s="38" t="inlineStr">
@@ -19419,7 +19419,7 @@
       </c>
       <c r="I78" s="41" t="inlineStr">
         <is>
-          <t>https://www.mensjournal.com/shopping/merrell-moab-3-hiking-shoes-sale-february-2026</t>
+          <t>https://www.rei.com/product/201989/merrell-moab-3-hiking-shoes-mens</t>
         </is>
       </c>
       <c r="J78" s="38" t="inlineStr">
@@ -19698,7 +19698,7 @@
       </c>
       <c r="I81" s="41" t="inlineStr">
         <is>
-          <t>https://www.rei.com/b/darn-tough/c/hiking-socks</t>
+          <t>https://www.rei.com/product/825037/darn-tough-hiker-micro-crew-cushion-socks-mens</t>
         </is>
       </c>
       <c r="J81" s="38" t="inlineStr">
@@ -19977,7 +19977,7 @@
       </c>
       <c r="I84" s="41" t="inlineStr">
         <is>
-          <t>https://www.rei.com/learn/expert-advice/best-hiking-pants.html</t>
+          <t>https://www.rei.com/product/127336/rei-co-op-rainier-rain-jacket-mens</t>
         </is>
       </c>
       <c r="J84" s="38" t="inlineStr">
@@ -20248,7 +20248,7 @@
       </c>
       <c r="I87" s="41" t="inlineStr">
         <is>
-          <t>https://slickdeals.net/f/19253062-patagonia-nano-puff-115-w-hoody-145-select-colors</t>
+          <t>https://www.patagonia.com/product/mens-nano-puff-insulated-jacket/84212.html</t>
         </is>
       </c>
       <c r="J87" s="38" t="inlineStr">
@@ -20527,7 +20527,7 @@
       </c>
       <c r="I90" s="41" t="inlineStr">
         <is>
-          <t>https://www.skyestoury.com/blog/fleece-mid-layers-hiking-backpacking</t>
+          <t>https://senchidesigns.com/products/a90-half-zip-hoodie</t>
         </is>
       </c>
       <c r="J90" s="38" t="inlineStr">
@@ -20802,7 +20802,7 @@
       </c>
       <c r="I93" s="41" t="inlineStr">
         <is>
-          <t>https://bikehikesafari.com/best-baselayers/</t>
+          <t>https://www.rei.com/product/174769/smartwool-classic-thermal-merino-crew-base-layer-top-mens</t>
         </is>
       </c>
       <c r="J93" s="38" t="inlineStr">
@@ -21073,7 +21073,7 @@
       </c>
       <c r="I96" s="41" t="inlineStr">
         <is>
-          <t>https://www.outdoorgearlab.com/best-hiking-pants</t>
+          <t>https://www.rei.com/product/244516/outdoor-research-ferrosi-pants-mens</t>
         </is>
       </c>
       <c r="J96" s="38" t="inlineStr">
@@ -21340,7 +21340,7 @@
       </c>
       <c r="I99" s="41" t="inlineStr">
         <is>
-          <t>https://www.adventurealan.com/best-hiking-hats/</t>
+          <t>https://www.farpointeog.com/stock/p/alpha-caps</t>
         </is>
       </c>
       <c r="J99" s="38" t="inlineStr">
@@ -21607,7 +21607,7 @@
       </c>
       <c r="I102" s="41" t="inlineStr">
         <is>
-          <t>https://www.iheartpacificnorthwest.com/blog_post/hats-gloves-and-neck-gaiters-for-hiking/</t>
+          <t>https://www.rei.com/product/871650/outdoor-research-pl-400-sensor-gloves-mens</t>
         </is>
       </c>
       <c r="J102" s="38" t="inlineStr">
@@ -21878,7 +21878,7 @@
       </c>
       <c r="I105" s="41" t="inlineStr">
         <is>
-          <t>https://www.walmart.com/c/kp/orange-hunting-vests</t>
+          <t>https://www.walmart.com/ip/Allen-Company-Deluxe-Blaze-Orange-Safety-Hunting-Vest-Medium/956427108</t>
         </is>
       </c>
       <c r="J105" s="38" t="inlineStr">
@@ -22153,7 +22153,7 @@
       </c>
       <c r="I108" s="41" t="inlineStr">
         <is>
-          <t>https://bikepacking.com/gear/ultralight-camp-shoes/</t>
+          <t>https://www.crocs.com/p/classic-clog/10001.html</t>
         </is>
       </c>
       <c r="J108" s="38" t="inlineStr">
@@ -22695,7 +22695,7 @@
       </c>
       <c r="I114" s="41" t="inlineStr">
         <is>
-          <t>https://www.walmart.com/c/kp/sock-wade</t>
+          <t>https://www.amazon.com/Fans-Neoprene-Wading-Socks-Fishing/dp/B0DW8VW4HY</t>
         </is>
       </c>
       <c r="J114" s="38" t="inlineStr">
@@ -23152,7 +23152,7 @@
       </c>
       <c r="I119" s="41" t="inlineStr">
         <is>
-          <t>https://www.goldprospectors.org/Forum/aft/9275</t>
+          <t>https://www.amazon.com/Fiskars-94216974J-Ultralight-Kneeling-Cushion/dp/B0002YTVJA</t>
         </is>
       </c>
       <c r="J119" s="38" t="inlineStr">
@@ -23795,7 +23795,7 @@
       </c>
       <c r="I126" s="41" t="inlineStr">
         <is>
-          <t>https://www.highplainsprospectors.com/products/sifting-pan</t>
+          <t>https://www.walmart.com/ip/ASR-Outdoor-Gold-Panning-Classifier-Set-Mesh-Soil-Sifter-Coarse-Combo-1-2-1-4-1-8-Inch-Mesh/585755027</t>
         </is>
       </c>
       <c r="J126" s="38" t="inlineStr">
@@ -24070,7 +24070,7 @@
       </c>
       <c r="I129" s="41" t="inlineStr">
         <is>
-          <t>https://www.adventuresinprospecting.com/products/fine-gold-recovery-clean-up-kit-vials-tweezers-snuffer-bottle-funnel-magnifer-1</t>
+          <t>https://www.amazon.com/Panning-Sniffer-Snuffer-Bottle-Tweezer/dp/B0D38QYGYR</t>
         </is>
       </c>
       <c r="J129" s="38" t="inlineStr">
@@ -24337,7 +24337,7 @@
       </c>
       <c r="I132" s="41" t="inlineStr">
         <is>
-          <t>https://www.goldfeverprospecting.com/clscandsi.html</t>
+          <t>https://www.amazon.com/Gold-Digger-Ultimate-Prospecting-Crevice/dp/B0HFKW1ZG4</t>
         </is>
       </c>
       <c r="J132" s="38" t="inlineStr">
@@ -24608,7 +24608,7 @@
       </c>
       <c r="I135" s="41" t="inlineStr">
         <is>
-          <t>https://www.highplainsprospectors.com/collections/gold-prospecting/vials-snuffer-bottles</t>
+          <t>https://www.amazon.com/ASR-Outdoor-Flake-Collection-Vials/dp/B010YGC7DM</t>
         </is>
       </c>
       <c r="J135" s="38" t="inlineStr">
@@ -24879,7 +24879,7 @@
       </c>
       <c r="I138" s="41" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Complete-Sluice-Equipment-Prospecting-Magnifier/dp/B0DBKVTLM7</t>
+          <t>https://www.amazon.com/JARLINK-Illuminated-Jewelers-Magnifier-Foldable/dp/B078N34WZR</t>
         </is>
       </c>
       <c r="J138" s="38" t="inlineStr">
@@ -25150,7 +25150,7 @@
       </c>
       <c r="I141" s="41" t="inlineStr">
         <is>
-          <t>https://www.rei.com/learn/expert-advice/best-hiking-pants.html</t>
+          <t>https://www.thetentlab.com/Deuce/DeuceofSpadespage.html</t>
         </is>
       </c>
       <c r="J141" s="38" t="inlineStr">

--- a/Gear_Picker.xlsx
+++ b/Gear_Picker.xlsx
@@ -1090,7 +1090,7 @@
     <row r="19" ht="30" customHeight="1">
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Vogel SP Oct 15-21 lows, 2020-2025, averaged 39-48F; the coldest single night was 29F (Oct 2022). NOAA's Oct-Dec 2026 outlook favors a warmer, wetter season (strong El Nino). A 30F-rated bag/quilt plus a puffy and base layer covers this comfortably for most people, and rain protection matters more than an extra 10F of bag rating this year. The 30F group is the RECOMMENDED DEFAULT on the Picker; the existing 20F group is kept as an 'alt' row (backup / more cold margin) rather than deleted.</t>
+          <t>Vogel SP Oct 15-21 lows, 2020-2025, averaged 39-48F; the coldest single night was 29F (Oct 2022). NOAA's Oct-Dec 2026 outlook favors a warmer, wetter season (strong El Nino). A 30F-rated bag/quilt plus a puffy and base layer covers this comfortably for most people, and rain protection matters more than an extra 10F of bag rating this year. The 30F group is the RECOMMENDED DEFAULT on the Picker, specifically the Budget synthetic bag (zippered, no draft-sealing technique needed) -- the Value/Premium quilts in that group are flagged BEGINNER CAUTION and are upgrade options, not the default, since a quilt with an unsealed pad gap can be a cold, unpleasant surprise on a first cold-weather trip. the existing 20F group is kept as an 'alt' row (backup / more cold margin) rather than deleted.</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Tent/shelter (his share, split w/ tentmate)</t>
+          <t>Tent/shelter (shared, split w/ tentmate)</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Sleeping bag/quilt (30F) -- RECOMMENDED default</t>
+          <t>Sleeping bag/quilt (30F) -- RECOMMENDED default, beginner-safe</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Budget</t>
         </is>
       </c>
       <c r="F11" s="10">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Stove (his share of group stove)</t>
+          <t>Stove (group/shared item)</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Cook pot (his share)</t>
+          <t>Cook pot (group/shared item)</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>Fuel canister (his share)</t>
+          <t>Fuel canister (group/shared item)</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Water filter (his share)</t>
+          <t>Water filter (group/shared item)</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>Bear-proof food storage (his share)</t>
+          <t>Bear-proof food storage (group/shared item)</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>First aid kit (his share, overnight-size)</t>
+          <t>First aid kit (group/shared item, overnight-size)</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>Satellite messenger (his share)</t>
+          <t>Satellite messenger (group/shared item)</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -5815,14 +5815,14 @@
       </c>
       <c r="C3" s="32" t="inlineStr">
         <is>
-          <t>Rook 50 (men's) / Renn 50 (women's)</t>
+          <t>Rook 65 (men's) / Renn 65 (women's)</t>
         </is>
       </c>
       <c r="D3" s="33" t="n">
         <v>66</v>
       </c>
       <c r="E3" s="34" t="n">
-        <v>155</v>
+        <v>205</v>
       </c>
       <c r="F3" s="11" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>91</v>
       </c>
       <c r="E4" s="34" t="n">
-        <v>159</v>
+        <v>259</v>
       </c>
       <c r="F4" s="11" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>18.5</v>
       </c>
       <c r="W4" s="34" t="n">
-        <v>699</v>
+        <v>749</v>
       </c>
       <c r="X4" s="11" t="inlineStr">
         <is>
@@ -6073,14 +6073,14 @@
       </c>
       <c r="C5" s="32" t="inlineStr">
         <is>
-          <t>Trestles 15 (or Kelty Cosmic 20 Synthetic)</t>
+          <t>Trestles Elite Eco 20 (or Kelty Cosmic 20 Synthetic)</t>
         </is>
       </c>
       <c r="D5" s="33" t="n">
         <v>53</v>
       </c>
       <c r="E5" s="34" t="n">
-        <v>99</v>
+        <v>179</v>
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
         <v>26</v>
       </c>
       <c r="N5" s="34" t="n">
-        <v>355</v>
+        <v>280</v>
       </c>
       <c r="O5" s="11" t="inlineStr">
         <is>
@@ -6202,14 +6202,14 @@
       </c>
       <c r="C6" s="32" t="inlineStr">
         <is>
-          <t>Insulated Static V (or Static V2)</t>
+          <t>Insulated Static V Peak</t>
         </is>
       </c>
       <c r="D6" s="33" t="n">
         <v>25</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>74.95</v>
+        <v>99.95</v>
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>2</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>2.5</v>
       </c>
       <c r="N7" s="34" t="n">
-        <v>54.95</v>
+        <v>64.95</v>
       </c>
       <c r="O7" s="11" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>2.5</v>
       </c>
       <c r="W7" s="34" t="n">
-        <v>54.95</v>
+        <v>59.95</v>
       </c>
       <c r="X7" s="11" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>2</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
@@ -6506,7 +6506,7 @@
         <v>5</v>
       </c>
       <c r="N8" s="34" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="O8" s="11" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>3.5</v>
       </c>
       <c r="W8" s="34" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="X8" s="11" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
@@ -6628,14 +6628,14 @@
       </c>
       <c r="L9" s="35" t="inlineStr">
         <is>
-          <t>Ultra-Sil Dry Sack (set of 2-3 sizes, e.g. 8L + 13L)</t>
+          <t>Ultra-Sil Dry Bag - Set of 3</t>
         </is>
       </c>
       <c r="M9" s="33" t="n">
         <v>2.5</v>
       </c>
       <c r="N9" s="34" t="n">
-        <v>40</v>
+        <v>69.95</v>
       </c>
       <c r="O9" s="11" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>1</v>
       </c>
       <c r="W9" s="34" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="X9" s="11" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         <v>1.4</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>0.9</v>
       </c>
       <c r="N10" s="34" t="n">
-        <v>6</v>
+        <v>2.49</v>
       </c>
       <c r="O10" s="11" t="inlineStr">
         <is>
@@ -6796,7 +6796,7 @@
       </c>
       <c r="U10" s="36" t="inlineStr">
         <is>
-          <t>eVent Dry Pack Liner</t>
+          <t>Evac Lightweight Dry Bag (35L)</t>
         </is>
       </c>
       <c r="V10" s="33" t="n">
@@ -6893,7 +6893,7 @@
         <v>3.5</v>
       </c>
       <c r="N11" s="34" t="n">
-        <v>64.95</v>
+        <v>69.95</v>
       </c>
       <c r="O11" s="11" t="inlineStr">
         <is>
@@ -6932,7 +6932,7 @@
         <v>7.1</v>
       </c>
       <c r="W11" s="34" t="n">
-        <v>154.95</v>
+        <v>131</v>
       </c>
       <c r="X11" s="11" t="inlineStr">
         <is>
@@ -6976,14 +6976,14 @@
       </c>
       <c r="C12" s="32" t="inlineStr">
         <is>
-          <t>Aluminum camp pot ~1.5qt</t>
+          <t>A004-025001 Aluminum Sauce Pan, 1-Quart</t>
         </is>
       </c>
       <c r="D12" s="33" t="n">
         <v>6</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>11.99</v>
+        <v>12.99</v>
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
@@ -7015,14 +7015,14 @@
       </c>
       <c r="L12" s="35" t="inlineStr">
         <is>
-          <t>750ml Titanium Pot (POT-750-RS)</t>
+          <t>750ml Titanium Pot with Bail Handle (POT-750-BH)</t>
         </is>
       </c>
       <c r="M12" s="33" t="n">
         <v>4.1</v>
       </c>
       <c r="N12" s="34" t="n">
-        <v>33.95</v>
+        <v>30</v>
       </c>
       <c r="O12" s="11" t="inlineStr">
         <is>
@@ -7054,18 +7054,18 @@
       </c>
       <c r="U12" s="36" t="inlineStr">
         <is>
-          <t>Titanium UL Pasta Pot (ECA267)</t>
+          <t>Trek 900 Titanium Cookset</t>
         </is>
       </c>
       <c r="V12" s="33" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="W12" s="34" t="n">
-        <v>54.99</v>
+        <v>54.95</v>
       </c>
       <c r="X12" s="11" t="inlineStr">
         <is>
-          <t>$35-45 (limited US stock)</t>
+          <t>$35-45</t>
         </is>
       </c>
       <c r="Y12" s="11" t="n">
@@ -7078,7 +7078,7 @@
       </c>
       <c r="AA12" s="11" t="inlineStr">
         <is>
-          <t>Long-time favorite among serious UL hikers for its insulated handles and slightly better pour spout; Treeline Review calls it a runner-up 'Best Upgrade' pick, but flags Evernew has cut back US distribution, making it harder to buy than TOAKS in 2026.</t>
+          <t>Snow Peak's Trek 900 is the standard premium alternative once Evernew stock dries up; Treeline Review and forum threads treat TOAKS/Snow Peak/Evernew as near-interchangeable in quality at this size.</t>
         </is>
       </c>
       <c r="AB12" s="11" t="inlineStr">
@@ -7105,11 +7105,11 @@
       </c>
       <c r="C13" s="32" t="inlineStr">
         <is>
-          <t>PowerMax 100g canister</t>
+          <t>Butane/Propane Mix Fuel, 7.75oz (220g)</t>
         </is>
       </c>
       <c r="D13" s="33" t="n">
-        <v>7.4</v>
+        <v>7.75</v>
       </c>
       <c r="E13" s="34" t="n">
         <v>5.97</v>
@@ -7151,7 +7151,7 @@
         <v>13.7</v>
       </c>
       <c r="N13" s="34" t="n">
-        <v>10.95</v>
+        <v>6.95</v>
       </c>
       <c r="O13" s="11" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         <v>7.6</v>
       </c>
       <c r="W13" s="34" t="n">
-        <v>6.95</v>
+        <v>5.95</v>
       </c>
       <c r="X13" s="11" t="inlineStr">
         <is>
@@ -7234,14 +7234,14 @@
       </c>
       <c r="C14" s="32" t="inlineStr">
         <is>
-          <t>Titanium long-handled spork</t>
+          <t>Titanium Spork</t>
         </is>
       </c>
       <c r="D14" s="33" t="n">
         <v>0.6</v>
       </c>
       <c r="E14" s="34" t="n">
-        <v>7.99</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
@@ -7273,14 +7273,14 @@
       </c>
       <c r="L14" s="35" t="inlineStr">
         <is>
-          <t>Alpha Light Long Spoon</t>
+          <t>Frontier Ultralight Spoon - Long Handle</t>
         </is>
       </c>
       <c r="M14" s="33" t="n">
         <v>0.6</v>
       </c>
       <c r="N14" s="34" t="n">
-        <v>9.949999999999999</v>
+        <v>10.95</v>
       </c>
       <c r="O14" s="11" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>0.6</v>
       </c>
       <c r="W14" s="34" t="n">
-        <v>14.5</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="X14" s="11" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>3</v>
       </c>
       <c r="E15" s="34" t="n">
-        <v>29.96</v>
+        <v>45.95</v>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
@@ -7448,7 +7448,7 @@
         <v>15.9</v>
       </c>
       <c r="W15" s="34" t="n">
-        <v>89.95</v>
+        <v>99.95</v>
       </c>
       <c r="X15" s="11" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>1.6</v>
       </c>
       <c r="E16" s="34" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>1.4</v>
       </c>
       <c r="N16" s="34" t="n">
-        <v>21.95</v>
+        <v>18</v>
       </c>
       <c r="O16" s="11" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
         <v>3.6</v>
       </c>
       <c r="W16" s="34" t="n">
-        <v>27.95</v>
+        <v>25</v>
       </c>
       <c r="X16" s="11" t="inlineStr">
         <is>
@@ -7621,14 +7621,14 @@
       </c>
       <c r="C17" s="32" t="inlineStr">
         <is>
-          <t>PCT-style bear hang kit (rope + stuff sack + carabiner)</t>
+          <t>Easy to Throw Bear Bag Hanging Kit (#371486)</t>
         </is>
       </c>
       <c r="D17" s="33" t="n">
         <v>6</v>
       </c>
       <c r="E17" s="34" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
@@ -7667,7 +7667,7 @@
         <v>10.8</v>
       </c>
       <c r="N17" s="34" t="n">
-        <v>109.9</v>
+        <v>149.95</v>
       </c>
       <c r="O17" s="11" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         <v>3</v>
       </c>
       <c r="N18" s="34" t="n">
-        <v>44.95</v>
+        <v>59.95</v>
       </c>
       <c r="O18" s="11" t="inlineStr">
         <is>
@@ -7879,14 +7879,14 @@
       </c>
       <c r="C19" s="32" t="inlineStr">
         <is>
-          <t>PowerCore Slim 10000</t>
+          <t>Power Bank, 10,000mAh Portable Charger (PowerIQ, USB-C)</t>
         </is>
       </c>
       <c r="D19" s="33" t="n">
         <v>6.3</v>
       </c>
       <c r="E19" s="34" t="n">
-        <v>23.99</v>
+        <v>21.99</v>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>5.1</v>
       </c>
       <c r="N19" s="34" t="n">
-        <v>54.95</v>
+        <v>64.95</v>
       </c>
       <c r="O19" s="11" t="inlineStr">
         <is>
@@ -7964,7 +7964,7 @@
         <v>5</v>
       </c>
       <c r="W19" s="34" t="n">
-        <v>59.95</v>
+        <v>83.95</v>
       </c>
       <c r="X19" s="11" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>5.4</v>
       </c>
       <c r="N20" s="34" t="n">
-        <v>199.99</v>
+        <v>199</v>
       </c>
       <c r="O20" s="11" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>1.6</v>
       </c>
       <c r="E22" s="34" t="n">
-        <v>19.95</v>
+        <v>22</v>
       </c>
       <c r="F22" s="11" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         <v>7.2</v>
       </c>
       <c r="N22" s="34" t="n">
-        <v>44.95</v>
+        <v>49.95</v>
       </c>
       <c r="O22" s="11" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>4.4</v>
       </c>
       <c r="N23" s="34" t="n">
-        <v>31.95</v>
+        <v>44.99</v>
       </c>
       <c r="O23" s="11" t="inlineStr">
         <is>
@@ -8480,7 +8480,7 @@
         <v>16</v>
       </c>
       <c r="W23" s="34" t="n">
-        <v>74.95</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="X23" s="11" t="inlineStr">
         <is>
@@ -8524,14 +8524,14 @@
       </c>
       <c r="C24" s="32" t="inlineStr">
         <is>
-          <t>Plastic trowel + basic hygiene bag</t>
+          <t>Backpackers Trowel + basic hygiene bag</t>
         </is>
       </c>
       <c r="D24" s="33" t="n">
         <v>2</v>
       </c>
       <c r="E24" s="34" t="n">
-        <v>8</v>
+        <v>8.75</v>
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>2.4</v>
       </c>
       <c r="N24" s="34" t="n">
-        <v>9.949999999999999</v>
+        <v>7.95</v>
       </c>
       <c r="O24" s="11" t="inlineStr">
         <is>
@@ -8602,14 +8602,14 @@
       </c>
       <c r="U24" s="36" t="inlineStr">
         <is>
-          <t>The Deuce of Spades #2 (titanium)</t>
+          <t>The DirtSaw Deuce #2 Trowel</t>
         </is>
       </c>
       <c r="V24" s="33" t="n">
         <v>0.6</v>
       </c>
       <c r="W24" s="34" t="n">
-        <v>24.95</v>
+        <v>21.95</v>
       </c>
       <c r="X24" s="11" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         <v>18</v>
       </c>
       <c r="E25" s="34" t="n">
-        <v>35.99</v>
+        <v>39.99</v>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>10.9</v>
       </c>
       <c r="W25" s="34" t="n">
-        <v>189.95</v>
+        <v>219.95</v>
       </c>
       <c r="X25" s="11" t="inlineStr">
         <is>
@@ -8911,14 +8911,14 @@
       </c>
       <c r="C27" s="32" t="inlineStr">
         <is>
-          <t>Foam slide sandals</t>
+          <t>Gabe Cloud Slide Sandals</t>
         </is>
       </c>
       <c r="D27" s="33" t="n">
         <v>6</v>
       </c>
       <c r="E27" s="34" t="n">
-        <v>9.99</v>
+        <v>19.99</v>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
@@ -8989,14 +8989,14 @@
       </c>
       <c r="U27" s="36" t="inlineStr">
         <is>
-          <t>Z-Trail sandal</t>
+          <t>Z-Trail EV Sandals</t>
         </is>
       </c>
       <c r="V27" s="33" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="W27" s="34" t="n">
-        <v>69.98999999999999</v>
+        <v>80</v>
       </c>
       <c r="X27" s="11" t="inlineStr">
         <is>
@@ -9055,11 +9055,11 @@
         </is>
       </c>
       <c r="G28" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>Fine for warm-ish days (50s-60s) with wool socks; cold nights mean you must have a fully dry pair to change into</t>
+          <t>BEGINNER CAUTION: fine for warm-ish days (50s-60s) with wool socks, but repeated wading in low-30s/40s creek water in non-insulated mesh trail runners risks cold feet/mild hypothermia for someone inexperienced with cold-water wading; a beginner should plan on wading boots/neoprene socks or accept wet feet only briefly and dry out fast near a fire, not as an all-day creek-panning shoe</t>
         </is>
       </c>
       <c r="I28" s="11" t="inlineStr">
@@ -9254,7 +9254,7 @@
         <v>3.2</v>
       </c>
       <c r="W29" s="34" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="X29" s="11" t="inlineStr">
         <is>
@@ -9512,7 +9512,7 @@
         <v>8.9</v>
       </c>
       <c r="W31" s="34" t="n">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="X31" s="11" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>12</v>
       </c>
       <c r="E32" s="34" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>8</v>
       </c>
       <c r="E33" s="34" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>11</v>
       </c>
       <c r="W33" s="34" t="n">
-        <v>190</v>
+        <v>235</v>
       </c>
       <c r="X33" s="11" t="inlineStr">
         <is>
@@ -9821,7 +9821,7 @@
         <v>11</v>
       </c>
       <c r="E34" s="34" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
@@ -9892,14 +9892,14 @@
       </c>
       <c r="U34" s="36" t="inlineStr">
         <is>
-          <t>Stretch Zion Cargo Pants</t>
+          <t>Stretch Zion Straight Pants (cargo version discontinued, replaced by current lineup)</t>
         </is>
       </c>
       <c r="V34" s="33" t="n">
         <v>14</v>
       </c>
       <c r="W34" s="34" t="n">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="X34" s="11" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
       </c>
       <c r="U38" s="36" t="inlineStr">
         <is>
-          <t>Cairn Adventure Sandals</t>
+          <t>Cairn Evo Adventure Sandals (current lineup; original Cairn Adventure Sandal discontinued)</t>
         </is>
       </c>
       <c r="V38" s="33" t="n">
@@ -10802,7 +10802,7 @@
         <v>38</v>
       </c>
       <c r="W41" s="34" t="n">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="X41" s="11" t="inlineStr">
         <is>
@@ -11627,7 +11627,7 @@
         <v>1</v>
       </c>
       <c r="E48" s="34" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F48" s="11" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>2</v>
       </c>
       <c r="W48" s="34" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="X48" s="11" t="inlineStr">
         <is>
@@ -11756,7 +11756,7 @@
         <v>6</v>
       </c>
       <c r="E49" s="34" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
@@ -11795,7 +11795,7 @@
         <v>0.6</v>
       </c>
       <c r="N49" s="34" t="n">
-        <v>22.5</v>
+        <v>20.95</v>
       </c>
       <c r="O49" s="11" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>30F-rated sleeping bag/quilt (RECOMMENDED default)</t>
+          <t>30F-rated sleeping bag/quilt (RECOMMENDED default -- beginner-safe pick)</t>
         </is>
       </c>
       <c r="C52" s="32" t="inlineStr">
@@ -12415,7 +12415,7 @@
       </c>
       <c r="E2" s="37" t="inlineStr">
         <is>
-          <t>Rook 50 (men's) / Renn 50 (women's)</t>
+          <t>Rook 65 (men's) / Renn 65 (women's)</t>
         </is>
       </c>
       <c r="F2" s="39" t="n">
@@ -12427,11 +12427,11 @@
         </is>
       </c>
       <c r="H2" s="40" t="n">
-        <v>155</v>
+        <v>205</v>
       </c>
       <c r="I2" s="41" t="inlineStr">
         <is>
-          <t>https://www.rei.com/product/231462/osprey-rook-50-pack-mens</t>
+          <t>https://www.rei.com/product/231463/osprey-rook-65-pack-mens</t>
         </is>
       </c>
       <c r="J2" s="38" t="inlineStr">
@@ -12706,11 +12706,11 @@
         </is>
       </c>
       <c r="H5" s="40" t="n">
-        <v>159</v>
+        <v>259</v>
       </c>
       <c r="I5" s="41" t="inlineStr">
         <is>
-          <t>https://www.rei.com/product/199426/rei-co-op-trail-hut-2-tent</t>
+          <t>https://www.rei.com/product/C03309/rei-co-op-trail-hut-2-tent-with-footprint</t>
         </is>
       </c>
       <c r="J5" s="38" t="inlineStr">
@@ -12892,7 +12892,7 @@
         </is>
       </c>
       <c r="H7" s="40" t="n">
-        <v>699</v>
+        <v>749</v>
       </c>
       <c r="I7" s="41" t="inlineStr">
         <is>
@@ -12973,7 +12973,7 @@
       </c>
       <c r="E8" s="37" t="inlineStr">
         <is>
-          <t>Trestles 15 (or Kelty Cosmic 20 Synthetic)</t>
+          <t>Trestles Elite Eco 20 (or Kelty Cosmic 20 Synthetic)</t>
         </is>
       </c>
       <c r="F8" s="39" t="n">
@@ -12985,11 +12985,11 @@
         </is>
       </c>
       <c r="H8" s="40" t="n">
-        <v>99</v>
+        <v>179</v>
       </c>
       <c r="I8" s="41" t="inlineStr">
         <is>
-          <t>https://www.rei.com/product/126630/marmot-trestles-15-sleeping-bag</t>
+          <t>https://www.rei.com/product/245787/marmot-trestles-elite-eco-20-sleeping-bag</t>
         </is>
       </c>
       <c r="J8" s="38" t="inlineStr">
@@ -13078,7 +13078,7 @@
         </is>
       </c>
       <c r="H9" s="40" t="n">
-        <v>355</v>
+        <v>280</v>
       </c>
       <c r="I9" s="41" t="inlineStr">
         <is>
@@ -13252,7 +13252,7 @@
       </c>
       <c r="E11" s="37" t="inlineStr">
         <is>
-          <t>Insulated Static V (or Static V2)</t>
+          <t>Insulated Static V Peak</t>
         </is>
       </c>
       <c r="F11" s="39" t="n">
@@ -13264,11 +13264,11 @@
         </is>
       </c>
       <c r="H11" s="40" t="n">
-        <v>74.95</v>
+        <v>99.95</v>
       </c>
       <c r="I11" s="41" t="inlineStr">
         <is>
-          <t>https://klymit.com/products/insulated-static-v-sleeping-pad-4-pack</t>
+          <t>https://klymit.com/products/insulated-static-v-peak-sleeping-pads</t>
         </is>
       </c>
       <c r="J11" s="38" t="inlineStr">
@@ -13543,11 +13543,11 @@
         </is>
       </c>
       <c r="H14" s="40" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I14" s="41" t="inlineStr">
         <is>
-          <t>https://www.rei.com/product/199426/rei-co-op-trail-hut-2-tent</t>
+          <t>https://www.amazon.com/dp/B0896WCB5D</t>
         </is>
       </c>
       <c r="J14" s="38" t="inlineStr">
@@ -13636,7 +13636,7 @@
         </is>
       </c>
       <c r="H15" s="40" t="n">
-        <v>54.95</v>
+        <v>64.95</v>
       </c>
       <c r="I15" s="41" t="inlineStr">
         <is>
@@ -13686,7 +13686,7 @@
       </c>
       <c r="S15" s="38" t="inlineStr">
         <is>
-          <t>The standard (non-down) Aeros Premium is ~$10 cheaper and works fine too if warmth-at-the-head doesn't matter</t>
+          <t>The standard (non-down) Aeros Premium is ~$10 cheaper and works fine too if warmth-at-the-head doesn't matter | TIER ODDITY: Value ($64.95) costs more than Premium ($59.95) in this category -- kept as sourced, not auto-corrected.</t>
         </is>
       </c>
       <c r="T15">
@@ -13729,11 +13729,11 @@
         </is>
       </c>
       <c r="H16" s="40" t="n">
-        <v>54.95</v>
+        <v>59.95</v>
       </c>
       <c r="I16" s="41" t="inlineStr">
         <is>
-          <t>https://www.rei.com/product/128558/nemo-fillo-elite-pillow</t>
+          <t>https://www.rei.com/product/170457/nemo-fillo-elite-pillow</t>
         </is>
       </c>
       <c r="J16" s="38" t="inlineStr">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="S16" s="38" t="inlineStr">
         <is>
-          <t>Genuinely a coin-flip vs. the Sea to Summit Aeros — 'premium' here reflects feel/comfort preference, not a real capability gap; buy whichever is on sale</t>
+          <t>Genuinely a coin-flip vs. the Sea to Summit Aeros — 'premium' here reflects feel/comfort preference, not a real capability gap; buy whichever is on sale | TIER ODDITY: Premium ($59.95) is cheaper than Value ($64.95) in this category -- kept as sourced.</t>
         </is>
       </c>
       <c r="T16">
@@ -13822,11 +13822,11 @@
         </is>
       </c>
       <c r="H17" s="40" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I17" s="41" t="inlineStr">
         <is>
-          <t>https://www.gossamergear.com/products/polycryo-ground-cloth</t>
+          <t>https://www.gossamergear.com/products/polycryo-tent-footprint-ground-cloths</t>
         </is>
       </c>
       <c r="J17" s="38" t="inlineStr">
@@ -13915,11 +13915,11 @@
         </is>
       </c>
       <c r="H18" s="40" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I18" s="41" t="inlineStr">
         <is>
-          <t>https://sectionhiker.com/ultralight-backpacking-tent-footprint-substitutions/</t>
+          <t>https://www.amazon.com/dp/B0CWDQDS32</t>
         </is>
       </c>
       <c r="J18" s="38" t="inlineStr">
@@ -14008,11 +14008,11 @@
         </is>
       </c>
       <c r="H19" s="40" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="I19" s="41" t="inlineStr">
         <is>
-          <t>https://durstongear.com/products/x-mid-2-footprint</t>
+          <t>https://durstongear.com/products/x-mid-2-groundsheet</t>
         </is>
       </c>
       <c r="J19" s="38" t="inlineStr">
@@ -14101,11 +14101,11 @@
         </is>
       </c>
       <c r="H20" s="40" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I20" s="41" t="inlineStr">
         <is>
-          <t>https://www.walmart.com/ip/55048225</t>
+          <t>https://www.amazon.com/dp/B0028CXKQE</t>
         </is>
       </c>
       <c r="J20" s="38" t="inlineStr">
@@ -14182,7 +14182,7 @@
       </c>
       <c r="E21" s="37" t="inlineStr">
         <is>
-          <t>Ultra-Sil Dry Sack (set of 2-3 sizes, e.g. 8L + 13L)</t>
+          <t>Ultra-Sil Dry Bag - Set of 3</t>
         </is>
       </c>
       <c r="F21" s="39" t="n">
@@ -14194,11 +14194,11 @@
         </is>
       </c>
       <c r="H21" s="40" t="n">
-        <v>40</v>
+        <v>69.95</v>
       </c>
       <c r="I21" s="41" t="inlineStr">
         <is>
-          <t>https://www.rei.com/product/205635/sea-to-summit-ultra-sil-dry-sack-set-of-3</t>
+          <t>https://www.rei.com/product/218733/sea-to-summit-ultra-sil-dry-bag-set-of-3</t>
         </is>
       </c>
       <c r="J21" s="38" t="inlineStr">
@@ -14244,7 +14244,7 @@
       </c>
       <c r="S21" s="38" t="inlineStr">
         <is>
-          <t>Sized an 8L for the sleeping bag/quilt + a 4L or 1L for electronics/fire-starting kit covers this trip well | TIER ODDITY: Value ($40.00) costs more than Premium ($33.00) in this category -- kept as sourced, not auto-corrected.</t>
+          <t>Sized an 8L for the sleeping bag/quilt + a 4L or 1L for electronics/fire-starting kit covers this trip well | TIER ODDITY: Value ($69.95) costs more than Premium ($31.00) in this category -- kept as sourced, not auto-corrected.</t>
         </is>
       </c>
       <c r="T21">
@@ -14287,11 +14287,11 @@
         </is>
       </c>
       <c r="H22" s="40" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I22" s="41" t="inlineStr">
         <is>
-          <t>https://hyperlitemountaingear.com/products/stuff-sacks</t>
+          <t>https://hyperlitemountaingear.com/products/drawstring-stuff-sacks</t>
         </is>
       </c>
       <c r="J22" s="38" t="inlineStr">
@@ -14337,7 +14337,7 @@
       </c>
       <c r="S22" s="38" t="inlineStr">
         <is>
-          <t>Skip for this trip specifically — recommended only if the buyer is already committed to backpacking as an ongoing hobby | TIER ODDITY: Premium ($33.00) is cheaper than Value ($40.00) in this category -- kept as sourced.</t>
+          <t>Skip for this trip specifically — recommended only if the buyer is already committed to backpacking as an ongoing hobby | TIER ODDITY: Premium ($31.00) is cheaper than Value ($69.95) in this category -- kept as sourced.</t>
         </is>
       </c>
       <c r="T22">
@@ -14380,11 +14380,11 @@
         </is>
       </c>
       <c r="H23" s="40" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I23" s="41" t="inlineStr">
         <is>
-          <t>https://www.99boulders.com/best-pack-liners</t>
+          <t>https://www.amazon.com/dp/B07SM88VVF</t>
         </is>
       </c>
       <c r="J23" s="38" t="inlineStr">
@@ -14430,7 +14430,7 @@
       </c>
       <c r="S23" s="38" t="inlineStr">
         <is>
-          <t>Already correctly identified in the existing gear.md as the go-to; this confirms it against wider community sourcing</t>
+          <t>Already correctly identified in the existing gear.md as the go-to; this confirms it against wider community sourcing | TIER ODDITY: Budget ($10.00) costs more than Value ($2.49) in this category -- kept as sourced.</t>
         </is>
       </c>
       <c r="T23">
@@ -14473,7 +14473,7 @@
         </is>
       </c>
       <c r="H24" s="40" t="n">
-        <v>6</v>
+        <v>2.49</v>
       </c>
       <c r="I24" s="41" t="inlineStr">
         <is>
@@ -14523,7 +14523,7 @@
       </c>
       <c r="S24" s="38" t="inlineStr">
         <is>
-          <t>Marginal upgrade — not worth agonizing over vs. the free compactor-bag option for a single trip</t>
+          <t>Marginal upgrade — not worth agonizing over vs. the free compactor-bag option for a single trip | TIER ODDITY: Value ($2.49) is cheaper than Budget ($10.00) in this category -- kept as sourced.</t>
         </is>
       </c>
       <c r="T24">
@@ -14554,7 +14554,7 @@
       </c>
       <c r="E25" s="37" t="inlineStr">
         <is>
-          <t>eVent Dry Pack Liner</t>
+          <t>Evac Lightweight Dry Bag (35L)</t>
         </is>
       </c>
       <c r="F25" s="39" t="n">
@@ -14570,7 +14570,7 @@
       </c>
       <c r="I25" s="41" t="inlineStr">
         <is>
-          <t>https://www.rei.com/product/106325/sea-to-summit-event-dry-pack-liner</t>
+          <t>https://www.rei.com/product/246133/sea-to-summit-evac-lightweight-dry-bag</t>
         </is>
       </c>
       <c r="J25" s="38" t="inlineStr">
@@ -14752,11 +14752,11 @@
         </is>
       </c>
       <c r="H27" s="40" t="n">
-        <v>64.95</v>
+        <v>69.95</v>
       </c>
       <c r="I27" s="41" t="inlineStr">
         <is>
-          <t>https://www.rei.com/product/128793/soto-windmaster-stove</t>
+          <t>https://www.rei.com/product/177954/soto-windmaster-stove-with-4flex-pot-support</t>
         </is>
       </c>
       <c r="J27" s="38" t="inlineStr">
@@ -14845,11 +14845,11 @@
         </is>
       </c>
       <c r="H28" s="40" t="n">
-        <v>154.95</v>
+        <v>131</v>
       </c>
       <c r="I28" s="41" t="inlineStr">
         <is>
-          <t>https://www.jetboil.com/products/stash-cooking-system</t>
+          <t>https://www.amazon.com/Jetboil-Ultralight-Camping-Backpacking-Cooking/dp/B08QRLT8QH</t>
         </is>
       </c>
       <c r="J28" s="38" t="inlineStr">
@@ -14921,12 +14921,12 @@
       </c>
       <c r="D29" s="37" t="inlineStr">
         <is>
-          <t>IMUSA / generic</t>
+          <t>IMUSA</t>
         </is>
       </c>
       <c r="E29" s="37" t="inlineStr">
         <is>
-          <t>Aluminum camp pot ~1.5qt</t>
+          <t>A004-025001 Aluminum Sauce Pan, 1-Quart</t>
         </is>
       </c>
       <c r="F29" s="39" t="n">
@@ -14934,15 +14934,15 @@
       </c>
       <c r="G29" s="38" t="inlineStr">
         <is>
-          <t>typical stamped-aluminum camp pot weight; EST from category norms, not individually spec-verified this session</t>
+          <t>typical stamped-aluminum camp pot weight; EST from category norms, not individually spec-verified this session; only 1qt capacity — buy two for group boiling of 6</t>
         </is>
       </c>
       <c r="H29" s="40" t="n">
-        <v>11.99</v>
+        <v>12.99</v>
       </c>
       <c r="I29" s="41" t="inlineStr">
         <is>
-          <t>https://www.walmart.com/browse/camping-cookware</t>
+          <t>https://www.amazon.com/IMUSA-A004-025001-Aluminum-1-Quart-Silver/dp/B0018E9UV2</t>
         </is>
       </c>
       <c r="J29" s="38" t="inlineStr">
@@ -15019,7 +15019,7 @@
       </c>
       <c r="E30" s="37" t="inlineStr">
         <is>
-          <t>750ml Titanium Pot (POT-750-RS)</t>
+          <t>750ml Titanium Pot with Bail Handle (POT-750-BH)</t>
         </is>
       </c>
       <c r="F30" s="39" t="n">
@@ -15031,7 +15031,7 @@
         </is>
       </c>
       <c r="H30" s="40" t="n">
-        <v>33.95</v>
+        <v>30</v>
       </c>
       <c r="I30" s="41" t="inlineStr">
         <is>
@@ -15107,43 +15107,43 @@
       </c>
       <c r="D31" s="37" t="inlineStr">
         <is>
-          <t>Evernew</t>
+          <t>Snow Peak</t>
         </is>
       </c>
       <c r="E31" s="37" t="inlineStr">
         <is>
-          <t>Titanium UL Pasta Pot (ECA267)</t>
+          <t>Trek 900 Titanium Cookset</t>
         </is>
       </c>
       <c r="F31" s="39" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="G31" s="38" t="inlineStr">
         <is>
-          <t>manufacturer spec ~100g/3.5oz for the 0.9L pasta pot; increasingly hard to find due to reduced US distribution</t>
+          <t>REI spec 6oz/170g for the 2-piece cookset (900ml pot + pan/lid); swapped in for the Evernew pasta pot, which is discontinued/unavailable in the US as of 2026</t>
         </is>
       </c>
       <c r="H31" s="40" t="n">
-        <v>54.99</v>
+        <v>54.95</v>
       </c>
       <c r="I31" s="41" t="inlineStr">
         <is>
-          <t>https://www.evernew-outdoor.jp/</t>
+          <t>https://www.rei.com/product/768602/snow-peak-trek-900-titanium-cookset</t>
         </is>
       </c>
       <c r="J31" s="38" t="inlineStr">
         <is>
-          <t>$35-45 (limited US stock)</t>
+          <t>$35-45</t>
         </is>
       </c>
       <c r="K31" s="38" t="inlineStr">
         <is>
-          <t>Evernew Japan direct, occasional REI/Backcountry stock, eBay</t>
+          <t>REI, Amazon, Snow Peak direct</t>
         </is>
       </c>
       <c r="L31" s="38" t="inlineStr">
         <is>
-          <t>Long-time favorite among serious UL hikers for its insulated handles and slightly better pour spout; Treeline Review calls it a runner-up 'Best Upgrade' pick, but flags Evernew has cut back US distribution, making it harder to buy than TOAKS in 2026.</t>
+          <t>Snow Peak's Trek 900 is the standard premium alternative once Evernew stock dries up; Treeline Review and forum threads treat TOAKS/Snow Peak/Evernew as near-interchangeable in quality at this size.</t>
         </is>
       </c>
       <c r="M31" s="38" t="inlineStr">
@@ -15174,7 +15174,7 @@
       </c>
       <c r="S31" s="38" t="inlineStr">
         <is>
-          <t>Group share $9.17 — flag as possibly discontinued/limited in US retail as of 2026</t>
+          <t>Group share $9.16</t>
         </is>
       </c>
       <c r="T31">
@@ -15205,15 +15205,15 @@
       </c>
       <c r="E32" s="37" t="inlineStr">
         <is>
-          <t>PowerMax 100g canister</t>
+          <t>Butane/Propane Mix Fuel, 7.75oz (220g)</t>
         </is>
       </c>
       <c r="F32" s="39" t="n">
-        <v>7.4</v>
+        <v>7.75</v>
       </c>
       <c r="G32" s="38" t="inlineStr">
         <is>
-          <t>100g fuel + canister, ~7.4oz total per typical 100g canister spec</t>
+          <t>Walmart spec, 220g fuel canister</t>
         </is>
       </c>
       <c r="H32" s="40" t="n">
@@ -15221,7 +15221,7 @@
       </c>
       <c r="I32" s="41" t="inlineStr">
         <is>
-          <t>https://www.walmart.com/browse/camping-fuel</t>
+          <t>https://www.walmart.com/ip/Coleman-Butane-Propane-Mix-Fuel-7-75oz/20595064</t>
         </is>
       </c>
       <c r="J32" s="38" t="inlineStr">
@@ -15310,7 +15310,7 @@
         </is>
       </c>
       <c r="H33" s="40" t="n">
-        <v>10.95</v>
+        <v>6.95</v>
       </c>
       <c r="I33" s="41" t="inlineStr">
         <is>
@@ -15360,7 +15360,7 @@
       </c>
       <c r="S33" s="38" t="inlineStr">
         <is>
-          <t>Group share $1.83; consider the 4oz can instead ($6-7) to match actual need | TIER ODDITY: Value ($10.95) costs more than Premium ($6.95) in this category -- kept as sourced, not auto-corrected.</t>
+          <t>Group share $1.83; consider the 4oz can instead ($6-7) to match actual need | TIER ODDITY: Value ($6.95) costs more than Premium ($5.95) in this category -- kept as sourced, not auto-corrected.</t>
         </is>
       </c>
       <c r="T33">
@@ -15403,11 +15403,11 @@
         </is>
       </c>
       <c r="H34" s="40" t="n">
-        <v>6.95</v>
+        <v>5.95</v>
       </c>
       <c r="I34" s="41" t="inlineStr">
         <is>
-          <t>https://www.rei.com/product/807823/msr-isopro-fuel</t>
+          <t>https://www.rei.com/product/849634/msr-isopro-fuel-canister-39-oz-110-g</t>
         </is>
       </c>
       <c r="J34" s="38" t="inlineStr">
@@ -15453,7 +15453,7 @@
       </c>
       <c r="S34" s="38" t="inlineStr">
         <is>
-          <t>Group share $1.16; fuel is not a category worth upgrading — put the money into the stove instead | TIER ODDITY: Premium ($6.95) is cheaper than Value ($10.95) in this category -- kept as sourced.</t>
+          <t>Group share $1.16; fuel is not a category worth upgrading — put the money into the stove instead | TIER ODDITY: Premium ($5.95) is cheaper than Value ($6.95) in this category -- kept as sourced.</t>
         </is>
       </c>
       <c r="T34">
@@ -15479,12 +15479,12 @@
       </c>
       <c r="D35" s="37" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>TOAKS</t>
         </is>
       </c>
       <c r="E35" s="37" t="inlineStr">
         <is>
-          <t>Titanium long-handled spork</t>
+          <t>Titanium Spork</t>
         </is>
       </c>
       <c r="F35" s="39" t="n">
@@ -15496,11 +15496,11 @@
         </is>
       </c>
       <c r="H35" s="40" t="n">
-        <v>7.99</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="I35" s="41" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/s?k=titanium+long+spork</t>
+          <t>https://www.rei.com/product/139476/toaks-titanium-spork</t>
         </is>
       </c>
       <c r="J35" s="38" t="inlineStr">
@@ -15577,7 +15577,7 @@
       </c>
       <c r="E36" s="37" t="inlineStr">
         <is>
-          <t>Alpha Light Long Spoon</t>
+          <t>Frontier Ultralight Spoon - Long Handle</t>
         </is>
       </c>
       <c r="F36" s="39" t="n">
@@ -15589,7 +15589,7 @@
         </is>
       </c>
       <c r="H36" s="40" t="n">
-        <v>9.949999999999999</v>
+        <v>10.95</v>
       </c>
       <c r="I36" s="41" t="inlineStr">
         <is>
@@ -15637,7 +15637,11 @@
       <c r="R36" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="S36" s="38" t="inlineStr"/>
+      <c r="S36" s="38" t="inlineStr">
+        <is>
+          <t>TIER ODDITY: Value ($10.95) costs more than Premium ($9.95) in this category -- kept as sourced, not auto-corrected.</t>
+        </is>
+      </c>
       <c r="T36">
         <f>A36&amp;"|"&amp;C36</f>
         <v/>
@@ -15678,11 +15682,11 @@
         </is>
       </c>
       <c r="H37" s="40" t="n">
-        <v>14.5</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="I37" s="41" t="inlineStr">
         <is>
-          <t>https://www.snowpeak.com/products/spork-single-eat-105</t>
+          <t>https://www.rei.com/product/660002/snow-peak-titanium-spork</t>
         </is>
       </c>
       <c r="J37" s="38" t="inlineStr">
@@ -15728,7 +15732,7 @@
       </c>
       <c r="S37" s="38" t="inlineStr">
         <is>
-          <t>Skip this upgrade — put the money toward the water filter or bag instead</t>
+          <t>Skip this upgrade — put the money toward the water filter or bag instead | TIER ODDITY: Premium ($9.95) is cheaper than Value ($10.95) in this category -- kept as sourced.</t>
         </is>
       </c>
       <c r="T37">
@@ -15771,11 +15775,11 @@
         </is>
       </c>
       <c r="H38" s="40" t="n">
-        <v>29.96</v>
+        <v>45.95</v>
       </c>
       <c r="I38" s="41" t="inlineStr">
         <is>
-          <t>https://www.sawyer.com/products/squeeze-filter</t>
+          <t>https://www.rei.com/product/103050/sawyer-squeeze-water-filter-system</t>
         </is>
       </c>
       <c r="J38" s="38" t="inlineStr">
@@ -15821,7 +15825,7 @@
       </c>
       <c r="S38" s="38" t="inlineStr">
         <is>
-          <t>Group share $5.00</t>
+          <t>Group share $5.00 | TIER ODDITY: Budget ($45.95) costs more than Value ($44.95) in this category -- kept as sourced.</t>
         </is>
       </c>
       <c r="T38">
@@ -15914,7 +15918,7 @@
       </c>
       <c r="S39" s="38" t="inlineStr">
         <is>
-          <t>Group share $7.49; still needs to sleep in the bag on the cold night</t>
+          <t>Group share $7.49; still needs to sleep in the bag on the cold night | TIER ODDITY: Value ($44.95) is cheaper than Budget ($45.95) in this category -- kept as sourced.</t>
         </is>
       </c>
       <c r="T39">
@@ -15957,11 +15961,11 @@
         </is>
       </c>
       <c r="H40" s="40" t="n">
-        <v>89.95</v>
+        <v>99.95</v>
       </c>
       <c r="I40" s="41" t="inlineStr">
         <is>
-          <t>https://grayl.com/products/geopress</t>
+          <t>https://www.rei.com/product/150116/grayl-geopress-water-filter-and-purifier-bottle-24-fl-oz</t>
         </is>
       </c>
       <c r="J40" s="38" t="inlineStr">
@@ -16050,11 +16054,11 @@
         </is>
       </c>
       <c r="H41" s="40" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="I41" s="41" t="inlineStr">
         <is>
-          <t>https://www.walmart.com/ip/smartwater-1-liter/</t>
+          <t>https://www.walmart.com/ip/smartwater-vapor-distilled-premium-water-1-liter-bottle/14944716</t>
         </is>
       </c>
       <c r="J41" s="38" t="inlineStr">
@@ -16143,7 +16147,7 @@
         </is>
       </c>
       <c r="H42" s="40" t="n">
-        <v>21.95</v>
+        <v>18</v>
       </c>
       <c r="I42" s="41" t="inlineStr">
         <is>
@@ -16232,11 +16236,11 @@
         </is>
       </c>
       <c r="H43" s="40" t="n">
-        <v>27.95</v>
+        <v>25</v>
       </c>
       <c r="I43" s="41" t="inlineStr">
         <is>
-          <t>https://cnocoutdoors.com/products/vecto-2l-water-container</t>
+          <t>https://www.amazon.com/Cnoc-Outdoors-Container-Thread-Orange/dp/B07QBQ894L</t>
         </is>
       </c>
       <c r="J43" s="38" t="inlineStr">
@@ -16308,12 +16312,12 @@
       </c>
       <c r="D44" s="37" t="inlineStr">
         <is>
-          <t>DIY</t>
+          <t>Liberty Mountain</t>
         </is>
       </c>
       <c r="E44" s="37" t="inlineStr">
         <is>
-          <t>PCT-style bear hang kit (rope + stuff sack + carabiner)</t>
+          <t>Easy to Throw Bear Bag Hanging Kit (#371486)</t>
         </is>
       </c>
       <c r="F44" s="39" t="n">
@@ -16325,11 +16329,11 @@
         </is>
       </c>
       <c r="H44" s="40" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="I44" s="41" t="inlineStr">
         <is>
-          <t>https://www.rei.com/c/paracord</t>
+          <t>https://www.amazon.com/Liberty-Mountain-371486-Throw-Hanging/dp/B005U5J934</t>
         </is>
       </c>
       <c r="J44" s="38" t="inlineStr">
@@ -16418,7 +16422,7 @@
         </is>
       </c>
       <c r="H45" s="40" t="n">
-        <v>109.9</v>
+        <v>149.95</v>
       </c>
       <c r="I45" s="41" t="inlineStr">
         <is>
@@ -16468,7 +16472,7 @@
       </c>
       <c r="S45" s="38" t="inlineStr">
         <is>
-          <t>Group share $18.32; this is the pick most aligned with what experienced Southeast hikers use | TIER ODDITY: Value ($109.90) costs more than Premium ($99.95) in this category -- kept as sourced, not auto-corrected.</t>
+          <t>Group share $18.32; this is the pick most aligned with what experienced Southeast hikers use | TIER ODDITY: Value ($149.95) costs more than Premium ($99.95) in this category -- kept as sourced, not auto-corrected.</t>
         </is>
       </c>
       <c r="T45">
@@ -16561,7 +16565,7 @@
       </c>
       <c r="S46" s="38" t="inlineStr">
         <is>
-          <t>Group share $16.66; not necessary for this specific trip | TIER ODDITY: Premium ($99.95) is cheaper than Value ($109.90) in this category -- kept as sourced.</t>
+          <t>Group share $16.66; not necessary for this specific trip | TIER ODDITY: Premium ($99.95) is cheaper than Value ($149.95) in this category -- kept as sourced.</t>
         </is>
       </c>
       <c r="T46">
@@ -16693,7 +16697,7 @@
         </is>
       </c>
       <c r="H48" s="40" t="n">
-        <v>44.95</v>
+        <v>59.95</v>
       </c>
       <c r="I48" s="41" t="inlineStr">
         <is>
@@ -16741,7 +16745,11 @@
       <c r="R48" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="S48" s="38" t="inlineStr"/>
+      <c r="S48" s="38" t="inlineStr">
+        <is>
+          <t>TIER ODDITY: Value ($59.95) costs more than Premium ($54.95) in this category -- kept as sourced, not auto-corrected.</t>
+        </is>
+      </c>
       <c r="T48">
         <f>A48&amp;"|"&amp;C48</f>
         <v/>
@@ -16786,7 +16794,7 @@
       </c>
       <c r="I49" s="41" t="inlineStr">
         <is>
-          <t>https://flashlight.nitecore.com/product/nu25</t>
+          <t>https://www.nitecore.com/product/nu25</t>
         </is>
       </c>
       <c r="J49" s="38" t="inlineStr">
@@ -16832,7 +16840,7 @@
       </c>
       <c r="S49" s="38" t="inlineStr">
         <is>
-          <t>Bring the power bank to recharge it if the trip runs long</t>
+          <t>Bring the power bank to recharge it if the trip runs long | TIER ODDITY: Premium ($54.95) is cheaper than Value ($59.95) in this category -- kept as sourced.</t>
         </is>
       </c>
       <c r="T49">
@@ -16863,7 +16871,7 @@
       </c>
       <c r="E50" s="37" t="inlineStr">
         <is>
-          <t>PowerCore Slim 10000</t>
+          <t>Power Bank, 10,000mAh Portable Charger (PowerIQ, USB-C)</t>
         </is>
       </c>
       <c r="F50" s="39" t="n">
@@ -16875,11 +16883,11 @@
         </is>
       </c>
       <c r="H50" s="40" t="n">
-        <v>23.99</v>
+        <v>21.99</v>
       </c>
       <c r="I50" s="41" t="inlineStr">
         <is>
-          <t>https://www.anker.com/products/a1229-powercore-slim-10000</t>
+          <t>https://www.amazon.com/Anker-Portable-Charger-PowerIQ-Battery/dp/B0D5CLSMFB</t>
         </is>
       </c>
       <c r="J50" s="38" t="inlineStr">
@@ -16964,11 +16972,11 @@
         </is>
       </c>
       <c r="H51" s="40" t="n">
-        <v>54.95</v>
+        <v>64.95</v>
       </c>
       <c r="I51" s="41" t="inlineStr">
         <is>
-          <t>https://www.nitecore.com/product/nb10000gen3</t>
+          <t>https://www.amazon.com/NITECORE-NB10000-GEN3-Portable-Charger/dp/B0H85CT2GM</t>
         </is>
       </c>
       <c r="J51" s="38" t="inlineStr">
@@ -17053,11 +17061,11 @@
         </is>
       </c>
       <c r="H52" s="40" t="n">
-        <v>59.95</v>
+        <v>83.95</v>
       </c>
       <c r="I52" s="41" t="inlineStr">
         <is>
-          <t>https://flashlight.nitecore.com/product/nb10000-gen4</t>
+          <t>https://www.amazon.com/Nitecore-NB10000-Gen4-Ultralight-Waterproof/dp/B0H61KHJ1X</t>
         </is>
       </c>
       <c r="J52" s="38" t="inlineStr">
@@ -17239,7 +17247,7 @@
         </is>
       </c>
       <c r="H54" s="40" t="n">
-        <v>199.99</v>
+        <v>199</v>
       </c>
       <c r="I54" s="41" t="inlineStr">
         <is>
@@ -17704,11 +17712,11 @@
         </is>
       </c>
       <c r="H59" s="40" t="n">
-        <v>19.95</v>
+        <v>22</v>
       </c>
       <c r="I59" s="41" t="inlineStr">
         <is>
-          <t>https://www.opinel-usa.com/products/no-08-stainless-steel</t>
+          <t>https://www.rei.com/product/884528/opinel-no-8-beechwood-handle-knife</t>
         </is>
       </c>
       <c r="J59" s="38" t="inlineStr">
@@ -17793,7 +17801,7 @@
         </is>
       </c>
       <c r="H60" s="40" t="n">
-        <v>44.95</v>
+        <v>49.95</v>
       </c>
       <c r="I60" s="41" t="inlineStr">
         <is>
@@ -17886,7 +17894,7 @@
       </c>
       <c r="I61" s="41" t="inlineStr">
         <is>
-          <t>https://www.leatherman.com/skeletool-cx-832180.html</t>
+          <t>https://www.rei.com/product/762082/leatherman-skeletool-cx-multi-tool</t>
         </is>
       </c>
       <c r="J61" s="38" t="inlineStr">
@@ -18064,7 +18072,7 @@
         </is>
       </c>
       <c r="H63" s="40" t="n">
-        <v>31.95</v>
+        <v>44.99</v>
       </c>
       <c r="I63" s="41" t="inlineStr">
         <is>
@@ -18157,7 +18165,7 @@
         </is>
       </c>
       <c r="H64" s="40" t="n">
-        <v>74.95</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="I64" s="41" t="inlineStr">
         <is>
@@ -18238,7 +18246,7 @@
       </c>
       <c r="E65" s="37" t="inlineStr">
         <is>
-          <t>Plastic trowel + basic hygiene bag</t>
+          <t>Backpackers Trowel + basic hygiene bag</t>
         </is>
       </c>
       <c r="F65" s="39" t="n">
@@ -18250,11 +18258,11 @@
         </is>
       </c>
       <c r="H65" s="40" t="n">
-        <v>8</v>
+        <v>8.75</v>
       </c>
       <c r="I65" s="41" t="inlineStr">
         <is>
-          <t>https://www.rei.com/c/first-aid</t>
+          <t>https://www.walmart.com/ip/Coghlan-S-Backpackers-Trowel/23233743</t>
         </is>
       </c>
       <c r="J65" s="38" t="inlineStr">
@@ -18298,7 +18306,11 @@
       <c r="R65" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="S65" s="38" t="inlineStr"/>
+      <c r="S65" s="38" t="inlineStr">
+        <is>
+          <t>TIER ODDITY: Budget ($8.75) costs more than Value ($7.95) in this category -- kept as sourced.</t>
+        </is>
+      </c>
       <c r="T65">
         <f>A65&amp;"|"&amp;C65</f>
         <v/>
@@ -18339,7 +18351,7 @@
         </is>
       </c>
       <c r="H66" s="40" t="n">
-        <v>9.949999999999999</v>
+        <v>7.95</v>
       </c>
       <c r="I66" s="41" t="inlineStr">
         <is>
@@ -18387,7 +18399,11 @@
       <c r="R66" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="S66" s="38" t="inlineStr"/>
+      <c r="S66" s="38" t="inlineStr">
+        <is>
+          <t>TIER ODDITY: Value ($7.95) is cheaper than Budget ($8.75) in this category -- kept as sourced.</t>
+        </is>
+      </c>
       <c r="T66">
         <f>A66&amp;"|"&amp;C66</f>
         <v/>
@@ -18416,7 +18432,7 @@
       </c>
       <c r="E67" s="37" t="inlineStr">
         <is>
-          <t>The Deuce of Spades #2 (titanium)</t>
+          <t>The DirtSaw Deuce #2 Trowel</t>
         </is>
       </c>
       <c r="F67" s="39" t="n">
@@ -18428,11 +18444,11 @@
         </is>
       </c>
       <c r="H67" s="40" t="n">
-        <v>24.95</v>
+        <v>21.95</v>
       </c>
       <c r="I67" s="41" t="inlineStr">
         <is>
-          <t>https://www.thetentlab.com/collections/the-deuce</t>
+          <t>https://www.rei.com/product/225131/thetentlab-the-dirtsaw-deuce-2-trowel</t>
         </is>
       </c>
       <c r="J67" s="38" t="inlineStr">
@@ -18517,11 +18533,11 @@
         </is>
       </c>
       <c r="H68" s="40" t="n">
-        <v>35.99</v>
+        <v>39.99</v>
       </c>
       <c r="I68" s="41" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/s?k=trailbuddy+trekking+poles</t>
+          <t>https://www.amazon.com/dp/B07C46QPTR</t>
         </is>
       </c>
       <c r="J68" s="38" t="inlineStr">
@@ -18695,11 +18711,11 @@
         </is>
       </c>
       <c r="H70" s="40" t="n">
-        <v>189.95</v>
+        <v>219.95</v>
       </c>
       <c r="I70" s="41" t="inlineStr">
         <is>
-          <t>https://www.blackdiamondequipment.com/en_US/distance-carbon-z-trekking-poles-BD1125.html</t>
+          <t>https://www.rei.com/product/246033/black-diamond-distance-carbon-z-trekking-poles-pair</t>
         </is>
       </c>
       <c r="J70" s="38" t="inlineStr">
@@ -18788,7 +18804,7 @@
       </c>
       <c r="I71" s="41" t="inlineStr">
         <is>
-          <t>https://www.rei.com/c/sleeping-pads</t>
+          <t>https://www.amazon.com/Hit-Delights-Backpacking-Insulation-Lightweight/dp/B06XCWC6T9</t>
         </is>
       </c>
       <c r="J71" s="38" t="inlineStr">
@@ -18798,7 +18814,7 @@
       </c>
       <c r="K71" s="38" t="inlineStr">
         <is>
-          <t>scrap from any CCF sleeping pad</t>
+          <t>scrap cut from any CCF sleeping pad (link is a cheap CCF pad to cut from if none on hand, ~$11)</t>
         </is>
       </c>
       <c r="L71" s="38" t="inlineStr">
@@ -19034,12 +19050,12 @@
       </c>
       <c r="D74" s="37" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>Alpine Swiss</t>
         </is>
       </c>
       <c r="E74" s="37" t="inlineStr">
         <is>
-          <t>Foam slide sandals</t>
+          <t>Gabe Cloud Slide Sandals</t>
         </is>
       </c>
       <c r="F74" s="39" t="n">
@@ -19051,11 +19067,11 @@
         </is>
       </c>
       <c r="H74" s="40" t="n">
-        <v>9.99</v>
+        <v>19.99</v>
       </c>
       <c r="I74" s="41" t="inlineStr">
         <is>
-          <t>https://www.walmart.com/browse/shoes</t>
+          <t>https://www.amazon.com/Alpine-Swiss-Sandals-Adjustable-Athletic/dp/B09G4P66R5</t>
         </is>
       </c>
       <c r="J74" s="38" t="inlineStr">
@@ -19221,7 +19237,7 @@
       </c>
       <c r="E76" s="37" t="inlineStr">
         <is>
-          <t>Z-Trail sandal</t>
+          <t>Z-Trail EV Sandals</t>
         </is>
       </c>
       <c r="F76" s="39" t="n">
@@ -19233,11 +19249,11 @@
         </is>
       </c>
       <c r="H76" s="40" t="n">
-        <v>69.98999999999999</v>
+        <v>80</v>
       </c>
       <c r="I76" s="41" t="inlineStr">
         <is>
-          <t>https://xeroshoes.com/shop/z-trail-mens/</t>
+          <t>https://www.rei.com/product/185226/xero-shoes-z-trail-ev-sandals-mens</t>
         </is>
       </c>
       <c r="J76" s="38" t="inlineStr">
@@ -19361,18 +19377,18 @@
       </c>
       <c r="P77" s="38" t="inlineStr">
         <is>
-          <t>Fine for warm-ish days (50s-60s) with wool socks; cold nights mean you must have a fully dry pair to change into</t>
+          <t>BEGINNER CAUTION: fine for warm-ish days (50s-60s) with wool socks, but repeated wading in low-30s/40s creek water in non-insulated mesh trail runners risks cold feet/mild hypothermia for someone inexperienced with cold-water wading; a beginner should plan on wading boots/neoprene socks or accept wet feet only briefly and dry out fast near a fire, not as an all-day creek-panning shoe</t>
         </is>
       </c>
       <c r="Q77" s="37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R77" s="37" t="n">
         <v>1</v>
       </c>
       <c r="S77" s="38" t="inlineStr">
         <is>
-          <t>Only use if already broken in — do not wear brand-new unbroken shoes on the trip</t>
+          <t>Only use if already broken in — do not wear brand-new unbroken shoes on the trip. Not the recommended default for beginners on this trip; pair with the neoprene wading sock / water shoe options below for cold creek work</t>
         </is>
       </c>
       <c r="T77">
@@ -19605,7 +19621,7 @@
       </c>
       <c r="I80" s="41" t="inlineStr">
         <is>
-          <t>https://www.rei.com/b/darn-tough/c/hiking-socks</t>
+          <t>https://www.rei.com/product/165398/rei-co-op-merino-wool-lightweight-hiking-crew-socks</t>
         </is>
       </c>
       <c r="J80" s="38" t="inlineStr">
@@ -19787,11 +19803,11 @@
         </is>
       </c>
       <c r="H82" s="40" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="I82" s="41" t="inlineStr">
         <is>
-          <t>https://www.rei.com/b/darn-tough/c/hiking-socks</t>
+          <t>https://www.sealskinzusa.com/products/waterproof-all-weather-mid-length-sock</t>
         </is>
       </c>
       <c r="J82" s="38" t="inlineStr">
@@ -20066,7 +20082,7 @@
       </c>
       <c r="I85" s="41" t="inlineStr">
         <is>
-          <t>https://www.treelinereview.com/gearreviews/best-lightweight-rain-jackets</t>
+          <t>https://www.rei.com/product/166198/outdoor-research-helium-rain-jacket-mens</t>
         </is>
       </c>
       <c r="J85" s="38" t="inlineStr">
@@ -20294,7 +20310,7 @@
       </c>
       <c r="S87" s="38" t="inlineStr">
         <is>
-          <t>Watch for sales — this jacket routinely drops to $115-150 | TIER ODDITY: Value ($239.00) costs more than Premium ($200.00) in this category -- kept as sourced, not auto-corrected.</t>
+          <t>Watch for sales — this jacket routinely drops to $115-150 | TIER ODDITY: Value ($239.00) costs more than Premium ($170.00) in this category -- kept as sourced, not auto-corrected.</t>
         </is>
       </c>
       <c r="T87">
@@ -20337,11 +20353,11 @@
         </is>
       </c>
       <c r="H88" s="40" t="n">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="I88" s="41" t="inlineStr">
         <is>
-          <t>https://www.adventurealan.com/enlightened-equipment-torrid-apex-jacket-review/</t>
+          <t>https://enlightenedequipment.com/mens-torrid-jacket/</t>
         </is>
       </c>
       <c r="J88" s="38" t="inlineStr">
@@ -20387,7 +20403,7 @@
       </c>
       <c r="S88" s="38" t="inlineStr">
         <is>
-          <t>Order now if going this route — cottage lead times can blow the Oct 15 deadline | TIER ODDITY: Premium ($200.00) is cheaper than Value ($239.00) in this category -- kept as sourced.</t>
+          <t>Order now if going this route — cottage lead times can blow the Oct 15 deadline | TIER ODDITY: Premium ($170.00) is cheaper than Value ($239.00) in this category -- kept as sourced.</t>
         </is>
       </c>
       <c r="T88">
@@ -20430,11 +20446,11 @@
         </is>
       </c>
       <c r="H89" s="40" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I89" s="41" t="inlineStr">
         <is>
-          <t>https://www.skyestoury.com/blog/fleece-mid-layers-hiking-backpacking</t>
+          <t>https://www.decathlon.com/products/mens-hiking-fleece-mh100-312361</t>
         </is>
       </c>
       <c r="J89" s="38" t="inlineStr">
@@ -20705,11 +20721,11 @@
         </is>
       </c>
       <c r="H92" s="40" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="I92" s="41" t="inlineStr">
         <is>
-          <t>https://mydroneauthority.com/best-merino-wool-base-layers/</t>
+          <t>https://merino.tech/products/men-250-base-layer-set-wool-clothing</t>
         </is>
       </c>
       <c r="J92" s="38" t="inlineStr">
@@ -20755,7 +20771,7 @@
       </c>
       <c r="S92" s="38" t="inlineStr">
         <is>
-          <t>Reserve this set exclusively as dry sleep clothes — never wear it panning</t>
+          <t>Reserve this set exclusively as dry sleep clothes — never wear it panning | TIER ODDITY: Budget ($100.00) costs more than Value ($95.00) in this category -- kept as sourced.</t>
         </is>
       </c>
       <c r="T92">
@@ -20846,7 +20862,11 @@
       <c r="R93" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="S93" s="38" t="inlineStr"/>
+      <c r="S93" s="38" t="inlineStr">
+        <is>
+          <t>TIER ODDITY: Value ($95.00) is cheaper than Budget ($100.00) in this category -- kept as sourced.</t>
+        </is>
+      </c>
       <c r="T93">
         <f>A93&amp;"|"&amp;C93</f>
         <v/>
@@ -20887,11 +20907,11 @@
         </is>
       </c>
       <c r="H94" s="40" t="n">
-        <v>190</v>
+        <v>235</v>
       </c>
       <c r="I94" s="41" t="inlineStr">
         <is>
-          <t>https://bettertrail.com/outdoor-gear/best-base-layers</t>
+          <t>https://www.rei.com/product/139520/icebreaker-200-oasis-half-zip-base-layer-top-mens</t>
         </is>
       </c>
       <c r="J94" s="38" t="inlineStr">
@@ -20976,11 +20996,11 @@
         </is>
       </c>
       <c r="H95" s="40" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="I95" s="41" t="inlineStr">
         <is>
-          <t>https://www.rei.com/learn/expert-advice/best-hiking-pants.html</t>
+          <t>https://www.rei.com/product/236137/rei-co-op-trailmade-pants-mens</t>
         </is>
       </c>
       <c r="J95" s="38" t="inlineStr">
@@ -21146,7 +21166,7 @@
       </c>
       <c r="E97" s="37" t="inlineStr">
         <is>
-          <t>Stretch Zion Cargo Pants</t>
+          <t>Stretch Zion Straight Pants (cargo version discontinued, replaced by current lineup)</t>
         </is>
       </c>
       <c r="F97" s="39" t="n">
@@ -21158,11 +21178,11 @@
         </is>
       </c>
       <c r="H97" s="40" t="n">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="I97" s="41" t="inlineStr">
         <is>
-          <t>https://www.rei.com/b/prana/c/mens-hiking-pants</t>
+          <t>https://www.rei.com/product/134025/prana-stretch-zion-straight-pants-mens</t>
         </is>
       </c>
       <c r="J97" s="38" t="inlineStr">
@@ -21251,7 +21271,7 @@
       </c>
       <c r="I98" s="41" t="inlineStr">
         <is>
-          <t>https://www.iheartpacificnorthwest.com/blog_post/hats-gloves-and-neck-gaiters-for-hiking/</t>
+          <t>https://www.amazon.com/Wmcaps-Winter-Beanie-Hats-for-Men-Women-Fleece-Lined-Beanie-Soft-Warm-Knit-Hat-Ski-Stocking-Cuffed-Cap/dp/B0BBZZZH84</t>
         </is>
       </c>
       <c r="J98" s="38" t="inlineStr">
@@ -21429,7 +21449,7 @@
       </c>
       <c r="I100" s="41" t="inlineStr">
         <is>
-          <t>https://www.iheartpacificnorthwest.com/blog_post/hats-gloves-and-neck-gaiters-for-hiking/</t>
+          <t>https://www.rei.com/product/217179/smartwool-merino-250-reversible-pattern-cuffed-beanie</t>
         </is>
       </c>
       <c r="J100" s="38" t="inlineStr">
@@ -21518,7 +21538,7 @@
       </c>
       <c r="I101" s="41" t="inlineStr">
         <is>
-          <t>https://www.iheartpacificnorthwest.com/blog_post/hats-gloves-and-neck-gaiters-for-hiking/</t>
+          <t>https://www.walmart.com/ip/2844295050</t>
         </is>
       </c>
       <c r="J101" s="38" t="inlineStr">
@@ -21696,7 +21716,7 @@
       </c>
       <c r="I103" s="41" t="inlineStr">
         <is>
-          <t>https://www.iheartpacificnorthwest.com/blog_post/hats-gloves-and-neck-gaiters-for-hiking/</t>
+          <t>https://opossumworld.com/collections/mens-gloves/possum-merino</t>
         </is>
       </c>
       <c r="J103" s="38" t="inlineStr">
@@ -22226,7 +22246,7 @@
       </c>
       <c r="E109" s="37" t="inlineStr">
         <is>
-          <t>Cairn Adventure Sandals</t>
+          <t>Cairn Evo Adventure Sandals (current lineup; original Cairn Adventure Sandal discontinued)</t>
         </is>
       </c>
       <c r="F109" s="39" t="n">
@@ -22242,7 +22262,7 @@
       </c>
       <c r="I109" s="41" t="inlineStr">
         <is>
-          <t>https://www.adventurealan.com/ultralight-sandals-backpacking/</t>
+          <t>https://bedrocksandals.com/products/cairn-evo</t>
         </is>
       </c>
       <c r="J109" s="38" t="inlineStr">
@@ -23055,11 +23075,11 @@
         </is>
       </c>
       <c r="H118" s="40" t="n">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="I118" s="41" t="inlineStr">
         <is>
-          <t>https://www.rei.com/learn/expert-advice/best-hiking-pants.html</t>
+          <t>https://fishwest.com/products/simms-tributary-stockingfoot-waders-mens</t>
         </is>
       </c>
       <c r="J118" s="38" t="inlineStr">
@@ -23245,7 +23265,7 @@
       </c>
       <c r="I120" s="41" t="inlineStr">
         <is>
-          <t>https://www.goldprospectors.org/Forum/aft/9275</t>
+          <t>https://www.amazon.com/NoCry-Home-Gardening-Knee-Pads/dp/B06XJ2BFW7</t>
         </is>
       </c>
       <c r="J120" s="38" t="inlineStr">
@@ -23837,11 +23857,11 @@
         <v>4</v>
       </c>
       <c r="R126" s="37" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S126" s="38" t="inlineStr">
         <is>
-          <t>Could be one shared set at the base-camp pan-out station rather than one per person</t>
+          <t>One shared set at the base-camp pan-out station, split 6 ways, rather than one per person</t>
         </is>
       </c>
       <c r="T126">
@@ -24786,11 +24806,11 @@
         </is>
       </c>
       <c r="H137" s="40" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="I137" s="41" t="inlineStr">
         <is>
-          <t>https://ukgoldprospector.co.uk/news/best-equipment-gold-prospecting-uk.html</t>
+          <t>https://www.amazon.com/Magnifier-Portable-Keychain-Diamonds-Antiques/dp/B09B1ZBY47</t>
         </is>
       </c>
       <c r="J137" s="38" t="inlineStr">
@@ -24834,7 +24854,11 @@
       <c r="R137" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="S137" s="38" t="inlineStr"/>
+      <c r="S137" s="38" t="inlineStr">
+        <is>
+          <t>TIER ODDITY: Budget ($19.00) costs more than Value ($13.00) in this category -- kept as sourced.</t>
+        </is>
+      </c>
       <c r="T137">
         <f>A137&amp;"|"&amp;C137</f>
         <v/>
@@ -24923,7 +24947,11 @@
       <c r="R138" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="S138" s="38" t="inlineStr"/>
+      <c r="S138" s="38" t="inlineStr">
+        <is>
+          <t>TIER ODDITY: Value ($13.00) is cheaper than Budget ($19.00) in this category -- kept as sourced.</t>
+        </is>
+      </c>
       <c r="T138">
         <f>A138&amp;"|"&amp;C138</f>
         <v/>
@@ -24964,11 +24992,11 @@
         </is>
       </c>
       <c r="H139" s="40" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I139" s="41" t="inlineStr">
         <is>
-          <t>https://ukgoldprospector.co.uk/news/best-equipment-gold-prospecting-uk.html</t>
+          <t>https://cooltools.us/products/loupe-triplet-10x</t>
         </is>
       </c>
       <c r="J139" s="38" t="inlineStr">
@@ -25053,11 +25081,11 @@
         </is>
       </c>
       <c r="H140" s="40" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I140" s="41" t="inlineStr">
         <is>
-          <t>https://www.walmart.com/ip/613426092</t>
+          <t>https://www.walmart.com/ip/Fiskars-Indoor-and-More-Garden-Trowel-Soil-Scoop-Black/5371466767</t>
         </is>
       </c>
       <c r="J140" s="38" t="inlineStr">
@@ -25146,7 +25174,7 @@
         </is>
       </c>
       <c r="H141" s="40" t="n">
-        <v>22.5</v>
+        <v>20.95</v>
       </c>
       <c r="I141" s="41" t="inlineStr">
         <is>
@@ -25851,7 +25879,7 @@
       </c>
       <c r="B149" s="38" t="inlineStr">
         <is>
-          <t>30F-rated sleeping bag/quilt (RECOMMENDED default)</t>
+          <t>30F-rated sleeping bag/quilt (RECOMMENDED default -- beginner-safe pick)</t>
         </is>
       </c>
       <c r="C149" s="37" t="inlineStr">
@@ -25928,7 +25956,7 @@
       </c>
       <c r="S149" s="38" t="inlineStr">
         <is>
-          <t>NEW group added 2026-09-21 alongside the existing 20F group per updated weather research; recommended DEFAULT pick for this trip</t>
+          <t>NEW group added 2026-09-21 alongside the existing 20F group per updated weather research; RECOMMENDED DEFAULT pick for this trip -- zippered synthetic bag is the beginner-safe choice for freezing/damp deer-season nights (no draft-sealing technique to learn)</t>
         </is>
       </c>
       <c r="T149">
@@ -25944,7 +25972,7 @@
       </c>
       <c r="B150" s="38" t="inlineStr">
         <is>
-          <t>30F-rated sleeping bag/quilt (RECOMMENDED default)</t>
+          <t>30F-rated sleeping bag/quilt (upgrade option, not the default -- BEGINNER CAUTION: quilt)</t>
         </is>
       </c>
       <c r="C150" s="37" t="inlineStr">
@@ -26021,7 +26049,7 @@
       </c>
       <c r="S150" s="38" t="inlineStr">
         <is>
-          <t>NEW group added 2026-09-21; recommended DEFAULT pick — best weight/cost balance for this trip's actual verified temps</t>
+          <t>NEW group added 2026-09-21; BEGINNER CAUTION -- quilts have no zipper/hood and rely on a correct pad seal to avoid drafts; risky for a first cold-weather trip if unpracticed. Best weight/cost balance IF the group is comfortable with a quilt, but the Budget synthetic bag above is the safer default for beginners.</t>
         </is>
       </c>
       <c r="T150">
@@ -26037,7 +26065,7 @@
       </c>
       <c r="B151" s="38" t="inlineStr">
         <is>
-          <t>30F-rated sleeping bag/quilt (RECOMMENDED default)</t>
+          <t>30F-rated sleeping bag/quilt (upgrade option, not the default -- BEGINNER CAUTION: quilt)</t>
         </is>
       </c>
       <c r="C151" s="37" t="inlineStr">

--- a/Gear_Picker.xlsx
+++ b/Gear_Picker.xlsx
@@ -968,7 +968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B28"/>
+  <dimension ref="B2:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1083,68 +1083,75 @@
     <row r="18">
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Sleep system note (added 2026-09-21)</t>
+          <t>Sleep system note (updated 2026-09-23 -- now a temperature choice)</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="B19" s="4" t="inlineStr">
         <is>
+          <t>The sleeping bag/quilt + pad is now a mutually exclusive TEMPERATURE choice -- 40F+, 30F, or 20F -- each with its own Budget and Solid bag+pad pair, sourced in research\gear-tiers-sleep-temp.json. Only ONE band counts toward the trip totals; see the 'Sleep system -- temperature choice' table near the top of BUY_LIST.md for all three bands' prices side by side (the other two are priced alternatives, not added in). DEFAULT = 30F. Pad R-value floor per band: 40F+ needs R2-3, 30F needs R3-4, 20F needs R4.5+ -- the Budget pick in each band is the cheapest bag/pad that still clears that band's own floor, never the cheapest bag/pad overall. The three legacy Picker rows for sleep_system/sleep_system_30f/sleeping_pad are kept Skipped for reference weight only and no longer drive the buy list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="B20" s="4" t="inlineStr">
+        <is>
           <t>Vogel SP Oct 15-21 lows, 2020-2025, averaged 39-48F; the coldest single night was 29F (Oct 2022). NOAA's Oct-Dec 2026 outlook favors a warmer, wetter season (strong El Nino). A 30F-rated bag/quilt plus a puffy and base layer covers this comfortably for most people, and rain protection matters more than an extra 10F of bag rating this year. The 30F group is the RECOMMENDED DEFAULT on the Picker, specifically the Budget synthetic bag (zippered, no draft-sealing technique needed) -- the Value/Premium quilts in that group are flagged BEGINNER CAUTION and are upgrade options, not the default, since a quilt with an unsealed pad gap can be a cold, unpleasant surprise on a first cold-weather trip. the existing 20F group is kept as an 'alt' row (backup / more cold margin) rather than deleted.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="3" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Tier oddities</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="B21" s="4" t="inlineStr">
+    <row r="22" ht="30" customHeight="1">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Where a Value pick is priced above its Premium counterpart (or Budget above Value) in the source research, it is kept exactly as sourced and flagged with a 'TIER ODDITY' note in that item's Notes column on Options/Picker/Compare -- never silently re-tiered.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="3" t="inlineStr">
+    <row r="23">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Sources &amp; date</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="B23" s="4" t="inlineStr">
+    <row r="24" ht="30" customHeight="1">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Built 2026-09-21 from research\gear-tiers-*.json, research\gear.md, and a short web check for the new 30F sleep-system picks (REI, Enlightened Equipment, Katabatic Gear). Prices/weights are as sourced on that date -- re-verify before buying, especially anything cottage-made (lead times) or on sale.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="5" t="inlineStr">
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>Tier color key:</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="6" t="inlineStr">
+    <row r="27">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="7" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="8" t="inlineStr">
+    <row r="29">
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
@@ -1866,7 +1873,7 @@
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Budget</t>
         </is>
       </c>
       <c r="F9" s="10">
@@ -1931,7 +1938,7 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Sleeping bag/quilt (20F) -- backup/colder-margin option</t>
+          <t>Sleeping bag/quilt (20F) -- superseded by temperature choice, see BUY_LIST.md</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -2005,7 +2012,7 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Sleeping bag/quilt (30F) -- RECOMMENDED default, beginner-safe</t>
+          <t>Sleeping bag/quilt (30F) -- superseded by temperature choice, see BUY_LIST.md</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
@@ -2015,12 +2022,12 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>must</t>
+          <t>alt</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>Budget</t>
+          <t>Skip</t>
         </is>
       </c>
       <c r="F11" s="10">
@@ -2085,7 +2092,7 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Sleeping pad, insulated R&gt;=4</t>
+          <t>Sleeping pad -- superseded by temperature choice, see BUY_LIST.md</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
@@ -2095,12 +2102,12 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>must</t>
+          <t>alt</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Skip</t>
         </is>
       </c>
       <c r="F12" s="10">
@@ -2180,7 +2187,7 @@
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Budget</t>
         </is>
       </c>
       <c r="F13" s="10">
@@ -2660,7 +2667,7 @@
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Budget</t>
         </is>
       </c>
       <c r="F19" s="10">
@@ -6847,41 +6854,41 @@
       </c>
       <c r="C11" s="32" t="inlineStr">
         <is>
-          <t>BRS-3000T</t>
+          <t>Amicus Stove Cookset Combo</t>
         </is>
       </c>
       <c r="D11" s="33" t="n">
-        <v>0.9</v>
+        <v>11.2</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>14.99</v>
+        <v>49.95</v>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>$10-13 (rarely resold, cheap enough people just buy new)</t>
+          <t>$28-38 used</t>
         </is>
       </c>
       <c r="G11" s="11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>Fine for boiling water at a sheltered site; pair with a windscreen for cold mornings</t>
+          <t>A real, sturdy stove that six first-time backpackers can trust to actually light and stay lit -- pair with a simple foil or titanium windscreen for cold, breezy mornings</t>
         </is>
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>The r/Ultralight/backpacking go-to budget stove for years; QC varies canister to canister (some arms crack) but at this price most consider it disposable/spare-worthy. Weak in wind, fine for a sheltered Oct GA camp.</t>
+          <t>Verified on REI's live catalog 2026-09-23: REI Staff Pick, 217 reviews averaging 4.5/5, $49.95, in stock. A real name-brand stove with sturdy tri-flex pot supports and a built-in piezo igniter -- SectionHiker rates the plain Amicus stove as one of the most dependable budget canister stoves, unlike the BRS-3000T's flimsy stamped-wire arms.</t>
         </is>
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>Absurdly light; Cheap enough to carry a spare</t>
+          <t>Sturdy tri-flex pot supports, not flimsy stamped wire; Built-in piezo igniter -- no separate lighter needed to start it; Comes with a usable 0.6L pot/cup, useful backup to the main group pot</t>
         </is>
       </c>
       <c r="K11" s="11" t="inlineStr">
         <is>
-          <t>Flimsy pot supports; No wind protection/simmer control; QC variance reported</t>
+          <t>No integrated wind protection -- still needs a windscreen in a breeze; Heavier than the ultralight BRS-3000T it replaces</t>
         </is>
       </c>
       <c r="L11" s="35" t="inlineStr">
@@ -9298,41 +9305,41 @@
       </c>
       <c r="C30" s="32" t="inlineStr">
         <is>
-          <t>Ultra-Lite2</t>
+          <t>Watertight II Rain Jacket (Men's)</t>
         </is>
       </c>
       <c r="D30" s="33" t="n">
-        <v>5.5</v>
+        <v>12</v>
       </c>
       <c r="E30" s="34" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="F30" s="11" t="inlineStr">
         <is>
-          <t>$8-12 used</t>
+          <t>$25-35 used/thrift</t>
         </is>
       </c>
       <c r="G30" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>Fine for the base-camp days; pack duct tape for field repairs on the overnight leg</t>
+          <t>Real rain protection for a week of mixed hiking/creek work — sturdier and more durable than a disposable-style shell for 6 first-time backpackers who may not baby their gear</t>
         </is>
       </c>
       <c r="I30" s="11" t="inlineStr">
         <is>
-          <t>r/Ultralight regularly cites Frogg Toggs as the budget go-to — nonwoven fabric isn't durable or breathable, but a set can survive ~1,300 miles of use and costs a fraction of name-brand shells.</t>
+          <t>OutdoorGearLab's long-running budget rain jacket pick — real seam-sealed Omni-Tech waterproof/breathable fabric with a mesh liner and adjustable hood, not a disposable nonwoven shell. Verified live on Columbia.com 2026-09-23: $70 (regularly $100, some colors on sale to $50).</t>
         </is>
       </c>
       <c r="J30" s="11" t="inlineStr">
         <is>
-          <t>cheapest usable rain shell that exists; very light; packs tiny</t>
+          <t>real waterproof/breathable membrane, not disposable nonwoven; seam-sealed, adjustable hood; durable enough to actually re-wear after this trip</t>
         </is>
       </c>
       <c r="K30" s="11" t="inlineStr">
         <is>
-          <t>zipper leaks in sustained rain; tears easily on brush; no pit zips/breathability</t>
+          <t>heavier and less packable than Frogg Toggs; not as breathable as the pricier Value/Premium shells</t>
         </is>
       </c>
       <c r="L30" s="35" t="inlineStr">
@@ -14642,74 +14649,74 @@
       </c>
       <c r="D26" s="37" t="inlineStr">
         <is>
-          <t>BRS</t>
+          <t>Soto</t>
         </is>
       </c>
       <c r="E26" s="37" t="inlineStr">
         <is>
-          <t>BRS-3000T</t>
+          <t>Amicus Stove Cookset Combo</t>
         </is>
       </c>
       <c r="F26" s="39" t="n">
-        <v>0.9</v>
+        <v>11.2</v>
       </c>
       <c r="G26" s="38" t="inlineStr">
         <is>
-          <t>spec 25g/0.88oz; real-world with case ~1.0oz — widely confirmed by owners, lightest canister stove sold</t>
+          <t>REI spec 11.2oz for the stove + 0.6L aluminum pot/cup combo</t>
         </is>
       </c>
       <c r="H26" s="40" t="n">
-        <v>14.99</v>
+        <v>49.95</v>
       </c>
       <c r="I26" s="41" t="inlineStr">
         <is>
-          <t>https://www.walmart.com/ip/911283406</t>
+          <t>https://www.rei.com/product/149091/soto-amicus-stove-cookset-combo</t>
         </is>
       </c>
       <c r="J26" s="38" t="inlineStr">
         <is>
-          <t>$10-13 (rarely resold, cheap enough people just buy new)</t>
+          <t>$28-38 used</t>
         </is>
       </c>
       <c r="K26" s="38" t="inlineStr">
         <is>
-          <t>Amazon, Walmart, AliExpress</t>
+          <t>REI, Amazon, Soto direct</t>
         </is>
       </c>
       <c r="L26" s="38" t="inlineStr">
         <is>
-          <t>The r/Ultralight/backpacking go-to budget stove for years; QC varies canister to canister (some arms crack) but at this price most consider it disposable/spare-worthy. Weak in wind, fine for a sheltered Oct GA camp.</t>
+          <t>Verified on REI's live catalog 2026-09-23: REI Staff Pick, 217 reviews averaging 4.5/5, $49.95, in stock. A real name-brand stove with sturdy tri-flex pot supports and a built-in piezo igniter -- SectionHiker rates the plain Amicus stove as one of the most dependable budget canister stoves, unlike the BRS-3000T's flimsy stamped-wire arms.</t>
         </is>
       </c>
       <c r="M26" s="38" t="inlineStr">
         <is>
-          <t>https://www.backpacker.com/gear/ultralight-backpacking-canister-stove-brs-3000t/, https://www.walmart.com/ip/911283406</t>
+          <t>https://sectionhiker.com/soto-amicus-canister-stove/, https://www.rei.com/product/149091/soto-amicus-stove-cookset-combo</t>
         </is>
       </c>
       <c r="N26" s="38" t="inlineStr">
         <is>
-          <t>Absurdly light; Cheap enough to carry a spare</t>
+          <t>Sturdy tri-flex pot supports, not flimsy stamped wire; Built-in piezo igniter -- no separate lighter needed to start it; Comes with a usable 0.6L pot/cup, useful backup to the main group pot</t>
         </is>
       </c>
       <c r="O26" s="38" t="inlineStr">
         <is>
-          <t>Flimsy pot supports; No wind protection/simmer control; QC variance reported</t>
+          <t>No integrated wind protection -- still needs a windscreen in a breeze; Heavier than the ultralight BRS-3000T it replaces</t>
         </is>
       </c>
       <c r="P26" s="38" t="inlineStr">
         <is>
-          <t>Fine for boiling water at a sheltered site; pair with a windscreen for cold mornings</t>
+          <t>A real, sturdy stove that six first-time backpackers can trust to actually light and stay lit -- pair with a simple foil or titanium windscreen for cold, breezy mornings</t>
         </is>
       </c>
       <c r="Q26" s="37" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R26" s="37" t="n">
         <v>6</v>
       </c>
       <c r="S26" s="38" t="inlineStr">
         <is>
-          <t>Group's single stove — his cost share $2.50 (1/6 of $14.99)</t>
+          <t>SWAPPED 2026-09-23 (sanity review): previously BRS-3000T ($14.99) -- its own cons (flimsy pot supports, no wind protection, QC variance reported) were too risky as the group's ONLY stove for 6 beginners. Group's single stove -- his cost share $8.33 (1/6 of $49.95). Bring a cheap foil or titanium windscreen (see repair-kit/small-items list) for wind.</t>
         </is>
       </c>
       <c r="T26">
@@ -15825,7 +15832,7 @@
       </c>
       <c r="S38" s="38" t="inlineStr">
         <is>
-          <t>Group share $5.00 | TIER ODDITY: Budget ($45.95) costs more than Value ($44.95) in this category -- kept as sourced.</t>
+          <t>Group share $5.00 | SAFETY NOTE (added 2026-09-23): sleep with it below freezing -- a wetted Sawyer membrane cracks if it freezes, so it must go inside the sleeping bag with you on any night near/below 32F, not left in a pack pocket. Cheap chemical backup already on the buy list: Aquatabs 30-pack (research/gear-tiers-extras-food.json, section A -- water_treatment_backup, https://www.rei.com/product/109906/aquatabs-water-purification-tablets-package-of-30) covers the group if the filter ever fails. | TIER ODDITY: Budget ($45.95) costs more than Value ($44.95) in this category -- kept as sourced.</t>
         </is>
       </c>
       <c r="T38">
@@ -15918,7 +15925,7 @@
       </c>
       <c r="S39" s="38" t="inlineStr">
         <is>
-          <t>Group share $7.49; still needs to sleep in the bag on the cold night | TIER ODDITY: Value ($44.95) is cheaper than Budget ($45.95) in this category -- kept as sourced.</t>
+          <t>Group share $7.49 | SAFETY NOTE (added 2026-09-23): sleep with it below freezing -- same hollow-fiber freeze-crack risk as the Sawyer, keep it in the sleeping bag on any night near/below 32F. Cheap chemical backup already on the buy list: Aquatabs 30-pack (research/gear-tiers-extras-food.json, section A, https://www.rei.com/product/109906/aquatabs-water-purification-tablets-package-of-30). | TIER ODDITY: Value ($44.95) is cheaper than Budget ($45.95) in this category -- kept as sourced.</t>
         </is>
       </c>
       <c r="T39">
@@ -19879,74 +19886,74 @@
       </c>
       <c r="D83" s="37" t="inlineStr">
         <is>
-          <t>Frogg Toggs</t>
+          <t>Columbia</t>
         </is>
       </c>
       <c r="E83" s="37" t="inlineStr">
         <is>
-          <t>Ultra-Lite2</t>
+          <t>Watertight II Rain Jacket (Men's)</t>
         </is>
       </c>
       <c r="F83" s="39" t="n">
-        <v>5.5</v>
+        <v>12</v>
       </c>
       <c r="G83" s="38" t="inlineStr">
         <is>
-          <t>per Frogg Toggs spec</t>
+          <t>typical packable Omni-Tech shell weight per Columbia/OGL testing</t>
         </is>
       </c>
       <c r="H83" s="40" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="I83" s="41" t="inlineStr">
         <is>
-          <t>https://www.froggtoggs.com/products/the-frogg-toggsr-ultra-lite2tm-4749</t>
+          <t>https://www.columbia.com/p/mens-watertight-ii-jacket-1533891.html</t>
         </is>
       </c>
       <c r="J83" s="38" t="inlineStr">
         <is>
-          <t>$8-12 used</t>
+          <t>$25-35 used/thrift</t>
         </is>
       </c>
       <c r="K83" s="38" t="inlineStr">
         <is>
-          <t>Froggtoggs.com, Walmart, Amazon</t>
+          <t>Columbia.com, REI, Amazon, Dick's Sporting Goods</t>
         </is>
       </c>
       <c r="L83" s="38" t="inlineStr">
         <is>
-          <t>r/Ultralight regularly cites Frogg Toggs as the budget go-to — nonwoven fabric isn't durable or breathable, but a set can survive ~1,300 miles of use and costs a fraction of name-brand shells.</t>
+          <t>OutdoorGearLab's long-running budget rain jacket pick — real seam-sealed Omni-Tech waterproof/breathable fabric with a mesh liner and adjustable hood, not a disposable nonwoven shell. Verified live on Columbia.com 2026-09-23: $70 (regularly $100, some colors on sale to $50).</t>
         </is>
       </c>
       <c r="M83" s="38" t="inlineStr">
         <is>
-          <t>https://sectionhiker.com/10-best-backpacking-rain-jackets/, https://www.froggtoggs.com/products/the-frogg-toggsr-ultra-lite2tm-4749</t>
+          <t>https://www.outdoorgearlab.com/reviews/clothing-mens/rain-jacket-men/columbia-watertight-ii, https://www.columbia.com/p/mens-watertight-ii-jacket-1533891.html</t>
         </is>
       </c>
       <c r="N83" s="38" t="inlineStr">
         <is>
-          <t>cheapest usable rain shell that exists; very light; packs tiny</t>
+          <t>real waterproof/breathable membrane, not disposable nonwoven; seam-sealed, adjustable hood; durable enough to actually re-wear after this trip</t>
         </is>
       </c>
       <c r="O83" s="38" t="inlineStr">
         <is>
-          <t>zipper leaks in sustained rain; tears easily on brush; no pit zips/breathability</t>
+          <t>heavier and less packable than Frogg Toggs; not as breathable as the pricier Value/Premium shells</t>
         </is>
       </c>
       <c r="P83" s="38" t="inlineStr">
         <is>
-          <t>Fine for the base-camp days; pack duct tape for field repairs on the overnight leg</t>
+          <t>Real rain protection for a week of mixed hiking/creek work — sturdier and more durable than a disposable-style shell for 6 first-time backpackers who may not baby their gear</t>
         </is>
       </c>
       <c r="Q83" s="37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R83" s="37" t="n">
         <v>1</v>
       </c>
       <c r="S83" s="38" t="inlineStr">
         <is>
-          <t>Buy a size up — cut runs slim</t>
+          <t>SWAPPED 2026-09-23 (sanity review): previously Frogg Toggs Ultra-Lite2 ($20) -- its own cons (zipper leaks in sustained rain, tears easily on brush) were too flimsy as the ONLY rain shell for beginners in a rainy-forecast trip. Frogg Toggs Ultra-Lite2 ($20, https://www.froggtoggs.com/products/the-frogg-toggsr-ultra-lite2tm-4749) is still fine as a cheap EMERGENCY backup/spare layer, just not the primary shell.</t>
         </is>
       </c>
       <c r="T83">

--- a/Gear_Picker.xlsx
+++ b/Gear_Picker.xlsx
@@ -9996,7 +9996,7 @@
         <v>0.7</v>
       </c>
       <c r="N35" s="34" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="O35" s="11" t="inlineStr">
         <is>
@@ -11028,7 +11028,7 @@
         <v>10</v>
       </c>
       <c r="N43" s="34" t="n">
-        <v>16</v>
+        <v>8.99</v>
       </c>
       <c r="O43" s="11" t="inlineStr">
         <is>
@@ -11415,7 +11415,7 @@
         <v>6</v>
       </c>
       <c r="N46" s="34" t="n">
-        <v>16</v>
+        <v>59.95</v>
       </c>
       <c r="O46" s="11" t="inlineStr">
         <is>
@@ -21363,7 +21363,7 @@
         </is>
       </c>
       <c r="H99" s="40" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="I99" s="41" t="inlineStr">
         <is>
@@ -21411,7 +21411,11 @@
       <c r="R99" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="S99" s="38" t="inlineStr"/>
+      <c r="S99" s="38" t="inlineStr">
+        <is>
+          <t>TIER ODDITY: Value ($38.00) costs more than Premium ($35.00) in this category -- kept as sourced, not auto-corrected.</t>
+        </is>
+      </c>
       <c r="T99">
         <f>A99&amp;"|"&amp;C99</f>
         <v/>
@@ -21500,7 +21504,11 @@
       <c r="R100" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="S100" s="38" t="inlineStr"/>
+      <c r="S100" s="38" t="inlineStr">
+        <is>
+          <t>TIER ODDITY: Premium ($35.00) is cheaper than Value ($38.00) in this category -- kept as sourced.</t>
+        </is>
+      </c>
       <c r="T100">
         <f>A100&amp;"|"&amp;C100</f>
         <v/>
@@ -23496,7 +23504,7 @@
       </c>
       <c r="S122" s="38" t="inlineStr">
         <is>
-          <t>Great for beginners; experienced members of the group may prefer the value-tier Garrett</t>
+          <t>Great for beginners; experienced members of the group may prefer the value-tier Garrett | TIER ODDITY: Budget ($9.00) costs more than Value ($8.99) in this category -- kept as sourced.</t>
         </is>
       </c>
       <c r="T122">
@@ -23539,7 +23547,7 @@
         </is>
       </c>
       <c r="H123" s="40" t="n">
-        <v>16</v>
+        <v>8.99</v>
       </c>
       <c r="I123" s="41" t="inlineStr">
         <is>
@@ -23589,7 +23597,7 @@
       </c>
       <c r="S123" s="38" t="inlineStr">
         <is>
-          <t>This is the pan genuinely worth buying one of per person if budget allows even a small step up from bare-minimum</t>
+          <t>This is the pan genuinely worth buying one of per person if budget allows even a small step up from bare-minimum | TIER ODDITY: Value ($8.99) is cheaper than Budget ($9.00) in this category -- kept as sourced.</t>
         </is>
       </c>
       <c r="T123">
@@ -24360,7 +24368,7 @@
         </is>
       </c>
       <c r="H132" s="40" t="n">
-        <v>16</v>
+        <v>59.95</v>
       </c>
       <c r="I132" s="41" t="inlineStr">
         <is>
@@ -24408,7 +24416,11 @@
       <c r="R132" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="S132" s="38" t="inlineStr"/>
+      <c r="S132" s="38" t="inlineStr">
+        <is>
+          <t>TIER ODDITY: Value ($59.95) costs more than Premium ($25.00) in this category -- kept as sourced, not auto-corrected.</t>
+        </is>
+      </c>
       <c r="T132">
         <f>A132&amp;"|"&amp;C132</f>
         <v/>
@@ -24497,7 +24509,11 @@
       <c r="R133" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="S133" s="38" t="inlineStr"/>
+      <c r="S133" s="38" t="inlineStr">
+        <is>
+          <t>TIER ODDITY: Premium ($25.00) is cheaper than Value ($59.95) in this category -- kept as sourced.</t>
+        </is>
+      </c>
       <c r="T133">
         <f>A133&amp;"|"&amp;C133</f>
         <v/>

--- a/Gear_Picker.xlsx
+++ b/Gear_Picker.xlsx
@@ -6209,14 +6209,14 @@
       </c>
       <c r="C6" s="32" t="inlineStr">
         <is>
-          <t>Insulated Static V Peak</t>
+          <t>Insulated Static V</t>
         </is>
       </c>
       <c r="D6" s="33" t="n">
         <v>25</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>99.95</v>
+        <v>74.20999999999999</v>
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
@@ -9434,14 +9434,14 @@
       </c>
       <c r="C31" s="32" t="inlineStr">
         <is>
-          <t>MT100 Down Jacket</t>
+          <t>MT100 Hooded Down Puffer Jacket</t>
         </is>
       </c>
       <c r="D31" s="33" t="n">
         <v>10.6</v>
       </c>
       <c r="E31" s="34" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
@@ -10079,14 +10079,14 @@
       </c>
       <c r="C36" s="32" t="inlineStr">
         <is>
-          <t>Knit fleece gloves</t>
+          <t>Wool Fleece-Liner Knit Gloves (3-pack)</t>
         </is>
       </c>
       <c r="D36" s="33" t="n">
         <v>2</v>
       </c>
       <c r="E36" s="34" t="n">
-        <v>9</v>
+        <v>12.99</v>
       </c>
       <c r="F36" s="11" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>6</v>
       </c>
       <c r="E40" s="34" t="n">
-        <v>25</v>
+        <v>41.59</v>
       </c>
       <c r="F40" s="11" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>6.5</v>
       </c>
       <c r="N40" s="34" t="n">
-        <v>28</v>
+        <v>30.19</v>
       </c>
       <c r="O40" s="11" t="inlineStr">
         <is>
@@ -10763,14 +10763,14 @@
       </c>
       <c r="L41" s="35" t="inlineStr">
         <is>
-          <t>Neoprene Hip Waders</t>
+          <t>Mackenzie Cleated Hip Bootfoot Fishing Wader</t>
         </is>
       </c>
       <c r="M41" s="33" t="n">
         <v>48</v>
       </c>
       <c r="N41" s="34" t="n">
-        <v>55</v>
+        <v>43.51</v>
       </c>
       <c r="O41" s="11" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>9</v>
       </c>
       <c r="E43" s="34" t="n">
-        <v>9</v>
+        <v>7.26</v>
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
@@ -11118,7 +11118,7 @@
         <v>16</v>
       </c>
       <c r="E44" s="34" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F44" s="11" t="inlineStr">
         <is>
@@ -11157,7 +11157,7 @@
         <v>30</v>
       </c>
       <c r="N44" s="34" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="O44" s="11" t="inlineStr">
         <is>
@@ -11369,14 +11369,14 @@
       </c>
       <c r="C46" s="32" t="inlineStr">
         <is>
-          <t>3-4 Piece Crevice Pick Set</t>
+          <t>Hook and Pick Precision Crevice Tool Set, 6 Pieces</t>
         </is>
       </c>
       <c r="D46" s="33" t="n">
         <v>4</v>
       </c>
       <c r="E46" s="34" t="n">
-        <v>9</v>
+        <v>17.25</v>
       </c>
       <c r="F46" s="11" t="inlineStr">
         <is>
@@ -11537,14 +11537,14 @@
       </c>
       <c r="L47" s="35" t="inlineStr">
         <is>
-          <t>Glass Vials with Foam-Lined Screw Caps</t>
+          <t>Glass Vials with Foam-Lined Screw Caps (12-pack)</t>
         </is>
       </c>
       <c r="M47" s="33" t="n">
         <v>1.5</v>
       </c>
       <c r="N47" s="34" t="n">
-        <v>2</v>
+        <v>9.99</v>
       </c>
       <c r="O47" s="11" t="inlineStr">
         <is>
@@ -13259,7 +13259,7 @@
       </c>
       <c r="E11" s="37" t="inlineStr">
         <is>
-          <t>Insulated Static V Peak</t>
+          <t>Insulated Static V</t>
         </is>
       </c>
       <c r="F11" s="39" t="n">
@@ -13271,11 +13271,11 @@
         </is>
       </c>
       <c r="H11" s="40" t="n">
-        <v>99.95</v>
+        <v>74.20999999999999</v>
       </c>
       <c r="I11" s="41" t="inlineStr">
         <is>
-          <t>https://klymit.com/products/insulated-static-v-peak-sleeping-pads</t>
+          <t>https://www.amazon.com/Insulated-Inflatable-Comfortable-Lightweight-Backpacking/dp/B07YP8QDJR</t>
         </is>
       </c>
       <c r="J11" s="38" t="inlineStr">
@@ -13285,7 +13285,7 @@
       </c>
       <c r="K11" s="38" t="inlineStr">
         <is>
-          <t>Klymit.com, REI, Amazon</t>
+          <t>Amazon, REI</t>
         </is>
       </c>
       <c r="L11" s="38" t="inlineStr">
@@ -20157,12 +20157,12 @@
       </c>
       <c r="D86" s="37" t="inlineStr">
         <is>
-          <t>Decathlon (Forclaz)</t>
+          <t>Decathlon (Simond, formerly Forclaz)</t>
         </is>
       </c>
       <c r="E86" s="37" t="inlineStr">
         <is>
-          <t>MT100 Down Jacket</t>
+          <t>MT100 Hooded Down Puffer Jacket</t>
         </is>
       </c>
       <c r="F86" s="39" t="n">
@@ -20170,15 +20170,15 @@
       </c>
       <c r="G86" s="38" t="inlineStr">
         <is>
-          <t>packable down jacket, per Decathlon/GearJunkie</t>
+          <t>packable down jacket, per Decathlon/GearJunkie; rebranded from Forclaz to Simond</t>
         </is>
       </c>
       <c r="H86" s="40" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="I86" s="41" t="inlineStr">
         <is>
-          <t>https://slickdeals.net/f/17521533-decathlon-forclaz-mt100-hooded-down-puffer-jacket-40</t>
+          <t>https://www.decathlon.com/products/simond-mt100-hooded-down-puffer-jacket-167571</t>
         </is>
       </c>
       <c r="J86" s="38" t="inlineStr">
@@ -21532,12 +21532,12 @@
       </c>
       <c r="D101" s="37" t="inlineStr">
         <is>
-          <t>Generic</t>
+          <t>SUCUUI</t>
         </is>
       </c>
       <c r="E101" s="37" t="inlineStr">
         <is>
-          <t>Knit fleece gloves</t>
+          <t>Wool Fleece-Liner Knit Gloves (3-pack)</t>
         </is>
       </c>
       <c r="F101" s="39" t="n">
@@ -21545,15 +21545,15 @@
       </c>
       <c r="G101" s="38" t="inlineStr">
         <is>
-          <t>typical knit glove pair</t>
+          <t>typical knit glove pair; sold as a 3-pack for $12.99</t>
         </is>
       </c>
       <c r="H101" s="40" t="n">
-        <v>9</v>
+        <v>12.99</v>
       </c>
       <c r="I101" s="41" t="inlineStr">
         <is>
-          <t>https://www.walmart.com/ip/2844295050</t>
+          <t>https://www.walmart.com/ip/SUCUUI-3-Pairs-Wool-Winter-Gloves-Men-Women-Thick-Wool-Fleece-Liner-Thermal-Knit-Touchscreen-Elastic-Cuff-Insulated-Gloves-for-Cold-Weather-Gifts/17509322663</t>
         </is>
       </c>
       <c r="J101" s="38" t="inlineStr">
@@ -22633,11 +22633,11 @@
       </c>
       <c r="G113" s="38" t="inlineStr">
         <is>
-          <t>per pair, per Walmart listing</t>
+          <t>per pair, per Walmart listing (verified live price)</t>
         </is>
       </c>
       <c r="H113" s="40" t="n">
-        <v>25</v>
+        <v>41.59</v>
       </c>
       <c r="I113" s="41" t="inlineStr">
         <is>
@@ -22685,7 +22685,11 @@
       <c r="R113" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="S113" s="38" t="inlineStr"/>
+      <c r="S113" s="38" t="inlineStr">
+        <is>
+          <t>TIER ODDITY: Budget ($41.59) costs more than Value ($30.19) in this category -- kept as sourced.</t>
+        </is>
+      </c>
       <c r="T113">
         <f>A113&amp;"|"&amp;C113</f>
         <v/>
@@ -22709,7 +22713,7 @@
       </c>
       <c r="D114" s="37" t="inlineStr">
         <is>
-          <t>NeoSport / Level Six</t>
+          <t>8 Fans</t>
         </is>
       </c>
       <c r="E114" s="37" t="inlineStr">
@@ -22722,11 +22726,11 @@
       </c>
       <c r="G114" s="38" t="inlineStr">
         <is>
-          <t>per pair, typical 3mm dive/water sock</t>
+          <t>per pair, typical 3mm dive/water sock (verified live price)</t>
         </is>
       </c>
       <c r="H114" s="40" t="n">
-        <v>28</v>
+        <v>30.19</v>
       </c>
       <c r="I114" s="41" t="inlineStr">
         <is>
@@ -22774,7 +22778,11 @@
       <c r="R114" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="S114" s="38" t="inlineStr"/>
+      <c r="S114" s="38" t="inlineStr">
+        <is>
+          <t>TIER ODDITY: Value ($30.19) is cheaper than Budget ($41.59) in this category -- kept as sourced.</t>
+        </is>
+      </c>
       <c r="T114">
         <f>A114&amp;"|"&amp;C114</f>
         <v/>
@@ -22980,12 +22988,12 @@
       </c>
       <c r="D117" s="37" t="inlineStr">
         <is>
-          <t>Hodgman / Caddis</t>
+          <t>Hodgman</t>
         </is>
       </c>
       <c r="E117" s="37" t="inlineStr">
         <is>
-          <t>Neoprene Hip Waders</t>
+          <t>Mackenzie Cleated Hip Bootfoot Fishing Wader</t>
         </is>
       </c>
       <c r="F117" s="39" t="n">
@@ -22997,11 +23005,11 @@
         </is>
       </c>
       <c r="H117" s="40" t="n">
-        <v>55</v>
+        <v>43.51</v>
       </c>
       <c r="I117" s="41" t="inlineStr">
         <is>
-          <t>https://www.walmart.com/ip/45087389</t>
+          <t>https://www.walmart.com/ip/Hodgman-Mackenzie-Cleated-Hip-Bootfoot-Fishing-Wader/43927288</t>
         </is>
       </c>
       <c r="J117" s="38" t="inlineStr">
@@ -23021,7 +23029,7 @@
       </c>
       <c r="M117" s="38" t="inlineStr">
         <is>
-          <t>https://www.walmart.com/ip/45087389</t>
+          <t>https://www.walmart.com/ip/Hodgman-Mackenzie-Cleated-Hip-Bootfoot-Fishing-Wader/43927288</t>
         </is>
       </c>
       <c r="N117" s="38" t="inlineStr">
@@ -23450,11 +23458,11 @@
       </c>
       <c r="G122" s="38" t="inlineStr">
         <is>
-          <t>per Toolup listing</t>
+          <t>per Toolup listing (verified live price)</t>
         </is>
       </c>
       <c r="H122" s="40" t="n">
-        <v>9</v>
+        <v>7.26</v>
       </c>
       <c r="I122" s="41" t="inlineStr">
         <is>
@@ -23504,7 +23512,7 @@
       </c>
       <c r="S122" s="38" t="inlineStr">
         <is>
-          <t>Great for beginners; experienced members of the group may prefer the value-tier Garrett | TIER ODDITY: Budget ($9.00) costs more than Value ($8.99) in this category -- kept as sourced.</t>
+          <t>Great for beginners; experienced members of the group may prefer the value-tier Garrett</t>
         </is>
       </c>
       <c r="T122">
@@ -23597,7 +23605,7 @@
       </c>
       <c r="S123" s="38" t="inlineStr">
         <is>
-          <t>This is the pan genuinely worth buying one of per person if budget allows even a small step up from bare-minimum | TIER ODDITY: Value ($8.99) is cheaper than Budget ($9.00) in this category -- kept as sourced.</t>
+          <t>This is the pan genuinely worth buying one of per person if budget allows even a small step up from bare-minimum</t>
         </is>
       </c>
       <c r="T123">
@@ -23733,11 +23741,11 @@
         </is>
       </c>
       <c r="H125" s="40" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I125" s="41" t="inlineStr">
         <is>
-          <t>https://asroutdoor.com/blogs/journal/gold-classifier-screens-mesh-sizes-guide</t>
+          <t>https://asroutdoor.com/products/half-inch-plastic-sifting-screen-classifier-4-holes-per-square-inch</t>
         </is>
       </c>
       <c r="J125" s="38" t="inlineStr">
@@ -23826,7 +23834,7 @@
         </is>
       </c>
       <c r="H126" s="40" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="I126" s="41" t="inlineStr">
         <is>
@@ -23876,7 +23884,7 @@
       </c>
       <c r="S126" s="38" t="inlineStr">
         <is>
-          <t>One shared set at the base-camp pan-out station, split 6 ways, rather than one per person</t>
+          <t>One shared set at the base-camp pan-out station, split 6 ways, rather than one per person | TIER ODDITY: Value ($75.00) costs more than Premium ($65.00) in this category -- kept as sourced, not auto-corrected.</t>
         </is>
       </c>
       <c r="T126">
@@ -23967,7 +23975,11 @@
       <c r="R127" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="S127" s="38" t="inlineStr"/>
+      <c r="S127" s="38" t="inlineStr">
+        <is>
+          <t>TIER ODDITY: Premium ($65.00) is cheaper than Value ($75.00) in this category -- kept as sourced.</t>
+        </is>
+      </c>
       <c r="T127">
         <f>A127&amp;"|"&amp;C127</f>
         <v/>
@@ -24262,12 +24274,12 @@
       </c>
       <c r="D131" s="37" t="inlineStr">
         <is>
-          <t>Generic</t>
+          <t>ASR Outdoor</t>
         </is>
       </c>
       <c r="E131" s="37" t="inlineStr">
         <is>
-          <t>3-4 Piece Crevice Pick Set</t>
+          <t>Hook and Pick Precision Crevice Tool Set, 6 Pieces</t>
         </is>
       </c>
       <c r="F131" s="39" t="n">
@@ -24279,11 +24291,11 @@
         </is>
       </c>
       <c r="H131" s="40" t="n">
-        <v>9</v>
+        <v>17.25</v>
       </c>
       <c r="I131" s="41" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Complete-Sluice-Equipment-Prospecting-Magnifier/dp/B0DBKVTLM7</t>
+          <t>https://www.amazon.com/ASR-Outdoor-Precision-Prospecting-Crevice/dp/B09YCDQPL6</t>
         </is>
       </c>
       <c r="J131" s="38" t="inlineStr">
@@ -24303,7 +24315,7 @@
       </c>
       <c r="M131" s="38" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Complete-Sluice-Equipment-Prospecting-Magnifier/dp/B0DBKVTLM7</t>
+          <t>https://www.amazon.com/ASR-Outdoor-Precision-Prospecting-Crevice/dp/B09YCDQPL6</t>
         </is>
       </c>
       <c r="N131" s="38" t="inlineStr">
@@ -24602,11 +24614,7 @@
       <c r="R134" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="S134" s="38" t="inlineStr">
-        <is>
-          <t>TIER ODDITY: Budget ($5.00) costs more than Value ($2.00) in this category -- kept as sourced.</t>
-        </is>
-      </c>
+      <c r="S134" s="38" t="inlineStr"/>
       <c r="T134">
         <f>A134&amp;"|"&amp;C134</f>
         <v/>
@@ -24635,7 +24643,7 @@
       </c>
       <c r="E135" s="37" t="inlineStr">
         <is>
-          <t>Glass Vials with Foam-Lined Screw Caps</t>
+          <t>Glass Vials with Foam-Lined Screw Caps (12-pack)</t>
         </is>
       </c>
       <c r="F135" s="39" t="n">
@@ -24643,11 +24651,11 @@
       </c>
       <c r="G135" s="38" t="inlineStr">
         <is>
-          <t>per vial</t>
+          <t>price is for the 12-pack, not per vial</t>
         </is>
       </c>
       <c r="H135" s="40" t="n">
-        <v>2</v>
+        <v>9.99</v>
       </c>
       <c r="I135" s="41" t="inlineStr">
         <is>
@@ -24697,7 +24705,7 @@
       </c>
       <c r="S135" s="38" t="inlineStr">
         <is>
-          <t>TIER ODDITY: Value ($2.00) is cheaper than Budget ($5.00) in this category -- kept as sourced.</t>
+          <t>TIER ODDITY: Value ($9.99) costs more than Premium ($4.00) in this category -- kept as sourced, not auto-corrected.</t>
         </is>
       </c>
       <c r="T135">
@@ -24788,7 +24796,11 @@
       <c r="R136" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="S136" s="38" t="inlineStr"/>
+      <c r="S136" s="38" t="inlineStr">
+        <is>
+          <t>TIER ODDITY: Premium ($4.00) is cheaper than Value ($9.99) in this category -- kept as sourced.</t>
+        </is>
+      </c>
       <c r="T136">
         <f>A136&amp;"|"&amp;C136</f>
         <v/>

--- a/Gear_Picker.xlsx
+++ b/Gear_Picker.xlsx
@@ -1858,7 +1858,7 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Tent/shelter (shared, split w/ tentmate)</t>
+          <t>Tent/shelter (personal, 1-person tent, one per hiker)</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -5946,23 +5946,23 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>2-person 3-season shelter</t>
+          <t>1-person 3-season shelter (each hiker carries and owns his own tent, not split)</t>
         </is>
       </c>
       <c r="C4" s="32" t="inlineStr">
         <is>
-          <t>Trail Hut 2</t>
+          <t>Late Start 1P Tent</t>
         </is>
       </c>
       <c r="D4" s="33" t="n">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="E4" s="34" t="n">
-        <v>259</v>
+        <v>149.95</v>
       </c>
       <c r="F4" s="11" t="inlineStr">
         <is>
-          <t>$70-100 on REI Re/Gear</t>
+          <t>n/a, new arrival</t>
         </is>
       </c>
       <c r="G4" s="11" t="n">
@@ -5970,100 +5970,100 @@
       </c>
       <c r="H4" s="11" t="inlineStr">
         <is>
-          <t>Full double-wall keeps condensation off you in cold, damp Oct nights at 3-4k ft; freestanding handles the rocky NC/GA mountain sites</t>
+          <t>Freestanding pole tent handles rocky/root-y GA sites and is easy for a beginner to pitch solo in the dark or rain</t>
         </is>
       </c>
       <c r="I4" s="11" t="inlineStr">
         <is>
-          <t>CleverHiker's budget-tent pick and cited on r/WildernessBackpacking as the tent that 'won't fail you' for the price — freestanding, easy setup, good rain performance for a budget double-wall tent, just heavy at 5.75 lb split 2 ways (~2.9 lb each).</t>
+          <t>REI's cheapest current 1-person freestanding backpacking tent -- 'Quick Corner' pole design pitches fast, full-coverage rainfly, straightforward freestanding setup that suits a first-time solo tent buyer.</t>
         </is>
       </c>
       <c r="J4" s="11" t="inlineStr">
         <is>
-          <t>Freestanding — easy on rocky/root-y GA campsites; Full double-wall with good ventilation, handles rain well; REI return policy de-risks a first tent purchase</t>
+          <t>Freestanding, fast/easy pitch; Full-coverage rainfly; Cheapest in-stock 1P option with a return policy</t>
         </is>
       </c>
       <c r="K4" s="11" t="inlineStr">
         <is>
-          <t>Heavy vs. anything UL; Single door/vestibule on some configs — check current version; Not worth buying new if a friend already owns any 2P tent</t>
+          <t>Heavier than UL 1P tents; New model, few reviews yet</t>
         </is>
       </c>
       <c r="L4" s="35" t="inlineStr">
         <is>
-          <t>X-Mid 2 (mesh inner)</t>
+          <t>Elixir 1 Tent with Footprint</t>
         </is>
       </c>
       <c r="M4" s="33" t="n">
-        <v>31.3</v>
+        <v>65</v>
       </c>
       <c r="N4" s="34" t="n">
-        <v>319</v>
+        <v>289.95</v>
       </c>
       <c r="O4" s="11" t="inlineStr">
         <is>
-          <t>$220-270 on r/ULgeartrade (high demand, holds value)</t>
+          <t>$150-200 used</t>
         </is>
       </c>
       <c r="P4" s="11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q4" s="11" t="inlineStr">
         <is>
-          <t>Excellent: double-wall sheds condensation and rain better than single-wall UL shelters at low-30s temps; needs a taut pitch on rocky ground so practice at home first</t>
+          <t>Easy solo pitch on rocky NC/GA sites, full double-wall handles humid cold-30s condensation well</t>
         </is>
       </c>
       <c r="R4" s="11" t="inlineStr">
         <is>
-          <t>The single most-recommended value shelter on r/Ultralight and in CleverHiker/Switchback Travel roundups — 33 sq ft of floor space for two people at under 2 lb, storm-worthy double-wall trekking-pole design; widely called the best space-to-weight ratio in the category.</t>
+          <t>REI markets the Elixir line explicitly to newer backpackers -- freestanding traditional pole tent (not trekking-pole-only, not DCF), roomy 18 sq ft interior, includes footprint.</t>
         </is>
       </c>
       <c r="S4" s="11" t="inlineStr">
         <is>
-          <t>Roomiest 2P UL shelter for the weight; Full double-wall (less condensation risk than single-wall) — good for humid GA fall nights; Two doors/vestibules</t>
+          <t>Freestanding, beginner-friendly per REI's own description; Roomy 18 sq ft floor, tall 39in headroom; Includes footprint</t>
         </is>
       </c>
       <c r="T4" s="11" t="inlineStr">
         <is>
-          <t>Requires trekking poles (2x 48") to pitch — not freestanding; Pitch has a learning curve first time out; Direct-order only, 2-4 week lead time typical — order well before Oct 15</t>
+          <t>Heavier than UL trekking-pole shelters; Not as light as the old shared 2P split-weight math</t>
         </is>
       </c>
       <c r="U4" s="36" t="inlineStr">
         <is>
-          <t>Duplex (Classic, DCF)</t>
+          <t>Dragonfly OSMO 1P Ultralight Backpacking Tent</t>
         </is>
       </c>
       <c r="V4" s="33" t="n">
-        <v>18.5</v>
+        <v>34</v>
       </c>
       <c r="W4" s="34" t="n">
-        <v>749</v>
+        <v>499.95</v>
       </c>
       <c r="X4" s="11" t="inlineStr">
         <is>
-          <t>$400-550 on r/ULgeartrade — DCF tents hold value extremely well</t>
+          <t>$300-380 used, holds value well</t>
         </is>
       </c>
       <c r="Y4" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z4" s="11" t="inlineStr">
         <is>
-          <t>Doable but the riskiest of the three for this trip's conditions — humid low-30s nights are exactly when single-wall DCF shelters condense worst; only recommended if already owned or borrowed, not a first purchase for this trip</t>
+          <t>Freestanding and forgiving for a beginner while being light enough to actually enjoy carrying solo</t>
         </is>
       </c>
       <c r="AA4" s="11" t="inlineStr">
         <is>
-          <t>The benchmark UL 2-person shelter — most-cited trekking-pole tent in PCT/CDT gear surveys and the classic 'endgame' shelter serious UL hikers graduate to; DCF is nearly waterproof and doesn't sag when wet, but single-wall means real condensation management is needed.</t>
+          <t>One of the most-recommended freestanding 1-person UL tents in CleverHiker/OutdoorGearLab roundups -- true freestanding pole design (not DCF, not trekking-pole-only), light enough to matter, easy livability for a first solo backpacking tent.</t>
         </is>
       </c>
       <c r="AB4" s="11" t="inlineStr">
         <is>
-          <t>Sub-1.2 lb for a true 2-person shelter; DCF doesn't absorb water or sag when wet; Huge resale value if hiking stops after this trip</t>
+          <t>True freestanding -- no trekking poles/DCF pitch skills required; Well under 2.5 lb; High headroom/livability for the weight</t>
         </is>
       </c>
       <c r="AC4" s="11" t="inlineStr">
         <is>
-          <t>$699 is a serious spend for one trip; Single-wall DCF condenses heavily in humid, cold GA fall air — wipe-down towel and careful venting are mandatory; Requires trekking poles; less forgiving pitch than X-Mid</t>
+          <t>$499.95 is a real spend for one trip; Still needs practice pitching before the trip</t>
         </is>
       </c>
     </row>
@@ -9093,7 +9093,7 @@
         <v>33</v>
       </c>
       <c r="N28" s="34" t="n">
-        <v>75</v>
+        <v>100.93</v>
       </c>
       <c r="O28" s="11" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>11.4</v>
       </c>
       <c r="N34" s="34" t="n">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="O34" s="11" t="inlineStr">
         <is>
@@ -10254,7 +10254,7 @@
         <v>5</v>
       </c>
       <c r="N37" s="34" t="n">
-        <v>8.5</v>
+        <v>13.51</v>
       </c>
       <c r="O37" s="11" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
       </c>
       <c r="B5" s="38" t="inlineStr">
         <is>
-          <t>2-person 3-season shelter</t>
+          <t>1-person 3-season shelter (each hiker carries and owns his own tent, not split)</t>
         </is>
       </c>
       <c r="C5" s="37" t="inlineStr">
@@ -12696,33 +12696,33 @@
       </c>
       <c r="D5" s="37" t="inlineStr">
         <is>
-          <t>REI Co-op</t>
+          <t>Kelty</t>
         </is>
       </c>
       <c r="E5" s="37" t="inlineStr">
         <is>
-          <t>Trail Hut 2</t>
+          <t>Late Start 1P Tent</t>
         </is>
       </c>
       <c r="F5" s="39" t="n">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="G5" s="38" t="inlineStr">
         <is>
-          <t>5 lb 11 oz (91 oz) packaged weight per REI/CleverHiker</t>
+          <t>3 lb 9 oz (57 oz) minimum trail weight per REI spec</t>
         </is>
       </c>
       <c r="H5" s="40" t="n">
-        <v>259</v>
+        <v>149.95</v>
       </c>
       <c r="I5" s="41" t="inlineStr">
         <is>
-          <t>https://www.rei.com/product/C03309/rei-co-op-trail-hut-2-tent-with-footprint</t>
+          <t>https://www.rei.com/product/C17058/kelty-late-start-1p-tent</t>
         </is>
       </c>
       <c r="J5" s="38" t="inlineStr">
         <is>
-          <t>$70-100 on REI Re/Gear</t>
+          <t>n/a, new arrival</t>
         </is>
       </c>
       <c r="K5" s="38" t="inlineStr">
@@ -12732,38 +12732,38 @@
       </c>
       <c r="L5" s="38" t="inlineStr">
         <is>
-          <t>CleverHiker's budget-tent pick and cited on r/WildernessBackpacking as the tent that 'won't fail you' for the price — freestanding, easy setup, good rain performance for a budget double-wall tent, just heavy at 5.75 lb split 2 ways (~2.9 lb each).</t>
+          <t>REI's cheapest current 1-person freestanding backpacking tent -- 'Quick Corner' pole design pitches fast, full-coverage rainfly, straightforward freestanding setup that suits a first-time solo tent buyer.</t>
         </is>
       </c>
       <c r="M5" s="38" t="inlineStr">
         <is>
-          <t>https://www.cleverhiker.com/backpacking/rei-trail-hut-2-tent-review/, https://www.outdoorgearlab.com/reviews/camping-and-hiking/backpacking-tent/rei-co-op-trailmade-2</t>
+          <t>https://www.rei.com/product/C17058/kelty-late-start-1p-tent</t>
         </is>
       </c>
       <c r="N5" s="38" t="inlineStr">
         <is>
-          <t>Freestanding — easy on rocky/root-y GA campsites; Full double-wall with good ventilation, handles rain well; REI return policy de-risks a first tent purchase</t>
+          <t>Freestanding, fast/easy pitch; Full-coverage rainfly; Cheapest in-stock 1P option with a return policy</t>
         </is>
       </c>
       <c r="O5" s="38" t="inlineStr">
         <is>
-          <t>Heavy vs. anything UL; Single door/vestibule on some configs — check current version; Not worth buying new if a friend already owns any 2P tent</t>
+          <t>Heavier than UL 1P tents; New model, few reviews yet</t>
         </is>
       </c>
       <c r="P5" s="38" t="inlineStr">
         <is>
-          <t>Full double-wall keeps condensation off you in cold, damp Oct nights at 3-4k ft; freestanding handles the rocky NC/GA mountain sites</t>
+          <t>Freestanding pole tent handles rocky/root-y GA sites and is easy for a beginner to pitch solo in the dark or rain</t>
         </is>
       </c>
       <c r="Q5" s="37" t="n">
         <v>5</v>
       </c>
       <c r="R5" s="37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S5" s="38" t="inlineStr">
         <is>
-          <t>Supersedes the Ozark Trail 2P used in the existing gear.md — better rain performance for similar weight/price and available new with a return policy</t>
+          <t>2026-09-23: replaces the old shared 2-person REI Trail Hut 2 -- each hiker now carries/buys his own 1-person tent, full price, no split</t>
         </is>
       </c>
       <c r="T5">
@@ -12779,7 +12779,7 @@
       </c>
       <c r="B6" s="38" t="inlineStr">
         <is>
-          <t>2-person 3-season shelter</t>
+          <t>1-person 3-season shelter (each hiker carries and owns his own tent, not split)</t>
         </is>
       </c>
       <c r="C6" s="37" t="inlineStr">
@@ -12789,74 +12789,74 @@
       </c>
       <c r="D6" s="37" t="inlineStr">
         <is>
-          <t>Durston Gear</t>
+          <t>MSR</t>
         </is>
       </c>
       <c r="E6" s="37" t="inlineStr">
         <is>
-          <t>X-Mid 2 (mesh inner)</t>
+          <t>Elixir 1 Tent with Footprint</t>
         </is>
       </c>
       <c r="F6" s="39" t="n">
-        <v>31.3</v>
+        <v>65</v>
       </c>
       <c r="G6" s="38" t="inlineStr">
         <is>
-          <t>31.3 oz (890 g) tent-only per Durston specs; 34.3 oz (975 g) with stuff sack + 6 stakes</t>
+          <t>4 lb 1 oz (65 oz) minimum trail weight per REI spec</t>
         </is>
       </c>
       <c r="H6" s="40" t="n">
-        <v>319</v>
+        <v>289.95</v>
       </c>
       <c r="I6" s="41" t="inlineStr">
         <is>
-          <t>https://durstongear.com/products/x-mid-2-tent-ultralight-backpacking</t>
+          <t>https://www.rei.com/product/246230/msr-elixir-1-tent-with-footprint</t>
         </is>
       </c>
       <c r="J6" s="38" t="inlineStr">
         <is>
-          <t>$220-270 on r/ULgeartrade (high demand, holds value)</t>
+          <t>$150-200 used</t>
         </is>
       </c>
       <c r="K6" s="38" t="inlineStr">
         <is>
-          <t>Durston Gear (direct)</t>
+          <t>REI</t>
         </is>
       </c>
       <c r="L6" s="38" t="inlineStr">
         <is>
-          <t>The single most-recommended value shelter on r/Ultralight and in CleverHiker/Switchback Travel roundups — 33 sq ft of floor space for two people at under 2 lb, storm-worthy double-wall trekking-pole design; widely called the best space-to-weight ratio in the category.</t>
+          <t>REI markets the Elixir line explicitly to newer backpackers -- freestanding traditional pole tent (not trekking-pole-only, not DCF), roomy 18 sq ft interior, includes footprint.</t>
         </is>
       </c>
       <c r="M6" s="38" t="inlineStr">
         <is>
-          <t>https://www.switchbacktravel.com/reviews/durston-x-mid-2, https://www.cleverhiker.com/backpacking/best-ultralight-backpacks/, https://www.adventurealan.com/durston-x-mid-2p-tent-review/</t>
+          <t>https://www.rei.com/product/246230/msr-elixir-1-tent-with-footprint</t>
         </is>
       </c>
       <c r="N6" s="38" t="inlineStr">
         <is>
-          <t>Roomiest 2P UL shelter for the weight; Full double-wall (less condensation risk than single-wall) — good for humid GA fall nights; Two doors/vestibules</t>
+          <t>Freestanding, beginner-friendly per REI's own description; Roomy 18 sq ft floor, tall 39in headroom; Includes footprint</t>
         </is>
       </c>
       <c r="O6" s="38" t="inlineStr">
         <is>
-          <t>Requires trekking poles (2x 48") to pitch — not freestanding; Pitch has a learning curve first time out; Direct-order only, 2-4 week lead time typical — order well before Oct 15</t>
+          <t>Heavier than UL trekking-pole shelters; Not as light as the old shared 2P split-weight math</t>
         </is>
       </c>
       <c r="P6" s="38" t="inlineStr">
         <is>
-          <t>Excellent: double-wall sheds condensation and rain better than single-wall UL shelters at low-30s temps; needs a taut pitch on rocky ground so practice at home first</t>
+          <t>Easy solo pitch on rocky NC/GA sites, full double-wall handles humid cold-30s condensation well</t>
         </is>
       </c>
       <c r="Q6" s="37" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R6" s="37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S6" s="38" t="inlineStr">
         <is>
-          <t>Solid-inner version exists for more privacy/warmth at a small weight penalty; order in advance, this is not a same-week Amazon item</t>
+          <t>2026-09-23: replaces the old shared 2-person Durston X-Mid 2 (trekking-pole-only, beginner_score 3) -- freestanding 1-person alternative, full price, no split</t>
         </is>
       </c>
       <c r="T6">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="B7" s="38" t="inlineStr">
         <is>
-          <t>2-person 3-season shelter</t>
+          <t>1-person 3-season shelter (each hiker carries and owns his own tent, not split)</t>
         </is>
       </c>
       <c r="C7" s="37" t="inlineStr">
@@ -12882,74 +12882,74 @@
       </c>
       <c r="D7" s="37" t="inlineStr">
         <is>
-          <t>Zpacks</t>
+          <t>NEMO</t>
         </is>
       </c>
       <c r="E7" s="37" t="inlineStr">
         <is>
-          <t>Duplex (Classic, DCF)</t>
+          <t>Dragonfly OSMO 1P Ultralight Backpacking Tent</t>
         </is>
       </c>
       <c r="F7" s="39" t="n">
-        <v>18.5</v>
+        <v>34</v>
       </c>
       <c r="G7" s="38" t="inlineStr">
         <is>
-          <t>17.8-20.4 oz depending on source/config; 18.5 oz commonly cited incl. stuff sack, excl. stakes, per Zpacks/CleverHiker</t>
+          <t>~2 lb 2 oz (34 oz) minimum trail weight per NEMO/REI spec</t>
         </is>
       </c>
       <c r="H7" s="40" t="n">
-        <v>749</v>
+        <v>499.95</v>
       </c>
       <c r="I7" s="41" t="inlineStr">
         <is>
-          <t>https://zpacks.com/products/duplex-tent</t>
+          <t>https://www.rei.com/product/C01602/nemo-dragonfly-osmo-1p-ultralight-backpacking-tent</t>
         </is>
       </c>
       <c r="J7" s="38" t="inlineStr">
         <is>
-          <t>$400-550 on r/ULgeartrade — DCF tents hold value extremely well</t>
+          <t>$300-380 used, holds value well</t>
         </is>
       </c>
       <c r="K7" s="38" t="inlineStr">
         <is>
-          <t>Zpacks (direct)</t>
+          <t>REI</t>
         </is>
       </c>
       <c r="L7" s="38" t="inlineStr">
         <is>
-          <t>The benchmark UL 2-person shelter — most-cited trekking-pole tent in PCT/CDT gear surveys and the classic 'endgame' shelter serious UL hikers graduate to; DCF is nearly waterproof and doesn't sag when wet, but single-wall means real condensation management is needed.</t>
+          <t>One of the most-recommended freestanding 1-person UL tents in CleverHiker/OutdoorGearLab roundups -- true freestanding pole design (not DCF, not trekking-pole-only), light enough to matter, easy livability for a first solo backpacking tent.</t>
         </is>
       </c>
       <c r="M7" s="38" t="inlineStr">
         <is>
-          <t>https://wildernesstimes.com/tents/zpacks-duplex-tent-review/, https://www.treelinereview.com/gearreviews/zpacks-duplex-tent-review</t>
+          <t>https://www.rei.com/product/C01602/nemo-dragonfly-osmo-1p-ultralight-backpacking-tent</t>
         </is>
       </c>
       <c r="N7" s="38" t="inlineStr">
         <is>
-          <t>Sub-1.2 lb for a true 2-person shelter; DCF doesn't absorb water or sag when wet; Huge resale value if hiking stops after this trip</t>
+          <t>True freestanding -- no trekking poles/DCF pitch skills required; Well under 2.5 lb; High headroom/livability for the weight</t>
         </is>
       </c>
       <c r="O7" s="38" t="inlineStr">
         <is>
-          <t>$699 is a serious spend for one trip; Single-wall DCF condenses heavily in humid, cold GA fall air — wipe-down towel and careful venting are mandatory; Requires trekking poles; less forgiving pitch than X-Mid</t>
+          <t>$499.95 is a real spend for one trip; Still needs practice pitching before the trip</t>
         </is>
       </c>
       <c r="P7" s="38" t="inlineStr">
         <is>
-          <t>Doable but the riskiest of the three for this trip's conditions — humid low-30s nights are exactly when single-wall DCF shelters condense worst; only recommended if already owned or borrowed, not a first purchase for this trip</t>
+          <t>Freestanding and forgiving for a beginner while being light enough to actually enjoy carrying solo</t>
         </is>
       </c>
       <c r="Q7" s="37" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R7" s="37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S7" s="38" t="inlineStr">
         <is>
-          <t>Zip version (Duplex Zip) adds a zippered door for a small weight/price premium; not the pick to buy new just for one October GA overnight</t>
+          <t>2026-09-23: replaces the old shared 2-person Zpacks Duplex (single-wall DCF, beginner_score 2) -- freestanding, beginner-friendly 1-person premium pick, full price, no split</t>
         </is>
       </c>
       <c r="T7">
@@ -13875,7 +13875,7 @@
         <v>4</v>
       </c>
       <c r="R17" s="37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S17" s="38" t="inlineStr">
         <is>
@@ -13968,7 +13968,7 @@
         <v>4</v>
       </c>
       <c r="R18" s="37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S18" s="38" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>4</v>
       </c>
       <c r="R19" s="37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S19" s="38" t="inlineStr">
         <is>
@@ -18311,7 +18311,7 @@
         <v>5</v>
       </c>
       <c r="R65" s="37" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S65" s="38" t="inlineStr">
         <is>
@@ -18404,7 +18404,7 @@
         <v>5</v>
       </c>
       <c r="R66" s="37" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S66" s="38" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>4</v>
       </c>
       <c r="R67" s="37" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S67" s="38" t="inlineStr"/>
       <c r="T67">
@@ -19438,7 +19438,7 @@
         </is>
       </c>
       <c r="H78" s="40" t="n">
-        <v>75</v>
+        <v>100.93</v>
       </c>
       <c r="I78" s="41" t="inlineStr">
         <is>
@@ -21096,7 +21096,7 @@
         </is>
       </c>
       <c r="H96" s="40" t="n">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="I96" s="41" t="inlineStr">
         <is>
@@ -21144,7 +21144,11 @@
       <c r="R96" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="S96" s="38" t="inlineStr"/>
+      <c r="S96" s="38" t="inlineStr">
+        <is>
+          <t>TIER ODDITY: Value ($110.00) costs more than Premium ($98.00) in this category -- kept as sourced, not auto-corrected.</t>
+        </is>
+      </c>
       <c r="T96">
         <f>A96&amp;"|"&amp;C96</f>
         <v/>
@@ -21233,7 +21237,11 @@
       <c r="R97" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="S97" s="38" t="inlineStr"/>
+      <c r="S97" s="38" t="inlineStr">
+        <is>
+          <t>TIER ODDITY: Premium ($98.00) is cheaper than Value ($110.00) in this category -- kept as sourced.</t>
+        </is>
+      </c>
       <c r="T97">
         <f>A97&amp;"|"&amp;C97</f>
         <v/>
@@ -21866,7 +21874,7 @@
       </c>
       <c r="S104" s="38" t="inlineStr">
         <is>
-          <t>Required, not optional, during GA firearms deer season in Chattahoochee NF — confirm GA DNR's current blaze-orange sq-inch/coverage rule before the trip | TIER ODDITY: Budget ($16.96) costs more than Value ($8.50) in this category -- kept as sourced.</t>
+          <t>Required, not optional, during GA firearms deer season in Chattahoochee NF — confirm GA DNR's current blaze-orange sq-inch/coverage rule before the trip | TIER ODDITY: Budget ($16.96) costs more than Value ($13.51) in this category -- kept as sourced.</t>
         </is>
       </c>
       <c r="T104">
@@ -21909,7 +21917,7 @@
         </is>
       </c>
       <c r="H105" s="40" t="n">
-        <v>8.5</v>
+        <v>13.51</v>
       </c>
       <c r="I105" s="41" t="inlineStr">
         <is>
@@ -21959,7 +21967,7 @@
       </c>
       <c r="S105" s="38" t="inlineStr">
         <is>
-          <t>TIER ODDITY: Value ($8.50) is cheaper than Budget ($16.96) in this category -- kept as sourced.</t>
+          <t>TIER ODDITY: Value ($13.51) is cheaper than Budget ($16.96) in this category -- kept as sourced.</t>
         </is>
       </c>
       <c r="T105">
@@ -23508,7 +23516,7 @@
         <v>5</v>
       </c>
       <c r="R122" s="37" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S122" s="38" t="inlineStr">
         <is>
@@ -23601,7 +23609,7 @@
         <v>5</v>
       </c>
       <c r="R123" s="37" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S123" s="38" t="inlineStr">
         <is>
@@ -23694,7 +23702,7 @@
         <v>3</v>
       </c>
       <c r="R124" s="37" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S124" s="38" t="inlineStr">
         <is>
@@ -23787,7 +23795,7 @@
         <v>5</v>
       </c>
       <c r="R125" s="37" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S125" s="38" t="inlineStr">
         <is>
@@ -24066,7 +24074,7 @@
         <v>5</v>
       </c>
       <c r="R128" s="37" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S128" s="38" t="inlineStr">
         <is>
@@ -24159,7 +24167,7 @@
         <v>5</v>
       </c>
       <c r="R129" s="37" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S129" s="38" t="inlineStr"/>
       <c r="T129">
@@ -24248,7 +24256,7 @@
         <v>3</v>
       </c>
       <c r="R130" s="37" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S130" s="38" t="inlineStr"/>
       <c r="T130">
@@ -24337,7 +24345,7 @@
         <v>5</v>
       </c>
       <c r="R131" s="37" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S131" s="38" t="inlineStr"/>
       <c r="T131">
@@ -24426,7 +24434,7 @@
         <v>5</v>
       </c>
       <c r="R132" s="37" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S132" s="38" t="inlineStr">
         <is>
@@ -24519,7 +24527,7 @@
         <v>3</v>
       </c>
       <c r="R133" s="37" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S133" s="38" t="inlineStr">
         <is>
@@ -24612,7 +24620,7 @@
         <v>5</v>
       </c>
       <c r="R134" s="37" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S134" s="38" t="inlineStr"/>
       <c r="T134">
@@ -24701,7 +24709,7 @@
         <v>5</v>
       </c>
       <c r="R135" s="37" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S135" s="38" t="inlineStr">
         <is>
@@ -24794,7 +24802,7 @@
         <v>4</v>
       </c>
       <c r="R136" s="37" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S136" s="38" t="inlineStr">
         <is>
@@ -24887,7 +24895,7 @@
         <v>5</v>
       </c>
       <c r="R137" s="37" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S137" s="38" t="inlineStr">
         <is>
@@ -24980,7 +24988,7 @@
         <v>5</v>
       </c>
       <c r="R138" s="37" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S138" s="38" t="inlineStr">
         <is>
@@ -25073,7 +25081,7 @@
         <v>3</v>
       </c>
       <c r="R139" s="37" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S139" s="38" t="inlineStr"/>
       <c r="T139">
@@ -25162,7 +25170,7 @@
         <v>5</v>
       </c>
       <c r="R140" s="37" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S140" s="38" t="inlineStr">
         <is>
@@ -25255,7 +25263,7 @@
         <v>4</v>
       </c>
       <c r="R141" s="37" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S141" s="38" t="inlineStr">
         <is>
@@ -25348,7 +25356,7 @@
         <v>3</v>
       </c>
       <c r="R142" s="37" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S142" s="38" t="inlineStr"/>
       <c r="T142">

--- a/Gear_Picker.xlsx
+++ b/Gear_Picker.xlsx
@@ -7496,7 +7496,7 @@
         <v>2.3</v>
       </c>
       <c r="N15" s="34" t="n">
-        <v>44.95</v>
+        <v>52.95</v>
       </c>
       <c r="O15" s="11" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
         <v>1.6</v>
       </c>
       <c r="E16" s="34" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
         <v>1.5</v>
       </c>
       <c r="E24" s="34" t="n">
-        <v>4.25</v>
+        <v>8.75</v>
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         <v>3.5</v>
       </c>
       <c r="E25" s="34" t="n">
-        <v>6</v>
+        <v>3.94</v>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>18</v>
       </c>
       <c r="E26" s="34" t="n">
-        <v>39.99</v>
+        <v>49.99</v>
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         <v>8.1</v>
       </c>
       <c r="N26" s="34" t="n">
-        <v>51.98</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="O26" s="11" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>2</v>
       </c>
       <c r="N27" s="34" t="n">
-        <v>19.95</v>
+        <v>34.28</v>
       </c>
       <c r="O27" s="11" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         <v>2.5</v>
       </c>
       <c r="E30" s="34" t="n">
-        <v>18</v>
+        <v>8.83</v>
       </c>
       <c r="F30" s="11" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>12.5</v>
       </c>
       <c r="N31" s="34" t="n">
-        <v>100</v>
+        <v>99.95</v>
       </c>
       <c r="O31" s="11" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>11.6</v>
       </c>
       <c r="N32" s="34" t="n">
-        <v>239</v>
+        <v>118.99</v>
       </c>
       <c r="O32" s="11" t="inlineStr">
         <is>
@@ -9947,7 +9947,7 @@
         <v>10</v>
       </c>
       <c r="N34" s="34" t="n">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="O34" s="11" t="inlineStr">
         <is>
@@ -10166,7 +10166,7 @@
         <v>2</v>
       </c>
       <c r="E36" s="34" t="n">
-        <v>10</v>
+        <v>14.99</v>
       </c>
       <c r="F36" s="11" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         <v>2.3</v>
       </c>
       <c r="N37" s="34" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="O37" s="11" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>6</v>
       </c>
       <c r="E40" s="34" t="n">
-        <v>10</v>
+        <v>17.37</v>
       </c>
       <c r="F40" s="11" t="inlineStr">
         <is>
@@ -10721,7 +10721,7 @@
         <v>7</v>
       </c>
       <c r="N40" s="34" t="n">
-        <v>18</v>
+        <v>14.99</v>
       </c>
       <c r="O40" s="11" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>5</v>
       </c>
       <c r="E43" s="34" t="n">
-        <v>8</v>
+        <v>8.99</v>
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
         <v>2</v>
       </c>
       <c r="N46" s="34" t="n">
-        <v>9</v>
+        <v>11.99</v>
       </c>
       <c r="O46" s="11" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>1</v>
       </c>
       <c r="E49" s="34" t="n">
-        <v>19</v>
+        <v>7.99</v>
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>2.5</v>
       </c>
       <c r="N49" s="34" t="n">
-        <v>13</v>
+        <v>8.98</v>
       </c>
       <c r="O49" s="11" t="inlineStr">
         <is>
@@ -11972,7 +11972,7 @@
         <v>6</v>
       </c>
       <c r="E50" s="34" t="n">
-        <v>9</v>
+        <v>6.28</v>
       </c>
       <c r="F50" s="11" t="inlineStr">
         <is>
@@ -12230,7 +12230,7 @@
         <v>30</v>
       </c>
       <c r="E52" s="34" t="n">
-        <v>45</v>
+        <v>7.26</v>
       </c>
       <c r="F52" s="11" t="inlineStr">
         <is>
@@ -12308,7 +12308,7 @@
         <v>52</v>
       </c>
       <c r="W52" s="34" t="n">
-        <v>95</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="X52" s="11" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
       </c>
       <c r="I36" s="41" t="inlineStr">
         <is>
-          <t>https://seatosummit.com/products/alpha-light-utensil-long-spoon</t>
+          <t>https://www.amazon.com/dp/B0CWVSLQ4J</t>
         </is>
       </c>
       <c r="J36" s="38" t="inlineStr">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="S36" s="38" t="inlineStr">
         <is>
-          <t>TIER ODDITY: Value ($10.95) costs more than Premium ($9.95) in this category -- kept as sourced, not auto-corrected.</t>
+          <t>seatosummit.com product page is dead (site sells nothing directly); replacement is the same Frontier Ultralight Long Handle Spoon on Amazon, same $10.95 price. | TIER ODDITY: Value ($10.95) costs more than Premium ($9.95) in this category -- kept as sourced, not auto-corrected.</t>
         </is>
       </c>
       <c r="T36">
@@ -16041,7 +16041,7 @@
       </c>
       <c r="S38" s="38" t="inlineStr">
         <is>
-          <t>Group share $5.00 | SAFETY NOTE (added 2026-09-23): sleep with it below freezing -- a wetted Sawyer membrane cracks if it freezes, so it must go inside the sleeping bag with you on any night near/below 32F, not left in a pack pocket. Cheap chemical backup already on the buy list: Aquatabs 30-pack (research/gear-tiers-extras-food.json, section A -- water_treatment_backup, https://www.rei.com/product/109906/aquatabs-water-purification-tablets-package-of-30) covers the group if the filter ever fails. | TIER ODDITY: Budget ($45.95) costs more than Value ($44.95) in this category -- kept as sourced.</t>
+          <t>Group share $5.00 | SAFETY NOTE (added 2026-09-23): sleep with it below freezing -- a wetted Sawyer membrane cracks if it freezes, so it must go inside the sleeping bag with you on any night near/below 32F, not left in a pack pocket. Cheap chemical backup already on the buy list: Aquatabs 30-pack (research/gear-tiers-extras-food.json, section A -- water_treatment_backup, https://www.rei.com/product/109906/aquatabs-water-purification-tablets-package-of-30) covers the group if the filter ever fails.</t>
         </is>
       </c>
       <c r="T38">
@@ -16084,11 +16084,11 @@
         </is>
       </c>
       <c r="H39" s="40" t="n">
-        <v>44.95</v>
+        <v>52.95</v>
       </c>
       <c r="I39" s="41" t="inlineStr">
         <is>
-          <t>https://www.rei.com/product/116364/katadyn-befree-10-l-water-filter-bottle-338-fl-oz</t>
+          <t>https://www.rei.com/product/247273/katadyn-befree-ac-10-l-water-filter-bottle</t>
         </is>
       </c>
       <c r="J39" s="38" t="inlineStr">
@@ -16134,7 +16134,7 @@
       </c>
       <c r="S39" s="38" t="inlineStr">
         <is>
-          <t>Group share $7.49 | SAFETY NOTE (added 2026-09-23): sleep with it below freezing -- same hollow-fiber freeze-crack risk as the Sawyer, keep it in the sleeping bag on any night near/below 32F. Cheap chemical backup already on the buy list: Aquatabs 30-pack (research/gear-tiers-extras-food.json, section A, https://www.rei.com/product/109906/aquatabs-water-purification-tablets-package-of-30). | TIER ODDITY: Value ($44.95) is cheaper than Budget ($45.95) in this category -- kept as sourced.</t>
+          <t>Group share $8.83 | SAFETY NOTE (added 2026-09-23): sleep with it below freezing -- same hollow-fiber freeze-crack risk as the Sawyer, keep it in the sleeping bag on any night near/below 32F. Cheap chemical backup already on the buy list: Aquatabs 30-pack (research/gear-tiers-extras-food.json, section A, https://www.rei.com/product/109906/aquatabs-water-purification-tablets-package-of-30). Old plain BeFree 1.0L listing (product 116364) is dead; REI now only sells the BeFree AC version (adds activated carbon for taste/odor), $52.95 not $44.95 -- price jump is real, not a mispick.</t>
         </is>
       </c>
       <c r="T39">
@@ -16270,7 +16270,7 @@
         </is>
       </c>
       <c r="H41" s="40" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="I41" s="41" t="inlineStr">
         <is>
@@ -18474,7 +18474,7 @@
         </is>
       </c>
       <c r="H65" s="40" t="n">
-        <v>4.25</v>
+        <v>8.75</v>
       </c>
       <c r="I65" s="41" t="inlineStr">
         <is>
@@ -18524,7 +18524,7 @@
       </c>
       <c r="S65" s="38" t="inlineStr">
         <is>
-          <t>Split 6 ways (shared cathole trowel, carried on the overnight leg)</t>
+          <t>Split 6 ways (shared cathole trowel, carried on the overnight leg) | TIER ODDITY: Budget ($8.75) costs more than Value ($7.95) in this category -- kept as sourced.</t>
         </is>
       </c>
       <c r="T65">
@@ -18617,7 +18617,7 @@
       </c>
       <c r="S66" s="38" t="inlineStr">
         <is>
-          <t>Split 6 ways (shared cathole trowel, carried on the overnight leg)</t>
+          <t>Split 6 ways (shared cathole trowel, carried on the overnight leg) | TIER ODDITY: Value ($7.95) is cheaper than Budget ($8.75) in this category -- kept as sourced.</t>
         </is>
       </c>
       <c r="T66">
@@ -18753,11 +18753,11 @@
         </is>
       </c>
       <c r="H68" s="40" t="n">
-        <v>6</v>
+        <v>3.94</v>
       </c>
       <c r="I68" s="41" t="inlineStr">
         <is>
-          <t>https://www.walmart.com/ip/Equate-Travel-Size-Toiletry-Kit/</t>
+          <t>https://www.walmart.com/ip/Equate-Travel-Kit-8-Piece-Plastics/831029303</t>
         </is>
       </c>
       <c r="J68" s="38" t="inlineStr">
@@ -18799,7 +18799,7 @@
       </c>
       <c r="S68" s="38" t="inlineStr">
         <is>
-          <t>Personal, full price -- each hiker buys/packs their own</t>
+          <t>Personal, full price -- each hiker buys/packs their own. Old direct-slug URL didn't resolve; replacement is Equate's current 8-Piece Travel Kit (empty refillable bottles, not toothbrush/toothpaste/TP bundled) at its real product ID, $3.94 not $6.00 -- fill it with the toothbrush kit and TP already on the buy list.</t>
         </is>
       </c>
       <c r="T68">
@@ -19020,7 +19020,7 @@
         </is>
       </c>
       <c r="H71" s="40" t="n">
-        <v>39.99</v>
+        <v>49.99</v>
       </c>
       <c r="I71" s="41" t="inlineStr">
         <is>
@@ -19109,11 +19109,11 @@
         </is>
       </c>
       <c r="H72" s="40" t="n">
-        <v>51.98</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="I72" s="41" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Cascade-Mountain-Tech-Carbon-Trekking/dp/B07RH3P6MT</t>
+          <t>https://www.amazon.com/dp/B07S4DRDNT</t>
         </is>
       </c>
       <c r="J72" s="38" t="inlineStr">
@@ -19157,7 +19157,11 @@
       <c r="R72" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="S72" s="38" t="inlineStr"/>
+      <c r="S72" s="38" t="inlineStr">
+        <is>
+          <t>Old ASIN listing is dead; replacement is the current Cascade Mountain Tech Carbon Fiber Quick Lock poles listing, same product line, $64.99 not $51.98 -- flagging the jump.</t>
+        </is>
+      </c>
       <c r="T72">
         <f>A72&amp;"|"&amp;C72</f>
         <v/>
@@ -19376,11 +19380,11 @@
         </is>
       </c>
       <c r="H75" s="40" t="n">
-        <v>19.95</v>
+        <v>34.28</v>
       </c>
       <c r="I75" s="41" t="inlineStr">
         <is>
-          <t>https://www.rei.com/product/734520/therm-a-rest-z-seat</t>
+          <t>https://www.amazon.com/dp/B07MV959N6</t>
         </is>
       </c>
       <c r="J75" s="38" t="inlineStr">
@@ -19424,7 +19428,11 @@
       <c r="R75" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="S75" s="38" t="inlineStr"/>
+      <c r="S75" s="38" t="inlineStr">
+        <is>
+          <t>Old REI product ID dead; renamed "Z Seat Cushion Insulated Sitting Pad" -- replacement is the same product on Amazon (REI access-blocked on repeated checks), $34.28 not $19.95 -- flagging the jump. | TIER ODDITY: Value ($34.28) costs more than Premium ($22.50) in this category -- kept as sourced, not auto-corrected.</t>
+        </is>
+      </c>
       <c r="T75">
         <f>A75&amp;"|"&amp;C75</f>
         <v/>
@@ -19513,7 +19521,11 @@
       <c r="R76" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="S76" s="38" t="inlineStr"/>
+      <c r="S76" s="38" t="inlineStr">
+        <is>
+          <t>TIER ODDITY: Premium ($22.50) is cheaper than Value ($34.28) in this category -- kept as sourced.</t>
+        </is>
+      </c>
       <c r="T76">
         <f>A76&amp;"|"&amp;C76</f>
         <v/>
@@ -20104,7 +20116,7 @@
         </is>
       </c>
       <c r="H83" s="40" t="n">
-        <v>18</v>
+        <v>8.83</v>
       </c>
       <c r="I83" s="41" t="inlineStr">
         <is>
@@ -20476,11 +20488,11 @@
         </is>
       </c>
       <c r="H87" s="40" t="n">
-        <v>100</v>
+        <v>99.95</v>
       </c>
       <c r="I87" s="41" t="inlineStr">
         <is>
-          <t>https://www.rei.com/product/127336/rei-co-op-rainier-rain-jacket-mens</t>
+          <t>https://www.rei.com/product/227570/rei-co-op-rainier-rain-jacket-mens</t>
         </is>
       </c>
       <c r="J87" s="38" t="inlineStr">
@@ -20524,7 +20536,11 @@
       <c r="R87" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="S87" s="38" t="inlineStr"/>
+      <c r="S87" s="38" t="inlineStr">
+        <is>
+          <t>Old listing (#127336) is discontinued; replacement is the current-generation Rainier Rain Jacket (#227570), same name/role/price point (product #127336 no longer sold).</t>
+        </is>
+      </c>
       <c r="T87">
         <f>A87&amp;"|"&amp;C87</f>
         <v/>
@@ -20747,7 +20763,7 @@
         </is>
       </c>
       <c r="H90" s="40" t="n">
-        <v>239</v>
+        <v>118.99</v>
       </c>
       <c r="I90" s="41" t="inlineStr">
         <is>
@@ -20797,7 +20813,7 @@
       </c>
       <c r="S90" s="38" t="inlineStr">
         <is>
-          <t>Watch for sales — this jacket routinely drops to $115-150 | TIER ODDITY: Value ($239.00) costs more than Premium ($170.00) in this category -- kept as sourced, not auto-corrected.</t>
+          <t>Watch for sales — this jacket routinely drops to $115-150</t>
         </is>
       </c>
       <c r="T90">
@@ -20890,7 +20906,7 @@
       </c>
       <c r="S91" s="38" t="inlineStr">
         <is>
-          <t>Order now if going this route — cottage lead times can blow the Oct 15 deadline | TIER ODDITY: Premium ($170.00) is cheaper than Value ($239.00) in this category -- kept as sourced.</t>
+          <t>Order now if going this route — cottage lead times can blow the Oct 15 deadline</t>
         </is>
       </c>
       <c r="T91">
@@ -21258,7 +21274,7 @@
       </c>
       <c r="S95" s="38" t="inlineStr">
         <is>
-          <t>Reserve this set exclusively as dry sleep clothes — never wear it panning | TIER ODDITY: Budget ($100.00) costs more than Value ($95.00) in this category -- kept as sourced.</t>
+          <t>Reserve this set exclusively as dry sleep clothes — never wear it panning</t>
         </is>
       </c>
       <c r="T95">
@@ -21301,7 +21317,7 @@
         </is>
       </c>
       <c r="H96" s="40" t="n">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="I96" s="41" t="inlineStr">
         <is>
@@ -21349,11 +21365,7 @@
       <c r="R96" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="S96" s="38" t="inlineStr">
-        <is>
-          <t>TIER ODDITY: Value ($95.00) is cheaper than Budget ($100.00) in this category -- kept as sourced.</t>
-        </is>
-      </c>
+      <c r="S96" s="38" t="inlineStr"/>
       <c r="T96">
         <f>A96&amp;"|"&amp;C96</f>
         <v/>
@@ -21762,7 +21774,7 @@
         </is>
       </c>
       <c r="H101" s="40" t="n">
-        <v>10</v>
+        <v>14.99</v>
       </c>
       <c r="I101" s="41" t="inlineStr">
         <is>
@@ -22126,11 +22138,11 @@
         </is>
       </c>
       <c r="H105" s="40" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I105" s="41" t="inlineStr">
         <is>
-          <t>https://www.rei.com/product/871650/outdoor-research-pl-400-sensor-gloves-mens</t>
+          <t>https://www.rei.com/product/C08576/outdoor-research-trail-mix-xt-gloves-mens</t>
         </is>
       </c>
       <c r="J105" s="38" t="inlineStr">
@@ -22174,7 +22186,11 @@
       <c r="R105" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="S105" s="38" t="inlineStr"/>
+      <c r="S105" s="38" t="inlineStr">
+        <is>
+          <t>Replacement is Outdoor Research Trail Mix XT Gloves, recycled fleece liner glove, not the PL 400 Sensor Gloves (PL 400 no longer sold).</t>
+        </is>
+      </c>
       <c r="T105">
         <f>A105&amp;"|"&amp;C105</f>
         <v/>
@@ -22850,11 +22866,11 @@
         </is>
       </c>
       <c r="H113" s="40" t="n">
-        <v>10</v>
+        <v>17.37</v>
       </c>
       <c r="I113" s="41" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/SHOWA-Showa-620L-09-1-Pair/dp/B000VNO2BE</t>
+          <t>https://www.amazon.com/620-Coated-Liquid-Chemical-Resistant/dp/B002PJ0WRK</t>
         </is>
       </c>
       <c r="J113" s="38" t="inlineStr">
@@ -22900,7 +22916,7 @@
       </c>
       <c r="S113" s="38" t="inlineStr">
         <is>
-          <t>Order true to hand size; too small and they crack, too large and dexterity for panning suffers</t>
+          <t>Order true to hand size; too small and they crack, too large and dexterity for panning suffers. Replacement listing is the same Atlas 620 model, Small/Orange, from a different seller (original ASIN listing no longer has a valid buyable price). | TIER ODDITY: Budget ($17.37) costs more than Value ($14.99) in this category -- kept as sourced.</t>
         </is>
       </c>
       <c r="T113">
@@ -22943,7 +22959,7 @@
         </is>
       </c>
       <c r="H114" s="40" t="n">
-        <v>18</v>
+        <v>14.99</v>
       </c>
       <c r="I114" s="41" t="inlineStr">
         <is>
@@ -22993,7 +23009,7 @@
       </c>
       <c r="S114" s="38" t="inlineStr">
         <is>
-          <t>Pair with a thin liner glove for the coldest mornings</t>
+          <t>Pair with a thin liner glove for the coldest mornings | TIER ODDITY: Value ($14.99) is cheaper than Budget ($17.37) in this category -- kept as sourced.</t>
         </is>
       </c>
       <c r="T114">
@@ -23679,7 +23695,7 @@
         </is>
       </c>
       <c r="H122" s="40" t="n">
-        <v>8</v>
+        <v>8.99</v>
       </c>
       <c r="I122" s="41" t="inlineStr">
         <is>
@@ -24601,11 +24617,11 @@
         </is>
       </c>
       <c r="H132" s="40" t="n">
-        <v>9</v>
+        <v>11.99</v>
       </c>
       <c r="I132" s="41" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Panning-Sniffer-Snuffer-Bottle-Tweezer/dp/B0D38QYGYR</t>
+          <t>https://www.amazon.com/Mining-Clean-Snuffer-Suction-Tweezers/dp/B01NBXHLVA</t>
         </is>
       </c>
       <c r="J132" s="38" t="inlineStr">
@@ -24649,7 +24665,11 @@
       <c r="R132" s="37" t="n">
         <v>6</v>
       </c>
-      <c r="S132" s="38" t="inlineStr"/>
+      <c r="S132" s="38" t="inlineStr">
+        <is>
+          <t>Replacement is APGOLF's single Clean Up Kit (vials + snuffer + tweezers), not a 2-pack glass-tip snuffer (the 2-pack glass-tip bottle w/ tweezers is no longer sold by any live Amazon listing).</t>
+        </is>
+      </c>
       <c r="T132">
         <f>A132&amp;"|"&amp;C132</f>
         <v/>
@@ -25329,11 +25349,11 @@
         </is>
       </c>
       <c r="H140" s="40" t="n">
-        <v>19</v>
+        <v>7.99</v>
       </c>
       <c r="I140" s="41" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Magnifier-Portable-Keychain-Diamonds-Antiques/dp/B09B1ZBY47</t>
+          <t>https://www.amazon.com/Keychain-Magnifier-Portable-Foldable-Magnifying/dp/B07RVF35W4</t>
         </is>
       </c>
       <c r="J140" s="38" t="inlineStr">
@@ -25379,7 +25399,7 @@
       </c>
       <c r="S140" s="38" t="inlineStr">
         <is>
-          <t>TIER ODDITY: Budget ($19.00) costs more than Value ($13.00) in this category -- kept as sourced.</t>
+          <t>Replacement is Rongon 10x metal folding keychain loupe, not the original plastic keychain magnifier (original listing no longer sold).</t>
         </is>
       </c>
       <c r="T140">
@@ -25422,7 +25442,7 @@
         </is>
       </c>
       <c r="H141" s="40" t="n">
-        <v>13</v>
+        <v>8.98</v>
       </c>
       <c r="I141" s="41" t="inlineStr">
         <is>
@@ -25470,11 +25490,7 @@
       <c r="R141" s="37" t="n">
         <v>6</v>
       </c>
-      <c r="S141" s="38" t="inlineStr">
-        <is>
-          <t>TIER ODDITY: Value ($13.00) is cheaper than Budget ($19.00) in this category -- kept as sourced.</t>
-        </is>
-      </c>
+      <c r="S141" s="38" t="inlineStr"/>
       <c r="T141">
         <f>A141&amp;"|"&amp;C141</f>
         <v/>
@@ -25604,7 +25620,7 @@
         </is>
       </c>
       <c r="H143" s="40" t="n">
-        <v>9</v>
+        <v>6.28</v>
       </c>
       <c r="I143" s="41" t="inlineStr">
         <is>
@@ -26150,7 +26166,7 @@
         </is>
       </c>
       <c r="H149" s="40" t="n">
-        <v>45</v>
+        <v>7.26</v>
       </c>
       <c r="I149" s="41" t="inlineStr">
         <is>
@@ -26200,7 +26216,7 @@
       </c>
       <c r="S149" s="38" t="inlineStr">
         <is>
-          <t>Pack in a mesh bag separate from dry gear per the two-bag wet/dry system in Section C of the main gear plan | TIER ODDITY: Budget ($45.00) costs more than Value ($40.00) in this category -- kept as sourced.</t>
+          <t>Pack in a mesh bag separate from dry gear per the two-bag wet/dry system in Section C of the main gear plan</t>
         </is>
       </c>
       <c r="T149">
@@ -26293,7 +26309,7 @@
       </c>
       <c r="S150" s="38" t="inlineStr">
         <is>
-          <t>Confirm before buying that the kit's non-sluice parts alone meet your needs — don't pay for parts you can't legally use here | TIER ODDITY: Value ($40.00) is cheaper than Budget ($45.00) in this category -- kept as sourced.</t>
+          <t>Confirm before buying that the kit's non-sluice parts alone meet your needs — don't pay for parts you can't legally use here</t>
         </is>
       </c>
       <c r="T150">
@@ -26336,11 +26352,11 @@
         </is>
       </c>
       <c r="H151" s="40" t="n">
-        <v>95</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="I151" s="41" t="inlineStr">
         <is>
-          <t>https://garrett.com/garrett-14-gold-trap-pan/</t>
+          <t>https://www.amazon.com/Garrett-Deluxe-Gold-Pan-Kit/dp/B01LZI4OWD</t>
         </is>
       </c>
       <c r="J151" s="38" t="inlineStr">
@@ -26386,7 +26402,7 @@
       </c>
       <c r="S151" s="38" t="inlineStr">
         <is>
-          <t>Assemble this from the individual premium/value picks above rather than buying a single bundled product</t>
+          <t>Assemble this from the individual premium/value picks above rather than buying a single bundled product. Old garrett.com link now resolves to just the bare 14" pan ($8.99), not a bundle -- replacement is the real Garrett Deluxe Gold Pan Kit (9-piece: 4 pans, classifier, snuffer bottle, tweezers, magnifier) sold on Amazon, the closest verified in-stock equivalent to this curated bundle (no exact stainless-crevice-tools + mesh-sack combo is currently sold as a single product).</t>
         </is>
       </c>
       <c r="T151">

--- a/Gear_Picker.xlsx
+++ b/Gear_Picker.xlsx
@@ -10675,14 +10675,14 @@
       </c>
       <c r="C40" s="32" t="inlineStr">
         <is>
-          <t>Atlas 620 PVC-Coated Gauntlet Glove</t>
+          <t>Kenai Original</t>
         </is>
       </c>
       <c r="D40" s="33" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E40" s="34" t="n">
-        <v>17.37</v>
+        <v>24.99</v>
       </c>
       <c r="F40" s="11" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="I40" s="11" t="inlineStr">
         <is>
-          <t>TreasureNet and prospecting forums repeatedly recommend cheap PVC-dipped work gloves like the Atlas 620 for cold-water panning — a fleece-lined double-dipped PVC glove originally designed for the Alaskan fishing trade, giving real cold/wet protection for around $10.</t>
+          <t>Captain's pick 2026-09-23: 35-year standard for cold fly-fishing, 2mm fleece-lined neoprene with a sharkskin palm -- chose dexterity (feel the pan, pick gravel) over staying bone-dry.</t>
         </is>
       </c>
       <c r="J40" s="11" t="inlineStr">
@@ -10714,14 +10714,14 @@
       </c>
       <c r="L40" s="35" t="inlineStr">
         <is>
-          <t>24" Rubber Gauntlet Gloves, Texturized Palm</t>
+          <t>Kenai Original</t>
         </is>
       </c>
       <c r="M40" s="33" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N40" s="34" t="n">
-        <v>14.99</v>
+        <v>24.99</v>
       </c>
       <c r="O40" s="11" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="R40" s="11" t="inlineStr">
         <is>
-          <t>Purpose-marketed for gold panning specifically, with a longer 24" gauntlet that leaves interior room for a thin knit or fleece glove liner underneath for extra warmth in cold conditions — a step up from generic work gloves at a similar price.</t>
+          <t>Captain's pick 2026-09-23: 35-year standard for cold fly-fishing, 2mm fleece-lined neoprene with a sharkskin palm -- chose dexterity (feel the pan, pick gravel) over staying bone-dry.</t>
         </is>
       </c>
       <c r="S40" s="11" t="inlineStr">
@@ -10972,18 +10972,18 @@
       </c>
       <c r="L42" s="35" t="inlineStr">
         <is>
-          <t>Mackenzie Cleated Hip Bootfoot Fishing Wader</t>
+          <t>Canyon II Stockingfoot Hip Wader, Medium (needs separate wading shoe)</t>
         </is>
       </c>
       <c r="M42" s="33" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="N42" s="34" t="n">
-        <v>43.51</v>
+        <v>98.29000000000001</v>
       </c>
       <c r="O42" s="11" t="inlineStr">
         <is>
-          <t>$20-30 used</t>
+          <t>n/a, cheap enough to buy new</t>
         </is>
       </c>
       <c r="P42" s="11" t="n">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="R42" s="11" t="inlineStr">
         <is>
-          <t>Hip waders show up in wading/fishing gear guides as an affordable step up for anyone who wants to stand in deeper pools without soaking pants — useful if scouting deeper holes, though most panning happens in water too shallow to need them.</t>
+          <t>Breathable upgrade over the rubber/PVC Hodgman pick -- highest-rated breathable hip wader at this size, and hip height already exceeds what shin-deep hand-panning needs. Needs a separate wading shoe (not bundled).</t>
         </is>
       </c>
       <c r="S42" s="11" t="inlineStr">
@@ -11062,18 +11062,18 @@
       </c>
       <c r="C43" s="32" t="inlineStr">
         <is>
-          <t>Foam Gardening Knee Pad</t>
+          <t>Protective Knee Pads, Thick Sponge Anti-Slip Knee Sleeve</t>
         </is>
       </c>
       <c r="D43" s="33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E43" s="34" t="n">
-        <v>8.99</v>
+        <v>15.99</v>
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>$2-4 thrift</t>
+          <t>n/a, cheap enough to buy new</t>
         </is>
       </c>
       <c r="G43" s="11" t="n">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>GPAA forum members discussing favorite knee pads note basic foam gardening pads work fine for short sessions, though some complain the straps can cut into legs over long days.</t>
+          <t>Captain's pick 2026-09-23, replacing the flat foam gardening pad research flagged as not moving with you on uneven creek rock -- a strap-on sleeve that stays on through repeated kneel/reposition.</t>
         </is>
       </c>
       <c r="J43" s="11" t="inlineStr">
@@ -22849,28 +22849,28 @@
       </c>
       <c r="D113" s="37" t="inlineStr">
         <is>
-          <t>Showa</t>
+          <t>Glacier Glove</t>
         </is>
       </c>
       <c r="E113" s="37" t="inlineStr">
         <is>
-          <t>Atlas 620 PVC-Coated Gauntlet Glove</t>
+          <t>Kenai Original</t>
         </is>
       </c>
       <c r="F113" s="39" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G113" s="38" t="inlineStr">
         <is>
-          <t>per pair, estimate from similar PVC gauntlet gloves</t>
+          <t>per pair, 2mm neoprene glove</t>
         </is>
       </c>
       <c r="H113" s="40" t="n">
-        <v>17.37</v>
+        <v>24.99</v>
       </c>
       <c r="I113" s="41" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/620-Coated-Liquid-Chemical-Resistant/dp/B002PJ0WRK</t>
+          <t>https://glacieroutdoor.com/products/kenai-original</t>
         </is>
       </c>
       <c r="J113" s="38" t="inlineStr">
@@ -22880,17 +22880,17 @@
       </c>
       <c r="K113" s="38" t="inlineStr">
         <is>
-          <t>Amazon, Palmflex, Magid</t>
+          <t>Glacier Outdoor, Amazon</t>
         </is>
       </c>
       <c r="L113" s="38" t="inlineStr">
         <is>
-          <t>TreasureNet and prospecting forums repeatedly recommend cheap PVC-dipped work gloves like the Atlas 620 for cold-water panning — a fleece-lined double-dipped PVC glove originally designed for the Alaskan fishing trade, giving real cold/wet protection for around $10.</t>
+          <t>Captain's pick 2026-09-23: 35-year standard for cold fly-fishing, 2mm fleece-lined neoprene with a sharkskin palm -- chose dexterity (feel the pan, pick gravel) over staying bone-dry.</t>
         </is>
       </c>
       <c r="M113" s="38" t="inlineStr">
         <is>
-          <t>https://www.treasurenet.com/threads/prospecting-gloves-advice.379227/, https://www.amazon.com/SHOWA-Showa-620L-09-1-Pair/dp/B000VNO2BE</t>
+          <t>https://glacieroutdoor.com/products/kenai-original</t>
         </is>
       </c>
       <c r="N113" s="38" t="inlineStr">
@@ -22916,7 +22916,7 @@
       </c>
       <c r="S113" s="38" t="inlineStr">
         <is>
-          <t>Order true to hand size; too small and they crack, too large and dexterity for panning suffers. Replacement listing is the same Atlas 620 model, Small/Orange, from a different seller (original ASIN listing no longer has a valid buyable price). | TIER ODDITY: Budget ($17.37) costs more than Value ($14.99) in this category -- kept as sourced.</t>
+          <t>Order true to hand size; too small and they crack, too large and dexterity for panning suffers. Replacement listing is the same Atlas 620 model, Small/Orange, from a different seller (original ASIN listing no longer has a valid buyable price).</t>
         </is>
       </c>
       <c r="T113">
@@ -22942,28 +22942,28 @@
       </c>
       <c r="D114" s="37" t="inlineStr">
         <is>
-          <t>SE / Prospector's Choice</t>
+          <t>Glacier Glove</t>
         </is>
       </c>
       <c r="E114" s="37" t="inlineStr">
         <is>
-          <t>24" Rubber Gauntlet Gloves, Texturized Palm</t>
+          <t>Kenai Original</t>
         </is>
       </c>
       <c r="F114" s="39" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G114" s="38" t="inlineStr">
         <is>
-          <t>per pair, per product listing</t>
+          <t>per pair, 2mm neoprene glove</t>
         </is>
       </c>
       <c r="H114" s="40" t="n">
-        <v>14.99</v>
+        <v>24.99</v>
       </c>
       <c r="I114" s="41" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/SE-GP3-RG60-Prospectors-Choice-Rubber/dp/B06XJDFYWS</t>
+          <t>https://glacieroutdoor.com/products/kenai-original</t>
         </is>
       </c>
       <c r="J114" s="38" t="inlineStr">
@@ -22973,17 +22973,17 @@
       </c>
       <c r="K114" s="38" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Glacier Outdoor, Amazon</t>
         </is>
       </c>
       <c r="L114" s="38" t="inlineStr">
         <is>
-          <t>Purpose-marketed for gold panning specifically, with a longer 24" gauntlet that leaves interior room for a thin knit or fleece glove liner underneath for extra warmth in cold conditions — a step up from generic work gloves at a similar price.</t>
+          <t>Captain's pick 2026-09-23: 35-year standard for cold fly-fishing, 2mm fleece-lined neoprene with a sharkskin palm -- chose dexterity (feel the pan, pick gravel) over staying bone-dry.</t>
         </is>
       </c>
       <c r="M114" s="38" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/SE-GP3-RG60-Prospectors-Choice-Rubber/dp/B06XJDFYWS</t>
+          <t>https://glacieroutdoor.com/products/kenai-original</t>
         </is>
       </c>
       <c r="N114" s="38" t="inlineStr">
@@ -23009,7 +23009,7 @@
       </c>
       <c r="S114" s="38" t="inlineStr">
         <is>
-          <t>Pair with a thin liner glove for the coldest mornings | TIER ODDITY: Value ($14.99) is cheaper than Budget ($17.37) in this category -- kept as sourced.</t>
+          <t>Pair with a thin liner glove for the coldest mornings</t>
         </is>
       </c>
       <c r="T114">
@@ -23492,48 +23492,48 @@
       </c>
       <c r="D120" s="37" t="inlineStr">
         <is>
-          <t>Hodgman</t>
+          <t>FROGG TOGGS</t>
         </is>
       </c>
       <c r="E120" s="37" t="inlineStr">
         <is>
-          <t>Mackenzie Cleated Hip Bootfoot Fishing Wader</t>
+          <t>Canyon II Stockingfoot Hip Wader, Medium (needs separate wading shoe)</t>
         </is>
       </c>
       <c r="F120" s="39" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="G120" s="38" t="inlineStr">
         <is>
-          <t>~3 lb, typical neoprene hip wader pair</t>
+          <t>category estimate, no vendor spec published -- 4-ply nylon, no attached boot</t>
         </is>
       </c>
       <c r="H120" s="40" t="n">
-        <v>43.51</v>
+        <v>98.29000000000001</v>
       </c>
       <c r="I120" s="41" t="inlineStr">
         <is>
-          <t>https://www.walmart.com/ip/Hodgman-Mackenzie-Cleated-Hip-Bootfoot-Fishing-Wader/43927288</t>
+          <t>https://www.amazon.com/Frogg-Toggs-Canyon-Breathable-Stockingfoot/dp/B07FKMB1DB</t>
         </is>
       </c>
       <c r="J120" s="38" t="inlineStr">
         <is>
-          <t>$20-30 used</t>
+          <t>n/a, cheap enough to buy new</t>
         </is>
       </c>
       <c r="K120" s="38" t="inlineStr">
         <is>
-          <t>Walmart, Bass Pro</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="L120" s="38" t="inlineStr">
         <is>
-          <t>Hip waders show up in wading/fishing gear guides as an affordable step up for anyone who wants to stand in deeper pools without soaking pants — useful if scouting deeper holes, though most panning happens in water too shallow to need them.</t>
+          <t>Breathable upgrade over the rubber/PVC Hodgman pick -- highest-rated breathable hip wader at this size, and hip height already exceeds what shin-deep hand-panning needs. Needs a separate wading shoe (not bundled).</t>
         </is>
       </c>
       <c r="M120" s="38" t="inlineStr">
         <is>
-          <t>https://www.walmart.com/ip/Hodgman-Mackenzie-Cleated-Hip-Bootfoot-Fishing-Wader/43927288</t>
+          <t>https://www.froggtoggs.com/canyon-ii-stockingfoot-breathable-hip-wader</t>
         </is>
       </c>
       <c r="N120" s="38" t="inlineStr">
@@ -23678,48 +23678,48 @@
       </c>
       <c r="D122" s="37" t="inlineStr">
         <is>
-          <t>Generic</t>
+          <t>Bodyprox</t>
         </is>
       </c>
       <c r="E122" s="37" t="inlineStr">
         <is>
-          <t>Foam Gardening Knee Pad</t>
+          <t>Protective Knee Pads, Thick Sponge Anti-Slip Knee Sleeve</t>
         </is>
       </c>
       <c r="F122" s="39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G122" s="38" t="inlineStr">
         <is>
-          <t>per pair, standard foam kneeler</t>
+          <t>per pair, strap-on sleeve</t>
         </is>
       </c>
       <c r="H122" s="40" t="n">
-        <v>8.99</v>
+        <v>15.99</v>
       </c>
       <c r="I122" s="41" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Fiskars-94216974J-Ultralight-Kneeling-Cushion/dp/B0002YTVJA</t>
+          <t>https://www.amazon.com/gp/product/B01L379FPE</t>
         </is>
       </c>
       <c r="J122" s="38" t="inlineStr">
         <is>
-          <t>$2-4 thrift</t>
+          <t>n/a, cheap enough to buy new</t>
         </is>
       </c>
       <c r="K122" s="38" t="inlineStr">
         <is>
-          <t>Walmart, hardware store</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="L122" s="38" t="inlineStr">
         <is>
-          <t>GPAA forum members discussing favorite knee pads note basic foam gardening pads work fine for short sessions, though some complain the straps can cut into legs over long days.</t>
+          <t>Captain's pick 2026-09-23, replacing the flat foam gardening pad research flagged as not moving with you on uneven creek rock -- a strap-on sleeve that stays on through repeated kneel/reposition.</t>
         </is>
       </c>
       <c r="M122" s="38" t="inlineStr">
         <is>
-          <t>https://www.goldprospectors.org/Forum/aft/9275</t>
+          <t>https://www.amazon.com/gp/product/B01L379FPE</t>
         </is>
       </c>
       <c r="N122" s="38" t="inlineStr">

--- a/Gear_Picker.xlsx
+++ b/Gear_Picker.xlsx
@@ -28,10 +28,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="0.0&quot; oz&quot;"/>
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="0.00&quot; lb&quot;"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0.00&quot; lb&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.0&quot; oz&quot;"/>
   </numFmts>
   <fonts count="19">
     <font>
@@ -191,7 +191,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -211,26 +211,26 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="11" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="11" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="9" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="9" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -239,10 +239,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -257,10 +257,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -270,6 +270,30 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="11" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="9" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -436,7 +460,6 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -534,7 +557,6 @@
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="11"/>
   <chart>
     <title>
       <tx>
@@ -968,13 +990,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B29"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -985,10 +1008,11 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Captain's personal gear plan -- Oct 15-21 2026, base camp at Vogel State Park + one backcountry overnight (hike 3-5 mi)</t>
-        </is>
-      </c>
-    </row>
+          <t>Jordan's personal gear plan -- Oct 15-21 2026, base camp at Vogel State Park + one backcountry overnight (hike 3-5 mi)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -1129,6 +1153,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="B26" s="5" t="inlineStr">
         <is>
@@ -1328,7 +1353,7 @@
         <f>IF($E2="Own",N($J2),IF(OR($E2="Skip",$E2=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F2)/INDEX(Options!$R$2:$R$174,$F2),0)))</f>
         <v/>
       </c>
-      <c r="I2" s="13">
+      <c r="I2" s="46">
         <f>IF($E2="Own",0,IF(OR($E2="Skip",$E2=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F2)/INDEX(Options!$R$2:$R$174,$F2),0)))</f>
         <v/>
       </c>
@@ -1408,7 +1433,7 @@
         <f>IF($E3="Own",N($J3),IF(OR($E3="Skip",$E3=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F3)/INDEX(Options!$R$2:$R$174,$F3),0)))</f>
         <v/>
       </c>
-      <c r="I3" s="13">
+      <c r="I3" s="46">
         <f>IF($E3="Own",0,IF(OR($E3="Skip",$E3=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F3)/INDEX(Options!$R$2:$R$174,$F3),0)))</f>
         <v/>
       </c>
@@ -1488,7 +1513,7 @@
         <f>IF($E4="Own",N($J4),IF(OR($E4="Skip",$E4=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F4)/INDEX(Options!$R$2:$R$174,$F4),0)))</f>
         <v/>
       </c>
-      <c r="I4" s="13">
+      <c r="I4" s="46">
         <f>IF($E4="Own",0,IF(OR($E4="Skip",$E4=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F4)/INDEX(Options!$R$2:$R$174,$F4),0)))</f>
         <v/>
       </c>
@@ -1568,7 +1593,7 @@
         <f>IF($E5="Own",N($J5),IF(OR($E5="Skip",$E5=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F5)/INDEX(Options!$R$2:$R$174,$F5),0)))</f>
         <v/>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="46">
         <f>IF($E5="Own",0,IF(OR($E5="Skip",$E5=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F5)/INDEX(Options!$R$2:$R$174,$F5),0)))</f>
         <v/>
       </c>
@@ -1648,7 +1673,7 @@
         <f>IF($E6="Own",N($J6),IF(OR($E6="Skip",$E6=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F6)/INDEX(Options!$R$2:$R$174,$F6),0)))</f>
         <v/>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="46">
         <f>IF($E6="Own",0,IF(OR($E6="Skip",$E6=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F6)/INDEX(Options!$R$2:$R$174,$F6),0)))</f>
         <v/>
       </c>
@@ -1728,7 +1753,7 @@
         <f>IF($E7="Own",N($J7),IF(OR($E7="Skip",$E7=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F7)/INDEX(Options!$R$2:$R$174,$F7),0)))</f>
         <v/>
       </c>
-      <c r="I7" s="13">
+      <c r="I7" s="46">
         <f>IF($E7="Own",0,IF(OR($E7="Skip",$E7=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F7)/INDEX(Options!$R$2:$R$174,$F7),0)))</f>
         <v/>
       </c>
@@ -1808,7 +1833,7 @@
         <f>IF($E8="Own",N($J8),IF(OR($E8="Skip",$E8=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F8)/INDEX(Options!$R$2:$R$174,$F8),0)))</f>
         <v/>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="46">
         <f>IF($E8="Own",0,IF(OR($E8="Skip",$E8=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F8)/INDEX(Options!$R$2:$R$174,$F8),0)))</f>
         <v/>
       </c>
@@ -1888,7 +1913,7 @@
         <f>IF($E9="Own",N($J9),IF(OR($E9="Skip",$E9=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F9)/INDEX(Options!$R$2:$R$174,$F9),0)))</f>
         <v/>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="46">
         <f>IF($E9="Own",0,IF(OR($E9="Skip",$E9=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F9)/INDEX(Options!$R$2:$R$174,$F9),0)))</f>
         <v/>
       </c>
@@ -1968,7 +1993,7 @@
         <f>IF($E10="Own",N($J10),IF(OR($E10="Skip",$E10=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F10)/INDEX(Options!$R$2:$R$174,$F10),0)))</f>
         <v/>
       </c>
-      <c r="I10" s="13">
+      <c r="I10" s="46">
         <f>IF($E10="Own",0,IF(OR($E10="Skip",$E10=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F10)/INDEX(Options!$R$2:$R$174,$F10),0)))</f>
         <v/>
       </c>
@@ -2042,7 +2067,7 @@
         <f>IF($E11="Own",N($J11),IF(OR($E11="Skip",$E11=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F11)/INDEX(Options!$R$2:$R$174,$F11),0)))</f>
         <v/>
       </c>
-      <c r="I11" s="13">
+      <c r="I11" s="46">
         <f>IF($E11="Own",0,IF(OR($E11="Skip",$E11=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F11)/INDEX(Options!$R$2:$R$174,$F11),0)))</f>
         <v/>
       </c>
@@ -2122,7 +2147,7 @@
         <f>IF($E12="Own",N($J12),IF(OR($E12="Skip",$E12=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F12)/INDEX(Options!$R$2:$R$174,$F12),0)))</f>
         <v/>
       </c>
-      <c r="I12" s="13">
+      <c r="I12" s="46">
         <f>IF($E12="Own",0,IF(OR($E12="Skip",$E12=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F12)/INDEX(Options!$R$2:$R$174,$F12),0)))</f>
         <v/>
       </c>
@@ -2202,7 +2227,7 @@
         <f>IF($E13="Own",N($J13),IF(OR($E13="Skip",$E13=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F13)/INDEX(Options!$R$2:$R$174,$F13),0)))</f>
         <v/>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="46">
         <f>IF($E13="Own",0,IF(OR($E13="Skip",$E13=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F13)/INDEX(Options!$R$2:$R$174,$F13),0)))</f>
         <v/>
       </c>
@@ -2282,7 +2307,7 @@
         <f>IF($E14="Own",N($J14),IF(OR($E14="Skip",$E14=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F14)/INDEX(Options!$R$2:$R$174,$F14),0)))</f>
         <v/>
       </c>
-      <c r="I14" s="13">
+      <c r="I14" s="46">
         <f>IF($E14="Own",0,IF(OR($E14="Skip",$E14=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F14)/INDEX(Options!$R$2:$R$174,$F14),0)))</f>
         <v/>
       </c>
@@ -2362,7 +2387,7 @@
         <f>IF($E15="Own",N($J15),IF(OR($E15="Skip",$E15=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F15)/INDEX(Options!$R$2:$R$174,$F15),0)))</f>
         <v/>
       </c>
-      <c r="I15" s="13">
+      <c r="I15" s="46">
         <f>IF($E15="Own",0,IF(OR($E15="Skip",$E15=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F15)/INDEX(Options!$R$2:$R$174,$F15),0)))</f>
         <v/>
       </c>
@@ -2442,7 +2467,7 @@
         <f>IF($E16="Own",N($J16),IF(OR($E16="Skip",$E16=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F16)/INDEX(Options!$R$2:$R$174,$F16),0)))</f>
         <v/>
       </c>
-      <c r="I16" s="13">
+      <c r="I16" s="46">
         <f>IF($E16="Own",0,IF(OR($E16="Skip",$E16=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F16)/INDEX(Options!$R$2:$R$174,$F16),0)))</f>
         <v/>
       </c>
@@ -2522,7 +2547,7 @@
         <f>IF($E17="Own",N($J17),IF(OR($E17="Skip",$E17=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F17)/INDEX(Options!$R$2:$R$174,$F17),0)))</f>
         <v/>
       </c>
-      <c r="I17" s="13">
+      <c r="I17" s="46">
         <f>IF($E17="Own",0,IF(OR($E17="Skip",$E17=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F17)/INDEX(Options!$R$2:$R$174,$F17),0)))</f>
         <v/>
       </c>
@@ -2602,7 +2627,7 @@
         <f>IF($E18="Own",N($J18),IF(OR($E18="Skip",$E18=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F18)/INDEX(Options!$R$2:$R$174,$F18),0)))</f>
         <v/>
       </c>
-      <c r="I18" s="13">
+      <c r="I18" s="46">
         <f>IF($E18="Own",0,IF(OR($E18="Skip",$E18=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F18)/INDEX(Options!$R$2:$R$174,$F18),0)))</f>
         <v/>
       </c>
@@ -2682,7 +2707,7 @@
         <f>IF($E19="Own",N($J19),IF(OR($E19="Skip",$E19=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F19)/INDEX(Options!$R$2:$R$174,$F19),0)))</f>
         <v/>
       </c>
-      <c r="I19" s="13">
+      <c r="I19" s="46">
         <f>IF($E19="Own",0,IF(OR($E19="Skip",$E19=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F19)/INDEX(Options!$R$2:$R$174,$F19),0)))</f>
         <v/>
       </c>
@@ -2762,7 +2787,7 @@
         <f>IF($E20="Own",N($J20),IF(OR($E20="Skip",$E20=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F20)/INDEX(Options!$R$2:$R$174,$F20),0)))</f>
         <v/>
       </c>
-      <c r="I20" s="13">
+      <c r="I20" s="46">
         <f>IF($E20="Own",0,IF(OR($E20="Skip",$E20=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F20)/INDEX(Options!$R$2:$R$174,$F20),0)))</f>
         <v/>
       </c>
@@ -2842,7 +2867,7 @@
         <f>IF($E21="Own",N($J21),IF(OR($E21="Skip",$E21=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F21)/INDEX(Options!$R$2:$R$174,$F21),0)))</f>
         <v/>
       </c>
-      <c r="I21" s="13">
+      <c r="I21" s="46">
         <f>IF($E21="Own",0,IF(OR($E21="Skip",$E21=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F21)/INDEX(Options!$R$2:$R$174,$F21),0)))</f>
         <v/>
       </c>
@@ -2922,7 +2947,7 @@
         <f>IF($E22="Own",N($J22),IF(OR($E22="Skip",$E22=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F22)/INDEX(Options!$R$2:$R$174,$F22),0)))</f>
         <v/>
       </c>
-      <c r="I22" s="13">
+      <c r="I22" s="46">
         <f>IF($E22="Own",0,IF(OR($E22="Skip",$E22=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F22)/INDEX(Options!$R$2:$R$174,$F22),0)))</f>
         <v/>
       </c>
@@ -3002,7 +3027,7 @@
         <f>IF($E23="Own",N($J23),IF(OR($E23="Skip",$E23=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F23)/INDEX(Options!$R$2:$R$174,$F23),0)))</f>
         <v/>
       </c>
-      <c r="I23" s="13">
+      <c r="I23" s="46">
         <f>IF($E23="Own",0,IF(OR($E23="Skip",$E23=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F23)/INDEX(Options!$R$2:$R$174,$F23),0)))</f>
         <v/>
       </c>
@@ -3082,7 +3107,7 @@
         <f>IF($E24="Own",N($J24),IF(OR($E24="Skip",$E24=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F24)/INDEX(Options!$R$2:$R$174,$F24),0)))</f>
         <v/>
       </c>
-      <c r="I24" s="13">
+      <c r="I24" s="46">
         <f>IF($E24="Own",0,IF(OR($E24="Skip",$E24=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F24)/INDEX(Options!$R$2:$R$174,$F24),0)))</f>
         <v/>
       </c>
@@ -3162,7 +3187,7 @@
         <f>IF($E25="Own",N($J25),IF(OR($E25="Skip",$E25=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F25)/INDEX(Options!$R$2:$R$174,$F25),0)))</f>
         <v/>
       </c>
-      <c r="I25" s="13">
+      <c r="I25" s="46">
         <f>IF($E25="Own",0,IF(OR($E25="Skip",$E25=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F25)/INDEX(Options!$R$2:$R$174,$F25),0)))</f>
         <v/>
       </c>
@@ -3242,7 +3267,7 @@
         <f>IF($E26="Own",N($J26),IF(OR($E26="Skip",$E26=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F26)/INDEX(Options!$R$2:$R$174,$F26),0)))</f>
         <v/>
       </c>
-      <c r="I26" s="13">
+      <c r="I26" s="46">
         <f>IF($E26="Own",0,IF(OR($E26="Skip",$E26=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F26)/INDEX(Options!$R$2:$R$174,$F26),0)))</f>
         <v/>
       </c>
@@ -3322,7 +3347,7 @@
         <f>IF($E27="Own",N($J27),IF(OR($E27="Skip",$E27=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F27)/INDEX(Options!$R$2:$R$174,$F27),0)))</f>
         <v/>
       </c>
-      <c r="I27" s="13">
+      <c r="I27" s="46">
         <f>IF($E27="Own",0,IF(OR($E27="Skip",$E27=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F27)/INDEX(Options!$R$2:$R$174,$F27),0)))</f>
         <v/>
       </c>
@@ -3402,7 +3427,7 @@
         <f>IF($E28="Own",N($J28),IF(OR($E28="Skip",$E28=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F28)/INDEX(Options!$R$2:$R$174,$F28),0)))</f>
         <v/>
       </c>
-      <c r="I28" s="13">
+      <c r="I28" s="46">
         <f>IF($E28="Own",0,IF(OR($E28="Skip",$E28=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F28)/INDEX(Options!$R$2:$R$174,$F28),0)))</f>
         <v/>
       </c>
@@ -3482,7 +3507,7 @@
         <f>IF($E29="Own",N($J29),IF(OR($E29="Skip",$E29=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F29)/INDEX(Options!$R$2:$R$174,$F29),0)))</f>
         <v/>
       </c>
-      <c r="I29" s="13">
+      <c r="I29" s="46">
         <f>IF($E29="Own",0,IF(OR($E29="Skip",$E29=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F29)/INDEX(Options!$R$2:$R$174,$F29),0)))</f>
         <v/>
       </c>
@@ -3562,7 +3587,7 @@
         <f>IF($E30="Own",N($J30),IF(OR($E30="Skip",$E30=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F30)/INDEX(Options!$R$2:$R$174,$F30),0)))</f>
         <v/>
       </c>
-      <c r="I30" s="13">
+      <c r="I30" s="46">
         <f>IF($E30="Own",0,IF(OR($E30="Skip",$E30=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F30)/INDEX(Options!$R$2:$R$174,$F30),0)))</f>
         <v/>
       </c>
@@ -3642,7 +3667,7 @@
         <f>IF($E31="Own",N($J31),IF(OR($E31="Skip",$E31=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F31)/INDEX(Options!$R$2:$R$174,$F31),0)))</f>
         <v/>
       </c>
-      <c r="I31" s="13">
+      <c r="I31" s="46">
         <f>IF($E31="Own",0,IF(OR($E31="Skip",$E31=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F31)/INDEX(Options!$R$2:$R$174,$F31),0)))</f>
         <v/>
       </c>
@@ -3722,7 +3747,7 @@
         <f>IF($E32="Own",N($J32),IF(OR($E32="Skip",$E32=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F32)/INDEX(Options!$R$2:$R$174,$F32),0)))</f>
         <v/>
       </c>
-      <c r="I32" s="13">
+      <c r="I32" s="46">
         <f>IF($E32="Own",0,IF(OR($E32="Skip",$E32=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F32)/INDEX(Options!$R$2:$R$174,$F32),0)))</f>
         <v/>
       </c>
@@ -3802,7 +3827,7 @@
         <f>IF($E33="Own",N($J33),IF(OR($E33="Skip",$E33=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F33)/INDEX(Options!$R$2:$R$174,$F33),0)))</f>
         <v/>
       </c>
-      <c r="I33" s="13">
+      <c r="I33" s="46">
         <f>IF($E33="Own",0,IF(OR($E33="Skip",$E33=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F33)/INDEX(Options!$R$2:$R$174,$F33),0)))</f>
         <v/>
       </c>
@@ -3882,7 +3907,7 @@
         <f>IF($E34="Own",N($J34),IF(OR($E34="Skip",$E34=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F34)/INDEX(Options!$R$2:$R$174,$F34),0)))</f>
         <v/>
       </c>
-      <c r="I34" s="13">
+      <c r="I34" s="46">
         <f>IF($E34="Own",0,IF(OR($E34="Skip",$E34=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F34)/INDEX(Options!$R$2:$R$174,$F34),0)))</f>
         <v/>
       </c>
@@ -3962,7 +3987,7 @@
         <f>IF($E35="Own",N($J35),IF(OR($E35="Skip",$E35=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F35)/INDEX(Options!$R$2:$R$174,$F35),0)))</f>
         <v/>
       </c>
-      <c r="I35" s="13">
+      <c r="I35" s="46">
         <f>IF($E35="Own",0,IF(OR($E35="Skip",$E35=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F35)/INDEX(Options!$R$2:$R$174,$F35),0)))</f>
         <v/>
       </c>
@@ -4042,7 +4067,7 @@
         <f>IF($E36="Own",N($J36),IF(OR($E36="Skip",$E36=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F36)/INDEX(Options!$R$2:$R$174,$F36),0)))</f>
         <v/>
       </c>
-      <c r="I36" s="13">
+      <c r="I36" s="46">
         <f>IF($E36="Own",0,IF(OR($E36="Skip",$E36=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F36)/INDEX(Options!$R$2:$R$174,$F36),0)))</f>
         <v/>
       </c>
@@ -4122,7 +4147,7 @@
         <f>IF($E37="Own",N($J37),IF(OR($E37="Skip",$E37=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F37)/INDEX(Options!$R$2:$R$174,$F37),0)))</f>
         <v/>
       </c>
-      <c r="I37" s="13">
+      <c r="I37" s="46">
         <f>IF($E37="Own",0,IF(OR($E37="Skip",$E37=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F37)/INDEX(Options!$R$2:$R$174,$F37),0)))</f>
         <v/>
       </c>
@@ -4202,7 +4227,7 @@
         <f>IF($E38="Own",N($J38),IF(OR($E38="Skip",$E38=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F38)/INDEX(Options!$R$2:$R$174,$F38),0)))</f>
         <v/>
       </c>
-      <c r="I38" s="13">
+      <c r="I38" s="46">
         <f>IF($E38="Own",0,IF(OR($E38="Skip",$E38=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F38)/INDEX(Options!$R$2:$R$174,$F38),0)))</f>
         <v/>
       </c>
@@ -4282,7 +4307,7 @@
         <f>IF($E39="Own",N($J39),IF(OR($E39="Skip",$E39=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F39)/INDEX(Options!$R$2:$R$174,$F39),0)))</f>
         <v/>
       </c>
-      <c r="I39" s="13">
+      <c r="I39" s="46">
         <f>IF($E39="Own",0,IF(OR($E39="Skip",$E39=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F39)/INDEX(Options!$R$2:$R$174,$F39),0)))</f>
         <v/>
       </c>
@@ -4362,7 +4387,7 @@
         <f>IF($E40="Own",N($J40),IF(OR($E40="Skip",$E40=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F40)/INDEX(Options!$R$2:$R$174,$F40),0)))</f>
         <v/>
       </c>
-      <c r="I40" s="13">
+      <c r="I40" s="46">
         <f>IF($E40="Own",0,IF(OR($E40="Skip",$E40=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F40)/INDEX(Options!$R$2:$R$174,$F40),0)))</f>
         <v/>
       </c>
@@ -4442,7 +4467,7 @@
         <f>IF($E41="Own",N($J41),IF(OR($E41="Skip",$E41=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F41)/INDEX(Options!$R$2:$R$174,$F41),0)))</f>
         <v/>
       </c>
-      <c r="I41" s="13">
+      <c r="I41" s="46">
         <f>IF($E41="Own",0,IF(OR($E41="Skip",$E41=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F41)/INDEX(Options!$R$2:$R$174,$F41),0)))</f>
         <v/>
       </c>
@@ -4522,7 +4547,7 @@
         <f>IF($E42="Own",N($J42),IF(OR($E42="Skip",$E42=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F42)/INDEX(Options!$R$2:$R$174,$F42),0)))</f>
         <v/>
       </c>
-      <c r="I42" s="13">
+      <c r="I42" s="46">
         <f>IF($E42="Own",0,IF(OR($E42="Skip",$E42=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F42)/INDEX(Options!$R$2:$R$174,$F42),0)))</f>
         <v/>
       </c>
@@ -4602,7 +4627,7 @@
         <f>IF($E43="Own",N($J43),IF(OR($E43="Skip",$E43=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F43)/INDEX(Options!$R$2:$R$174,$F43),0)))</f>
         <v/>
       </c>
-      <c r="I43" s="13">
+      <c r="I43" s="46">
         <f>IF($E43="Own",0,IF(OR($E43="Skip",$E43=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F43)/INDEX(Options!$R$2:$R$174,$F43),0)))</f>
         <v/>
       </c>
@@ -4682,7 +4707,7 @@
         <f>IF($E44="Own",N($J44),IF(OR($E44="Skip",$E44=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F44)/INDEX(Options!$R$2:$R$174,$F44),0)))</f>
         <v/>
       </c>
-      <c r="I44" s="13">
+      <c r="I44" s="46">
         <f>IF($E44="Own",0,IF(OR($E44="Skip",$E44=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F44)/INDEX(Options!$R$2:$R$174,$F44),0)))</f>
         <v/>
       </c>
@@ -4762,7 +4787,7 @@
         <f>IF($E45="Own",N($J45),IF(OR($E45="Skip",$E45=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F45)/INDEX(Options!$R$2:$R$174,$F45),0)))</f>
         <v/>
       </c>
-      <c r="I45" s="13">
+      <c r="I45" s="46">
         <f>IF($E45="Own",0,IF(OR($E45="Skip",$E45=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F45)/INDEX(Options!$R$2:$R$174,$F45),0)))</f>
         <v/>
       </c>
@@ -4812,7 +4837,7 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>Waders (Captain wants them; plan only needs shin-deep, but his call)</t>
+          <t>Waders (Jordan wants them; plan only needs shin-deep, but his call)</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
@@ -4842,7 +4867,7 @@
         <f>IF($E46="Own",N($J46),IF(OR($E46="Skip",$E46=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F46)/INDEX(Options!$R$2:$R$174,$F46),0)))</f>
         <v/>
       </c>
-      <c r="I46" s="13">
+      <c r="I46" s="46">
         <f>IF($E46="Own",0,IF(OR($E46="Skip",$E46=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F46)/INDEX(Options!$R$2:$R$174,$F46),0)))</f>
         <v/>
       </c>
@@ -4922,7 +4947,7 @@
         <f>IF($E47="Own",N($J47),IF(OR($E47="Skip",$E47=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F47)/INDEX(Options!$R$2:$R$174,$F47),0)))</f>
         <v/>
       </c>
-      <c r="I47" s="13">
+      <c r="I47" s="46">
         <f>IF($E47="Own",0,IF(OR($E47="Skip",$E47=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F47)/INDEX(Options!$R$2:$R$174,$F47),0)))</f>
         <v/>
       </c>
@@ -5002,7 +5027,7 @@
         <f>IF($E48="Own",N($J48),IF(OR($E48="Skip",$E48=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F48)/INDEX(Options!$R$2:$R$174,$F48),0)))</f>
         <v/>
       </c>
-      <c r="I48" s="13">
+      <c r="I48" s="46">
         <f>IF($E48="Own",0,IF(OR($E48="Skip",$E48=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F48)/INDEX(Options!$R$2:$R$174,$F48),0)))</f>
         <v/>
       </c>
@@ -5082,7 +5107,7 @@
         <f>IF($E49="Own",N($J49),IF(OR($E49="Skip",$E49=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F49)/INDEX(Options!$R$2:$R$174,$F49),0)))</f>
         <v/>
       </c>
-      <c r="I49" s="13">
+      <c r="I49" s="46">
         <f>IF($E49="Own",0,IF(OR($E49="Skip",$E49=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F49)/INDEX(Options!$R$2:$R$174,$F49),0)))</f>
         <v/>
       </c>
@@ -5136,11 +5161,11 @@
       <c r="E50" s="14" t="n"/>
       <c r="F50" s="14" t="n"/>
       <c r="G50" s="14" t="n"/>
-      <c r="H50" s="15">
+      <c r="H50" s="47">
         <f>SUM(H2:H7)</f>
         <v/>
       </c>
-      <c r="I50" s="16">
+      <c r="I50" s="48">
         <f>SUM(I2:I7)</f>
         <v/>
       </c>
@@ -5161,11 +5186,11 @@
       <c r="E51" s="14" t="n"/>
       <c r="F51" s="14" t="n"/>
       <c r="G51" s="14" t="n"/>
-      <c r="H51" s="15">
+      <c r="H51" s="47">
         <f>SUM(H8:H35)</f>
         <v/>
       </c>
-      <c r="I51" s="16">
+      <c r="I51" s="48">
         <f>SUM(I8:I35)</f>
         <v/>
       </c>
@@ -5186,11 +5211,11 @@
       <c r="E52" s="14" t="n"/>
       <c r="F52" s="14" t="n"/>
       <c r="G52" s="14" t="n"/>
-      <c r="H52" s="15">
+      <c r="H52" s="47">
         <f>SUM(H36:H43)</f>
         <v/>
       </c>
-      <c r="I52" s="16">
+      <c r="I52" s="48">
         <f>SUM(I36:I43)</f>
         <v/>
       </c>
@@ -5211,11 +5236,11 @@
       <c r="E53" s="14" t="n"/>
       <c r="F53" s="14" t="n"/>
       <c r="G53" s="14" t="n"/>
-      <c r="H53" s="15">
+      <c r="H53" s="47">
         <f>SUM(H44:H49)</f>
         <v/>
       </c>
-      <c r="I53" s="16">
+      <c r="I53" s="48">
         <f>SUM(I44:I49)</f>
         <v/>
       </c>
@@ -5236,11 +5261,11 @@
       <c r="E54" s="17" t="n"/>
       <c r="F54" s="17" t="n"/>
       <c r="G54" s="17" t="n"/>
-      <c r="H54" s="18">
+      <c r="H54" s="49">
         <f>SUM(H2:H49)</f>
         <v/>
       </c>
-      <c r="I54" s="19">
+      <c r="I54" s="50">
         <f>SUM(I2:I49)</f>
         <v/>
       </c>
@@ -5303,7 +5328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:E24"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -5313,6 +5338,7 @@
     <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -5327,6 +5353,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="16" customHeight="1">
       <c r="B5" s="20" t="inlineStr">
         <is>
@@ -5350,29 +5377,31 @@
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="B6" s="21">
+      <c r="B6" s="51">
         <f>SUM(Picker!H2:H7)/16</f>
         <v/>
       </c>
-      <c r="C6" s="21">
+      <c r="C6" s="51">
         <f>(SUM(Picker!H8:H35)+SUM(Picker!H36:H43))/16</f>
         <v/>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="51">
         <f>((SUM(Picker!H8:H35)+SUM(Picker!H36:H43))+48+35.2)/16</f>
         <v/>
       </c>
-      <c r="E6" s="22">
+      <c r="E6" s="52">
         <f>SUM(Picker!I2:I49)</f>
         <v/>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="B8" s="23">
         <f>TEXT(INT(((SUM(Picker!H8:H35)+SUM(Picker!H36:H43))+48+35.2)/16),"0")&amp;" lb "&amp;TEXT(MOD((SUM(Picker!H8:H35)+SUM(Picker!H36:H43))+48+35.2,16),"0.0")&amp;" oz  (includes food 3.0 lb + water 2.2 lb)"</f>
         <v/>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="B10" s="24" t="inlineStr">
         <is>
@@ -5407,7 +5436,7 @@
         <f>Picker!H50/16</f>
         <v/>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="53">
         <f>Picker!I50</f>
         <v/>
       </c>
@@ -5422,7 +5451,7 @@
         <f>Picker!H51/16</f>
         <v/>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="53">
         <f>Picker!I51</f>
         <v/>
       </c>
@@ -5437,7 +5466,7 @@
         <f>Picker!H52/16</f>
         <v/>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="53">
         <f>Picker!I52</f>
         <v/>
       </c>
@@ -5452,11 +5481,12 @@
         <f>Picker!H53/16</f>
         <v/>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="53">
         <f>Picker!I53</f>
         <v/>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="B17" s="5" t="inlineStr">
         <is>
@@ -5468,6 +5498,7 @@
         <v/>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="B19" s="24" t="inlineStr">
         <is>
@@ -5502,7 +5533,7 @@
         <f>(SUM(Picker!N8:N35)+SUM(Picker!N36:N43))/16</f>
         <v/>
       </c>
-      <c r="D21" s="26">
+      <c r="D21" s="53">
         <f>SUM(Picker!O2:O49)</f>
         <v/>
       </c>
@@ -5517,7 +5548,7 @@
         <f>(SUM(Picker!P8:P35)+SUM(Picker!P36:P43))/16</f>
         <v/>
       </c>
-      <c r="D22" s="26">
+      <c r="D22" s="53">
         <f>SUM(Picker!Q2:Q49)</f>
         <v/>
       </c>
@@ -5532,7 +5563,7 @@
         <f>(SUM(Picker!R8:R35)+SUM(Picker!R36:R43))/16</f>
         <v/>
       </c>
-      <c r="D23" s="26">
+      <c r="D23" s="53">
         <f>SUM(Picker!S2:S49)</f>
         <v/>
       </c>
@@ -5905,10 +5936,10 @@
           <t>Rook 65 (men's) / Renn 65 (women's)</t>
         </is>
       </c>
-      <c r="D3" s="33" t="n">
+      <c r="D3" s="54" t="n">
         <v>66</v>
       </c>
-      <c r="E3" s="34" t="n">
+      <c r="E3" s="55" t="n">
         <v>205</v>
       </c>
       <c r="F3" s="11" t="inlineStr">
@@ -5944,10 +5975,10 @@
           <t>Flash 55</t>
         </is>
       </c>
-      <c r="M3" s="33" t="n">
+      <c r="M3" s="54" t="n">
         <v>45</v>
       </c>
-      <c r="N3" s="34" t="n">
+      <c r="N3" s="55" t="n">
         <v>229</v>
       </c>
       <c r="O3" s="11" t="inlineStr">
@@ -5983,10 +6014,10 @@
           <t>Mariposa 60</t>
         </is>
       </c>
-      <c r="V3" s="33" t="n">
+      <c r="V3" s="54" t="n">
         <v>34.2</v>
       </c>
-      <c r="W3" s="34" t="n">
+      <c r="W3" s="55" t="n">
         <v>315</v>
       </c>
       <c r="X3" s="11" t="inlineStr">
@@ -6034,10 +6065,10 @@
           <t>Late Start 1P Tent</t>
         </is>
       </c>
-      <c r="D4" s="33" t="n">
+      <c r="D4" s="54" t="n">
         <v>57</v>
       </c>
-      <c r="E4" s="34" t="n">
+      <c r="E4" s="55" t="n">
         <v>149.95</v>
       </c>
       <c r="F4" s="11" t="inlineStr">
@@ -6073,10 +6104,10 @@
           <t>Elixir 1 Tent with Footprint</t>
         </is>
       </c>
-      <c r="M4" s="33" t="n">
+      <c r="M4" s="54" t="n">
         <v>65</v>
       </c>
-      <c r="N4" s="34" t="n">
+      <c r="N4" s="55" t="n">
         <v>289.95</v>
       </c>
       <c r="O4" s="11" t="inlineStr">
@@ -6112,10 +6143,10 @@
           <t>Dragonfly OSMO 1P Ultralight Backpacking Tent</t>
         </is>
       </c>
-      <c r="V4" s="33" t="n">
+      <c r="V4" s="54" t="n">
         <v>34</v>
       </c>
-      <c r="W4" s="34" t="n">
+      <c r="W4" s="55" t="n">
         <v>499.95</v>
       </c>
       <c r="X4" s="11" t="inlineStr">
@@ -6163,10 +6194,10 @@
           <t>Trestles Elite Eco 20 (or Kelty Cosmic 20 Synthetic)</t>
         </is>
       </c>
-      <c r="D5" s="33" t="n">
+      <c r="D5" s="54" t="n">
         <v>53</v>
       </c>
-      <c r="E5" s="34" t="n">
+      <c r="E5" s="55" t="n">
         <v>179</v>
       </c>
       <c r="F5" s="11" t="inlineStr">
@@ -6202,10 +6233,10 @@
           <t>Revelation 20 (stock, 850fp)</t>
         </is>
       </c>
-      <c r="M5" s="33" t="n">
+      <c r="M5" s="54" t="n">
         <v>26</v>
       </c>
-      <c r="N5" s="34" t="n">
+      <c r="N5" s="55" t="n">
         <v>280</v>
       </c>
       <c r="O5" s="11" t="inlineStr">
@@ -6241,10 +6272,10 @@
           <t>Alsek 22</t>
         </is>
       </c>
-      <c r="V5" s="33" t="n">
+      <c r="V5" s="54" t="n">
         <v>25.5</v>
       </c>
-      <c r="W5" s="34" t="n">
+      <c r="W5" s="55" t="n">
         <v>399</v>
       </c>
       <c r="X5" s="11" t="inlineStr">
@@ -6292,10 +6323,10 @@
           <t>Insulated Static V</t>
         </is>
       </c>
-      <c r="D6" s="33" t="n">
+      <c r="D6" s="54" t="n">
         <v>25</v>
       </c>
-      <c r="E6" s="34" t="n">
+      <c r="E6" s="55" t="n">
         <v>74.20999999999999</v>
       </c>
       <c r="F6" s="11" t="inlineStr">
@@ -6331,10 +6362,10 @@
           <t>Tensor All-Season Ultralight Insulated</t>
         </is>
       </c>
-      <c r="M6" s="33" t="n">
+      <c r="M6" s="54" t="n">
         <v>14.1</v>
       </c>
-      <c r="N6" s="34" t="n">
+      <c r="N6" s="55" t="n">
         <v>199.95</v>
       </c>
       <c r="O6" s="11" t="inlineStr">
@@ -6370,10 +6401,10 @@
           <t>Tensor Extreme Conditions</t>
         </is>
       </c>
-      <c r="V6" s="33" t="n">
+      <c r="V6" s="54" t="n">
         <v>19</v>
       </c>
-      <c r="W6" s="34" t="n">
+      <c r="W6" s="55" t="n">
         <v>259.95</v>
       </c>
       <c r="X6" s="11" t="inlineStr">
@@ -6421,10 +6452,10 @@
           <t>Stuff sack filled with spare clothes (or generic inflatable pillow)</t>
         </is>
       </c>
-      <c r="D7" s="33" t="n">
+      <c r="D7" s="54" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="34" t="n">
+      <c r="E7" s="55" t="n">
         <v>20</v>
       </c>
       <c r="F7" s="11" t="inlineStr">
@@ -6460,10 +6491,10 @@
           <t>Aeros Down Pillow (Regular)</t>
         </is>
       </c>
-      <c r="M7" s="33" t="n">
+      <c r="M7" s="54" t="n">
         <v>2.5</v>
       </c>
-      <c r="N7" s="34" t="n">
+      <c r="N7" s="55" t="n">
         <v>64.95</v>
       </c>
       <c r="O7" s="11" t="inlineStr">
@@ -6499,10 +6530,10 @@
           <t>Fillo Elite</t>
         </is>
       </c>
-      <c r="V7" s="33" t="n">
+      <c r="V7" s="54" t="n">
         <v>2.5</v>
       </c>
-      <c r="W7" s="34" t="n">
+      <c r="W7" s="55" t="n">
         <v>59.95</v>
       </c>
       <c r="X7" s="11" t="inlineStr">
@@ -6550,10 +6581,10 @@
           <t>Polycryo window-shrink-film sheet</t>
         </is>
       </c>
-      <c r="D8" s="33" t="n">
+      <c r="D8" s="54" t="n">
         <v>2</v>
       </c>
-      <c r="E8" s="34" t="n">
+      <c r="E8" s="55" t="n">
         <v>13</v>
       </c>
       <c r="F8" s="11" t="inlineStr">
@@ -6589,10 +6620,10 @@
           <t>Tyvek HomeWrap sheet</t>
         </is>
       </c>
-      <c r="M8" s="33" t="n">
+      <c r="M8" s="54" t="n">
         <v>5</v>
       </c>
-      <c r="N8" s="34" t="n">
+      <c r="N8" s="55" t="n">
         <v>22</v>
       </c>
       <c r="O8" s="11" t="inlineStr">
@@ -6628,10 +6659,10 @@
           <t>Matching branded tent footprint (polycro or DCF)</t>
         </is>
       </c>
-      <c r="V8" s="33" t="n">
+      <c r="V8" s="54" t="n">
         <v>3.5</v>
       </c>
-      <c r="W8" s="34" t="n">
+      <c r="W8" s="55" t="n">
         <v>59</v>
       </c>
       <c r="X8" s="11" t="inlineStr">
@@ -6679,10 +6710,10 @@
           <t>Ziploc freezer bags + a cheap nylon stuff sack (or reused packaging bags)</t>
         </is>
       </c>
-      <c r="D9" s="33" t="n">
+      <c r="D9" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="34" t="n">
+      <c r="E9" s="55" t="n">
         <v>12</v>
       </c>
       <c r="F9" s="11" t="inlineStr">
@@ -6718,10 +6749,10 @@
           <t>Ultra-Sil Dry Bag - Set of 3</t>
         </is>
       </c>
-      <c r="M9" s="33" t="n">
+      <c r="M9" s="54" t="n">
         <v>2.5</v>
       </c>
-      <c r="N9" s="34" t="n">
+      <c r="N9" s="55" t="n">
         <v>69.95</v>
       </c>
       <c r="O9" s="11" t="inlineStr">
@@ -6757,10 +6788,10 @@
           <t>DCF Stuff Sack (assorted sizes)</t>
         </is>
       </c>
-      <c r="V9" s="33" t="n">
+      <c r="V9" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="W9" s="34" t="n">
+      <c r="W9" s="55" t="n">
         <v>31</v>
       </c>
       <c r="X9" s="11" t="inlineStr">
@@ -6808,10 +6839,10 @@
           <t>Compactor/contractor trash bag (heavy-duty, unscented)</t>
         </is>
       </c>
-      <c r="D10" s="33" t="n">
+      <c r="D10" s="54" t="n">
         <v>1.4</v>
       </c>
-      <c r="E10" s="34" t="n">
+      <c r="E10" s="55" t="n">
         <v>10</v>
       </c>
       <c r="F10" s="11" t="inlineStr">
@@ -6847,10 +6878,10 @@
           <t>Nylofume Pack Liner Bag</t>
         </is>
       </c>
-      <c r="M10" s="33" t="n">
+      <c r="M10" s="54" t="n">
         <v>0.9</v>
       </c>
-      <c r="N10" s="34" t="n">
+      <c r="N10" s="55" t="n">
         <v>2.49</v>
       </c>
       <c r="O10" s="11" t="inlineStr">
@@ -6886,10 +6917,10 @@
           <t>Evac Lightweight Dry Bag (35L)</t>
         </is>
       </c>
-      <c r="V10" s="33" t="n">
+      <c r="V10" s="54" t="n">
         <v>3.5</v>
       </c>
-      <c r="W10" s="34" t="n">
+      <c r="W10" s="55" t="n">
         <v>44.95</v>
       </c>
       <c r="X10" s="11" t="inlineStr">
@@ -6937,10 +6968,10 @@
           <t>Amicus Stove Cookset Combo</t>
         </is>
       </c>
-      <c r="D11" s="33" t="n">
+      <c r="D11" s="54" t="n">
         <v>11.2</v>
       </c>
-      <c r="E11" s="34" t="n">
+      <c r="E11" s="55" t="n">
         <v>49.95</v>
       </c>
       <c r="F11" s="11" t="inlineStr">
@@ -6976,10 +7007,10 @@
           <t>WindMaster (4Flex)</t>
         </is>
       </c>
-      <c r="M11" s="33" t="n">
+      <c r="M11" s="54" t="n">
         <v>3.5</v>
       </c>
-      <c r="N11" s="34" t="n">
+      <c r="N11" s="55" t="n">
         <v>69.95</v>
       </c>
       <c r="O11" s="11" t="inlineStr">
@@ -7015,10 +7046,10 @@
           <t>Stash</t>
         </is>
       </c>
-      <c r="V11" s="33" t="n">
+      <c r="V11" s="54" t="n">
         <v>7.1</v>
       </c>
-      <c r="W11" s="34" t="n">
+      <c r="W11" s="55" t="n">
         <v>131</v>
       </c>
       <c r="X11" s="11" t="inlineStr">
@@ -7066,10 +7097,10 @@
           <t>A004-025001 Aluminum Sauce Pan, 1-Quart</t>
         </is>
       </c>
-      <c r="D12" s="33" t="n">
+      <c r="D12" s="54" t="n">
         <v>6</v>
       </c>
-      <c r="E12" s="34" t="n">
+      <c r="E12" s="55" t="n">
         <v>12.99</v>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -7105,10 +7136,10 @@
           <t>750ml Titanium Pot with Bail Handle (POT-750-BH)</t>
         </is>
       </c>
-      <c r="M12" s="33" t="n">
+      <c r="M12" s="54" t="n">
         <v>4.1</v>
       </c>
-      <c r="N12" s="34" t="n">
+      <c r="N12" s="55" t="n">
         <v>30</v>
       </c>
       <c r="O12" s="11" t="inlineStr">
@@ -7144,10 +7175,10 @@
           <t>Trek 900 Titanium Cookset</t>
         </is>
       </c>
-      <c r="V12" s="33" t="n">
+      <c r="V12" s="54" t="n">
         <v>6</v>
       </c>
-      <c r="W12" s="34" t="n">
+      <c r="W12" s="55" t="n">
         <v>54.95</v>
       </c>
       <c r="X12" s="11" t="inlineStr">
@@ -7195,10 +7226,10 @@
           <t>Butane/Propane Mix Fuel, 7.75oz (220g)</t>
         </is>
       </c>
-      <c r="D13" s="33" t="n">
+      <c r="D13" s="54" t="n">
         <v>7.75</v>
       </c>
-      <c r="E13" s="34" t="n">
+      <c r="E13" s="55" t="n">
         <v>5.97</v>
       </c>
       <c r="F13" s="11" t="inlineStr">
@@ -7234,10 +7265,10 @@
           <t>IsoPro 8oz/227g canister</t>
         </is>
       </c>
-      <c r="M13" s="33" t="n">
+      <c r="M13" s="54" t="n">
         <v>13.7</v>
       </c>
-      <c r="N13" s="34" t="n">
+      <c r="N13" s="55" t="n">
         <v>6.95</v>
       </c>
       <c r="O13" s="11" t="inlineStr">
@@ -7273,10 +7304,10 @@
           <t>IsoPro (same blend, cold-weather use case)</t>
         </is>
       </c>
-      <c r="V13" s="33" t="n">
+      <c r="V13" s="54" t="n">
         <v>7.6</v>
       </c>
-      <c r="W13" s="34" t="n">
+      <c r="W13" s="55" t="n">
         <v>5.95</v>
       </c>
       <c r="X13" s="11" t="inlineStr">
@@ -7324,10 +7355,10 @@
           <t>Titanium Spork</t>
         </is>
       </c>
-      <c r="D14" s="33" t="n">
+      <c r="D14" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="E14" s="34" t="n">
+      <c r="E14" s="55" t="n">
         <v>9.949999999999999</v>
       </c>
       <c r="F14" s="11" t="inlineStr">
@@ -7363,10 +7394,10 @@
           <t>Frontier Ultralight Spoon - Long Handle</t>
         </is>
       </c>
-      <c r="M14" s="33" t="n">
+      <c r="M14" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="N14" s="34" t="n">
+      <c r="N14" s="55" t="n">
         <v>10.95</v>
       </c>
       <c r="O14" s="11" t="inlineStr">
@@ -7402,10 +7433,10 @@
           <t>Titanium Spork</t>
         </is>
       </c>
-      <c r="V14" s="33" t="n">
+      <c r="V14" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="W14" s="34" t="n">
+      <c r="W14" s="55" t="n">
         <v>9.949999999999999</v>
       </c>
       <c r="X14" s="11" t="inlineStr">
@@ -7453,10 +7484,10 @@
           <t>Squeeze (SP2129)</t>
         </is>
       </c>
-      <c r="D15" s="33" t="n">
+      <c r="D15" s="54" t="n">
         <v>3</v>
       </c>
-      <c r="E15" s="34" t="n">
+      <c r="E15" s="55" t="n">
         <v>45.95</v>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -7492,10 +7523,10 @@
           <t>BeFree 1.0L</t>
         </is>
       </c>
-      <c r="M15" s="33" t="n">
+      <c r="M15" s="54" t="n">
         <v>2.3</v>
       </c>
-      <c r="N15" s="34" t="n">
+      <c r="N15" s="55" t="n">
         <v>52.95</v>
       </c>
       <c r="O15" s="11" t="inlineStr">
@@ -7531,10 +7562,10 @@
           <t>GeoPress</t>
         </is>
       </c>
-      <c r="V15" s="33" t="n">
+      <c r="V15" s="54" t="n">
         <v>15.9</v>
       </c>
-      <c r="W15" s="34" t="n">
+      <c r="W15" s="55" t="n">
         <v>99.95</v>
       </c>
       <c r="X15" s="11" t="inlineStr">
@@ -7582,10 +7613,10 @@
           <t>1L reused disposable bottle</t>
         </is>
       </c>
-      <c r="D16" s="33" t="n">
+      <c r="D16" s="54" t="n">
         <v>1.6</v>
       </c>
-      <c r="E16" s="34" t="n">
+      <c r="E16" s="55" t="n">
         <v>2.17</v>
       </c>
       <c r="F16" s="11" t="inlineStr">
@@ -7621,10 +7652,10 @@
           <t>Stow 1L collapsible bottle</t>
         </is>
       </c>
-      <c r="M16" s="33" t="n">
+      <c r="M16" s="54" t="n">
         <v>1.4</v>
       </c>
-      <c r="N16" s="34" t="n">
+      <c r="N16" s="55" t="n">
         <v>18</v>
       </c>
       <c r="O16" s="11" t="inlineStr">
@@ -7660,10 +7691,10 @@
           <t>Vecto 2L</t>
         </is>
       </c>
-      <c r="V16" s="33" t="n">
+      <c r="V16" s="54" t="n">
         <v>3.6</v>
       </c>
-      <c r="W16" s="34" t="n">
+      <c r="W16" s="55" t="n">
         <v>25</v>
       </c>
       <c r="X16" s="11" t="inlineStr">
@@ -7711,10 +7742,10 @@
           <t>Easy to Throw Bear Bag Hanging Kit (#371486)</t>
         </is>
       </c>
-      <c r="D17" s="33" t="n">
+      <c r="D17" s="54" t="n">
         <v>6</v>
       </c>
-      <c r="E17" s="34" t="n">
+      <c r="E17" s="55" t="n">
         <v>27</v>
       </c>
       <c r="F17" s="11" t="inlineStr">
@@ -7750,10 +7781,10 @@
           <t>Major XL (with OPSak liner)</t>
         </is>
       </c>
-      <c r="M17" s="33" t="n">
+      <c r="M17" s="54" t="n">
         <v>10.8</v>
       </c>
-      <c r="N17" s="34" t="n">
+      <c r="N17" s="55" t="n">
         <v>149.95</v>
       </c>
       <c r="O17" s="11" t="inlineStr">
@@ -7789,10 +7820,10 @@
           <t>BV500</t>
         </is>
       </c>
-      <c r="V17" s="33" t="n">
+      <c r="V17" s="54" t="n">
         <v>41</v>
       </c>
-      <c r="W17" s="34" t="n">
+      <c r="W17" s="55" t="n">
         <v>99.95</v>
       </c>
       <c r="X17" s="11" t="inlineStr">
@@ -7840,10 +7871,10 @@
           <t>Tikkina</t>
         </is>
       </c>
-      <c r="D18" s="33" t="n">
+      <c r="D18" s="54" t="n">
         <v>2.9</v>
       </c>
-      <c r="E18" s="34" t="n">
+      <c r="E18" s="55" t="n">
         <v>19.95</v>
       </c>
       <c r="F18" s="11" t="inlineStr">
@@ -7879,10 +7910,10 @@
           <t>Spot 400</t>
         </is>
       </c>
-      <c r="M18" s="33" t="n">
+      <c r="M18" s="54" t="n">
         <v>3</v>
       </c>
-      <c r="N18" s="34" t="n">
+      <c r="N18" s="55" t="n">
         <v>59.95</v>
       </c>
       <c r="O18" s="11" t="inlineStr">
@@ -7918,10 +7949,10 @@
           <t>NU25 (rechargeable)</t>
         </is>
       </c>
-      <c r="V18" s="33" t="n">
+      <c r="V18" s="54" t="n">
         <v>1.75</v>
       </c>
-      <c r="W18" s="34" t="n">
+      <c r="W18" s="55" t="n">
         <v>54.95</v>
       </c>
       <c r="X18" s="11" t="inlineStr">
@@ -7969,10 +8000,10 @@
           <t>Power Bank, 10,000mAh Portable Charger (PowerIQ, USB-C)</t>
         </is>
       </c>
-      <c r="D19" s="33" t="n">
+      <c r="D19" s="54" t="n">
         <v>6.3</v>
       </c>
-      <c r="E19" s="34" t="n">
+      <c r="E19" s="55" t="n">
         <v>21.99</v>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -8008,10 +8039,10 @@
           <t>NB10000 Gen 3</t>
         </is>
       </c>
-      <c r="M19" s="33" t="n">
+      <c r="M19" s="54" t="n">
         <v>5.1</v>
       </c>
-      <c r="N19" s="34" t="n">
+      <c r="N19" s="55" t="n">
         <v>64.95</v>
       </c>
       <c r="O19" s="11" t="inlineStr">
@@ -8047,10 +8078,10 @@
           <t>NB10000 Gen 4</t>
         </is>
       </c>
-      <c r="V19" s="33" t="n">
+      <c r="V19" s="54" t="n">
         <v>5</v>
       </c>
-      <c r="W19" s="34" t="n">
+      <c r="W19" s="55" t="n">
         <v>83.95</v>
       </c>
       <c r="X19" s="11" t="inlineStr">
@@ -8098,10 +8129,10 @@
           <t>inReach Mini 2 (weekly rental)</t>
         </is>
       </c>
-      <c r="D20" s="33" t="n">
+      <c r="D20" s="54" t="n">
         <v>3.5</v>
       </c>
-      <c r="E20" s="34" t="n">
+      <c r="E20" s="55" t="n">
         <v>100</v>
       </c>
       <c r="F20" s="11" t="inlineStr">
@@ -8137,10 +8168,10 @@
           <t>Satellite Communicator</t>
         </is>
       </c>
-      <c r="M20" s="33" t="n">
+      <c r="M20" s="54" t="n">
         <v>5.4</v>
       </c>
-      <c r="N20" s="34" t="n">
+      <c r="N20" s="55" t="n">
         <v>199</v>
       </c>
       <c r="O20" s="11" t="inlineStr">
@@ -8176,10 +8207,10 @@
           <t>inReach Mini 2 (owned, Safety plan)</t>
         </is>
       </c>
-      <c r="V20" s="33" t="n">
+      <c r="V20" s="54" t="n">
         <v>3.5</v>
       </c>
-      <c r="W20" s="34" t="n">
+      <c r="W20" s="55" t="n">
         <v>349.99</v>
       </c>
       <c r="X20" s="11" t="inlineStr">
@@ -8227,10 +8258,10 @@
           <t>Free account + printed topo</t>
         </is>
       </c>
-      <c r="D21" s="33" t="n">
+      <c r="D21" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="34" t="n">
+      <c r="E21" s="55" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="11" t="inlineStr">
@@ -8266,10 +8297,10 @@
           <t>Premium subscription</t>
         </is>
       </c>
-      <c r="M21" s="33" t="n">
+      <c r="M21" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="N21" s="34" t="n">
+      <c r="N21" s="55" t="n">
         <v>39.99</v>
       </c>
       <c r="O21" s="11" t="inlineStr">
@@ -8305,10 +8336,10 @@
           <t>Regional trail guide (per-trail purchase)</t>
         </is>
       </c>
-      <c r="V21" s="33" t="n">
+      <c r="V21" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="W21" s="34" t="n">
+      <c r="W21" s="55" t="n">
         <v>14.99</v>
       </c>
       <c r="X21" s="11" t="inlineStr">
@@ -8356,10 +8387,10 @@
           <t>No.8 Carbon/Stainless folding knife</t>
         </is>
       </c>
-      <c r="D22" s="33" t="n">
+      <c r="D22" s="54" t="n">
         <v>1.6</v>
       </c>
-      <c r="E22" s="34" t="n">
+      <c r="E22" s="55" t="n">
         <v>22</v>
       </c>
       <c r="F22" s="11" t="inlineStr">
@@ -8395,10 +8426,10 @@
           <t>Wingman</t>
         </is>
       </c>
-      <c r="M22" s="33" t="n">
+      <c r="M22" s="54" t="n">
         <v>7.2</v>
       </c>
-      <c r="N22" s="34" t="n">
+      <c r="N22" s="55" t="n">
         <v>49.95</v>
       </c>
       <c r="O22" s="11" t="inlineStr">
@@ -8434,10 +8465,10 @@
           <t>Skeletool CX</t>
         </is>
       </c>
-      <c r="V22" s="33" t="n">
+      <c r="V22" s="54" t="n">
         <v>5</v>
       </c>
-      <c r="W22" s="34" t="n">
+      <c r="W22" s="55" t="n">
         <v>99.95</v>
       </c>
       <c r="X22" s="11" t="inlineStr">
@@ -8450,7 +8481,7 @@
       </c>
       <c r="Z22" s="11" t="inlineStr">
         <is>
-          <t>Great if the Captain wants one tool to keep long-term across future trips</t>
+          <t>Great if Jordan wants one tool to keep long-term across future trips</t>
         </is>
       </c>
       <c r="AA22" s="11" t="inlineStr">
@@ -8485,10 +8516,10 @@
           <t>Build-your-own kit (gauze, tape, meds, moleskin, blister care)</t>
         </is>
       </c>
-      <c r="D23" s="33" t="n">
+      <c r="D23" s="54" t="n">
         <v>4</v>
       </c>
-      <c r="E23" s="34" t="n">
+      <c r="E23" s="55" t="n">
         <v>22</v>
       </c>
       <c r="F23" s="11" t="inlineStr">
@@ -8524,10 +8555,10 @@
           <t>Ultralight/Watertight .7</t>
         </is>
       </c>
-      <c r="M23" s="33" t="n">
+      <c r="M23" s="54" t="n">
         <v>4.4</v>
       </c>
-      <c r="N23" s="34" t="n">
+      <c r="N23" s="55" t="n">
         <v>44.99</v>
       </c>
       <c r="O23" s="11" t="inlineStr">
@@ -8563,10 +8594,10 @@
           <t>Mountain Series Explorer</t>
         </is>
       </c>
-      <c r="V23" s="33" t="n">
+      <c r="V23" s="54" t="n">
         <v>16</v>
       </c>
-      <c r="W23" s="34" t="n">
+      <c r="W23" s="55" t="n">
         <v>86.48999999999999</v>
       </c>
       <c r="X23" s="11" t="inlineStr">
@@ -8614,10 +8645,10 @@
           <t>Backpackers Trowel</t>
         </is>
       </c>
-      <c r="D24" s="33" t="n">
+      <c r="D24" s="54" t="n">
         <v>1.5</v>
       </c>
-      <c r="E24" s="34" t="n">
+      <c r="E24" s="55" t="n">
         <v>8.75</v>
       </c>
       <c r="F24" s="11" t="inlineStr">
@@ -8653,10 +8684,10 @@
           <t>Cathole Trowel</t>
         </is>
       </c>
-      <c r="M24" s="33" t="n">
+      <c r="M24" s="54" t="n">
         <v>2.4</v>
       </c>
-      <c r="N24" s="34" t="n">
+      <c r="N24" s="55" t="n">
         <v>7.95</v>
       </c>
       <c r="O24" s="11" t="inlineStr">
@@ -8692,10 +8723,10 @@
           <t>The DirtSaw Deuce #2 Trowel</t>
         </is>
       </c>
-      <c r="V24" s="33" t="n">
+      <c r="V24" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="W24" s="34" t="n">
+      <c r="W24" s="55" t="n">
         <v>21.95</v>
       </c>
       <c r="X24" s="11" t="inlineStr">
@@ -8743,10 +8774,10 @@
           <t>Travel-size toothbrush, toothpaste, TP, hand sanitizer</t>
         </is>
       </c>
-      <c r="D25" s="33" t="n">
+      <c r="D25" s="54" t="n">
         <v>3.5</v>
       </c>
-      <c r="E25" s="34" t="n">
+      <c r="E25" s="55" t="n">
         <v>3.94</v>
       </c>
       <c r="F25" s="11" t="inlineStr">
@@ -8782,10 +8813,10 @@
           <t>Small toiletry bag + biodegradable wipes</t>
         </is>
       </c>
-      <c r="M25" s="33" t="n">
+      <c r="M25" s="54" t="n">
         <v>4</v>
       </c>
-      <c r="N25" s="34" t="n">
+      <c r="N25" s="55" t="n">
         <v>9</v>
       </c>
       <c r="O25" s="11" t="inlineStr">
@@ -8821,10 +8852,10 @@
           <t>Ultralight toiletry kit + pack towel wipes + sunscreen/lip balm travel set</t>
         </is>
       </c>
-      <c r="V25" s="33" t="n">
+      <c r="V25" s="54" t="n">
         <v>5</v>
       </c>
-      <c r="W25" s="34" t="n">
+      <c r="W25" s="55" t="n">
         <v>15</v>
       </c>
       <c r="X25" s="11" t="inlineStr">
@@ -8872,10 +8903,10 @@
           <t>Aluminum adjustable trekking poles (pair)</t>
         </is>
       </c>
-      <c r="D26" s="33" t="n">
+      <c r="D26" s="54" t="n">
         <v>18</v>
       </c>
-      <c r="E26" s="34" t="n">
+      <c r="E26" s="55" t="n">
         <v>49.99</v>
       </c>
       <c r="F26" s="11" t="inlineStr">
@@ -8911,10 +8942,10 @@
           <t>Carbon Fiber Quick Lock (pair)</t>
         </is>
       </c>
-      <c r="M26" s="33" t="n">
+      <c r="M26" s="54" t="n">
         <v>8.1</v>
       </c>
-      <c r="N26" s="34" t="n">
+      <c r="N26" s="55" t="n">
         <v>64.98999999999999</v>
       </c>
       <c r="O26" s="11" t="inlineStr">
@@ -8950,10 +8981,10 @@
           <t>Distance Carbon Z (pair)</t>
         </is>
       </c>
-      <c r="V26" s="33" t="n">
+      <c r="V26" s="54" t="n">
         <v>10.9</v>
       </c>
-      <c r="W26" s="34" t="n">
+      <c r="W26" s="55" t="n">
         <v>219.95</v>
       </c>
       <c r="X26" s="11" t="inlineStr">
@@ -9001,10 +9032,10 @@
           <t>Cut piece of leftover closed-cell foam pad</t>
         </is>
       </c>
-      <c r="D27" s="33" t="n">
+      <c r="D27" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="E27" s="34" t="n">
+      <c r="E27" s="55" t="n">
         <v>0</v>
       </c>
       <c r="F27" s="11" t="inlineStr">
@@ -9040,10 +9071,10 @@
           <t>Z Seat</t>
         </is>
       </c>
-      <c r="M27" s="33" t="n">
+      <c r="M27" s="54" t="n">
         <v>2</v>
       </c>
-      <c r="N27" s="34" t="n">
+      <c r="N27" s="55" t="n">
         <v>34.28</v>
       </c>
       <c r="O27" s="11" t="inlineStr">
@@ -9079,10 +9110,10 @@
           <t>1/8in Thinlight Foam Pad (full torso, multi-use)</t>
         </is>
       </c>
-      <c r="V27" s="33" t="n">
+      <c r="V27" s="54" t="n">
         <v>2.8</v>
       </c>
-      <c r="W27" s="34" t="n">
+      <c r="W27" s="55" t="n">
         <v>22.5</v>
       </c>
       <c r="X27" s="11" t="inlineStr">
@@ -9130,10 +9161,10 @@
           <t>Gabe Cloud Slide Sandals</t>
         </is>
       </c>
-      <c r="D28" s="33" t="n">
+      <c r="D28" s="54" t="n">
         <v>6</v>
       </c>
-      <c r="E28" s="34" t="n">
+      <c r="E28" s="55" t="n">
         <v>19.99</v>
       </c>
       <c r="F28" s="11" t="inlineStr">
@@ -9169,10 +9200,10 @@
           <t>Classic Clog</t>
         </is>
       </c>
-      <c r="M28" s="33" t="n">
+      <c r="M28" s="54" t="n">
         <v>12</v>
       </c>
-      <c r="N28" s="34" t="n">
+      <c r="N28" s="55" t="n">
         <v>49.99</v>
       </c>
       <c r="O28" s="11" t="inlineStr">
@@ -9208,10 +9239,10 @@
           <t>Z-Trail EV Sandals</t>
         </is>
       </c>
-      <c r="V28" s="33" t="n">
+      <c r="V28" s="54" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="W28" s="34" t="n">
+      <c r="W28" s="55" t="n">
         <v>80</v>
       </c>
       <c r="X28" s="11" t="inlineStr">
@@ -9259,10 +9290,10 @@
           <t>Any old/thrifted trail running shoe (mesh upper, non-waterproof)</t>
         </is>
       </c>
-      <c r="D29" s="33" t="n">
+      <c r="D29" s="54" t="n">
         <v>24</v>
       </c>
-      <c r="E29" s="34" t="n">
+      <c r="E29" s="55" t="n">
         <v>0</v>
       </c>
       <c r="F29" s="11" t="inlineStr">
@@ -9298,10 +9329,10 @@
           <t>Moab 3</t>
         </is>
       </c>
-      <c r="M29" s="33" t="n">
+      <c r="M29" s="54" t="n">
         <v>33</v>
       </c>
-      <c r="N29" s="34" t="n">
+      <c r="N29" s="55" t="n">
         <v>100.93</v>
       </c>
       <c r="O29" s="11" t="inlineStr">
@@ -9337,10 +9368,10 @@
           <t>Lone Peak 9</t>
         </is>
       </c>
-      <c r="V29" s="33" t="n">
+      <c r="V29" s="54" t="n">
         <v>22.5</v>
       </c>
-      <c r="W29" s="34" t="n">
+      <c r="W29" s="55" t="n">
         <v>145</v>
       </c>
       <c r="X29" s="11" t="inlineStr">
@@ -9388,10 +9419,10 @@
           <t>Merino Wool Lightweight Hiking Crew (3-pack budget alt)</t>
         </is>
       </c>
-      <c r="D30" s="33" t="n">
+      <c r="D30" s="54" t="n">
         <v>2.5</v>
       </c>
-      <c r="E30" s="34" t="n">
+      <c r="E30" s="55" t="n">
         <v>8.83</v>
       </c>
       <c r="F30" s="11" t="inlineStr">
@@ -9427,10 +9458,10 @@
           <t>Hiker Micro Crew Midweight with Cushion</t>
         </is>
       </c>
-      <c r="M30" s="33" t="n">
+      <c r="M30" s="54" t="n">
         <v>2.6</v>
       </c>
-      <c r="N30" s="34" t="n">
+      <c r="N30" s="55" t="n">
         <v>25.95</v>
       </c>
       <c r="O30" s="11" t="inlineStr">
@@ -9466,10 +9497,10 @@
           <t>Waterproof All Weather Mid Length Sock</t>
         </is>
       </c>
-      <c r="V30" s="33" t="n">
+      <c r="V30" s="54" t="n">
         <v>3.2</v>
       </c>
-      <c r="W30" s="34" t="n">
+      <c r="W30" s="55" t="n">
         <v>55</v>
       </c>
       <c r="X30" s="11" t="inlineStr">
@@ -9517,10 +9548,10 @@
           <t>Watertight II Rain Jacket (Men's)</t>
         </is>
       </c>
-      <c r="D31" s="33" t="n">
+      <c r="D31" s="54" t="n">
         <v>12</v>
       </c>
-      <c r="E31" s="34" t="n">
+      <c r="E31" s="55" t="n">
         <v>70</v>
       </c>
       <c r="F31" s="11" t="inlineStr">
@@ -9556,10 +9587,10 @@
           <t>Rainier Rain Jacket</t>
         </is>
       </c>
-      <c r="M31" s="33" t="n">
+      <c r="M31" s="54" t="n">
         <v>12.5</v>
       </c>
-      <c r="N31" s="34" t="n">
+      <c r="N31" s="55" t="n">
         <v>99.95</v>
       </c>
       <c r="O31" s="11" t="inlineStr">
@@ -9595,10 +9626,10 @@
           <t>Helium Rain Jacket</t>
         </is>
       </c>
-      <c r="V31" s="33" t="n">
+      <c r="V31" s="54" t="n">
         <v>6.4</v>
       </c>
-      <c r="W31" s="34" t="n">
+      <c r="W31" s="55" t="n">
         <v>199</v>
       </c>
       <c r="X31" s="11" t="inlineStr">
@@ -9646,10 +9677,10 @@
           <t>MT100 Hooded Down Puffer Jacket</t>
         </is>
       </c>
-      <c r="D32" s="33" t="n">
+      <c r="D32" s="54" t="n">
         <v>10.6</v>
       </c>
-      <c r="E32" s="34" t="n">
+      <c r="E32" s="55" t="n">
         <v>80</v>
       </c>
       <c r="F32" s="11" t="inlineStr">
@@ -9685,10 +9716,10 @@
           <t>Nano Puff Jacket</t>
         </is>
       </c>
-      <c r="M32" s="33" t="n">
+      <c r="M32" s="54" t="n">
         <v>11.6</v>
       </c>
-      <c r="N32" s="34" t="n">
+      <c r="N32" s="55" t="n">
         <v>118.99</v>
       </c>
       <c r="O32" s="11" t="inlineStr">
@@ -9724,10 +9755,10 @@
           <t>Torrid APEX Jacket</t>
         </is>
       </c>
-      <c r="V32" s="33" t="n">
+      <c r="V32" s="54" t="n">
         <v>8.9</v>
       </c>
-      <c r="W32" s="34" t="n">
+      <c r="W32" s="55" t="n">
         <v>170</v>
       </c>
       <c r="X32" s="11" t="inlineStr">
@@ -9775,10 +9806,10 @@
           <t>MH100 Fleece</t>
         </is>
       </c>
-      <c r="D33" s="33" t="n">
+      <c r="D33" s="54" t="n">
         <v>12</v>
       </c>
-      <c r="E33" s="34" t="n">
+      <c r="E33" s="55" t="n">
         <v>25</v>
       </c>
       <c r="F33" s="11" t="inlineStr">
@@ -9814,10 +9845,10 @@
           <t>Alpha 90 Half-Zip Hoodie</t>
         </is>
       </c>
-      <c r="M33" s="33" t="n">
+      <c r="M33" s="54" t="n">
         <v>4.8</v>
       </c>
-      <c r="N33" s="34" t="n">
+      <c r="N33" s="55" t="n">
         <v>115</v>
       </c>
       <c r="O33" s="11" t="inlineStr">
@@ -9853,10 +9884,10 @@
           <t>R1 Air Hoody</t>
         </is>
       </c>
-      <c r="V33" s="33" t="n">
+      <c r="V33" s="54" t="n">
         <v>10.5</v>
       </c>
-      <c r="W33" s="34" t="n">
+      <c r="W33" s="55" t="n">
         <v>179</v>
       </c>
       <c r="X33" s="11" t="inlineStr">
@@ -9904,10 +9935,10 @@
           <t>Men's/Women's Long Sleeve Base Layer Set</t>
         </is>
       </c>
-      <c r="D34" s="33" t="n">
+      <c r="D34" s="54" t="n">
         <v>8</v>
       </c>
-      <c r="E34" s="34" t="n">
+      <c r="E34" s="55" t="n">
         <v>100</v>
       </c>
       <c r="F34" s="11" t="inlineStr">
@@ -9943,10 +9974,10 @@
           <t>Classic Thermal Merino Base Layer (top + bottom)</t>
         </is>
       </c>
-      <c r="M34" s="33" t="n">
+      <c r="M34" s="54" t="n">
         <v>10</v>
       </c>
-      <c r="N34" s="34" t="n">
+      <c r="N34" s="55" t="n">
         <v>125</v>
       </c>
       <c r="O34" s="11" t="inlineStr">
@@ -9982,10 +10013,10 @@
           <t>200 Oasis (top + bottom)</t>
         </is>
       </c>
-      <c r="V34" s="33" t="n">
+      <c r="V34" s="54" t="n">
         <v>11</v>
       </c>
-      <c r="W34" s="34" t="n">
+      <c r="W34" s="55" t="n">
         <v>235</v>
       </c>
       <c r="X34" s="11" t="inlineStr">
@@ -10033,10 +10064,10 @@
           <t>Trailmade Pants</t>
         </is>
       </c>
-      <c r="D35" s="33" t="n">
+      <c r="D35" s="54" t="n">
         <v>11</v>
       </c>
-      <c r="E35" s="34" t="n">
+      <c r="E35" s="55" t="n">
         <v>80</v>
       </c>
       <c r="F35" s="11" t="inlineStr">
@@ -10072,10 +10103,10 @@
           <t>Ferrosi Pants</t>
         </is>
       </c>
-      <c r="M35" s="33" t="n">
+      <c r="M35" s="54" t="n">
         <v>11.4</v>
       </c>
-      <c r="N35" s="34" t="n">
+      <c r="N35" s="55" t="n">
         <v>110</v>
       </c>
       <c r="O35" s="11" t="inlineStr">
@@ -10111,10 +10142,10 @@
           <t>Stretch Zion Straight Pants (cargo version discontinued, replaced by current lineup)</t>
         </is>
       </c>
-      <c r="V35" s="33" t="n">
+      <c r="V35" s="54" t="n">
         <v>14</v>
       </c>
-      <c r="W35" s="34" t="n">
+      <c r="W35" s="55" t="n">
         <v>98</v>
       </c>
       <c r="X35" s="11" t="inlineStr">
@@ -10162,10 +10193,10 @@
           <t>Fleece-lined knit beanie</t>
         </is>
       </c>
-      <c r="D36" s="33" t="n">
+      <c r="D36" s="54" t="n">
         <v>2</v>
       </c>
-      <c r="E36" s="34" t="n">
+      <c r="E36" s="55" t="n">
         <v>14.99</v>
       </c>
       <c r="F36" s="11" t="inlineStr">
@@ -10201,10 +10232,10 @@
           <t>Alpha Drifter Beanie</t>
         </is>
       </c>
-      <c r="M36" s="33" t="n">
+      <c r="M36" s="54" t="n">
         <v>0.7</v>
       </c>
-      <c r="N36" s="34" t="n">
+      <c r="N36" s="55" t="n">
         <v>38</v>
       </c>
       <c r="O36" s="11" t="inlineStr">
@@ -10240,10 +10271,10 @@
           <t>Merino 250 Reversible Cuffed Beanie</t>
         </is>
       </c>
-      <c r="V36" s="33" t="n">
+      <c r="V36" s="54" t="n">
         <v>2.1</v>
       </c>
-      <c r="W36" s="34" t="n">
+      <c r="W36" s="55" t="n">
         <v>35</v>
       </c>
       <c r="X36" s="11" t="inlineStr">
@@ -10291,10 +10322,10 @@
           <t>Wool Fleece-Liner Knit Gloves (3-pack)</t>
         </is>
       </c>
-      <c r="D37" s="33" t="n">
+      <c r="D37" s="54" t="n">
         <v>2</v>
       </c>
-      <c r="E37" s="34" t="n">
+      <c r="E37" s="55" t="n">
         <v>12.99</v>
       </c>
       <c r="F37" s="11" t="inlineStr">
@@ -10330,10 +10361,10 @@
           <t>PL 400 Gloves</t>
         </is>
       </c>
-      <c r="M37" s="33" t="n">
+      <c r="M37" s="54" t="n">
         <v>2.3</v>
       </c>
-      <c r="N37" s="34" t="n">
+      <c r="N37" s="55" t="n">
         <v>35</v>
       </c>
       <c r="O37" s="11" t="inlineStr">
@@ -10369,10 +10400,10 @@
           <t>Merino/Possum Blend Gloves (touchscreen)</t>
         </is>
       </c>
-      <c r="V37" s="33" t="n">
+      <c r="V37" s="54" t="n">
         <v>1.5</v>
       </c>
-      <c r="W37" s="34" t="n">
+      <c r="W37" s="55" t="n">
         <v>40</v>
       </c>
       <c r="X37" s="11" t="inlineStr">
@@ -10420,10 +10451,10 @@
           <t>Mesh Safety Vest + Blaze Orange Insulated Beanie</t>
         </is>
       </c>
-      <c r="D38" s="33" t="n">
+      <c r="D38" s="54" t="n">
         <v>6</v>
       </c>
-      <c r="E38" s="34" t="n">
+      <c r="E38" s="55" t="n">
         <v>16.96</v>
       </c>
       <c r="F38" s="11" t="inlineStr">
@@ -10459,10 +10490,10 @@
           <t>Blaze Orange Safety Vest</t>
         </is>
       </c>
-      <c r="M38" s="33" t="n">
+      <c r="M38" s="54" t="n">
         <v>5</v>
       </c>
-      <c r="N38" s="34" t="n">
+      <c r="N38" s="55" t="n">
         <v>13.51</v>
       </c>
       <c r="O38" s="11" t="inlineStr">
@@ -10498,10 +10529,10 @@
           <t>Blaze Orange Hunting Vest &amp; Hat Combo</t>
         </is>
       </c>
-      <c r="V38" s="33" t="n">
+      <c r="V38" s="54" t="n">
         <v>10</v>
       </c>
-      <c r="W38" s="34" t="n">
+      <c r="W38" s="55" t="n">
         <v>45</v>
       </c>
       <c r="X38" s="11" t="inlineStr">
@@ -10549,10 +10580,10 @@
           <t>Old sneakers or flip-flops already owned</t>
         </is>
       </c>
-      <c r="D39" s="33" t="n">
+      <c r="D39" s="54" t="n">
         <v>10</v>
       </c>
-      <c r="E39" s="34" t="n">
+      <c r="E39" s="55" t="n">
         <v>0</v>
       </c>
       <c r="F39" s="11" t="inlineStr">
@@ -10588,10 +10619,10 @@
           <t>Classic Clog</t>
         </is>
       </c>
-      <c r="M39" s="33" t="n">
+      <c r="M39" s="54" t="n">
         <v>14</v>
       </c>
-      <c r="N39" s="34" t="n">
+      <c r="N39" s="55" t="n">
         <v>50</v>
       </c>
       <c r="O39" s="11" t="inlineStr">
@@ -10627,10 +10658,10 @@
           <t>Cairn Evo Adventure Sandals (current lineup; original Cairn Adventure Sandal discontinued)</t>
         </is>
       </c>
-      <c r="V39" s="33" t="n">
+      <c r="V39" s="54" t="n">
         <v>11</v>
       </c>
-      <c r="W39" s="34" t="n">
+      <c r="W39" s="55" t="n">
         <v>115</v>
       </c>
       <c r="X39" s="11" t="inlineStr">
@@ -10678,10 +10709,10 @@
           <t>Kenai Original</t>
         </is>
       </c>
-      <c r="D40" s="33" t="n">
+      <c r="D40" s="54" t="n">
         <v>4</v>
       </c>
-      <c r="E40" s="34" t="n">
+      <c r="E40" s="55" t="n">
         <v>24.99</v>
       </c>
       <c r="F40" s="11" t="inlineStr">
@@ -10699,7 +10730,7 @@
       </c>
       <c r="I40" s="11" t="inlineStr">
         <is>
-          <t>Captain's pick 2026-09-23: 35-year standard for cold fly-fishing, 2mm fleece-lined neoprene with a sharkskin palm -- chose dexterity (feel the pan, pick gravel) over staying bone-dry.</t>
+          <t>Jordan's pick 2026-09-23: 35-year standard for cold fly-fishing, 2mm fleece-lined neoprene with a sharkskin palm -- chose dexterity (feel the pan, pick gravel) over staying bone-dry.</t>
         </is>
       </c>
       <c r="J40" s="11" t="inlineStr">
@@ -10717,10 +10748,10 @@
           <t>Kenai Original</t>
         </is>
       </c>
-      <c r="M40" s="33" t="n">
+      <c r="M40" s="54" t="n">
         <v>4</v>
       </c>
-      <c r="N40" s="34" t="n">
+      <c r="N40" s="55" t="n">
         <v>24.99</v>
       </c>
       <c r="O40" s="11" t="inlineStr">
@@ -10738,7 +10769,7 @@
       </c>
       <c r="R40" s="11" t="inlineStr">
         <is>
-          <t>Captain's pick 2026-09-23: 35-year standard for cold fly-fishing, 2mm fleece-lined neoprene with a sharkskin palm -- chose dexterity (feel the pan, pick gravel) over staying bone-dry.</t>
+          <t>Jordan's pick 2026-09-23: 35-year standard for cold fly-fishing, 2mm fleece-lined neoprene with a sharkskin palm -- chose dexterity (feel the pan, pick gravel) over staying bone-dry.</t>
         </is>
       </c>
       <c r="S40" s="11" t="inlineStr">
@@ -10756,10 +10787,10 @@
           <t>Arctic Gauntlet Gloves for Cold Water Wading</t>
         </is>
       </c>
-      <c r="V40" s="33" t="n">
+      <c r="V40" s="54" t="n">
         <v>9</v>
       </c>
-      <c r="W40" s="34" t="n">
+      <c r="W40" s="55" t="n">
         <v>50</v>
       </c>
       <c r="X40" s="11" t="inlineStr">
@@ -10807,10 +10838,10 @@
           <t>3mm Knee-High Neoprene Sock</t>
         </is>
       </c>
-      <c r="D41" s="33" t="n">
+      <c r="D41" s="54" t="n">
         <v>6</v>
       </c>
-      <c r="E41" s="34" t="n">
+      <c r="E41" s="55" t="n">
         <v>41.59</v>
       </c>
       <c r="F41" s="11" t="inlineStr">
@@ -10846,10 +10877,10 @@
           <t>3mm Neoprene Wading/Water Socks</t>
         </is>
       </c>
-      <c r="M41" s="33" t="n">
+      <c r="M41" s="54" t="n">
         <v>6.5</v>
       </c>
-      <c r="N41" s="34" t="n">
+      <c r="N41" s="55" t="n">
         <v>30.19</v>
       </c>
       <c r="O41" s="11" t="inlineStr">
@@ -10885,10 +10916,10 @@
           <t>I-Drain Neoprene Guard Socks, 3.5mm</t>
         </is>
       </c>
-      <c r="V41" s="33" t="n">
+      <c r="V41" s="54" t="n">
         <v>7</v>
       </c>
-      <c r="W41" s="34" t="n">
+      <c r="W41" s="55" t="n">
         <v>44.99</v>
       </c>
       <c r="X41" s="11" t="inlineStr">
@@ -10936,10 +10967,10 @@
           <t>No waders — neoprene socks + quick-dry pants only</t>
         </is>
       </c>
-      <c r="D42" s="33" t="n">
+      <c r="D42" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="E42" s="34" t="n">
+      <c r="E42" s="55" t="n">
         <v>0</v>
       </c>
       <c r="F42" s="11" t="inlineStr">
@@ -10975,10 +11006,10 @@
           <t>Canyon II Stockingfoot Hip Wader, Medium (needs separate wading shoe)</t>
         </is>
       </c>
-      <c r="M42" s="33" t="n">
+      <c r="M42" s="54" t="n">
         <v>20</v>
       </c>
-      <c r="N42" s="34" t="n">
+      <c r="N42" s="55" t="n">
         <v>98.29000000000001</v>
       </c>
       <c r="O42" s="11" t="inlineStr">
@@ -11014,10 +11045,10 @@
           <t>Tributary Stockingfoot Waders</t>
         </is>
       </c>
-      <c r="V42" s="33" t="n">
+      <c r="V42" s="54" t="n">
         <v>38</v>
       </c>
-      <c r="W42" s="34" t="n">
+      <c r="W42" s="55" t="n">
         <v>300</v>
       </c>
       <c r="X42" s="11" t="inlineStr">
@@ -11065,10 +11096,10 @@
           <t>Protective Knee Pads, Thick Sponge Anti-Slip Knee Sleeve</t>
         </is>
       </c>
-      <c r="D43" s="33" t="n">
+      <c r="D43" s="54" t="n">
         <v>6</v>
       </c>
-      <c r="E43" s="34" t="n">
+      <c r="E43" s="55" t="n">
         <v>15.99</v>
       </c>
       <c r="F43" s="11" t="inlineStr">
@@ -11086,7 +11117,7 @@
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>Captain's pick 2026-09-23, replacing the flat foam gardening pad research flagged as not moving with you on uneven creek rock -- a strap-on sleeve that stays on through repeated kneel/reposition.</t>
+          <t>Jordan's pick 2026-09-23, replacing the flat foam gardening pad research flagged as not moving with you on uneven creek rock -- a strap-on sleeve that stays on through repeated kneel/reposition.</t>
         </is>
       </c>
       <c r="J43" s="11" t="inlineStr">
@@ -11104,10 +11135,10 @@
           <t>Neoprene Strap-On Knee Pads (gardening/volleyball style)</t>
         </is>
       </c>
-      <c r="M43" s="33" t="n">
+      <c r="M43" s="54" t="n">
         <v>8</v>
       </c>
-      <c r="N43" s="34" t="n">
+      <c r="N43" s="55" t="n">
         <v>16</v>
       </c>
       <c r="O43" s="11" t="inlineStr">
@@ -11143,10 +11174,10 @@
           <t>Gel-Cushion Kneeling Pad with adjustable straps</t>
         </is>
       </c>
-      <c r="V43" s="33" t="n">
+      <c r="V43" s="54" t="n">
         <v>14</v>
       </c>
-      <c r="W43" s="34" t="n">
+      <c r="W43" s="55" t="n">
         <v>28</v>
       </c>
       <c r="X43" s="11" t="inlineStr">
@@ -11194,10 +11225,10 @@
           <t>BP-14 14" Black Plastic Gold Pan</t>
         </is>
       </c>
-      <c r="D44" s="33" t="n">
+      <c r="D44" s="54" t="n">
         <v>9</v>
       </c>
-      <c r="E44" s="34" t="n">
+      <c r="E44" s="55" t="n">
         <v>7.26</v>
       </c>
       <c r="F44" s="11" t="inlineStr">
@@ -11233,10 +11264,10 @@
           <t>14" Gravity Trap Gold Pan (green)</t>
         </is>
       </c>
-      <c r="M44" s="33" t="n">
+      <c r="M44" s="54" t="n">
         <v>10</v>
       </c>
-      <c r="N44" s="34" t="n">
+      <c r="N44" s="55" t="n">
         <v>8.99</v>
       </c>
       <c r="O44" s="11" t="inlineStr">
@@ -11272,10 +11303,10 @@
           <t>15" Super Sluice Gold Pan (two-stage riffle pan)</t>
         </is>
       </c>
-      <c r="V44" s="33" t="n">
+      <c r="V44" s="54" t="n">
         <v>13</v>
       </c>
-      <c r="W44" s="34" t="n">
+      <c r="W44" s="55" t="n">
         <v>25</v>
       </c>
       <c r="X44" s="11" t="inlineStr">
@@ -11323,10 +11354,10 @@
           <t>1/2" Mesh Classifier</t>
         </is>
       </c>
-      <c r="D45" s="33" t="n">
+      <c r="D45" s="54" t="n">
         <v>16</v>
       </c>
-      <c r="E45" s="34" t="n">
+      <c r="E45" s="55" t="n">
         <v>25</v>
       </c>
       <c r="F45" s="11" t="inlineStr">
@@ -11362,10 +11393,10 @@
           <t>Stackable Classifier Set (1/2", 1/4", 1/8")</t>
         </is>
       </c>
-      <c r="M45" s="33" t="n">
+      <c r="M45" s="54" t="n">
         <v>30</v>
       </c>
-      <c r="N45" s="34" t="n">
+      <c r="N45" s="55" t="n">
         <v>75</v>
       </c>
       <c r="O45" s="11" t="inlineStr">
@@ -11401,10 +11432,10 @@
           <t>Stainless Mesh Classifier Set incl. 50-mesh fine screen</t>
         </is>
       </c>
-      <c r="V45" s="33" t="n">
+      <c r="V45" s="54" t="n">
         <v>34</v>
       </c>
-      <c r="W45" s="34" t="n">
+      <c r="W45" s="55" t="n">
         <v>65</v>
       </c>
       <c r="X45" s="11" t="inlineStr">
@@ -11452,10 +11483,10 @@
           <t>Plastic Snuffer Bottle</t>
         </is>
       </c>
-      <c r="D46" s="33" t="n">
+      <c r="D46" s="54" t="n">
         <v>1.5</v>
       </c>
-      <c r="E46" s="34" t="n">
+      <c r="E46" s="55" t="n">
         <v>4</v>
       </c>
       <c r="F46" s="11" t="inlineStr">
@@ -11491,10 +11522,10 @@
           <t>2-Pack Glass-Tip Snuffer Bottle with Tweezers</t>
         </is>
       </c>
-      <c r="M46" s="33" t="n">
+      <c r="M46" s="54" t="n">
         <v>2</v>
       </c>
-      <c r="N46" s="34" t="n">
+      <c r="N46" s="55" t="n">
         <v>11.99</v>
       </c>
       <c r="O46" s="11" t="inlineStr">
@@ -11530,10 +11561,10 @@
           <t>Brass-Tip Snuffer Bottle Set</t>
         </is>
       </c>
-      <c r="V46" s="33" t="n">
+      <c r="V46" s="54" t="n">
         <v>2.5</v>
       </c>
-      <c r="W46" s="34" t="n">
+      <c r="W46" s="55" t="n">
         <v>13</v>
       </c>
       <c r="X46" s="11" t="inlineStr">
@@ -11581,10 +11612,10 @@
           <t>Hook and Pick Precision Crevice Tool Set, 6 Pieces</t>
         </is>
       </c>
-      <c r="D47" s="33" t="n">
+      <c r="D47" s="54" t="n">
         <v>4</v>
       </c>
-      <c r="E47" s="34" t="n">
+      <c r="E47" s="55" t="n">
         <v>17.25</v>
       </c>
       <c r="F47" s="11" t="inlineStr">
@@ -11620,10 +11651,10 @@
           <t>Stainless Steel Crevice Tool Set with Magnet</t>
         </is>
       </c>
-      <c r="M47" s="33" t="n">
+      <c r="M47" s="54" t="n">
         <v>6</v>
       </c>
-      <c r="N47" s="34" t="n">
+      <c r="N47" s="55" t="n">
         <v>59.95</v>
       </c>
       <c r="O47" s="11" t="inlineStr">
@@ -11659,10 +11690,10 @@
           <t>Branded Crevice Tool Kit</t>
         </is>
       </c>
-      <c r="V47" s="33" t="n">
+      <c r="V47" s="54" t="n">
         <v>8</v>
       </c>
-      <c r="W47" s="34" t="n">
+      <c r="W47" s="55" t="n">
         <v>25</v>
       </c>
       <c r="X47" s="11" t="inlineStr">
@@ -11710,10 +11741,10 @@
           <t>Plastic Snap-Cap Vials (5-pack)</t>
         </is>
       </c>
-      <c r="D48" s="33" t="n">
+      <c r="D48" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="E48" s="34" t="n">
+      <c r="E48" s="55" t="n">
         <v>5</v>
       </c>
       <c r="F48" s="11" t="inlineStr">
@@ -11749,10 +11780,10 @@
           <t>Glass Vials with Foam-Lined Screw Caps (12-pack)</t>
         </is>
       </c>
-      <c r="M48" s="33" t="n">
+      <c r="M48" s="54" t="n">
         <v>1.5</v>
       </c>
-      <c r="N48" s="34" t="n">
+      <c r="N48" s="55" t="n">
         <v>9.99</v>
       </c>
       <c r="O48" s="11" t="inlineStr">
@@ -11788,10 +11819,10 @@
           <t>Leak-Proof Glass Gold Vials with Measurement Markings</t>
         </is>
       </c>
-      <c r="V48" s="33" t="n">
+      <c r="V48" s="54" t="n">
         <v>2</v>
       </c>
-      <c r="W48" s="34" t="n">
+      <c r="W48" s="55" t="n">
         <v>4</v>
       </c>
       <c r="X48" s="11" t="inlineStr">
@@ -11839,10 +11870,10 @@
           <t>10x Plastic Keychain Loupe</t>
         </is>
       </c>
-      <c r="D49" s="33" t="n">
+      <c r="D49" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="E49" s="34" t="n">
+      <c r="E49" s="55" t="n">
         <v>7.99</v>
       </c>
       <c r="F49" s="11" t="inlineStr">
@@ -11878,10 +11909,10 @@
           <t>30x60 Jeweler's Loupe with Built-In LED Light</t>
         </is>
       </c>
-      <c r="M49" s="33" t="n">
+      <c r="M49" s="54" t="n">
         <v>2.5</v>
       </c>
-      <c r="N49" s="34" t="n">
+      <c r="N49" s="55" t="n">
         <v>8.98</v>
       </c>
       <c r="O49" s="11" t="inlineStr">
@@ -11917,10 +11948,10 @@
           <t>10x Triplet Achromatic Loupe</t>
         </is>
       </c>
-      <c r="V49" s="33" t="n">
+      <c r="V49" s="54" t="n">
         <v>2</v>
       </c>
-      <c r="W49" s="34" t="n">
+      <c r="W49" s="55" t="n">
         <v>20</v>
       </c>
       <c r="X49" s="11" t="inlineStr">
@@ -11968,10 +11999,10 @@
           <t>Folding Garden Trowel</t>
         </is>
       </c>
-      <c r="D50" s="33" t="n">
+      <c r="D50" s="54" t="n">
         <v>6</v>
       </c>
-      <c r="E50" s="34" t="n">
+      <c r="E50" s="55" t="n">
         <v>6.28</v>
       </c>
       <c r="F50" s="11" t="inlineStr">
@@ -12007,10 +12038,10 @@
           <t>The Deuce of Spades UL Trowel</t>
         </is>
       </c>
-      <c r="M50" s="33" t="n">
+      <c r="M50" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="N50" s="34" t="n">
+      <c r="N50" s="55" t="n">
         <v>20.95</v>
       </c>
       <c r="O50" s="11" t="inlineStr">
@@ -12046,10 +12077,10 @@
           <t>Full-Tang Stainless Prospecting Hand Shovel</t>
         </is>
       </c>
-      <c r="V50" s="33" t="n">
+      <c r="V50" s="54" t="n">
         <v>10</v>
       </c>
-      <c r="W50" s="34" t="n">
+      <c r="W50" s="55" t="n">
         <v>28</v>
       </c>
       <c r="X50" s="11" t="inlineStr">
@@ -12097,10 +12128,10 @@
           <t>Plain 5-Gallon Bucket</t>
         </is>
       </c>
-      <c r="D51" s="33" t="n">
+      <c r="D51" s="54" t="n">
         <v>32</v>
       </c>
-      <c r="E51" s="34" t="n">
+      <c r="E51" s="55" t="n">
         <v>5</v>
       </c>
       <c r="F51" s="11" t="inlineStr">
@@ -12136,10 +12167,10 @@
           <t>5-Gallon Bucket with Built-In Classifier Lid</t>
         </is>
       </c>
-      <c r="M51" s="33" t="n">
+      <c r="M51" s="54" t="n">
         <v>40</v>
       </c>
-      <c r="N51" s="34" t="n">
+      <c r="N51" s="55" t="n">
         <v>28</v>
       </c>
       <c r="O51" s="11" t="inlineStr">
@@ -12175,10 +12206,10 @@
           <t>Bucket Riffle/Classifier Combo Kit</t>
         </is>
       </c>
-      <c r="V51" s="33" t="n">
+      <c r="V51" s="54" t="n">
         <v>48</v>
       </c>
-      <c r="W51" s="34" t="n">
+      <c r="W51" s="55" t="n">
         <v>45</v>
       </c>
       <c r="X51" s="11" t="inlineStr">
@@ -12226,10 +12257,10 @@
           <t>Estwing BP-14 pan + ASR 1/2" classifier + plastic snuffer + 2 vials</t>
         </is>
       </c>
-      <c r="D52" s="33" t="n">
+      <c r="D52" s="54" t="n">
         <v>30</v>
       </c>
-      <c r="E52" s="34" t="n">
+      <c r="E52" s="55" t="n">
         <v>7.26</v>
       </c>
       <c r="F52" s="11" t="inlineStr">
@@ -12265,10 +12296,10 @@
           <t>Compact Prospecting Kit (pan, 2 classifiers, magnet, magnifier, 3 snuffers, 3 vials) minus sluice</t>
         </is>
       </c>
-      <c r="M52" s="33" t="n">
+      <c r="M52" s="54" t="n">
         <v>38</v>
       </c>
-      <c r="N52" s="34" t="n">
+      <c r="N52" s="55" t="n">
         <v>40</v>
       </c>
       <c r="O52" s="11" t="inlineStr">
@@ -12304,10 +12335,10 @@
           <t>Curated kit: Garrett 14" Gravity Trap pan + stainless classifier set + stainless crevice tools + brass snuffer, packed in a dedicated mesh stuff sack</t>
         </is>
       </c>
-      <c r="V52" s="33" t="n">
+      <c r="V52" s="54" t="n">
         <v>52</v>
       </c>
-      <c r="W52" s="34" t="n">
+      <c r="W52" s="55" t="n">
         <v>69.98999999999999</v>
       </c>
       <c r="X52" s="11" t="inlineStr">
@@ -12355,10 +12386,10 @@
           <t>Trestles 30</t>
         </is>
       </c>
-      <c r="D53" s="33" t="n">
+      <c r="D53" s="54" t="n">
         <v>52</v>
       </c>
-      <c r="E53" s="34" t="n">
+      <c r="E53" s="55" t="n">
         <v>99.95</v>
       </c>
       <c r="F53" s="11" t="inlineStr">
@@ -12394,10 +12425,10 @@
           <t>Revelation 30 (stock, 850fp)</t>
         </is>
       </c>
-      <c r="M53" s="33" t="n">
+      <c r="M53" s="54" t="n">
         <v>19.8</v>
       </c>
-      <c r="N53" s="34" t="n">
+      <c r="N53" s="55" t="n">
         <v>365</v>
       </c>
       <c r="O53" s="11" t="inlineStr">
@@ -12433,10 +12464,10 @@
           <t>Flex 30</t>
         </is>
       </c>
-      <c r="V53" s="33" t="n">
+      <c r="V53" s="54" t="n">
         <v>20.3</v>
       </c>
-      <c r="W53" s="34" t="n">
+      <c r="W53" s="55" t="n">
         <v>365</v>
       </c>
       <c r="X53" s="11" t="inlineStr">
@@ -12634,7 +12665,7 @@
           <t>Rook 65 (men's) / Renn 65 (women's)</t>
         </is>
       </c>
-      <c r="F2" s="39" t="n">
+      <c r="F2" s="56" t="n">
         <v>66</v>
       </c>
       <c r="G2" s="38" t="inlineStr">
@@ -12642,7 +12673,7 @@
           <t>~4 lb 2 oz (66 oz) per Osprey specs; heavier than UL packs but has a real suspended mesh back panel and All Mighty Guarantee warranty</t>
         </is>
       </c>
-      <c r="H2" s="40" t="n">
+      <c r="H2" s="57" t="n">
         <v>205</v>
       </c>
       <c r="I2" s="41" t="inlineStr">
@@ -12727,7 +12758,7 @@
           <t>Flash 55</t>
         </is>
       </c>
-      <c r="F3" s="39" t="n">
+      <c r="F3" s="56" t="n">
         <v>45</v>
       </c>
       <c r="G3" s="38" t="inlineStr">
@@ -12735,7 +12766,7 @@
           <t>2 lb 13 oz (45 oz) men's medium per REI/Switchback Travel specs</t>
         </is>
       </c>
-      <c r="H3" s="40" t="n">
+      <c r="H3" s="57" t="n">
         <v>229</v>
       </c>
       <c r="I3" s="41" t="inlineStr">
@@ -12820,7 +12851,7 @@
           <t>Mariposa 60</t>
         </is>
       </c>
-      <c r="F4" s="39" t="n">
+      <c r="F4" s="56" t="n">
         <v>34.2</v>
       </c>
       <c r="G4" s="38" t="inlineStr">
@@ -12828,7 +12859,7 @@
           <t>2 lb 2.2 oz (34.2 oz) medium, straight hipbelt, per Gossamer Gear specs</t>
         </is>
       </c>
-      <c r="H4" s="40" t="n">
+      <c r="H4" s="57" t="n">
         <v>315</v>
       </c>
       <c r="I4" s="41" t="inlineStr">
@@ -12913,7 +12944,7 @@
           <t>Late Start 1P Tent</t>
         </is>
       </c>
-      <c r="F5" s="39" t="n">
+      <c r="F5" s="56" t="n">
         <v>57</v>
       </c>
       <c r="G5" s="38" t="inlineStr">
@@ -12921,7 +12952,7 @@
           <t>3 lb 9 oz (57 oz) minimum trail weight per REI spec</t>
         </is>
       </c>
-      <c r="H5" s="40" t="n">
+      <c r="H5" s="57" t="n">
         <v>149.95</v>
       </c>
       <c r="I5" s="41" t="inlineStr">
@@ -13006,7 +13037,7 @@
           <t>Elixir 1 Tent with Footprint</t>
         </is>
       </c>
-      <c r="F6" s="39" t="n">
+      <c r="F6" s="56" t="n">
         <v>65</v>
       </c>
       <c r="G6" s="38" t="inlineStr">
@@ -13014,7 +13045,7 @@
           <t>4 lb 1 oz (65 oz) minimum trail weight per REI spec</t>
         </is>
       </c>
-      <c r="H6" s="40" t="n">
+      <c r="H6" s="57" t="n">
         <v>289.95</v>
       </c>
       <c r="I6" s="41" t="inlineStr">
@@ -13099,7 +13130,7 @@
           <t>Dragonfly OSMO 1P Ultralight Backpacking Tent</t>
         </is>
       </c>
-      <c r="F7" s="39" t="n">
+      <c r="F7" s="56" t="n">
         <v>34</v>
       </c>
       <c r="G7" s="38" t="inlineStr">
@@ -13107,7 +13138,7 @@
           <t>~2 lb 2 oz (34 oz) minimum trail weight per NEMO/REI spec</t>
         </is>
       </c>
-      <c r="H7" s="40" t="n">
+      <c r="H7" s="57" t="n">
         <v>499.95</v>
       </c>
       <c r="I7" s="41" t="inlineStr">
@@ -13192,7 +13223,7 @@
           <t>Trestles Elite Eco 20 (or Kelty Cosmic 20 Synthetic)</t>
         </is>
       </c>
-      <c r="F8" s="39" t="n">
+      <c r="F8" s="56" t="n">
         <v>53</v>
       </c>
       <c r="G8" s="38" t="inlineStr">
@@ -13200,7 +13231,7 @@
           <t>Trestles 15 synthetic ~3.3 lb (53 oz) regular; Kelty Cosmic Synthetic 20 runs similar (~2.9-3.5 lb depending on source)</t>
         </is>
       </c>
-      <c r="H8" s="40" t="n">
+      <c r="H8" s="57" t="n">
         <v>179</v>
       </c>
       <c r="I8" s="41" t="inlineStr">
@@ -13285,7 +13316,7 @@
           <t>Revelation 20 (stock, 850fp)</t>
         </is>
       </c>
-      <c r="F9" s="39" t="n">
+      <c r="F9" s="56" t="n">
         <v>26</v>
       </c>
       <c r="G9" s="38" t="inlineStr">
@@ -13293,7 +13324,7 @@
           <t>Stock Revelation 20F, Regular/Regular ~26 oz with 850fp down (950fp version is lighter, ~20.9 oz)</t>
         </is>
       </c>
-      <c r="H9" s="40" t="n">
+      <c r="H9" s="57" t="n">
         <v>280</v>
       </c>
       <c r="I9" s="41" t="inlineStr">
@@ -13378,7 +13409,7 @@
           <t>Alsek 22</t>
         </is>
       </c>
-      <c r="F10" s="39" t="n">
+      <c r="F10" s="56" t="n">
         <v>25.5</v>
       </c>
       <c r="G10" s="38" t="inlineStr">
@@ -13386,7 +13417,7 @@
           <t>25.5 oz stated, range 20.9-27 oz by size; one tested Regular weighed 1 lb 7.3 oz per GearJunkie</t>
         </is>
       </c>
-      <c r="H10" s="40" t="n">
+      <c r="H10" s="57" t="n">
         <v>399</v>
       </c>
       <c r="I10" s="41" t="inlineStr">
@@ -13471,7 +13502,7 @@
           <t>Insulated Static V</t>
         </is>
       </c>
-      <c r="F11" s="39" t="n">
+      <c r="F11" s="56" t="n">
         <v>25</v>
       </c>
       <c r="G11" s="38" t="inlineStr">
@@ -13479,7 +13510,7 @@
           <t>Insulated Static V lists ~25 oz per Klymit specs (Lite version 19.6 oz has lower R-value, check spec before buying — need the full Insulated, not the Lite/Base, to clear R4)</t>
         </is>
       </c>
-      <c r="H11" s="40" t="n">
+      <c r="H11" s="57" t="n">
         <v>74.20999999999999</v>
       </c>
       <c r="I11" s="41" t="inlineStr">
@@ -13564,7 +13595,7 @@
           <t>Tensor All-Season Ultralight Insulated</t>
         </is>
       </c>
-      <c r="F12" s="39" t="n">
+      <c r="F12" s="56" t="n">
         <v>14.1</v>
       </c>
       <c r="G12" s="38" t="inlineStr">
@@ -13572,7 +13603,7 @@
           <t>14.1 oz regular per NEMO/REI specs</t>
         </is>
       </c>
-      <c r="H12" s="40" t="n">
+      <c r="H12" s="57" t="n">
         <v>199.95</v>
       </c>
       <c r="I12" s="41" t="inlineStr">
@@ -13657,7 +13688,7 @@
           <t>Tensor Extreme Conditions</t>
         </is>
       </c>
-      <c r="F13" s="39" t="n">
+      <c r="F13" s="56" t="n">
         <v>19</v>
       </c>
       <c r="G13" s="38" t="inlineStr">
@@ -13665,7 +13696,7 @@
           <t>~1 lb 3 oz (19 oz) per NEMO specs, R-value 8.5</t>
         </is>
       </c>
-      <c r="H13" s="40" t="n">
+      <c r="H13" s="57" t="n">
         <v>259.95</v>
       </c>
       <c r="I13" s="41" t="inlineStr">
@@ -13750,7 +13781,7 @@
           <t>Stuff sack filled with spare clothes (or generic inflatable pillow)</t>
         </is>
       </c>
-      <c r="F14" s="39" t="n">
+      <c r="F14" s="56" t="n">
         <v>2</v>
       </c>
       <c r="G14" s="38" t="inlineStr">
@@ -13758,7 +13789,7 @@
           <t>A stuff sack you're already carrying + a puffy/fleece stuffed inside is ~0 marginal oz; a generic $10 inflatable pillow runs 2-3 oz</t>
         </is>
       </c>
-      <c r="H14" s="40" t="n">
+      <c r="H14" s="57" t="n">
         <v>20</v>
       </c>
       <c r="I14" s="41" t="inlineStr">
@@ -13843,7 +13874,7 @@
           <t>Aeros Down Pillow (Regular)</t>
         </is>
       </c>
-      <c r="F15" s="39" t="n">
+      <c r="F15" s="56" t="n">
         <v>2.5</v>
       </c>
       <c r="G15" s="38" t="inlineStr">
@@ -13851,7 +13882,7 @@
           <t>~2.5 oz per Sea to Summit specs for the down-insulated Regular</t>
         </is>
       </c>
-      <c r="H15" s="40" t="n">
+      <c r="H15" s="57" t="n">
         <v>64.95</v>
       </c>
       <c r="I15" s="41" t="inlineStr">
@@ -13936,7 +13967,7 @@
           <t>Fillo Elite</t>
         </is>
       </c>
-      <c r="F16" s="39" t="n">
+      <c r="F16" s="56" t="n">
         <v>2.5</v>
       </c>
       <c r="G16" s="38" t="inlineStr">
@@ -13944,7 +13975,7 @@
           <t>~2.4-2.6 oz per NEMO specs</t>
         </is>
       </c>
-      <c r="H16" s="40" t="n">
+      <c r="H16" s="57" t="n">
         <v>59.95</v>
       </c>
       <c r="I16" s="41" t="inlineStr">
@@ -14029,7 +14060,7 @@
           <t>Polycryo window-shrink-film sheet</t>
         </is>
       </c>
-      <c r="F17" s="39" t="n">
+      <c r="F17" s="56" t="n">
         <v>2</v>
       </c>
       <c r="G17" s="38" t="inlineStr">
@@ -14037,7 +14068,7 @@
           <t>A cut sheet of polycryo/window film runs ~1-2 oz depending on tent footprint size</t>
         </is>
       </c>
-      <c r="H17" s="40" t="n">
+      <c r="H17" s="57" t="n">
         <v>13</v>
       </c>
       <c r="I17" s="41" t="inlineStr">
@@ -14122,7 +14153,7 @@
           <t>Tyvek HomeWrap sheet</t>
         </is>
       </c>
-      <c r="F18" s="39" t="n">
+      <c r="F18" s="56" t="n">
         <v>5</v>
       </c>
       <c r="G18" s="38" t="inlineStr">
@@ -14130,7 +14161,7 @@
           <t>~4-6 oz depending on footprint size (heavier than polycryo, more durable)</t>
         </is>
       </c>
-      <c r="H18" s="40" t="n">
+      <c r="H18" s="57" t="n">
         <v>22</v>
       </c>
       <c r="I18" s="41" t="inlineStr">
@@ -14215,7 +14246,7 @@
           <t>Matching branded tent footprint (polycro or DCF)</t>
         </is>
       </c>
-      <c r="F19" s="39" t="n">
+      <c r="F19" s="56" t="n">
         <v>3.5</v>
       </c>
       <c r="G19" s="38" t="inlineStr">
@@ -14223,7 +14254,7 @@
           <t>Manufacturer footprints for X-Mid/Duplex run ~2-5 oz depending on material and tent size</t>
         </is>
       </c>
-      <c r="H19" s="40" t="n">
+      <c r="H19" s="57" t="n">
         <v>59</v>
       </c>
       <c r="I19" s="41" t="inlineStr">
@@ -14308,7 +14339,7 @@
           <t>Ziploc freezer bags + a cheap nylon stuff sack (or reused packaging bags)</t>
         </is>
       </c>
-      <c r="F20" s="39" t="n">
+      <c r="F20" s="56" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="38" t="inlineStr">
@@ -14316,7 +14347,7 @@
           <t>A couple of gallon freezer bags + one $6 stuff sack run about 1 oz total</t>
         </is>
       </c>
-      <c r="H20" s="40" t="n">
+      <c r="H20" s="57" t="n">
         <v>12</v>
       </c>
       <c r="I20" s="41" t="inlineStr">
@@ -14401,7 +14432,7 @@
           <t>Ultra-Sil Dry Bag - Set of 3</t>
         </is>
       </c>
-      <c r="F21" s="39" t="n">
+      <c r="F21" s="56" t="n">
         <v>2.5</v>
       </c>
       <c r="G21" s="38" t="inlineStr">
@@ -14409,7 +14440,7 @@
           <t>~1-1.5 oz per bag depending on size; a useful 2-bag set (sleep system + electronics) runs ~2.5 oz combined</t>
         </is>
       </c>
-      <c r="H21" s="40" t="n">
+      <c r="H21" s="57" t="n">
         <v>69.95</v>
       </c>
       <c r="I21" s="41" t="inlineStr">
@@ -14494,7 +14525,7 @@
           <t>DCF Stuff Sack (assorted sizes)</t>
         </is>
       </c>
-      <c r="F22" s="39" t="n">
+      <c r="F22" s="56" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="38" t="inlineStr">
@@ -14502,7 +14533,7 @@
           <t>~0.5-1 oz per bag depending on size — DCF is lighter than silnylon at comparable volume</t>
         </is>
       </c>
-      <c r="H22" s="40" t="n">
+      <c r="H22" s="57" t="n">
         <v>31</v>
       </c>
       <c r="I22" s="41" t="inlineStr">
@@ -14587,7 +14618,7 @@
           <t>Compactor/contractor trash bag (heavy-duty, unscented)</t>
         </is>
       </c>
-      <c r="F23" s="39" t="n">
+      <c r="F23" s="56" t="n">
         <v>1.4</v>
       </c>
       <c r="G23" s="38" t="inlineStr">
@@ -14595,7 +14626,7 @@
           <t>18-gallon compactor bags run ~1.4 oz per 99Boulders/community measurements</t>
         </is>
       </c>
-      <c r="H23" s="40" t="n">
+      <c r="H23" s="57" t="n">
         <v>10</v>
       </c>
       <c r="I23" s="41" t="inlineStr">
@@ -14680,7 +14711,7 @@
           <t>Nylofume Pack Liner Bag</t>
         </is>
       </c>
-      <c r="F24" s="39" t="n">
+      <c r="F24" s="56" t="n">
         <v>0.9</v>
       </c>
       <c r="G24" s="38" t="inlineStr">
@@ -14688,7 +14719,7 @@
           <t>0.9 oz per bag per Litesmith/99Boulders specs</t>
         </is>
       </c>
-      <c r="H24" s="40" t="n">
+      <c r="H24" s="57" t="n">
         <v>2.49</v>
       </c>
       <c r="I24" s="41" t="inlineStr">
@@ -14773,7 +14804,7 @@
           <t>Evac Lightweight Dry Bag (35L)</t>
         </is>
       </c>
-      <c r="F25" s="39" t="n">
+      <c r="F25" s="56" t="n">
         <v>3.5</v>
       </c>
       <c r="G25" s="38" t="inlineStr">
@@ -14781,7 +14812,7 @@
           <t>~3.5 oz (100g) for the 35L/70L eVac-style liner per Sea to Summit specs</t>
         </is>
       </c>
-      <c r="H25" s="40" t="n">
+      <c r="H25" s="57" t="n">
         <v>44.95</v>
       </c>
       <c r="I25" s="41" t="inlineStr">
@@ -14866,7 +14897,7 @@
           <t>Amicus Stove Cookset Combo</t>
         </is>
       </c>
-      <c r="F26" s="39" t="n">
+      <c r="F26" s="56" t="n">
         <v>11.2</v>
       </c>
       <c r="G26" s="38" t="inlineStr">
@@ -14874,7 +14905,7 @@
           <t>REI spec 11.2oz for the stove + 0.6L aluminum pot/cup combo</t>
         </is>
       </c>
-      <c r="H26" s="40" t="n">
+      <c r="H26" s="57" t="n">
         <v>49.95</v>
       </c>
       <c r="I26" s="41" t="inlineStr">
@@ -14959,7 +14990,7 @@
           <t>WindMaster (4Flex)</t>
         </is>
       </c>
-      <c r="F27" s="39" t="n">
+      <c r="F27" s="56" t="n">
         <v>3.5</v>
       </c>
       <c r="G27" s="38" t="inlineStr">
@@ -14967,7 +14998,7 @@
           <t>stove 2.5oz + 4Flex 4-arm pot stand ~1oz, per Soto spec, matches independent reviews</t>
         </is>
       </c>
-      <c r="H27" s="40" t="n">
+      <c r="H27" s="57" t="n">
         <v>69.95</v>
       </c>
       <c r="I27" s="41" t="inlineStr">
@@ -15052,7 +15083,7 @@
           <t>Stash</t>
         </is>
       </c>
-      <c r="F28" s="39" t="n">
+      <c r="F28" s="56" t="n">
         <v>7.1</v>
       </c>
       <c r="G28" s="38" t="inlineStr">
@@ -15060,7 +15091,7 @@
           <t>full kit (stove + 0.8L pot + optional stabilizer), per Jetboil spec — matches Halfway Anywhere 2025 PCT survey listing</t>
         </is>
       </c>
-      <c r="H28" s="40" t="n">
+      <c r="H28" s="57" t="n">
         <v>131</v>
       </c>
       <c r="I28" s="41" t="inlineStr">
@@ -15145,7 +15176,7 @@
           <t>A004-025001 Aluminum Sauce Pan, 1-Quart</t>
         </is>
       </c>
-      <c r="F29" s="39" t="n">
+      <c r="F29" s="56" t="n">
         <v>6</v>
       </c>
       <c r="G29" s="38" t="inlineStr">
@@ -15153,7 +15184,7 @@
           <t>typical stamped-aluminum camp pot weight; EST from category norms, not individually spec-verified this session; only 1qt capacity — buy two for group boiling of 6</t>
         </is>
       </c>
-      <c r="H29" s="40" t="n">
+      <c r="H29" s="57" t="n">
         <v>12.99</v>
       </c>
       <c r="I29" s="41" t="inlineStr">
@@ -15238,7 +15269,7 @@
           <t>750ml Titanium Pot with Bail Handle (POT-750-BH)</t>
         </is>
       </c>
-      <c r="F30" s="39" t="n">
+      <c r="F30" s="56" t="n">
         <v>4.1</v>
       </c>
       <c r="G30" s="38" t="inlineStr">
@@ -15246,7 +15277,7 @@
           <t>TOAKS spec 4.1oz/116g, widely confirmed in reviews</t>
         </is>
       </c>
-      <c r="H30" s="40" t="n">
+      <c r="H30" s="57" t="n">
         <v>30</v>
       </c>
       <c r="I30" s="41" t="inlineStr">
@@ -15331,7 +15362,7 @@
           <t>Trek 900 Titanium Cookset</t>
         </is>
       </c>
-      <c r="F31" s="39" t="n">
+      <c r="F31" s="56" t="n">
         <v>6</v>
       </c>
       <c r="G31" s="38" t="inlineStr">
@@ -15339,7 +15370,7 @@
           <t>REI spec 6oz/170g for the 2-piece cookset (900ml pot + pan/lid); swapped in for the Evernew pasta pot, which is discontinued/unavailable in the US as of 2026</t>
         </is>
       </c>
-      <c r="H31" s="40" t="n">
+      <c r="H31" s="57" t="n">
         <v>54.95</v>
       </c>
       <c r="I31" s="41" t="inlineStr">
@@ -15424,7 +15455,7 @@
           <t>Butane/Propane Mix Fuel, 7.75oz (220g)</t>
         </is>
       </c>
-      <c r="F32" s="39" t="n">
+      <c r="F32" s="56" t="n">
         <v>7.75</v>
       </c>
       <c r="G32" s="38" t="inlineStr">
@@ -15432,7 +15463,7 @@
           <t>Walmart spec, 220g fuel canister</t>
         </is>
       </c>
-      <c r="H32" s="40" t="n">
+      <c r="H32" s="57" t="n">
         <v>5.97</v>
       </c>
       <c r="I32" s="41" t="inlineStr">
@@ -15517,7 +15548,7 @@
           <t>IsoPro 8oz/227g canister</t>
         </is>
       </c>
-      <c r="F33" s="39" t="n">
+      <c r="F33" s="56" t="n">
         <v>13.7</v>
       </c>
       <c r="G33" s="38" t="inlineStr">
@@ -15525,7 +15556,7 @@
           <t>manufacturer spec, 227g fuel</t>
         </is>
       </c>
-      <c r="H33" s="40" t="n">
+      <c r="H33" s="57" t="n">
         <v>6.95</v>
       </c>
       <c r="I33" s="41" t="inlineStr">
@@ -15610,7 +15641,7 @@
           <t>IsoPro (same blend, cold-weather use case)</t>
         </is>
       </c>
-      <c r="F34" s="39" t="n">
+      <c r="F34" s="56" t="n">
         <v>7.6</v>
       </c>
       <c r="G34" s="38" t="inlineStr">
@@ -15618,7 +15649,7 @@
           <t>4oz/113g canister spec</t>
         </is>
       </c>
-      <c r="H34" s="40" t="n">
+      <c r="H34" s="57" t="n">
         <v>5.95</v>
       </c>
       <c r="I34" s="41" t="inlineStr">
@@ -15703,7 +15734,7 @@
           <t>Titanium Spork</t>
         </is>
       </c>
-      <c r="F35" s="39" t="n">
+      <c r="F35" s="56" t="n">
         <v>0.6</v>
       </c>
       <c r="G35" s="38" t="inlineStr">
@@ -15711,7 +15742,7 @@
           <t>typical spec for generic Ti sporks sold on Amazon</t>
         </is>
       </c>
-      <c r="H35" s="40" t="n">
+      <c r="H35" s="57" t="n">
         <v>9.949999999999999</v>
       </c>
       <c r="I35" s="41" t="inlineStr">
@@ -15796,7 +15827,7 @@
           <t>Frontier Ultralight Spoon - Long Handle</t>
         </is>
       </c>
-      <c r="F36" s="39" t="n">
+      <c r="F36" s="56" t="n">
         <v>0.6</v>
       </c>
       <c r="G36" s="38" t="inlineStr">
@@ -15804,7 +15835,7 @@
           <t>manufacturer spec 17g/0.6oz</t>
         </is>
       </c>
-      <c r="H36" s="40" t="n">
+      <c r="H36" s="57" t="n">
         <v>10.95</v>
       </c>
       <c r="I36" s="41" t="inlineStr">
@@ -15889,7 +15920,7 @@
           <t>Titanium Spork</t>
         </is>
       </c>
-      <c r="F37" s="39" t="n">
+      <c r="F37" s="56" t="n">
         <v>0.6</v>
       </c>
       <c r="G37" s="38" t="inlineStr">
@@ -15897,7 +15928,7 @@
           <t>manufacturer spec ~17g</t>
         </is>
       </c>
-      <c r="H37" s="40" t="n">
+      <c r="H37" s="57" t="n">
         <v>9.949999999999999</v>
       </c>
       <c r="I37" s="41" t="inlineStr">
@@ -15982,7 +16013,7 @@
           <t>Squeeze (SP2129)</t>
         </is>
       </c>
-      <c r="F38" s="39" t="n">
+      <c r="F38" s="56" t="n">
         <v>3</v>
       </c>
       <c r="G38" s="38" t="inlineStr">
@@ -15990,7 +16021,7 @@
           <t>Sawyer spec ~3oz for filter alone</t>
         </is>
       </c>
-      <c r="H38" s="40" t="n">
+      <c r="H38" s="57" t="n">
         <v>45.95</v>
       </c>
       <c r="I38" s="41" t="inlineStr">
@@ -16075,7 +16106,7 @@
           <t>BeFree 1.0L</t>
         </is>
       </c>
-      <c r="F39" s="39" t="n">
+      <c r="F39" s="56" t="n">
         <v>2.3</v>
       </c>
       <c r="G39" s="38" t="inlineStr">
@@ -16083,7 +16114,7 @@
           <t>Katadyn spec 2.3oz filter+pouch</t>
         </is>
       </c>
-      <c r="H39" s="40" t="n">
+      <c r="H39" s="57" t="n">
         <v>52.95</v>
       </c>
       <c r="I39" s="41" t="inlineStr">
@@ -16168,7 +16199,7 @@
           <t>GeoPress</t>
         </is>
       </c>
-      <c r="F40" s="39" t="n">
+      <c r="F40" s="56" t="n">
         <v>15.9</v>
       </c>
       <c r="G40" s="38" t="inlineStr">
@@ -16176,7 +16207,7 @@
           <t>manufacturer spec 15.9oz/450g — notably heavier than squeeze filters</t>
         </is>
       </c>
-      <c r="H40" s="40" t="n">
+      <c r="H40" s="57" t="n">
         <v>99.95</v>
       </c>
       <c r="I40" s="41" t="inlineStr">
@@ -16261,7 +16292,7 @@
           <t>1L reused disposable bottle</t>
         </is>
       </c>
-      <c r="F41" s="39" t="n">
+      <c r="F41" s="56" t="n">
         <v>1.6</v>
       </c>
       <c r="G41" s="38" t="inlineStr">
@@ -16269,7 +16300,7 @@
           <t>empty bottle weight, widely cited in UL community measurements</t>
         </is>
       </c>
-      <c r="H41" s="40" t="n">
+      <c r="H41" s="57" t="n">
         <v>2.17</v>
       </c>
       <c r="I41" s="41" t="inlineStr">
@@ -16354,7 +16385,7 @@
           <t>Stow 1L collapsible bottle</t>
         </is>
       </c>
-      <c r="F42" s="39" t="n">
+      <c r="F42" s="56" t="n">
         <v>1.4</v>
       </c>
       <c r="G42" s="38" t="inlineStr">
@@ -16362,7 +16393,7 @@
           <t>manufacturer spec 1.4oz</t>
         </is>
       </c>
-      <c r="H42" s="40" t="n">
+      <c r="H42" s="57" t="n">
         <v>18</v>
       </c>
       <c r="I42" s="41" t="inlineStr">
@@ -16443,7 +16474,7 @@
           <t>Vecto 2L</t>
         </is>
       </c>
-      <c r="F43" s="39" t="n">
+      <c r="F43" s="56" t="n">
         <v>3.6</v>
       </c>
       <c r="G43" s="38" t="inlineStr">
@@ -16451,7 +16482,7 @@
           <t>manufacturer spec ~3.6oz for the 2L bag</t>
         </is>
       </c>
-      <c r="H43" s="40" t="n">
+      <c r="H43" s="57" t="n">
         <v>25</v>
       </c>
       <c r="I43" s="41" t="inlineStr">
@@ -16536,7 +16567,7 @@
           <t>Easy to Throw Bear Bag Hanging Kit (#371486)</t>
         </is>
       </c>
-      <c r="F44" s="39" t="n">
+      <c r="F44" s="56" t="n">
         <v>6</v>
       </c>
       <c r="G44" s="38" t="inlineStr">
@@ -16544,7 +16575,7 @@
           <t>typical DIY kit weight — 50ft of paracord/Zpacks cord + food sack; EST from common DIY builds</t>
         </is>
       </c>
-      <c r="H44" s="40" t="n">
+      <c r="H44" s="57" t="n">
         <v>27</v>
       </c>
       <c r="I44" s="41" t="inlineStr">
@@ -16629,7 +16660,7 @@
           <t>Major XL (with OPSak liner)</t>
         </is>
       </c>
-      <c r="F45" s="39" t="n">
+      <c r="F45" s="56" t="n">
         <v>10.8</v>
       </c>
       <c r="G45" s="38" t="inlineStr">
@@ -16637,7 +16668,7 @@
           <t>Ursack Major ~7.8oz + OPSak liner ~1oz + typical XL upsizing; Ursack Major listed at 8.8oz in category roundups, XL slightly more</t>
         </is>
       </c>
-      <c r="H45" s="40" t="n">
+      <c r="H45" s="57" t="n">
         <v>149.95</v>
       </c>
       <c r="I45" s="41" t="inlineStr">
@@ -16722,7 +16753,7 @@
           <t>BV500</t>
         </is>
       </c>
-      <c r="F46" s="39" t="n">
+      <c r="F46" s="56" t="n">
         <v>41</v>
       </c>
       <c r="G46" s="38" t="inlineStr">
@@ -16730,7 +16761,7 @@
           <t>manufacturer/retailer spec ~2lb 9oz (41oz)</t>
         </is>
       </c>
-      <c r="H46" s="40" t="n">
+      <c r="H46" s="57" t="n">
         <v>99.95</v>
       </c>
       <c r="I46" s="41" t="inlineStr">
@@ -16815,7 +16846,7 @@
           <t>Tikkina</t>
         </is>
       </c>
-      <c r="F47" s="39" t="n">
+      <c r="F47" s="56" t="n">
         <v>2.9</v>
       </c>
       <c r="G47" s="38" t="inlineStr">
@@ -16823,7 +16854,7 @@
           <t>Petzl spec 82g/2.9oz including batteries</t>
         </is>
       </c>
-      <c r="H47" s="40" t="n">
+      <c r="H47" s="57" t="n">
         <v>19.95</v>
       </c>
       <c r="I47" s="41" t="inlineStr">
@@ -16904,7 +16935,7 @@
           <t>Spot 400</t>
         </is>
       </c>
-      <c r="F48" s="39" t="n">
+      <c r="F48" s="56" t="n">
         <v>3</v>
       </c>
       <c r="G48" s="38" t="inlineStr">
@@ -16912,7 +16943,7 @@
           <t>Black Diamond spec ~90g/3.2oz with batteries; commonly listed ~3oz</t>
         </is>
       </c>
-      <c r="H48" s="40" t="n">
+      <c r="H48" s="57" t="n">
         <v>59.95</v>
       </c>
       <c r="I48" s="41" t="inlineStr">
@@ -16997,7 +17028,7 @@
           <t>NU25 (rechargeable)</t>
         </is>
       </c>
-      <c r="F49" s="39" t="n">
+      <c r="F49" s="56" t="n">
         <v>1.75</v>
       </c>
       <c r="G49" s="38" t="inlineStr">
@@ -17005,7 +17036,7 @@
           <t>Nitecore spec ~48g/1.7oz — notably lighter than AAA headlamps since it's built-in rechargeable</t>
         </is>
       </c>
-      <c r="H49" s="40" t="n">
+      <c r="H49" s="57" t="n">
         <v>54.95</v>
       </c>
       <c r="I49" s="41" t="inlineStr">
@@ -17090,7 +17121,7 @@
           <t>Power Bank, 10,000mAh Portable Charger (PowerIQ, USB-C)</t>
         </is>
       </c>
-      <c r="F50" s="39" t="n">
+      <c r="F50" s="56" t="n">
         <v>6.3</v>
       </c>
       <c r="G50" s="38" t="inlineStr">
@@ -17098,7 +17129,7 @@
           <t>Anker spec ~180g/6.3oz</t>
         </is>
       </c>
-      <c r="H50" s="40" t="n">
+      <c r="H50" s="57" t="n">
         <v>21.99</v>
       </c>
       <c r="I50" s="41" t="inlineStr">
@@ -17179,7 +17210,7 @@
           <t>NB10000 Gen 3</t>
         </is>
       </c>
-      <c r="F51" s="39" t="n">
+      <c r="F51" s="56" t="n">
         <v>5.1</v>
       </c>
       <c r="G51" s="38" t="inlineStr">
@@ -17187,7 +17218,7 @@
           <t>Nitecore spec ~144g/5.1oz</t>
         </is>
       </c>
-      <c r="H51" s="40" t="n">
+      <c r="H51" s="57" t="n">
         <v>64.95</v>
       </c>
       <c r="I51" s="41" t="inlineStr">
@@ -17268,7 +17299,7 @@
           <t>NB10000 Gen 4</t>
         </is>
       </c>
-      <c r="F52" s="39" t="n">
+      <c r="F52" s="56" t="n">
         <v>5</v>
       </c>
       <c r="G52" s="38" t="inlineStr">
@@ -17276,7 +17307,7 @@
           <t>manufacturer press release claims 143g/5.0oz with improved IPX7 rating</t>
         </is>
       </c>
-      <c r="H52" s="40" t="n">
+      <c r="H52" s="57" t="n">
         <v>83.95</v>
       </c>
       <c r="I52" s="41" t="inlineStr">
@@ -17361,7 +17392,7 @@
           <t>inReach Mini 2 (weekly rental)</t>
         </is>
       </c>
-      <c r="F53" s="39" t="n">
+      <c r="F53" s="56" t="n">
         <v>3.5</v>
       </c>
       <c r="G53" s="38" t="inlineStr">
@@ -17369,7 +17400,7 @@
           <t>Garmin spec 3.5oz for the device itself; rental means no ownership weight/cost beyond the trip</t>
         </is>
       </c>
-      <c r="H53" s="40" t="n">
+      <c r="H53" s="57" t="n">
         <v>100</v>
       </c>
       <c r="I53" s="41" t="inlineStr">
@@ -17454,7 +17485,7 @@
           <t>Satellite Communicator</t>
         </is>
       </c>
-      <c r="F54" s="39" t="n">
+      <c r="F54" s="56" t="n">
         <v>5.4</v>
       </c>
       <c r="G54" s="38" t="inlineStr">
@@ -17462,7 +17493,7 @@
           <t>ZOLEO manufacturer spec ~155g/5.4oz</t>
         </is>
       </c>
-      <c r="H54" s="40" t="n">
+      <c r="H54" s="57" t="n">
         <v>199</v>
       </c>
       <c r="I54" s="41" t="inlineStr">
@@ -17547,7 +17578,7 @@
           <t>inReach Mini 2 (owned, Safety plan)</t>
         </is>
       </c>
-      <c r="F55" s="39" t="n">
+      <c r="F55" s="56" t="n">
         <v>3.5</v>
       </c>
       <c r="G55" s="38" t="inlineStr">
@@ -17555,7 +17586,7 @@
           <t>Garmin spec 3.5oz</t>
         </is>
       </c>
-      <c r="H55" s="40" t="n">
+      <c r="H55" s="57" t="n">
         <v>349.99</v>
       </c>
       <c r="I55" s="41" t="inlineStr">
@@ -17640,7 +17671,7 @@
           <t>Free account + printed topo</t>
         </is>
       </c>
-      <c r="F56" s="39" t="n">
+      <c r="F56" s="56" t="n">
         <v>0</v>
       </c>
       <c r="G56" s="38" t="inlineStr">
@@ -17648,7 +17679,7 @@
           <t>n/a — software; printed map ~1oz on paper</t>
         </is>
       </c>
-      <c r="H56" s="40" t="n">
+      <c r="H56" s="57" t="n">
         <v>0</v>
       </c>
       <c r="I56" s="41" t="inlineStr">
@@ -17733,7 +17764,7 @@
           <t>Premium subscription</t>
         </is>
       </c>
-      <c r="F57" s="39" t="n">
+      <c r="F57" s="56" t="n">
         <v>0</v>
       </c>
       <c r="G57" s="38" t="inlineStr">
@@ -17741,7 +17772,7 @@
           <t>n/a — software</t>
         </is>
       </c>
-      <c r="H57" s="40" t="n">
+      <c r="H57" s="57" t="n">
         <v>39.99</v>
       </c>
       <c r="I57" s="41" t="inlineStr">
@@ -17826,7 +17857,7 @@
           <t>Regional trail guide (per-trail purchase)</t>
         </is>
       </c>
-      <c r="F58" s="39" t="n">
+      <c r="F58" s="56" t="n">
         <v>0</v>
       </c>
       <c r="G58" s="38" t="inlineStr">
@@ -17834,7 +17865,7 @@
           <t>n/a — software</t>
         </is>
       </c>
-      <c r="H58" s="40" t="n">
+      <c r="H58" s="57" t="n">
         <v>14.99</v>
       </c>
       <c r="I58" s="41" t="inlineStr">
@@ -17919,7 +17950,7 @@
           <t>No.8 Carbon/Stainless folding knife</t>
         </is>
       </c>
-      <c r="F59" s="39" t="n">
+      <c r="F59" s="56" t="n">
         <v>1.6</v>
       </c>
       <c r="G59" s="38" t="inlineStr">
@@ -17927,7 +17958,7 @@
           <t>Opinel spec ~45g/1.6oz for the No.8</t>
         </is>
       </c>
-      <c r="H59" s="40" t="n">
+      <c r="H59" s="57" t="n">
         <v>22</v>
       </c>
       <c r="I59" s="41" t="inlineStr">
@@ -18008,7 +18039,7 @@
           <t>Wingman</t>
         </is>
       </c>
-      <c r="F60" s="39" t="n">
+      <c r="F60" s="56" t="n">
         <v>7.2</v>
       </c>
       <c r="G60" s="38" t="inlineStr">
@@ -18016,7 +18047,7 @@
           <t>Leatherman spec 7.2oz/204g</t>
         </is>
       </c>
-      <c r="H60" s="40" t="n">
+      <c r="H60" s="57" t="n">
         <v>49.95</v>
       </c>
       <c r="I60" s="41" t="inlineStr">
@@ -18097,7 +18128,7 @@
           <t>Skeletool CX</t>
         </is>
       </c>
-      <c r="F61" s="39" t="n">
+      <c r="F61" s="56" t="n">
         <v>5</v>
       </c>
       <c r="G61" s="38" t="inlineStr">
@@ -18105,7 +18136,7 @@
           <t>Leatherman spec 5.0oz/142g</t>
         </is>
       </c>
-      <c r="H61" s="40" t="n">
+      <c r="H61" s="57" t="n">
         <v>99.95</v>
       </c>
       <c r="I61" s="41" t="inlineStr">
@@ -18145,7 +18176,7 @@
       </c>
       <c r="P61" s="38" t="inlineStr">
         <is>
-          <t>Great if the Captain wants one tool to keep long-term across future trips</t>
+          <t>Great if Jordan wants one tool to keep long-term across future trips</t>
         </is>
       </c>
       <c r="Q61" s="37" t="n">
@@ -18186,7 +18217,7 @@
           <t>Build-your-own kit (gauze, tape, meds, moleskin, blister care)</t>
         </is>
       </c>
-      <c r="F62" s="39" t="n">
+      <c r="F62" s="56" t="n">
         <v>4</v>
       </c>
       <c r="G62" s="38" t="inlineStr">
@@ -18194,7 +18225,7 @@
           <t>EST — typical DIY minimal kit weight for group use; not individually itemized/weighed this session</t>
         </is>
       </c>
-      <c r="H62" s="40" t="n">
+      <c r="H62" s="57" t="n">
         <v>22</v>
       </c>
       <c r="I62" s="41" t="inlineStr">
@@ -18279,7 +18310,7 @@
           <t>Ultralight/Watertight .7</t>
         </is>
       </c>
-      <c r="F63" s="39" t="n">
+      <c r="F63" s="56" t="n">
         <v>4.4</v>
       </c>
       <c r="G63" s="38" t="inlineStr">
@@ -18287,7 +18318,7 @@
           <t>AMK spec 4.4oz</t>
         </is>
       </c>
-      <c r="H63" s="40" t="n">
+      <c r="H63" s="57" t="n">
         <v>44.99</v>
       </c>
       <c r="I63" s="41" t="inlineStr">
@@ -18372,7 +18403,7 @@
           <t>Mountain Series Explorer</t>
         </is>
       </c>
-      <c r="F64" s="39" t="n">
+      <c r="F64" s="56" t="n">
         <v>16</v>
       </c>
       <c r="G64" s="38" t="inlineStr">
@@ -18380,7 +18411,7 @@
           <t>AMK spec/listing; built for 4 people/7 days per AMK product description, oversized for 6/1-night but most complete</t>
         </is>
       </c>
-      <c r="H64" s="40" t="n">
+      <c r="H64" s="57" t="n">
         <v>86.48999999999999</v>
       </c>
       <c r="I64" s="41" t="inlineStr">
@@ -18465,7 +18496,7 @@
           <t>Backpackers Trowel</t>
         </is>
       </c>
-      <c r="F65" s="39" t="n">
+      <c r="F65" s="56" t="n">
         <v>1.5</v>
       </c>
       <c r="G65" s="38" t="inlineStr">
@@ -18473,7 +18504,7 @@
           <t>typical plastic trowel weight ~1.5oz</t>
         </is>
       </c>
-      <c r="H65" s="40" t="n">
+      <c r="H65" s="57" t="n">
         <v>8.75</v>
       </c>
       <c r="I65" s="41" t="inlineStr">
@@ -18558,7 +18589,7 @@
           <t>Cathole Trowel</t>
         </is>
       </c>
-      <c r="F66" s="39" t="n">
+      <c r="F66" s="56" t="n">
         <v>2.4</v>
       </c>
       <c r="G66" s="38" t="inlineStr">
@@ -18566,7 +18597,7 @@
           <t>manufacturer spec ~2.4oz</t>
         </is>
       </c>
-      <c r="H66" s="40" t="n">
+      <c r="H66" s="57" t="n">
         <v>7.95</v>
       </c>
       <c r="I66" s="41" t="inlineStr">
@@ -18651,7 +18682,7 @@
           <t>The DirtSaw Deuce #2 Trowel</t>
         </is>
       </c>
-      <c r="F67" s="39" t="n">
+      <c r="F67" s="56" t="n">
         <v>0.6</v>
       </c>
       <c r="G67" s="38" t="inlineStr">
@@ -18659,7 +18690,7 @@
           <t>manufacturer spec ~17g/0.6oz for the #2 model</t>
         </is>
       </c>
-      <c r="H67" s="40" t="n">
+      <c r="H67" s="57" t="n">
         <v>21.95</v>
       </c>
       <c r="I67" s="41" t="inlineStr">
@@ -18744,7 +18775,7 @@
           <t>Travel-size toothbrush, toothpaste, TP, hand sanitizer</t>
         </is>
       </c>
-      <c r="F68" s="39" t="n">
+      <c r="F68" s="56" t="n">
         <v>3.5</v>
       </c>
       <c r="G68" s="38" t="inlineStr">
@@ -18752,7 +18783,7 @@
           <t>small personal hygiene bag, EST from category norms</t>
         </is>
       </c>
-      <c r="H68" s="40" t="n">
+      <c r="H68" s="57" t="n">
         <v>3.94</v>
       </c>
       <c r="I68" s="41" t="inlineStr">
@@ -18833,7 +18864,7 @@
           <t>Small toiletry bag + biodegradable wipes</t>
         </is>
       </c>
-      <c r="F69" s="39" t="n">
+      <c r="F69" s="56" t="n">
         <v>4</v>
       </c>
       <c r="G69" s="38" t="inlineStr">
@@ -18841,7 +18872,7 @@
           <t>small personal hygiene bag with wipes, EST from category norms</t>
         </is>
       </c>
-      <c r="H69" s="40" t="n">
+      <c r="H69" s="57" t="n">
         <v>9</v>
       </c>
       <c r="I69" s="41" t="inlineStr">
@@ -18922,7 +18953,7 @@
           <t>Ultralight toiletry kit + pack towel wipes + sunscreen/lip balm travel set</t>
         </is>
       </c>
-      <c r="F70" s="39" t="n">
+      <c r="F70" s="56" t="n">
         <v>5</v>
       </c>
       <c r="G70" s="38" t="inlineStr">
@@ -18930,7 +18961,7 @@
           <t>fuller personal hygiene kit, EST from category norms</t>
         </is>
       </c>
-      <c r="H70" s="40" t="n">
+      <c r="H70" s="57" t="n">
         <v>15</v>
       </c>
       <c r="I70" s="41" t="inlineStr">
@@ -19011,7 +19042,7 @@
           <t>Aluminum adjustable trekking poles (pair)</t>
         </is>
       </c>
-      <c r="F71" s="39" t="n">
+      <c r="F71" s="56" t="n">
         <v>18</v>
       </c>
       <c r="G71" s="38" t="inlineStr">
@@ -19019,7 +19050,7 @@
           <t>typical aluminum adjustable pole pair weight per category comparisons; EST from category norms</t>
         </is>
       </c>
-      <c r="H71" s="40" t="n">
+      <c r="H71" s="57" t="n">
         <v>49.99</v>
       </c>
       <c r="I71" s="41" t="inlineStr">
@@ -19100,7 +19131,7 @@
           <t>Carbon Fiber Quick Lock (pair)</t>
         </is>
       </c>
-      <c r="F72" s="39" t="n">
+      <c r="F72" s="56" t="n">
         <v>8.1</v>
       </c>
       <c r="G72" s="38" t="inlineStr">
@@ -19108,7 +19139,7 @@
           <t>per CleverHiker/OutdoorGearLab testing, 8.1oz for the pair</t>
         </is>
       </c>
-      <c r="H72" s="40" t="n">
+      <c r="H72" s="57" t="n">
         <v>64.98999999999999</v>
       </c>
       <c r="I72" s="41" t="inlineStr">
@@ -19193,7 +19224,7 @@
           <t>Distance Carbon Z (pair)</t>
         </is>
       </c>
-      <c r="F73" s="39" t="n">
+      <c r="F73" s="56" t="n">
         <v>10.9</v>
       </c>
       <c r="G73" s="38" t="inlineStr">
@@ -19201,7 +19232,7 @@
           <t>Black Diamond spec ~10.9oz/310g per pair (folding Z-pole design)</t>
         </is>
       </c>
-      <c r="H73" s="40" t="n">
+      <c r="H73" s="57" t="n">
         <v>219.95</v>
       </c>
       <c r="I73" s="41" t="inlineStr">
@@ -19282,7 +19313,7 @@
           <t>Cut piece of leftover closed-cell foam pad</t>
         </is>
       </c>
-      <c r="F74" s="39" t="n">
+      <c r="F74" s="56" t="n">
         <v>1</v>
       </c>
       <c r="G74" s="38" t="inlineStr">
@@ -19290,7 +19321,7 @@
           <t>EST — small cut piece of CCF foam, typical DIY weight</t>
         </is>
       </c>
-      <c r="H74" s="40" t="n">
+      <c r="H74" s="57" t="n">
         <v>0</v>
       </c>
       <c r="I74" s="41" t="inlineStr">
@@ -19371,7 +19402,7 @@
           <t>Z Seat</t>
         </is>
       </c>
-      <c r="F75" s="39" t="n">
+      <c r="F75" s="56" t="n">
         <v>2</v>
       </c>
       <c r="G75" s="38" t="inlineStr">
@@ -19379,7 +19410,7 @@
           <t>Therm-a-Rest spec 2oz/56g</t>
         </is>
       </c>
-      <c r="H75" s="40" t="n">
+      <c r="H75" s="57" t="n">
         <v>34.28</v>
       </c>
       <c r="I75" s="41" t="inlineStr">
@@ -19464,7 +19495,7 @@
           <t>1/8in Thinlight Foam Pad (full torso, multi-use)</t>
         </is>
       </c>
-      <c r="F76" s="39" t="n">
+      <c r="F76" s="56" t="n">
         <v>2.8</v>
       </c>
       <c r="G76" s="38" t="inlineStr">
@@ -19472,7 +19503,7 @@
           <t>Gossamer Gear spec ~2.8oz for the torso-length piece</t>
         </is>
       </c>
-      <c r="H76" s="40" t="n">
+      <c r="H76" s="57" t="n">
         <v>22.5</v>
       </c>
       <c r="I76" s="41" t="inlineStr">
@@ -19557,7 +19588,7 @@
           <t>Gabe Cloud Slide Sandals</t>
         </is>
       </c>
-      <c r="F77" s="39" t="n">
+      <c r="F77" s="56" t="n">
         <v>6</v>
       </c>
       <c r="G77" s="38" t="inlineStr">
@@ -19565,7 +19596,7 @@
           <t>typical foam slide pair weight, EST from category norms</t>
         </is>
       </c>
-      <c r="H77" s="40" t="n">
+      <c r="H77" s="57" t="n">
         <v>19.99</v>
       </c>
       <c r="I77" s="41" t="inlineStr">
@@ -19650,7 +19681,7 @@
           <t>Classic Clog</t>
         </is>
       </c>
-      <c r="F78" s="39" t="n">
+      <c r="F78" s="56" t="n">
         <v>12</v>
       </c>
       <c r="G78" s="38" t="inlineStr">
@@ -19658,7 +19689,7 @@
           <t>typical Crocs Classic Clog pair weight per size, widely cited around 11-13oz</t>
         </is>
       </c>
-      <c r="H78" s="40" t="n">
+      <c r="H78" s="57" t="n">
         <v>49.99</v>
       </c>
       <c r="I78" s="41" t="inlineStr">
@@ -19739,7 +19770,7 @@
           <t>Z-Trail EV Sandals</t>
         </is>
       </c>
-      <c r="F79" s="39" t="n">
+      <c r="F79" s="56" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="G79" s="38" t="inlineStr">
@@ -19747,7 +19778,7 @@
           <t>Xero Shoes spec ~8.8oz per pair (size-dependent)</t>
         </is>
       </c>
-      <c r="H79" s="40" t="n">
+      <c r="H79" s="57" t="n">
         <v>80</v>
       </c>
       <c r="I79" s="41" t="inlineStr">
@@ -19828,7 +19859,7 @@
           <t>Any old/thrifted trail running shoe (mesh upper, non-waterproof)</t>
         </is>
       </c>
-      <c r="F80" s="39" t="n">
+      <c r="F80" s="56" t="n">
         <v>24</v>
       </c>
       <c r="G80" s="38" t="inlineStr">
@@ -19836,7 +19867,7 @@
           <t>varies, ~1.5 lb/pair typical trail runner</t>
         </is>
       </c>
-      <c r="H80" s="40" t="n">
+      <c r="H80" s="57" t="n">
         <v>0</v>
       </c>
       <c r="I80" s="41" t="inlineStr">
@@ -19921,7 +19952,7 @@
           <t>Moab 3</t>
         </is>
       </c>
-      <c r="F81" s="39" t="n">
+      <c r="F81" s="56" t="n">
         <v>33</v>
       </c>
       <c r="G81" s="38" t="inlineStr">
@@ -19929,7 +19960,7 @@
           <t>2 lb 1 oz/pair men's per Merrell spec</t>
         </is>
       </c>
-      <c r="H81" s="40" t="n">
+      <c r="H81" s="57" t="n">
         <v>100.93</v>
       </c>
       <c r="I81" s="41" t="inlineStr">
@@ -20014,7 +20045,7 @@
           <t>Lone Peak 9</t>
         </is>
       </c>
-      <c r="F82" s="39" t="n">
+      <c r="F82" s="56" t="n">
         <v>22.5</v>
       </c>
       <c r="G82" s="38" t="inlineStr">
@@ -20022,7 +20053,7 @@
           <t>1 lb 6.3 oz/pair men's per REI spec</t>
         </is>
       </c>
-      <c r="H82" s="40" t="n">
+      <c r="H82" s="57" t="n">
         <v>145</v>
       </c>
       <c r="I82" s="41" t="inlineStr">
@@ -20107,7 +20138,7 @@
           <t>Merino Wool Lightweight Hiking Crew (3-pack budget alt)</t>
         </is>
       </c>
-      <c r="F83" s="39" t="n">
+      <c r="F83" s="56" t="n">
         <v>2.5</v>
       </c>
       <c r="G83" s="38" t="inlineStr">
@@ -20115,7 +20146,7 @@
           <t>per pair, typical crew weight</t>
         </is>
       </c>
-      <c r="H83" s="40" t="n">
+      <c r="H83" s="57" t="n">
         <v>8.83</v>
       </c>
       <c r="I83" s="41" t="inlineStr">
@@ -20200,7 +20231,7 @@
           <t>Hiker Micro Crew Midweight with Cushion</t>
         </is>
       </c>
-      <c r="F84" s="39" t="n">
+      <c r="F84" s="56" t="n">
         <v>2.6</v>
       </c>
       <c r="G84" s="38" t="inlineStr">
@@ -20208,7 +20239,7 @@
           <t>per pair</t>
         </is>
       </c>
-      <c r="H84" s="40" t="n">
+      <c r="H84" s="57" t="n">
         <v>25.95</v>
       </c>
       <c r="I84" s="41" t="inlineStr">
@@ -20293,7 +20324,7 @@
           <t>Waterproof All Weather Mid Length Sock</t>
         </is>
       </c>
-      <c r="F85" s="39" t="n">
+      <c r="F85" s="56" t="n">
         <v>3.2</v>
       </c>
       <c r="G85" s="38" t="inlineStr">
@@ -20301,7 +20332,7 @@
           <t>per pair, waterproof membrane sock</t>
         </is>
       </c>
-      <c r="H85" s="40" t="n">
+      <c r="H85" s="57" t="n">
         <v>55</v>
       </c>
       <c r="I85" s="41" t="inlineStr">
@@ -20386,7 +20417,7 @@
           <t>Watertight II Rain Jacket (Men's)</t>
         </is>
       </c>
-      <c r="F86" s="39" t="n">
+      <c r="F86" s="56" t="n">
         <v>12</v>
       </c>
       <c r="G86" s="38" t="inlineStr">
@@ -20394,7 +20425,7 @@
           <t>typical packable Omni-Tech shell weight per Columbia/OGL testing</t>
         </is>
       </c>
-      <c r="H86" s="40" t="n">
+      <c r="H86" s="57" t="n">
         <v>70</v>
       </c>
       <c r="I86" s="41" t="inlineStr">
@@ -20479,7 +20510,7 @@
           <t>Rainier Rain Jacket</t>
         </is>
       </c>
-      <c r="F87" s="39" t="n">
+      <c r="F87" s="56" t="n">
         <v>12.5</v>
       </c>
       <c r="G87" s="38" t="inlineStr">
@@ -20487,7 +20518,7 @@
           <t>approx per REI listing, men's</t>
         </is>
       </c>
-      <c r="H87" s="40" t="n">
+      <c r="H87" s="57" t="n">
         <v>99.95</v>
       </c>
       <c r="I87" s="41" t="inlineStr">
@@ -20572,7 +20603,7 @@
           <t>Helium Rain Jacket</t>
         </is>
       </c>
-      <c r="F88" s="39" t="n">
+      <c r="F88" s="56" t="n">
         <v>6.4</v>
       </c>
       <c r="G88" s="38" t="inlineStr">
@@ -20580,7 +20611,7 @@
           <t>per OR spec, men's</t>
         </is>
       </c>
-      <c r="H88" s="40" t="n">
+      <c r="H88" s="57" t="n">
         <v>199</v>
       </c>
       <c r="I88" s="41" t="inlineStr">
@@ -20661,7 +20692,7 @@
           <t>MT100 Hooded Down Puffer Jacket</t>
         </is>
       </c>
-      <c r="F89" s="39" t="n">
+      <c r="F89" s="56" t="n">
         <v>10.6</v>
       </c>
       <c r="G89" s="38" t="inlineStr">
@@ -20669,7 +20700,7 @@
           <t>packable down jacket, per Decathlon/GearJunkie; rebranded from Forclaz to Simond</t>
         </is>
       </c>
-      <c r="H89" s="40" t="n">
+      <c r="H89" s="57" t="n">
         <v>80</v>
       </c>
       <c r="I89" s="41" t="inlineStr">
@@ -20754,7 +20785,7 @@
           <t>Nano Puff Jacket</t>
         </is>
       </c>
-      <c r="F90" s="39" t="n">
+      <c r="F90" s="56" t="n">
         <v>11.6</v>
       </c>
       <c r="G90" s="38" t="inlineStr">
@@ -20762,7 +20793,7 @@
           <t>per Patagonia spec, men's, synthetic PrimaLoft fill</t>
         </is>
       </c>
-      <c r="H90" s="40" t="n">
+      <c r="H90" s="57" t="n">
         <v>118.99</v>
       </c>
       <c r="I90" s="41" t="inlineStr">
@@ -20847,7 +20878,7 @@
           <t>Torrid APEX Jacket</t>
         </is>
       </c>
-      <c r="F91" s="39" t="n">
+      <c r="F91" s="56" t="n">
         <v>8.9</v>
       </c>
       <c r="G91" s="38" t="inlineStr">
@@ -20855,7 +20886,7 @@
           <t>per Adventure Alan review, synthetic APEX fill</t>
         </is>
       </c>
-      <c r="H91" s="40" t="n">
+      <c r="H91" s="57" t="n">
         <v>170</v>
       </c>
       <c r="I91" s="41" t="inlineStr">
@@ -20940,7 +20971,7 @@
           <t>MH100 Fleece</t>
         </is>
       </c>
-      <c r="F92" s="39" t="n">
+      <c r="F92" s="56" t="n">
         <v>12</v>
       </c>
       <c r="G92" s="38" t="inlineStr">
@@ -20948,7 +20979,7 @@
           <t>typical 100-weight fleece pullover</t>
         </is>
       </c>
-      <c r="H92" s="40" t="n">
+      <c r="H92" s="57" t="n">
         <v>25</v>
       </c>
       <c r="I92" s="41" t="inlineStr">
@@ -21033,7 +21064,7 @@
           <t>Alpha 90 Half-Zip Hoodie</t>
         </is>
       </c>
-      <c r="F93" s="39" t="n">
+      <c r="F93" s="56" t="n">
         <v>4.8</v>
       </c>
       <c r="G93" s="38" t="inlineStr">
@@ -21041,7 +21072,7 @@
           <t>Polartec Alpha Direct, sub-5oz per community reporting</t>
         </is>
       </c>
-      <c r="H93" s="40" t="n">
+      <c r="H93" s="57" t="n">
         <v>115</v>
       </c>
       <c r="I93" s="41" t="inlineStr">
@@ -21126,7 +21157,7 @@
           <t>R1 Air Hoody</t>
         </is>
       </c>
-      <c r="F94" s="39" t="n">
+      <c r="F94" s="56" t="n">
         <v>10.5</v>
       </c>
       <c r="G94" s="38" t="inlineStr">
@@ -21134,7 +21165,7 @@
           <t>per Patagonia spec</t>
         </is>
       </c>
-      <c r="H94" s="40" t="n">
+      <c r="H94" s="57" t="n">
         <v>179</v>
       </c>
       <c r="I94" s="41" t="inlineStr">
@@ -21215,7 +21246,7 @@
           <t>Men's/Women's Long Sleeve Base Layer Set</t>
         </is>
       </c>
-      <c r="F95" s="39" t="n">
+      <c r="F95" s="56" t="n">
         <v>8</v>
       </c>
       <c r="G95" s="38" t="inlineStr">
@@ -21223,7 +21254,7 @@
           <t>top+bottom combined, lightweight merino blend</t>
         </is>
       </c>
-      <c r="H95" s="40" t="n">
+      <c r="H95" s="57" t="n">
         <v>100</v>
       </c>
       <c r="I95" s="41" t="inlineStr">
@@ -21308,7 +21339,7 @@
           <t>Classic Thermal Merino Base Layer (top + bottom)</t>
         </is>
       </c>
-      <c r="F96" s="39" t="n">
+      <c r="F96" s="56" t="n">
         <v>10</v>
       </c>
       <c r="G96" s="38" t="inlineStr">
@@ -21316,7 +21347,7 @@
           <t>combined top+bottom, midweight merino</t>
         </is>
       </c>
-      <c r="H96" s="40" t="n">
+      <c r="H96" s="57" t="n">
         <v>125</v>
       </c>
       <c r="I96" s="41" t="inlineStr">
@@ -21397,7 +21428,7 @@
           <t>200 Oasis (top + bottom)</t>
         </is>
       </c>
-      <c r="F97" s="39" t="n">
+      <c r="F97" s="56" t="n">
         <v>11</v>
       </c>
       <c r="G97" s="38" t="inlineStr">
@@ -21405,7 +21436,7 @@
           <t>200gsm merino jersey, combined top+bottom</t>
         </is>
       </c>
-      <c r="H97" s="40" t="n">
+      <c r="H97" s="57" t="n">
         <v>235</v>
       </c>
       <c r="I97" s="41" t="inlineStr">
@@ -21486,7 +21517,7 @@
           <t>Trailmade Pants</t>
         </is>
       </c>
-      <c r="F98" s="39" t="n">
+      <c r="F98" s="56" t="n">
         <v>11</v>
       </c>
       <c r="G98" s="38" t="inlineStr">
@@ -21494,7 +21525,7 @@
           <t>per REI product listing</t>
         </is>
       </c>
-      <c r="H98" s="40" t="n">
+      <c r="H98" s="57" t="n">
         <v>80</v>
       </c>
       <c r="I98" s="41" t="inlineStr">
@@ -21579,7 +21610,7 @@
           <t>Ferrosi Pants</t>
         </is>
       </c>
-      <c r="F99" s="39" t="n">
+      <c r="F99" s="56" t="n">
         <v>11.4</v>
       </c>
       <c r="G99" s="38" t="inlineStr">
@@ -21587,7 +21618,7 @@
           <t>per OGL/Switchback testing</t>
         </is>
       </c>
-      <c r="H99" s="40" t="n">
+      <c r="H99" s="57" t="n">
         <v>110</v>
       </c>
       <c r="I99" s="41" t="inlineStr">
@@ -21672,7 +21703,7 @@
           <t>Stretch Zion Straight Pants (cargo version discontinued, replaced by current lineup)</t>
         </is>
       </c>
-      <c r="F100" s="39" t="n">
+      <c r="F100" s="56" t="n">
         <v>14</v>
       </c>
       <c r="G100" s="38" t="inlineStr">
@@ -21680,7 +21711,7 @@
           <t>per prAna spec, recycled nylon</t>
         </is>
       </c>
-      <c r="H100" s="40" t="n">
+      <c r="H100" s="57" t="n">
         <v>98</v>
       </c>
       <c r="I100" s="41" t="inlineStr">
@@ -21765,7 +21796,7 @@
           <t>Fleece-lined knit beanie</t>
         </is>
       </c>
-      <c r="F101" s="39" t="n">
+      <c r="F101" s="56" t="n">
         <v>2</v>
       </c>
       <c r="G101" s="38" t="inlineStr">
@@ -21773,7 +21804,7 @@
           <t>typical knit beanie</t>
         </is>
       </c>
-      <c r="H101" s="40" t="n">
+      <c r="H101" s="57" t="n">
         <v>14.99</v>
       </c>
       <c r="I101" s="41" t="inlineStr">
@@ -21854,7 +21885,7 @@
           <t>Alpha Drifter Beanie</t>
         </is>
       </c>
-      <c r="F102" s="39" t="n">
+      <c r="F102" s="56" t="n">
         <v>0.7</v>
       </c>
       <c r="G102" s="38" t="inlineStr">
@@ -21862,7 +21893,7 @@
           <t>Polartec Alpha Direct, sub-1oz per community reporting</t>
         </is>
       </c>
-      <c r="H102" s="40" t="n">
+      <c r="H102" s="57" t="n">
         <v>38</v>
       </c>
       <c r="I102" s="41" t="inlineStr">
@@ -21947,7 +21978,7 @@
           <t>Merino 250 Reversible Cuffed Beanie</t>
         </is>
       </c>
-      <c r="F103" s="39" t="n">
+      <c r="F103" s="56" t="n">
         <v>2.1</v>
       </c>
       <c r="G103" s="38" t="inlineStr">
@@ -21955,7 +21986,7 @@
           <t>per Smartwool spec</t>
         </is>
       </c>
-      <c r="H103" s="40" t="n">
+      <c r="H103" s="57" t="n">
         <v>35</v>
       </c>
       <c r="I103" s="41" t="inlineStr">
@@ -22040,7 +22071,7 @@
           <t>Wool Fleece-Liner Knit Gloves (3-pack)</t>
         </is>
       </c>
-      <c r="F104" s="39" t="n">
+      <c r="F104" s="56" t="n">
         <v>2</v>
       </c>
       <c r="G104" s="38" t="inlineStr">
@@ -22048,7 +22079,7 @@
           <t>typical knit glove pair; sold as a 3-pack for $12.99</t>
         </is>
       </c>
-      <c r="H104" s="40" t="n">
+      <c r="H104" s="57" t="n">
         <v>12.99</v>
       </c>
       <c r="I104" s="41" t="inlineStr">
@@ -22129,7 +22160,7 @@
           <t>PL 400 Gloves</t>
         </is>
       </c>
-      <c r="F105" s="39" t="n">
+      <c r="F105" s="56" t="n">
         <v>2.3</v>
       </c>
       <c r="G105" s="38" t="inlineStr">
@@ -22137,7 +22168,7 @@
           <t>per OR spec, fleece liner glove</t>
         </is>
       </c>
-      <c r="H105" s="40" t="n">
+      <c r="H105" s="57" t="n">
         <v>35</v>
       </c>
       <c r="I105" s="41" t="inlineStr">
@@ -22222,7 +22253,7 @@
           <t>Merino/Possum Blend Gloves (touchscreen)</t>
         </is>
       </c>
-      <c r="F106" s="39" t="n">
+      <c r="F106" s="56" t="n">
         <v>1.5</v>
       </c>
       <c r="G106" s="38" t="inlineStr">
@@ -22230,7 +22261,7 @@
           <t>per community reporting on brushtail possum/merino gloves</t>
         </is>
       </c>
-      <c r="H106" s="40" t="n">
+      <c r="H106" s="57" t="n">
         <v>40</v>
       </c>
       <c r="I106" s="41" t="inlineStr">
@@ -22311,7 +22342,7 @@
           <t>Mesh Safety Vest + Blaze Orange Insulated Beanie</t>
         </is>
       </c>
-      <c r="F107" s="39" t="n">
+      <c r="F107" s="56" t="n">
         <v>6</v>
       </c>
       <c r="G107" s="38" t="inlineStr">
@@ -22319,7 +22350,7 @@
           <t>vest ~4oz + beanie ~2oz combined estimate</t>
         </is>
       </c>
-      <c r="H107" s="40" t="n">
+      <c r="H107" s="57" t="n">
         <v>16.96</v>
       </c>
       <c r="I107" s="41" t="inlineStr">
@@ -22404,7 +22435,7 @@
           <t>Blaze Orange Safety Vest</t>
         </is>
       </c>
-      <c r="F108" s="39" t="n">
+      <c r="F108" s="56" t="n">
         <v>5</v>
       </c>
       <c r="G108" s="38" t="inlineStr">
@@ -22412,7 +22443,7 @@
           <t>per prior sourcing in project gear.md</t>
         </is>
       </c>
-      <c r="H108" s="40" t="n">
+      <c r="H108" s="57" t="n">
         <v>13.51</v>
       </c>
       <c r="I108" s="41" t="inlineStr">
@@ -22497,7 +22528,7 @@
           <t>Blaze Orange Hunting Vest &amp; Hat Combo</t>
         </is>
       </c>
-      <c r="F109" s="39" t="n">
+      <c r="F109" s="56" t="n">
         <v>10</v>
       </c>
       <c r="G109" s="38" t="inlineStr">
@@ -22505,7 +22536,7 @@
           <t>combo vest+hat, estimate based on similar products</t>
         </is>
       </c>
-      <c r="H109" s="40" t="n">
+      <c r="H109" s="57" t="n">
         <v>45</v>
       </c>
       <c r="I109" s="41" t="inlineStr">
@@ -22586,7 +22617,7 @@
           <t>Old sneakers or flip-flops already owned</t>
         </is>
       </c>
-      <c r="F110" s="39" t="n">
+      <c r="F110" s="56" t="n">
         <v>10</v>
       </c>
       <c r="G110" s="38" t="inlineStr">
@@ -22594,7 +22625,7 @@
           <t>varies</t>
         </is>
       </c>
-      <c r="H110" s="40" t="n">
+      <c r="H110" s="57" t="n">
         <v>0</v>
       </c>
       <c r="I110" s="41" t="inlineStr">
@@ -22679,7 +22710,7 @@
           <t>Classic Clog</t>
         </is>
       </c>
-      <c r="F111" s="39" t="n">
+      <c r="F111" s="56" t="n">
         <v>14</v>
       </c>
       <c r="G111" s="38" t="inlineStr">
@@ -22687,7 +22718,7 @@
           <t>per pair, per Bikepacking.com testing</t>
         </is>
       </c>
-      <c r="H111" s="40" t="n">
+      <c r="H111" s="57" t="n">
         <v>50</v>
       </c>
       <c r="I111" s="41" t="inlineStr">
@@ -22768,7 +22799,7 @@
           <t>Cairn Evo Adventure Sandals (current lineup; original Cairn Adventure Sandal discontinued)</t>
         </is>
       </c>
-      <c r="F112" s="39" t="n">
+      <c r="F112" s="56" t="n">
         <v>11</v>
       </c>
       <c r="G112" s="38" t="inlineStr">
@@ -22776,7 +22807,7 @@
           <t>per Bedrock Sandals spec, per pair</t>
         </is>
       </c>
-      <c r="H112" s="40" t="n">
+      <c r="H112" s="57" t="n">
         <v>115</v>
       </c>
       <c r="I112" s="41" t="inlineStr">
@@ -22857,7 +22888,7 @@
           <t>Kenai Original</t>
         </is>
       </c>
-      <c r="F113" s="39" t="n">
+      <c r="F113" s="56" t="n">
         <v>4</v>
       </c>
       <c r="G113" s="38" t="inlineStr">
@@ -22865,7 +22896,7 @@
           <t>per pair, 2mm neoprene glove</t>
         </is>
       </c>
-      <c r="H113" s="40" t="n">
+      <c r="H113" s="57" t="n">
         <v>24.99</v>
       </c>
       <c r="I113" s="41" t="inlineStr">
@@ -22885,7 +22916,7 @@
       </c>
       <c r="L113" s="38" t="inlineStr">
         <is>
-          <t>Captain's pick 2026-09-23: 35-year standard for cold fly-fishing, 2mm fleece-lined neoprene with a sharkskin palm -- chose dexterity (feel the pan, pick gravel) over staying bone-dry.</t>
+          <t>Jordan's pick 2026-09-23: 35-year standard for cold fly-fishing, 2mm fleece-lined neoprene with a sharkskin palm -- chose dexterity (feel the pan, pick gravel) over staying bone-dry.</t>
         </is>
       </c>
       <c r="M113" s="38" t="inlineStr">
@@ -22950,7 +22981,7 @@
           <t>Kenai Original</t>
         </is>
       </c>
-      <c r="F114" s="39" t="n">
+      <c r="F114" s="56" t="n">
         <v>4</v>
       </c>
       <c r="G114" s="38" t="inlineStr">
@@ -22958,7 +22989,7 @@
           <t>per pair, 2mm neoprene glove</t>
         </is>
       </c>
-      <c r="H114" s="40" t="n">
+      <c r="H114" s="57" t="n">
         <v>24.99</v>
       </c>
       <c r="I114" s="41" t="inlineStr">
@@ -22978,7 +23009,7 @@
       </c>
       <c r="L114" s="38" t="inlineStr">
         <is>
-          <t>Captain's pick 2026-09-23: 35-year standard for cold fly-fishing, 2mm fleece-lined neoprene with a sharkskin palm -- chose dexterity (feel the pan, pick gravel) over staying bone-dry.</t>
+          <t>Jordan's pick 2026-09-23: 35-year standard for cold fly-fishing, 2mm fleece-lined neoprene with a sharkskin palm -- chose dexterity (feel the pan, pick gravel) over staying bone-dry.</t>
         </is>
       </c>
       <c r="M114" s="38" t="inlineStr">
@@ -23043,7 +23074,7 @@
           <t>Arctic Gauntlet Gloves for Cold Water Wading</t>
         </is>
       </c>
-      <c r="F115" s="39" t="n">
+      <c r="F115" s="56" t="n">
         <v>9</v>
       </c>
       <c r="G115" s="38" t="inlineStr">
@@ -23051,7 +23082,7 @@
           <t>per pair, lined arm-length gauntlet, estimate</t>
         </is>
       </c>
-      <c r="H115" s="40" t="n">
+      <c r="H115" s="57" t="n">
         <v>50</v>
       </c>
       <c r="I115" s="41" t="inlineStr">
@@ -23132,7 +23163,7 @@
           <t>3mm Knee-High Neoprene Sock</t>
         </is>
       </c>
-      <c r="F116" s="39" t="n">
+      <c r="F116" s="56" t="n">
         <v>6</v>
       </c>
       <c r="G116" s="38" t="inlineStr">
@@ -23140,7 +23171,7 @@
           <t>per pair, per Walmart listing (verified live price)</t>
         </is>
       </c>
-      <c r="H116" s="40" t="n">
+      <c r="H116" s="57" t="n">
         <v>41.59</v>
       </c>
       <c r="I116" s="41" t="inlineStr">
@@ -23225,7 +23256,7 @@
           <t>3mm Neoprene Wading/Water Socks</t>
         </is>
       </c>
-      <c r="F117" s="39" t="n">
+      <c r="F117" s="56" t="n">
         <v>6.5</v>
       </c>
       <c r="G117" s="38" t="inlineStr">
@@ -23233,7 +23264,7 @@
           <t>per pair, typical 3mm dive/water sock (verified live price)</t>
         </is>
       </c>
-      <c r="H117" s="40" t="n">
+      <c r="H117" s="57" t="n">
         <v>30.19</v>
       </c>
       <c r="I117" s="41" t="inlineStr">
@@ -23318,7 +23349,7 @@
           <t>I-Drain Neoprene Guard Socks, 3.5mm</t>
         </is>
       </c>
-      <c r="F118" s="39" t="n">
+      <c r="F118" s="56" t="n">
         <v>7</v>
       </c>
       <c r="G118" s="38" t="inlineStr">
@@ -23326,7 +23357,7 @@
           <t>per pair, per Korkers spec</t>
         </is>
       </c>
-      <c r="H118" s="40" t="n">
+      <c r="H118" s="57" t="n">
         <v>44.99</v>
       </c>
       <c r="I118" s="41" t="inlineStr">
@@ -23407,7 +23438,7 @@
           <t>No waders — neoprene socks + quick-dry pants only</t>
         </is>
       </c>
-      <c r="F119" s="39" t="n">
+      <c r="F119" s="56" t="n">
         <v>0</v>
       </c>
       <c r="G119" s="38" t="inlineStr">
@@ -23415,7 +23446,7 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="H119" s="40" t="n">
+      <c r="H119" s="57" t="n">
         <v>0</v>
       </c>
       <c r="I119" s="41" t="inlineStr">
@@ -23500,7 +23531,7 @@
           <t>Canyon II Stockingfoot Hip Wader, Medium (needs separate wading shoe)</t>
         </is>
       </c>
-      <c r="F120" s="39" t="n">
+      <c r="F120" s="56" t="n">
         <v>20</v>
       </c>
       <c r="G120" s="38" t="inlineStr">
@@ -23508,7 +23539,7 @@
           <t>category estimate, no vendor spec published -- 4-ply nylon, no attached boot</t>
         </is>
       </c>
-      <c r="H120" s="40" t="n">
+      <c r="H120" s="57" t="n">
         <v>98.29000000000001</v>
       </c>
       <c r="I120" s="41" t="inlineStr">
@@ -23593,7 +23624,7 @@
           <t>Tributary Stockingfoot Waders</t>
         </is>
       </c>
-      <c r="F121" s="39" t="n">
+      <c r="F121" s="56" t="n">
         <v>38</v>
       </c>
       <c r="G121" s="38" t="inlineStr">
@@ -23601,7 +23632,7 @@
           <t>per Simms spec, breathable stockingfoot chest wader</t>
         </is>
       </c>
-      <c r="H121" s="40" t="n">
+      <c r="H121" s="57" t="n">
         <v>300</v>
       </c>
       <c r="I121" s="41" t="inlineStr">
@@ -23686,7 +23717,7 @@
           <t>Protective Knee Pads, Thick Sponge Anti-Slip Knee Sleeve</t>
         </is>
       </c>
-      <c r="F122" s="39" t="n">
+      <c r="F122" s="56" t="n">
         <v>6</v>
       </c>
       <c r="G122" s="38" t="inlineStr">
@@ -23694,7 +23725,7 @@
           <t>per pair, strap-on sleeve</t>
         </is>
       </c>
-      <c r="H122" s="40" t="n">
+      <c r="H122" s="57" t="n">
         <v>15.99</v>
       </c>
       <c r="I122" s="41" t="inlineStr">
@@ -23714,7 +23745,7 @@
       </c>
       <c r="L122" s="38" t="inlineStr">
         <is>
-          <t>Captain's pick 2026-09-23, replacing the flat foam gardening pad research flagged as not moving with you on uneven creek rock -- a strap-on sleeve that stays on through repeated kneel/reposition.</t>
+          <t>Jordan's pick 2026-09-23, replacing the flat foam gardening pad research flagged as not moving with you on uneven creek rock -- a strap-on sleeve that stays on through repeated kneel/reposition.</t>
         </is>
       </c>
       <c r="M122" s="38" t="inlineStr">
@@ -23779,7 +23810,7 @@
           <t>Neoprene Strap-On Knee Pads (gardening/volleyball style)</t>
         </is>
       </c>
-      <c r="F123" s="39" t="n">
+      <c r="F123" s="56" t="n">
         <v>8</v>
       </c>
       <c r="G123" s="38" t="inlineStr">
@@ -23787,7 +23818,7 @@
           <t>per pair</t>
         </is>
       </c>
-      <c r="H123" s="40" t="n">
+      <c r="H123" s="57" t="n">
         <v>16</v>
       </c>
       <c r="I123" s="41" t="inlineStr">
@@ -23868,7 +23899,7 @@
           <t>Gel-Cushion Kneeling Pad with adjustable straps</t>
         </is>
       </c>
-      <c r="F124" s="39" t="n">
+      <c r="F124" s="56" t="n">
         <v>14</v>
       </c>
       <c r="G124" s="38" t="inlineStr">
@@ -23876,7 +23907,7 @@
           <t>per pair, gel-insert work knee pad</t>
         </is>
       </c>
-      <c r="H124" s="40" t="n">
+      <c r="H124" s="57" t="n">
         <v>28</v>
       </c>
       <c r="I124" s="41" t="inlineStr">
@@ -23957,7 +23988,7 @@
           <t>BP-14 14" Black Plastic Gold Pan</t>
         </is>
       </c>
-      <c r="F125" s="39" t="n">
+      <c r="F125" s="56" t="n">
         <v>9</v>
       </c>
       <c r="G125" s="38" t="inlineStr">
@@ -23965,7 +23996,7 @@
           <t>per Toolup listing (verified live price)</t>
         </is>
       </c>
-      <c r="H125" s="40" t="n">
+      <c r="H125" s="57" t="n">
         <v>7.26</v>
       </c>
       <c r="I125" s="41" t="inlineStr">
@@ -24050,7 +24081,7 @@
           <t>14" Gravity Trap Gold Pan (green)</t>
         </is>
       </c>
-      <c r="F126" s="39" t="n">
+      <c r="F126" s="56" t="n">
         <v>10</v>
       </c>
       <c r="G126" s="38" t="inlineStr">
@@ -24058,7 +24089,7 @@
           <t>per Garrett product spec</t>
         </is>
       </c>
-      <c r="H126" s="40" t="n">
+      <c r="H126" s="57" t="n">
         <v>8.99</v>
       </c>
       <c r="I126" s="41" t="inlineStr">
@@ -24143,7 +24174,7 @@
           <t>15" Super Sluice Gold Pan (two-stage riffle pan)</t>
         </is>
       </c>
-      <c r="F127" s="39" t="n">
+      <c r="F127" s="56" t="n">
         <v>13</v>
       </c>
       <c r="G127" s="38" t="inlineStr">
@@ -24151,7 +24182,7 @@
           <t>per Garrett/eBay listing</t>
         </is>
       </c>
-      <c r="H127" s="40" t="n">
+      <c r="H127" s="57" t="n">
         <v>25</v>
       </c>
       <c r="I127" s="41" t="inlineStr">
@@ -24236,7 +24267,7 @@
           <t>1/2" Mesh Classifier</t>
         </is>
       </c>
-      <c r="F128" s="39" t="n">
+      <c r="F128" s="56" t="n">
         <v>16</v>
       </c>
       <c r="G128" s="38" t="inlineStr">
@@ -24244,7 +24275,7 @@
           <t>per prior project sourcing (ASR 1/4" model confirmed $28.99, 1/2" comparable)</t>
         </is>
       </c>
-      <c r="H128" s="40" t="n">
+      <c r="H128" s="57" t="n">
         <v>25</v>
       </c>
       <c r="I128" s="41" t="inlineStr">
@@ -24329,7 +24360,7 @@
           <t>Stackable Classifier Set (1/2", 1/4", 1/8")</t>
         </is>
       </c>
-      <c r="F129" s="39" t="n">
+      <c r="F129" s="56" t="n">
         <v>30</v>
       </c>
       <c r="G129" s="38" t="inlineStr">
@@ -24337,7 +24368,7 @@
           <t>3-screen stacked set, estimate</t>
         </is>
       </c>
-      <c r="H129" s="40" t="n">
+      <c r="H129" s="57" t="n">
         <v>75</v>
       </c>
       <c r="I129" s="41" t="inlineStr">
@@ -24422,7 +24453,7 @@
           <t>Stainless Mesh Classifier Set incl. 50-mesh fine screen</t>
         </is>
       </c>
-      <c r="F130" s="39" t="n">
+      <c r="F130" s="56" t="n">
         <v>34</v>
       </c>
       <c r="G130" s="38" t="inlineStr">
@@ -24430,7 +24461,7 @@
           <t>multi-screen stainless set, estimate</t>
         </is>
       </c>
-      <c r="H130" s="40" t="n">
+      <c r="H130" s="57" t="n">
         <v>65</v>
       </c>
       <c r="I130" s="41" t="inlineStr">
@@ -24515,7 +24546,7 @@
           <t>Plastic Snuffer Bottle</t>
         </is>
       </c>
-      <c r="F131" s="39" t="n">
+      <c r="F131" s="56" t="n">
         <v>1.5</v>
       </c>
       <c r="G131" s="38" t="inlineStr">
@@ -24523,7 +24554,7 @@
           <t>typical squeeze snuffer bottle</t>
         </is>
       </c>
-      <c r="H131" s="40" t="n">
+      <c r="H131" s="57" t="n">
         <v>4</v>
       </c>
       <c r="I131" s="41" t="inlineStr">
@@ -24608,7 +24639,7 @@
           <t>2-Pack Glass-Tip Snuffer Bottle with Tweezers</t>
         </is>
       </c>
-      <c r="F132" s="39" t="n">
+      <c r="F132" s="56" t="n">
         <v>2</v>
       </c>
       <c r="G132" s="38" t="inlineStr">
@@ -24616,7 +24647,7 @@
           <t>per pair, bundled with tweezers</t>
         </is>
       </c>
-      <c r="H132" s="40" t="n">
+      <c r="H132" s="57" t="n">
         <v>11.99</v>
       </c>
       <c r="I132" s="41" t="inlineStr">
@@ -24701,7 +24732,7 @@
           <t>Brass-Tip Snuffer Bottle Set</t>
         </is>
       </c>
-      <c r="F133" s="39" t="n">
+      <c r="F133" s="56" t="n">
         <v>2.5</v>
       </c>
       <c r="G133" s="38" t="inlineStr">
@@ -24709,7 +24740,7 @@
           <t>estimate, metal-tip snuffer</t>
         </is>
       </c>
-      <c r="H133" s="40" t="n">
+      <c r="H133" s="57" t="n">
         <v>13</v>
       </c>
       <c r="I133" s="41" t="inlineStr">
@@ -24790,7 +24821,7 @@
           <t>Hook and Pick Precision Crevice Tool Set, 6 Pieces</t>
         </is>
       </c>
-      <c r="F134" s="39" t="n">
+      <c r="F134" s="56" t="n">
         <v>4</v>
       </c>
       <c r="G134" s="38" t="inlineStr">
@@ -24798,7 +24829,7 @@
           <t>per set</t>
         </is>
       </c>
-      <c r="H134" s="40" t="n">
+      <c r="H134" s="57" t="n">
         <v>17.25</v>
       </c>
       <c r="I134" s="41" t="inlineStr">
@@ -24879,7 +24910,7 @@
           <t>Stainless Steel Crevice Tool Set with Magnet</t>
         </is>
       </c>
-      <c r="F135" s="39" t="n">
+      <c r="F135" s="56" t="n">
         <v>6</v>
       </c>
       <c r="G135" s="38" t="inlineStr">
@@ -24887,7 +24918,7 @@
           <t>per set</t>
         </is>
       </c>
-      <c r="H135" s="40" t="n">
+      <c r="H135" s="57" t="n">
         <v>59.95</v>
       </c>
       <c r="I135" s="41" t="inlineStr">
@@ -24972,7 +25003,7 @@
           <t>Branded Crevice Tool Kit</t>
         </is>
       </c>
-      <c r="F136" s="39" t="n">
+      <c r="F136" s="56" t="n">
         <v>8</v>
       </c>
       <c r="G136" s="38" t="inlineStr">
@@ -24980,7 +25011,7 @@
           <t>per set, branded prospecting-tool kit</t>
         </is>
       </c>
-      <c r="H136" s="40" t="n">
+      <c r="H136" s="57" t="n">
         <v>25</v>
       </c>
       <c r="I136" s="41" t="inlineStr">
@@ -25065,7 +25096,7 @@
           <t>Plastic Snap-Cap Vials (5-pack)</t>
         </is>
       </c>
-      <c r="F137" s="39" t="n">
+      <c r="F137" s="56" t="n">
         <v>1</v>
       </c>
       <c r="G137" s="38" t="inlineStr">
@@ -25073,7 +25104,7 @@
           <t>5-pack combined</t>
         </is>
       </c>
-      <c r="H137" s="40" t="n">
+      <c r="H137" s="57" t="n">
         <v>5</v>
       </c>
       <c r="I137" s="41" t="inlineStr">
@@ -25154,7 +25185,7 @@
           <t>Glass Vials with Foam-Lined Screw Caps (12-pack)</t>
         </is>
       </c>
-      <c r="F138" s="39" t="n">
+      <c r="F138" s="56" t="n">
         <v>1.5</v>
       </c>
       <c r="G138" s="38" t="inlineStr">
@@ -25162,7 +25193,7 @@
           <t>price is for the 12-pack, not per vial</t>
         </is>
       </c>
-      <c r="H138" s="40" t="n">
+      <c r="H138" s="57" t="n">
         <v>9.99</v>
       </c>
       <c r="I138" s="41" t="inlineStr">
@@ -25247,7 +25278,7 @@
           <t>Leak-Proof Glass Gold Vials with Measurement Markings</t>
         </is>
       </c>
-      <c r="F139" s="39" t="n">
+      <c r="F139" s="56" t="n">
         <v>2</v>
       </c>
       <c r="G139" s="38" t="inlineStr">
@@ -25255,7 +25286,7 @@
           <t>per vial</t>
         </is>
       </c>
-      <c r="H139" s="40" t="n">
+      <c r="H139" s="57" t="n">
         <v>4</v>
       </c>
       <c r="I139" s="41" t="inlineStr">
@@ -25340,7 +25371,7 @@
           <t>10x Plastic Keychain Loupe</t>
         </is>
       </c>
-      <c r="F140" s="39" t="n">
+      <c r="F140" s="56" t="n">
         <v>1</v>
       </c>
       <c r="G140" s="38" t="inlineStr">
@@ -25348,7 +25379,7 @@
           <t>typical keychain loupe</t>
         </is>
       </c>
-      <c r="H140" s="40" t="n">
+      <c r="H140" s="57" t="n">
         <v>7.99</v>
       </c>
       <c r="I140" s="41" t="inlineStr">
@@ -25433,7 +25464,7 @@
           <t>30x60 Jeweler's Loupe with Built-In LED Light</t>
         </is>
       </c>
-      <c r="F141" s="39" t="n">
+      <c r="F141" s="56" t="n">
         <v>2.5</v>
       </c>
       <c r="G141" s="38" t="inlineStr">
@@ -25441,7 +25472,7 @@
           <t>typical illuminated folding loupe</t>
         </is>
       </c>
-      <c r="H141" s="40" t="n">
+      <c r="H141" s="57" t="n">
         <v>8.98</v>
       </c>
       <c r="I141" s="41" t="inlineStr">
@@ -25522,7 +25553,7 @@
           <t>10x Triplet Achromatic Loupe</t>
         </is>
       </c>
-      <c r="F142" s="39" t="n">
+      <c r="F142" s="56" t="n">
         <v>2</v>
       </c>
       <c r="G142" s="38" t="inlineStr">
@@ -25530,7 +25561,7 @@
           <t>typical premium triplet loupe</t>
         </is>
       </c>
-      <c r="H142" s="40" t="n">
+      <c r="H142" s="57" t="n">
         <v>20</v>
       </c>
       <c r="I142" s="41" t="inlineStr">
@@ -25611,7 +25642,7 @@
           <t>Folding Garden Trowel</t>
         </is>
       </c>
-      <c r="F143" s="39" t="n">
+      <c r="F143" s="56" t="n">
         <v>6</v>
       </c>
       <c r="G143" s="38" t="inlineStr">
@@ -25619,7 +25650,7 @@
           <t>typical small garden trowel</t>
         </is>
       </c>
-      <c r="H143" s="40" t="n">
+      <c r="H143" s="57" t="n">
         <v>6.28</v>
       </c>
       <c r="I143" s="41" t="inlineStr">
@@ -25704,7 +25735,7 @@
           <t>The Deuce of Spades UL Trowel</t>
         </is>
       </c>
-      <c r="F144" s="39" t="n">
+      <c r="F144" s="56" t="n">
         <v>0.6</v>
       </c>
       <c r="G144" s="38" t="inlineStr">
@@ -25712,7 +25743,7 @@
           <t>per TheTentLab spec, titanium</t>
         </is>
       </c>
-      <c r="H144" s="40" t="n">
+      <c r="H144" s="57" t="n">
         <v>20.95</v>
       </c>
       <c r="I144" s="41" t="inlineStr">
@@ -25797,7 +25828,7 @@
           <t>Full-Tang Stainless Prospecting Hand Shovel</t>
         </is>
       </c>
-      <c r="F145" s="39" t="n">
+      <c r="F145" s="56" t="n">
         <v>10</v>
       </c>
       <c r="G145" s="38" t="inlineStr">
@@ -25805,7 +25836,7 @@
           <t>estimate, full-tang stainless prospecting trowel</t>
         </is>
       </c>
-      <c r="H145" s="40" t="n">
+      <c r="H145" s="57" t="n">
         <v>28</v>
       </c>
       <c r="I145" s="41" t="inlineStr">
@@ -25886,7 +25917,7 @@
           <t>Plain 5-Gallon Bucket</t>
         </is>
       </c>
-      <c r="F146" s="39" t="n">
+      <c r="F146" s="56" t="n">
         <v>32</v>
       </c>
       <c r="G146" s="38" t="inlineStr">
@@ -25894,7 +25925,7 @@
           <t>empty bucket estimate</t>
         </is>
       </c>
-      <c r="H146" s="40" t="n">
+      <c r="H146" s="57" t="n">
         <v>5</v>
       </c>
       <c r="I146" s="41" t="inlineStr">
@@ -25979,7 +26010,7 @@
           <t>5-Gallon Bucket with Built-In Classifier Lid</t>
         </is>
       </c>
-      <c r="F147" s="39" t="n">
+      <c r="F147" s="56" t="n">
         <v>40</v>
       </c>
       <c r="G147" s="38" t="inlineStr">
@@ -25987,7 +26018,7 @@
           <t>bucket + mesh classifier lid, estimate</t>
         </is>
       </c>
-      <c r="H147" s="40" t="n">
+      <c r="H147" s="57" t="n">
         <v>28</v>
       </c>
       <c r="I147" s="41" t="inlineStr">
@@ -26068,7 +26099,7 @@
           <t>Bucket Riffle/Classifier Combo Kit</t>
         </is>
       </c>
-      <c r="F148" s="39" t="n">
+      <c r="F148" s="56" t="n">
         <v>48</v>
       </c>
       <c r="G148" s="38" t="inlineStr">
@@ -26076,7 +26107,7 @@
           <t>estimate, full combo kit</t>
         </is>
       </c>
-      <c r="H148" s="40" t="n">
+      <c r="H148" s="57" t="n">
         <v>45</v>
       </c>
       <c r="I148" s="41" t="inlineStr">
@@ -26157,7 +26188,7 @@
           <t>Estwing BP-14 pan + ASR 1/2" classifier + plastic snuffer + 2 vials</t>
         </is>
       </c>
-      <c r="F149" s="39" t="n">
+      <c r="F149" s="56" t="n">
         <v>30</v>
       </c>
       <c r="G149" s="38" t="inlineStr">
@@ -26165,7 +26196,7 @@
           <t>sum of budget-tier components above</t>
         </is>
       </c>
-      <c r="H149" s="40" t="n">
+      <c r="H149" s="57" t="n">
         <v>7.26</v>
       </c>
       <c r="I149" s="41" t="inlineStr">
@@ -26250,7 +26281,7 @@
           <t>Compact Prospecting Kit (pan, 2 classifiers, magnet, magnifier, 3 snuffers, 3 vials) minus sluice</t>
         </is>
       </c>
-      <c r="F150" s="39" t="n">
+      <c r="F150" s="56" t="n">
         <v>38</v>
       </c>
       <c r="G150" s="38" t="inlineStr">
@@ -26258,7 +26289,7 @@
           <t>per typical bundled-kit component list, sluice parts excluded/left home</t>
         </is>
       </c>
-      <c r="H150" s="40" t="n">
+      <c r="H150" s="57" t="n">
         <v>40</v>
       </c>
       <c r="I150" s="41" t="inlineStr">
@@ -26343,7 +26374,7 @@
           <t>Curated kit: Garrett 14" Gravity Trap pan + stainless classifier set + stainless crevice tools + brass snuffer, packed in a dedicated mesh stuff sack</t>
         </is>
       </c>
-      <c r="F151" s="39" t="n">
+      <c r="F151" s="56" t="n">
         <v>52</v>
       </c>
       <c r="G151" s="38" t="inlineStr">
@@ -26351,7 +26382,7 @@
           <t>sum of premium/value-tier components above plus ~2oz mesh sack</t>
         </is>
       </c>
-      <c r="H151" s="40" t="n">
+      <c r="H151" s="57" t="n">
         <v>69.98999999999999</v>
       </c>
       <c r="I151" s="41" t="inlineStr">
@@ -26436,7 +26467,7 @@
           <t>Trestles 30</t>
         </is>
       </c>
-      <c r="F152" s="39" t="n">
+      <c r="F152" s="56" t="n">
         <v>52</v>
       </c>
       <c r="G152" s="38" t="inlineStr">
@@ -26444,7 +26475,7 @@
           <t>Men's Reg listed 1450-1560g (~51-55oz) synthetic fill per REI spec</t>
         </is>
       </c>
-      <c r="H152" s="40" t="n">
+      <c r="H152" s="57" t="n">
         <v>99.95</v>
       </c>
       <c r="I152" s="41" t="inlineStr">
@@ -26529,7 +26560,7 @@
           <t>Revelation 30 (stock, 850fp)</t>
         </is>
       </c>
-      <c r="F153" s="39" t="n">
+      <c r="F153" s="56" t="n">
         <v>19.8</v>
       </c>
       <c r="G153" s="38" t="inlineStr">
@@ -26537,7 +26568,7 @@
           <t>Reg/Reg stock 850fp ~19.8oz per EE/retailer specs; all 30F+ quilts now include a draft collar</t>
         </is>
       </c>
-      <c r="H153" s="40" t="n">
+      <c r="H153" s="57" t="n">
         <v>365</v>
       </c>
       <c r="I153" s="41" t="inlineStr">
@@ -26622,7 +26653,7 @@
           <t>Flex 30</t>
         </is>
       </c>
-      <c r="F154" s="39" t="n">
+      <c r="F154" s="56" t="n">
         <v>20.3</v>
       </c>
       <c r="G154" s="38" t="inlineStr">
@@ -26630,7 +26661,7 @@
           <t>~575g (20.3oz) regular, 900fp water-resistant down, per Katabatic/retailer specs</t>
         </is>
       </c>
-      <c r="H154" s="40" t="n">
+      <c r="H154" s="57" t="n">
         <v>365</v>
       </c>
       <c r="I154" s="41" t="inlineStr">
@@ -26925,7 +26956,7 @@
       <c r="C2" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="13" t="n">
+      <c r="D2" s="46" t="n">
         <v>79.98999999999999</v>
       </c>
       <c r="E2" s="10" t="inlineStr"/>
@@ -26949,7 +26980,7 @@
       <c r="C3" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="D3" s="13" t="n">
+      <c r="D3" s="46" t="n">
         <v>36</v>
       </c>
       <c r="E3" s="10" t="inlineStr"/>
@@ -26973,7 +27004,7 @@
       <c r="C4" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="13" t="n">
+      <c r="D4" s="46" t="n">
         <v>40</v>
       </c>
       <c r="E4" s="10" t="inlineStr"/>
@@ -26997,7 +27028,7 @@
       <c r="C5" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="13" t="n">
+      <c r="D5" s="46" t="n">
         <v>130</v>
       </c>
       <c r="E5" s="10" t="inlineStr"/>
@@ -27021,7 +27052,7 @@
       <c r="C6" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="46" t="n">
         <v>34</v>
       </c>
       <c r="E6" s="10" t="inlineStr"/>
@@ -27045,7 +27076,7 @@
       <c r="C7" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="46" t="n">
         <v>15</v>
       </c>
       <c r="E7" s="10" t="inlineStr"/>
@@ -27069,7 +27100,7 @@
       <c r="C8" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="46" t="n">
         <v>40</v>
       </c>
       <c r="E8" s="10" t="inlineStr"/>
@@ -27093,7 +27124,7 @@
       <c r="C9" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="46" t="n">
         <v>80</v>
       </c>
       <c r="E9" s="10" t="inlineStr"/>
@@ -27117,7 +27148,7 @@
       <c r="C10" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="46" t="n">
         <v>40</v>
       </c>
       <c r="E10" s="10" t="inlineStr"/>
@@ -27141,7 +27172,7 @@
       <c r="C11" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="D11" s="46" t="n">
         <v>47</v>
       </c>
       <c r="E11" s="10" t="inlineStr"/>
@@ -27165,7 +27196,7 @@
       <c r="C12" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="46" t="n">
         <v>54</v>
       </c>
       <c r="E12" s="10" t="inlineStr"/>
@@ -27189,7 +27220,7 @@
       <c r="C13" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D13" s="46" t="n">
         <v>50</v>
       </c>
       <c r="E13" s="10" t="inlineStr"/>
@@ -27213,7 +27244,7 @@
       <c r="C14" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="D14" s="46" t="n">
         <v>15</v>
       </c>
       <c r="E14" s="10" t="inlineStr"/>
@@ -27237,7 +27268,7 @@
       <c r="C15" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="n">
+      <c r="D15" s="46" t="n">
         <v>76</v>
       </c>
       <c r="E15" s="10" t="inlineStr"/>
@@ -27261,7 +27292,7 @@
       <c r="C16" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="46" t="n">
         <v>55</v>
       </c>
       <c r="E16" s="10" t="inlineStr"/>
@@ -27285,7 +27316,7 @@
       <c r="C17" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="13" t="n">
+      <c r="D17" s="46" t="n">
         <v>10</v>
       </c>
       <c r="E17" s="10" t="inlineStr"/>
@@ -27309,7 +27340,7 @@
       <c r="C18" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="D18" s="13" t="n">
+      <c r="D18" s="46" t="n">
         <v>58</v>
       </c>
       <c r="E18" s="10" t="inlineStr"/>
@@ -27333,7 +27364,7 @@
       <c r="C19" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="13" t="n">
+      <c r="D19" s="46" t="n">
         <v>15</v>
       </c>
       <c r="E19" s="10" t="inlineStr"/>
@@ -27357,7 +27388,7 @@
       <c r="C20" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="D20" s="13" t="n">
+      <c r="D20" s="46" t="n">
         <v>24</v>
       </c>
       <c r="E20" s="10" t="inlineStr"/>
@@ -27381,7 +27412,7 @@
       <c r="C21" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="D21" s="13" t="n">
+      <c r="D21" s="46" t="n">
         <v>18</v>
       </c>
       <c r="E21" s="10" t="inlineStr"/>
@@ -27405,7 +27436,7 @@
       <c r="C22" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="13" t="n">
+      <c r="D22" s="46" t="n">
         <v>8</v>
       </c>
       <c r="E22" s="10" t="inlineStr"/>
@@ -27429,7 +27460,7 @@
       <c r="C23" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="13" t="n">
+      <c r="D23" s="46" t="n">
         <v>12</v>
       </c>
       <c r="E23" s="10" t="inlineStr"/>
@@ -27453,7 +27484,7 @@
       <c r="C24" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="13" t="n">
+      <c r="D24" s="46" t="n">
         <v>65</v>
       </c>
       <c r="E24" s="10" t="inlineStr"/>
@@ -27477,7 +27508,7 @@
       <c r="C25" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="13" t="n">
+      <c r="D25" s="46" t="n">
         <v>20</v>
       </c>
       <c r="E25" s="10" t="inlineStr"/>
@@ -27495,13 +27526,14 @@
         </is>
       </c>
       <c r="C26" s="42" t="n"/>
-      <c r="D26" s="16">
+      <c r="D26" s="48">
         <f>SUM(D2:D25)</f>
         <v/>
       </c>
       <c r="E26" s="42" t="n"/>
       <c r="F26" s="42" t="n"/>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="B28" s="43" t="inlineStr">
         <is>
@@ -27554,6 +27586,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>

--- a/Gear_Picker.xlsx
+++ b/Gear_Picker.xlsx
@@ -28,10 +28,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="0.00&quot; lb&quot;"/>
-    <numFmt numFmtId="167" formatCode="0.0&quot; oz&quot;"/>
+    <numFmt numFmtId="164" formatCode="0.0&quot; oz&quot;"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="0.00&quot; lb&quot;"/>
   </numFmts>
   <fonts count="19">
     <font>
@@ -191,7 +191,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -211,26 +211,26 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="11" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="11" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="9" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="9" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -239,10 +239,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -257,10 +257,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -270,30 +270,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="11" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="9" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -460,6 +436,7 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -557,6 +534,7 @@
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="11"/>
   <chart>
     <title>
       <tx>
@@ -990,14 +968,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="B2:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -1012,7 +989,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -1153,7 +1129,6 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
     <row r="26">
       <c r="B26" s="5" t="inlineStr">
         <is>
@@ -1353,7 +1328,7 @@
         <f>IF($E2="Own",N($J2),IF(OR($E2="Skip",$E2=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F2)/INDEX(Options!$R$2:$R$174,$F2),0)))</f>
         <v/>
       </c>
-      <c r="I2" s="46">
+      <c r="I2" s="13">
         <f>IF($E2="Own",0,IF(OR($E2="Skip",$E2=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F2)/INDEX(Options!$R$2:$R$174,$F2),0)))</f>
         <v/>
       </c>
@@ -1433,7 +1408,7 @@
         <f>IF($E3="Own",N($J3),IF(OR($E3="Skip",$E3=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F3)/INDEX(Options!$R$2:$R$174,$F3),0)))</f>
         <v/>
       </c>
-      <c r="I3" s="46">
+      <c r="I3" s="13">
         <f>IF($E3="Own",0,IF(OR($E3="Skip",$E3=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F3)/INDEX(Options!$R$2:$R$174,$F3),0)))</f>
         <v/>
       </c>
@@ -1513,7 +1488,7 @@
         <f>IF($E4="Own",N($J4),IF(OR($E4="Skip",$E4=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F4)/INDEX(Options!$R$2:$R$174,$F4),0)))</f>
         <v/>
       </c>
-      <c r="I4" s="46">
+      <c r="I4" s="13">
         <f>IF($E4="Own",0,IF(OR($E4="Skip",$E4=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F4)/INDEX(Options!$R$2:$R$174,$F4),0)))</f>
         <v/>
       </c>
@@ -1593,7 +1568,7 @@
         <f>IF($E5="Own",N($J5),IF(OR($E5="Skip",$E5=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F5)/INDEX(Options!$R$2:$R$174,$F5),0)))</f>
         <v/>
       </c>
-      <c r="I5" s="46">
+      <c r="I5" s="13">
         <f>IF($E5="Own",0,IF(OR($E5="Skip",$E5=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F5)/INDEX(Options!$R$2:$R$174,$F5),0)))</f>
         <v/>
       </c>
@@ -1673,7 +1648,7 @@
         <f>IF($E6="Own",N($J6),IF(OR($E6="Skip",$E6=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F6)/INDEX(Options!$R$2:$R$174,$F6),0)))</f>
         <v/>
       </c>
-      <c r="I6" s="46">
+      <c r="I6" s="13">
         <f>IF($E6="Own",0,IF(OR($E6="Skip",$E6=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F6)/INDEX(Options!$R$2:$R$174,$F6),0)))</f>
         <v/>
       </c>
@@ -1753,7 +1728,7 @@
         <f>IF($E7="Own",N($J7),IF(OR($E7="Skip",$E7=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F7)/INDEX(Options!$R$2:$R$174,$F7),0)))</f>
         <v/>
       </c>
-      <c r="I7" s="46">
+      <c r="I7" s="13">
         <f>IF($E7="Own",0,IF(OR($E7="Skip",$E7=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F7)/INDEX(Options!$R$2:$R$174,$F7),0)))</f>
         <v/>
       </c>
@@ -1833,7 +1808,7 @@
         <f>IF($E8="Own",N($J8),IF(OR($E8="Skip",$E8=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F8)/INDEX(Options!$R$2:$R$174,$F8),0)))</f>
         <v/>
       </c>
-      <c r="I8" s="46">
+      <c r="I8" s="13">
         <f>IF($E8="Own",0,IF(OR($E8="Skip",$E8=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F8)/INDEX(Options!$R$2:$R$174,$F8),0)))</f>
         <v/>
       </c>
@@ -1913,7 +1888,7 @@
         <f>IF($E9="Own",N($J9),IF(OR($E9="Skip",$E9=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F9)/INDEX(Options!$R$2:$R$174,$F9),0)))</f>
         <v/>
       </c>
-      <c r="I9" s="46">
+      <c r="I9" s="13">
         <f>IF($E9="Own",0,IF(OR($E9="Skip",$E9=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F9)/INDEX(Options!$R$2:$R$174,$F9),0)))</f>
         <v/>
       </c>
@@ -1993,7 +1968,7 @@
         <f>IF($E10="Own",N($J10),IF(OR($E10="Skip",$E10=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F10)/INDEX(Options!$R$2:$R$174,$F10),0)))</f>
         <v/>
       </c>
-      <c r="I10" s="46">
+      <c r="I10" s="13">
         <f>IF($E10="Own",0,IF(OR($E10="Skip",$E10=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F10)/INDEX(Options!$R$2:$R$174,$F10),0)))</f>
         <v/>
       </c>
@@ -2067,7 +2042,7 @@
         <f>IF($E11="Own",N($J11),IF(OR($E11="Skip",$E11=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F11)/INDEX(Options!$R$2:$R$174,$F11),0)))</f>
         <v/>
       </c>
-      <c r="I11" s="46">
+      <c r="I11" s="13">
         <f>IF($E11="Own",0,IF(OR($E11="Skip",$E11=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F11)/INDEX(Options!$R$2:$R$174,$F11),0)))</f>
         <v/>
       </c>
@@ -2147,7 +2122,7 @@
         <f>IF($E12="Own",N($J12),IF(OR($E12="Skip",$E12=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F12)/INDEX(Options!$R$2:$R$174,$F12),0)))</f>
         <v/>
       </c>
-      <c r="I12" s="46">
+      <c r="I12" s="13">
         <f>IF($E12="Own",0,IF(OR($E12="Skip",$E12=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F12)/INDEX(Options!$R$2:$R$174,$F12),0)))</f>
         <v/>
       </c>
@@ -2227,7 +2202,7 @@
         <f>IF($E13="Own",N($J13),IF(OR($E13="Skip",$E13=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F13)/INDEX(Options!$R$2:$R$174,$F13),0)))</f>
         <v/>
       </c>
-      <c r="I13" s="46">
+      <c r="I13" s="13">
         <f>IF($E13="Own",0,IF(OR($E13="Skip",$E13=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F13)/INDEX(Options!$R$2:$R$174,$F13),0)))</f>
         <v/>
       </c>
@@ -2307,7 +2282,7 @@
         <f>IF($E14="Own",N($J14),IF(OR($E14="Skip",$E14=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F14)/INDEX(Options!$R$2:$R$174,$F14),0)))</f>
         <v/>
       </c>
-      <c r="I14" s="46">
+      <c r="I14" s="13">
         <f>IF($E14="Own",0,IF(OR($E14="Skip",$E14=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F14)/INDEX(Options!$R$2:$R$174,$F14),0)))</f>
         <v/>
       </c>
@@ -2387,7 +2362,7 @@
         <f>IF($E15="Own",N($J15),IF(OR($E15="Skip",$E15=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F15)/INDEX(Options!$R$2:$R$174,$F15),0)))</f>
         <v/>
       </c>
-      <c r="I15" s="46">
+      <c r="I15" s="13">
         <f>IF($E15="Own",0,IF(OR($E15="Skip",$E15=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F15)/INDEX(Options!$R$2:$R$174,$F15),0)))</f>
         <v/>
       </c>
@@ -2467,7 +2442,7 @@
         <f>IF($E16="Own",N($J16),IF(OR($E16="Skip",$E16=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F16)/INDEX(Options!$R$2:$R$174,$F16),0)))</f>
         <v/>
       </c>
-      <c r="I16" s="46">
+      <c r="I16" s="13">
         <f>IF($E16="Own",0,IF(OR($E16="Skip",$E16=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F16)/INDEX(Options!$R$2:$R$174,$F16),0)))</f>
         <v/>
       </c>
@@ -2547,7 +2522,7 @@
         <f>IF($E17="Own",N($J17),IF(OR($E17="Skip",$E17=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F17)/INDEX(Options!$R$2:$R$174,$F17),0)))</f>
         <v/>
       </c>
-      <c r="I17" s="46">
+      <c r="I17" s="13">
         <f>IF($E17="Own",0,IF(OR($E17="Skip",$E17=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F17)/INDEX(Options!$R$2:$R$174,$F17),0)))</f>
         <v/>
       </c>
@@ -2627,7 +2602,7 @@
         <f>IF($E18="Own",N($J18),IF(OR($E18="Skip",$E18=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F18)/INDEX(Options!$R$2:$R$174,$F18),0)))</f>
         <v/>
       </c>
-      <c r="I18" s="46">
+      <c r="I18" s="13">
         <f>IF($E18="Own",0,IF(OR($E18="Skip",$E18=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F18)/INDEX(Options!$R$2:$R$174,$F18),0)))</f>
         <v/>
       </c>
@@ -2707,7 +2682,7 @@
         <f>IF($E19="Own",N($J19),IF(OR($E19="Skip",$E19=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F19)/INDEX(Options!$R$2:$R$174,$F19),0)))</f>
         <v/>
       </c>
-      <c r="I19" s="46">
+      <c r="I19" s="13">
         <f>IF($E19="Own",0,IF(OR($E19="Skip",$E19=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F19)/INDEX(Options!$R$2:$R$174,$F19),0)))</f>
         <v/>
       </c>
@@ -2787,7 +2762,7 @@
         <f>IF($E20="Own",N($J20),IF(OR($E20="Skip",$E20=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F20)/INDEX(Options!$R$2:$R$174,$F20),0)))</f>
         <v/>
       </c>
-      <c r="I20" s="46">
+      <c r="I20" s="13">
         <f>IF($E20="Own",0,IF(OR($E20="Skip",$E20=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F20)/INDEX(Options!$R$2:$R$174,$F20),0)))</f>
         <v/>
       </c>
@@ -2867,7 +2842,7 @@
         <f>IF($E21="Own",N($J21),IF(OR($E21="Skip",$E21=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F21)/INDEX(Options!$R$2:$R$174,$F21),0)))</f>
         <v/>
       </c>
-      <c r="I21" s="46">
+      <c r="I21" s="13">
         <f>IF($E21="Own",0,IF(OR($E21="Skip",$E21=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F21)/INDEX(Options!$R$2:$R$174,$F21),0)))</f>
         <v/>
       </c>
@@ -2947,7 +2922,7 @@
         <f>IF($E22="Own",N($J22),IF(OR($E22="Skip",$E22=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F22)/INDEX(Options!$R$2:$R$174,$F22),0)))</f>
         <v/>
       </c>
-      <c r="I22" s="46">
+      <c r="I22" s="13">
         <f>IF($E22="Own",0,IF(OR($E22="Skip",$E22=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F22)/INDEX(Options!$R$2:$R$174,$F22),0)))</f>
         <v/>
       </c>
@@ -3027,7 +3002,7 @@
         <f>IF($E23="Own",N($J23),IF(OR($E23="Skip",$E23=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F23)/INDEX(Options!$R$2:$R$174,$F23),0)))</f>
         <v/>
       </c>
-      <c r="I23" s="46">
+      <c r="I23" s="13">
         <f>IF($E23="Own",0,IF(OR($E23="Skip",$E23=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F23)/INDEX(Options!$R$2:$R$174,$F23),0)))</f>
         <v/>
       </c>
@@ -3107,7 +3082,7 @@
         <f>IF($E24="Own",N($J24),IF(OR($E24="Skip",$E24=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F24)/INDEX(Options!$R$2:$R$174,$F24),0)))</f>
         <v/>
       </c>
-      <c r="I24" s="46">
+      <c r="I24" s="13">
         <f>IF($E24="Own",0,IF(OR($E24="Skip",$E24=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F24)/INDEX(Options!$R$2:$R$174,$F24),0)))</f>
         <v/>
       </c>
@@ -3187,7 +3162,7 @@
         <f>IF($E25="Own",N($J25),IF(OR($E25="Skip",$E25=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F25)/INDEX(Options!$R$2:$R$174,$F25),0)))</f>
         <v/>
       </c>
-      <c r="I25" s="46">
+      <c r="I25" s="13">
         <f>IF($E25="Own",0,IF(OR($E25="Skip",$E25=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F25)/INDEX(Options!$R$2:$R$174,$F25),0)))</f>
         <v/>
       </c>
@@ -3267,7 +3242,7 @@
         <f>IF($E26="Own",N($J26),IF(OR($E26="Skip",$E26=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F26)/INDEX(Options!$R$2:$R$174,$F26),0)))</f>
         <v/>
       </c>
-      <c r="I26" s="46">
+      <c r="I26" s="13">
         <f>IF($E26="Own",0,IF(OR($E26="Skip",$E26=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F26)/INDEX(Options!$R$2:$R$174,$F26),0)))</f>
         <v/>
       </c>
@@ -3347,7 +3322,7 @@
         <f>IF($E27="Own",N($J27),IF(OR($E27="Skip",$E27=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F27)/INDEX(Options!$R$2:$R$174,$F27),0)))</f>
         <v/>
       </c>
-      <c r="I27" s="46">
+      <c r="I27" s="13">
         <f>IF($E27="Own",0,IF(OR($E27="Skip",$E27=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F27)/INDEX(Options!$R$2:$R$174,$F27),0)))</f>
         <v/>
       </c>
@@ -3427,7 +3402,7 @@
         <f>IF($E28="Own",N($J28),IF(OR($E28="Skip",$E28=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F28)/INDEX(Options!$R$2:$R$174,$F28),0)))</f>
         <v/>
       </c>
-      <c r="I28" s="46">
+      <c r="I28" s="13">
         <f>IF($E28="Own",0,IF(OR($E28="Skip",$E28=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F28)/INDEX(Options!$R$2:$R$174,$F28),0)))</f>
         <v/>
       </c>
@@ -3507,7 +3482,7 @@
         <f>IF($E29="Own",N($J29),IF(OR($E29="Skip",$E29=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F29)/INDEX(Options!$R$2:$R$174,$F29),0)))</f>
         <v/>
       </c>
-      <c r="I29" s="46">
+      <c r="I29" s="13">
         <f>IF($E29="Own",0,IF(OR($E29="Skip",$E29=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F29)/INDEX(Options!$R$2:$R$174,$F29),0)))</f>
         <v/>
       </c>
@@ -3587,7 +3562,7 @@
         <f>IF($E30="Own",N($J30),IF(OR($E30="Skip",$E30=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F30)/INDEX(Options!$R$2:$R$174,$F30),0)))</f>
         <v/>
       </c>
-      <c r="I30" s="46">
+      <c r="I30" s="13">
         <f>IF($E30="Own",0,IF(OR($E30="Skip",$E30=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F30)/INDEX(Options!$R$2:$R$174,$F30),0)))</f>
         <v/>
       </c>
@@ -3667,7 +3642,7 @@
         <f>IF($E31="Own",N($J31),IF(OR($E31="Skip",$E31=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F31)/INDEX(Options!$R$2:$R$174,$F31),0)))</f>
         <v/>
       </c>
-      <c r="I31" s="46">
+      <c r="I31" s="13">
         <f>IF($E31="Own",0,IF(OR($E31="Skip",$E31=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F31)/INDEX(Options!$R$2:$R$174,$F31),0)))</f>
         <v/>
       </c>
@@ -3747,7 +3722,7 @@
         <f>IF($E32="Own",N($J32),IF(OR($E32="Skip",$E32=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F32)/INDEX(Options!$R$2:$R$174,$F32),0)))</f>
         <v/>
       </c>
-      <c r="I32" s="46">
+      <c r="I32" s="13">
         <f>IF($E32="Own",0,IF(OR($E32="Skip",$E32=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F32)/INDEX(Options!$R$2:$R$174,$F32),0)))</f>
         <v/>
       </c>
@@ -3827,7 +3802,7 @@
         <f>IF($E33="Own",N($J33),IF(OR($E33="Skip",$E33=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F33)/INDEX(Options!$R$2:$R$174,$F33),0)))</f>
         <v/>
       </c>
-      <c r="I33" s="46">
+      <c r="I33" s="13">
         <f>IF($E33="Own",0,IF(OR($E33="Skip",$E33=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F33)/INDEX(Options!$R$2:$R$174,$F33),0)))</f>
         <v/>
       </c>
@@ -3907,7 +3882,7 @@
         <f>IF($E34="Own",N($J34),IF(OR($E34="Skip",$E34=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F34)/INDEX(Options!$R$2:$R$174,$F34),0)))</f>
         <v/>
       </c>
-      <c r="I34" s="46">
+      <c r="I34" s="13">
         <f>IF($E34="Own",0,IF(OR($E34="Skip",$E34=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F34)/INDEX(Options!$R$2:$R$174,$F34),0)))</f>
         <v/>
       </c>
@@ -3957,7 +3932,7 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>Cathole trowel (shared, split 6)</t>
+          <t>Cathole trowel (shared)</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
@@ -3987,7 +3962,7 @@
         <f>IF($E35="Own",N($J35),IF(OR($E35="Skip",$E35=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F35)/INDEX(Options!$R$2:$R$174,$F35),0)))</f>
         <v/>
       </c>
-      <c r="I35" s="46">
+      <c r="I35" s="13">
         <f>IF($E35="Own",0,IF(OR($E35="Skip",$E35=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F35)/INDEX(Options!$R$2:$R$174,$F35),0)))</f>
         <v/>
       </c>
@@ -4067,7 +4042,7 @@
         <f>IF($E36="Own",N($J36),IF(OR($E36="Skip",$E36=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F36)/INDEX(Options!$R$2:$R$174,$F36),0)))</f>
         <v/>
       </c>
-      <c r="I36" s="46">
+      <c r="I36" s="13">
         <f>IF($E36="Own",0,IF(OR($E36="Skip",$E36=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F36)/INDEX(Options!$R$2:$R$174,$F36),0)))</f>
         <v/>
       </c>
@@ -4147,7 +4122,7 @@
         <f>IF($E37="Own",N($J37),IF(OR($E37="Skip",$E37=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F37)/INDEX(Options!$R$2:$R$174,$F37),0)))</f>
         <v/>
       </c>
-      <c r="I37" s="46">
+      <c r="I37" s="13">
         <f>IF($E37="Own",0,IF(OR($E37="Skip",$E37=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F37)/INDEX(Options!$R$2:$R$174,$F37),0)))</f>
         <v/>
       </c>
@@ -4227,7 +4202,7 @@
         <f>IF($E38="Own",N($J38),IF(OR($E38="Skip",$E38=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F38)/INDEX(Options!$R$2:$R$174,$F38),0)))</f>
         <v/>
       </c>
-      <c r="I38" s="46">
+      <c r="I38" s="13">
         <f>IF($E38="Own",0,IF(OR($E38="Skip",$E38=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F38)/INDEX(Options!$R$2:$R$174,$F38),0)))</f>
         <v/>
       </c>
@@ -4307,7 +4282,7 @@
         <f>IF($E39="Own",N($J39),IF(OR($E39="Skip",$E39=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F39)/INDEX(Options!$R$2:$R$174,$F39),0)))</f>
         <v/>
       </c>
-      <c r="I39" s="46">
+      <c r="I39" s="13">
         <f>IF($E39="Own",0,IF(OR($E39="Skip",$E39=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F39)/INDEX(Options!$R$2:$R$174,$F39),0)))</f>
         <v/>
       </c>
@@ -4387,7 +4362,7 @@
         <f>IF($E40="Own",N($J40),IF(OR($E40="Skip",$E40=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F40)/INDEX(Options!$R$2:$R$174,$F40),0)))</f>
         <v/>
       </c>
-      <c r="I40" s="46">
+      <c r="I40" s="13">
         <f>IF($E40="Own",0,IF(OR($E40="Skip",$E40=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F40)/INDEX(Options!$R$2:$R$174,$F40),0)))</f>
         <v/>
       </c>
@@ -4467,7 +4442,7 @@
         <f>IF($E41="Own",N($J41),IF(OR($E41="Skip",$E41=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F41)/INDEX(Options!$R$2:$R$174,$F41),0)))</f>
         <v/>
       </c>
-      <c r="I41" s="46">
+      <c r="I41" s="13">
         <f>IF($E41="Own",0,IF(OR($E41="Skip",$E41=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F41)/INDEX(Options!$R$2:$R$174,$F41),0)))</f>
         <v/>
       </c>
@@ -4547,7 +4522,7 @@
         <f>IF($E42="Own",N($J42),IF(OR($E42="Skip",$E42=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F42)/INDEX(Options!$R$2:$R$174,$F42),0)))</f>
         <v/>
       </c>
-      <c r="I42" s="46">
+      <c r="I42" s="13">
         <f>IF($E42="Own",0,IF(OR($E42="Skip",$E42=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F42)/INDEX(Options!$R$2:$R$174,$F42),0)))</f>
         <v/>
       </c>
@@ -4627,7 +4602,7 @@
         <f>IF($E43="Own",N($J43),IF(OR($E43="Skip",$E43=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F43)/INDEX(Options!$R$2:$R$174,$F43),0)))</f>
         <v/>
       </c>
-      <c r="I43" s="46">
+      <c r="I43" s="13">
         <f>IF($E43="Own",0,IF(OR($E43="Skip",$E43=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F43)/INDEX(Options!$R$2:$R$174,$F43),0)))</f>
         <v/>
       </c>
@@ -4707,7 +4682,7 @@
         <f>IF($E44="Own",N($J44),IF(OR($E44="Skip",$E44=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F44)/INDEX(Options!$R$2:$R$174,$F44),0)))</f>
         <v/>
       </c>
-      <c r="I44" s="46">
+      <c r="I44" s="13">
         <f>IF($E44="Own",0,IF(OR($E44="Skip",$E44=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F44)/INDEX(Options!$R$2:$R$174,$F44),0)))</f>
         <v/>
       </c>
@@ -4787,7 +4762,7 @@
         <f>IF($E45="Own",N($J45),IF(OR($E45="Skip",$E45=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F45)/INDEX(Options!$R$2:$R$174,$F45),0)))</f>
         <v/>
       </c>
-      <c r="I45" s="46">
+      <c r="I45" s="13">
         <f>IF($E45="Own",0,IF(OR($E45="Skip",$E45=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F45)/INDEX(Options!$R$2:$R$174,$F45),0)))</f>
         <v/>
       </c>
@@ -4867,7 +4842,7 @@
         <f>IF($E46="Own",N($J46),IF(OR($E46="Skip",$E46=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F46)/INDEX(Options!$R$2:$R$174,$F46),0)))</f>
         <v/>
       </c>
-      <c r="I46" s="46">
+      <c r="I46" s="13">
         <f>IF($E46="Own",0,IF(OR($E46="Skip",$E46=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F46)/INDEX(Options!$R$2:$R$174,$F46),0)))</f>
         <v/>
       </c>
@@ -4947,7 +4922,7 @@
         <f>IF($E47="Own",N($J47),IF(OR($E47="Skip",$E47=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F47)/INDEX(Options!$R$2:$R$174,$F47),0)))</f>
         <v/>
       </c>
-      <c r="I47" s="46">
+      <c r="I47" s="13">
         <f>IF($E47="Own",0,IF(OR($E47="Skip",$E47=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F47)/INDEX(Options!$R$2:$R$174,$F47),0)))</f>
         <v/>
       </c>
@@ -5027,7 +5002,7 @@
         <f>IF($E48="Own",N($J48),IF(OR($E48="Skip",$E48=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F48)/INDEX(Options!$R$2:$R$174,$F48),0)))</f>
         <v/>
       </c>
-      <c r="I48" s="46">
+      <c r="I48" s="13">
         <f>IF($E48="Own",0,IF(OR($E48="Skip",$E48=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F48)/INDEX(Options!$R$2:$R$174,$F48),0)))</f>
         <v/>
       </c>
@@ -5107,7 +5082,7 @@
         <f>IF($E49="Own",N($J49),IF(OR($E49="Skip",$E49=""),0,IFERROR(INDEX(Options!$F$2:$F$174,$F49)/INDEX(Options!$R$2:$R$174,$F49),0)))</f>
         <v/>
       </c>
-      <c r="I49" s="46">
+      <c r="I49" s="13">
         <f>IF($E49="Own",0,IF(OR($E49="Skip",$E49=""),0,IFERROR(INDEX(Options!$H$2:$H$174,$F49)/INDEX(Options!$R$2:$R$174,$F49),0)))</f>
         <v/>
       </c>
@@ -5161,11 +5136,11 @@
       <c r="E50" s="14" t="n"/>
       <c r="F50" s="14" t="n"/>
       <c r="G50" s="14" t="n"/>
-      <c r="H50" s="47">
+      <c r="H50" s="15">
         <f>SUM(H2:H7)</f>
         <v/>
       </c>
-      <c r="I50" s="48">
+      <c r="I50" s="16">
         <f>SUM(I2:I7)</f>
         <v/>
       </c>
@@ -5186,11 +5161,11 @@
       <c r="E51" s="14" t="n"/>
       <c r="F51" s="14" t="n"/>
       <c r="G51" s="14" t="n"/>
-      <c r="H51" s="47">
+      <c r="H51" s="15">
         <f>SUM(H8:H35)</f>
         <v/>
       </c>
-      <c r="I51" s="48">
+      <c r="I51" s="16">
         <f>SUM(I8:I35)</f>
         <v/>
       </c>
@@ -5211,11 +5186,11 @@
       <c r="E52" s="14" t="n"/>
       <c r="F52" s="14" t="n"/>
       <c r="G52" s="14" t="n"/>
-      <c r="H52" s="47">
+      <c r="H52" s="15">
         <f>SUM(H36:H43)</f>
         <v/>
       </c>
-      <c r="I52" s="48">
+      <c r="I52" s="16">
         <f>SUM(I36:I43)</f>
         <v/>
       </c>
@@ -5236,11 +5211,11 @@
       <c r="E53" s="14" t="n"/>
       <c r="F53" s="14" t="n"/>
       <c r="G53" s="14" t="n"/>
-      <c r="H53" s="47">
+      <c r="H53" s="15">
         <f>SUM(H44:H49)</f>
         <v/>
       </c>
-      <c r="I53" s="48">
+      <c r="I53" s="16">
         <f>SUM(I44:I49)</f>
         <v/>
       </c>
@@ -5261,11 +5236,11 @@
       <c r="E54" s="17" t="n"/>
       <c r="F54" s="17" t="n"/>
       <c r="G54" s="17" t="n"/>
-      <c r="H54" s="49">
+      <c r="H54" s="18">
         <f>SUM(H2:H49)</f>
         <v/>
       </c>
-      <c r="I54" s="50">
+      <c r="I54" s="19">
         <f>SUM(I2:I49)</f>
         <v/>
       </c>
@@ -5328,7 +5303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="B2:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -5338,7 +5313,6 @@
     <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -5353,7 +5327,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="16" customHeight="1">
       <c r="B5" s="20" t="inlineStr">
         <is>
@@ -5377,31 +5350,29 @@
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="B6" s="51">
+      <c r="B6" s="21">
         <f>SUM(Picker!H2:H7)/16</f>
         <v/>
       </c>
-      <c r="C6" s="51">
+      <c r="C6" s="21">
         <f>(SUM(Picker!H8:H35)+SUM(Picker!H36:H43))/16</f>
         <v/>
       </c>
-      <c r="D6" s="51">
+      <c r="D6" s="21">
         <f>((SUM(Picker!H8:H35)+SUM(Picker!H36:H43))+48+35.2)/16</f>
         <v/>
       </c>
-      <c r="E6" s="52">
+      <c r="E6" s="22">
         <f>SUM(Picker!I2:I49)</f>
         <v/>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="B8" s="23">
         <f>TEXT(INT(((SUM(Picker!H8:H35)+SUM(Picker!H36:H43))+48+35.2)/16),"0")&amp;" lb "&amp;TEXT(MOD((SUM(Picker!H8:H35)+SUM(Picker!H36:H43))+48+35.2,16),"0.0")&amp;" oz  (includes food 3.0 lb + water 2.2 lb)"</f>
         <v/>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="B10" s="24" t="inlineStr">
         <is>
@@ -5436,7 +5407,7 @@
         <f>Picker!H50/16</f>
         <v/>
       </c>
-      <c r="D12" s="53">
+      <c r="D12" s="26">
         <f>Picker!I50</f>
         <v/>
       </c>
@@ -5451,7 +5422,7 @@
         <f>Picker!H51/16</f>
         <v/>
       </c>
-      <c r="D13" s="53">
+      <c r="D13" s="26">
         <f>Picker!I51</f>
         <v/>
       </c>
@@ -5466,7 +5437,7 @@
         <f>Picker!H52/16</f>
         <v/>
       </c>
-      <c r="D14" s="53">
+      <c r="D14" s="26">
         <f>Picker!I52</f>
         <v/>
       </c>
@@ -5481,12 +5452,11 @@
         <f>Picker!H53/16</f>
         <v/>
       </c>
-      <c r="D15" s="53">
+      <c r="D15" s="26">
         <f>Picker!I53</f>
         <v/>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="B17" s="5" t="inlineStr">
         <is>
@@ -5498,7 +5468,6 @@
         <v/>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="B19" s="24" t="inlineStr">
         <is>
@@ -5533,7 +5502,7 @@
         <f>(SUM(Picker!N8:N35)+SUM(Picker!N36:N43))/16</f>
         <v/>
       </c>
-      <c r="D21" s="53">
+      <c r="D21" s="26">
         <f>SUM(Picker!O2:O49)</f>
         <v/>
       </c>
@@ -5548,7 +5517,7 @@
         <f>(SUM(Picker!P8:P35)+SUM(Picker!P36:P43))/16</f>
         <v/>
       </c>
-      <c r="D22" s="53">
+      <c r="D22" s="26">
         <f>SUM(Picker!Q2:Q49)</f>
         <v/>
       </c>
@@ -5563,7 +5532,7 @@
         <f>(SUM(Picker!R8:R35)+SUM(Picker!R36:R43))/16</f>
         <v/>
       </c>
-      <c r="D23" s="53">
+      <c r="D23" s="26">
         <f>SUM(Picker!S2:S49)</f>
         <v/>
       </c>
@@ -5936,10 +5905,10 @@
           <t>Rook 65 (men's) / Renn 65 (women's)</t>
         </is>
       </c>
-      <c r="D3" s="54" t="n">
+      <c r="D3" s="33" t="n">
         <v>66</v>
       </c>
-      <c r="E3" s="55" t="n">
+      <c r="E3" s="34" t="n">
         <v>205</v>
       </c>
       <c r="F3" s="11" t="inlineStr">
@@ -5975,10 +5944,10 @@
           <t>Flash 55</t>
         </is>
       </c>
-      <c r="M3" s="54" t="n">
+      <c r="M3" s="33" t="n">
         <v>45</v>
       </c>
-      <c r="N3" s="55" t="n">
+      <c r="N3" s="34" t="n">
         <v>229</v>
       </c>
       <c r="O3" s="11" t="inlineStr">
@@ -6014,10 +5983,10 @@
           <t>Mariposa 60</t>
         </is>
       </c>
-      <c r="V3" s="54" t="n">
+      <c r="V3" s="33" t="n">
         <v>34.2</v>
       </c>
-      <c r="W3" s="55" t="n">
+      <c r="W3" s="34" t="n">
         <v>315</v>
       </c>
       <c r="X3" s="11" t="inlineStr">
@@ -6065,10 +6034,10 @@
           <t>Late Start 1P Tent</t>
         </is>
       </c>
-      <c r="D4" s="54" t="n">
+      <c r="D4" s="33" t="n">
         <v>57</v>
       </c>
-      <c r="E4" s="55" t="n">
+      <c r="E4" s="34" t="n">
         <v>149.95</v>
       </c>
       <c r="F4" s="11" t="inlineStr">
@@ -6104,10 +6073,10 @@
           <t>Elixir 1 Tent with Footprint</t>
         </is>
       </c>
-      <c r="M4" s="54" t="n">
+      <c r="M4" s="33" t="n">
         <v>65</v>
       </c>
-      <c r="N4" s="55" t="n">
+      <c r="N4" s="34" t="n">
         <v>289.95</v>
       </c>
       <c r="O4" s="11" t="inlineStr">
@@ -6143,10 +6112,10 @@
           <t>Dragonfly OSMO 1P Ultralight Backpacking Tent</t>
         </is>
       </c>
-      <c r="V4" s="54" t="n">
+      <c r="V4" s="33" t="n">
         <v>34</v>
       </c>
-      <c r="W4" s="55" t="n">
+      <c r="W4" s="34" t="n">
         <v>499.95</v>
       </c>
       <c r="X4" s="11" t="inlineStr">
@@ -6194,10 +6163,10 @@
           <t>Trestles Elite Eco 20 (or Kelty Cosmic 20 Synthetic)</t>
         </is>
       </c>
-      <c r="D5" s="54" t="n">
+      <c r="D5" s="33" t="n">
         <v>53</v>
       </c>
-      <c r="E5" s="55" t="n">
+      <c r="E5" s="34" t="n">
         <v>179</v>
       </c>
       <c r="F5" s="11" t="inlineStr">
@@ -6233,10 +6202,10 @@
           <t>Revelation 20 (stock, 850fp)</t>
         </is>
       </c>
-      <c r="M5" s="54" t="n">
+      <c r="M5" s="33" t="n">
         <v>26</v>
       </c>
-      <c r="N5" s="55" t="n">
+      <c r="N5" s="34" t="n">
         <v>280</v>
       </c>
       <c r="O5" s="11" t="inlineStr">
@@ -6272,10 +6241,10 @@
           <t>Alsek 22</t>
         </is>
       </c>
-      <c r="V5" s="54" t="n">
+      <c r="V5" s="33" t="n">
         <v>25.5</v>
       </c>
-      <c r="W5" s="55" t="n">
+      <c r="W5" s="34" t="n">
         <v>399</v>
       </c>
       <c r="X5" s="11" t="inlineStr">
@@ -6323,10 +6292,10 @@
           <t>Insulated Static V</t>
         </is>
       </c>
-      <c r="D6" s="54" t="n">
+      <c r="D6" s="33" t="n">
         <v>25</v>
       </c>
-      <c r="E6" s="55" t="n">
+      <c r="E6" s="34" t="n">
         <v>74.20999999999999</v>
       </c>
       <c r="F6" s="11" t="inlineStr">
@@ -6362,10 +6331,10 @@
           <t>Tensor All-Season Ultralight Insulated</t>
         </is>
       </c>
-      <c r="M6" s="54" t="n">
+      <c r="M6" s="33" t="n">
         <v>14.1</v>
       </c>
-      <c r="N6" s="55" t="n">
+      <c r="N6" s="34" t="n">
         <v>199.95</v>
       </c>
       <c r="O6" s="11" t="inlineStr">
@@ -6401,10 +6370,10 @@
           <t>Tensor Extreme Conditions</t>
         </is>
       </c>
-      <c r="V6" s="54" t="n">
+      <c r="V6" s="33" t="n">
         <v>19</v>
       </c>
-      <c r="W6" s="55" t="n">
+      <c r="W6" s="34" t="n">
         <v>259.95</v>
       </c>
       <c r="X6" s="11" t="inlineStr">
@@ -6452,10 +6421,10 @@
           <t>Stuff sack filled with spare clothes (or generic inflatable pillow)</t>
         </is>
       </c>
-      <c r="D7" s="54" t="n">
+      <c r="D7" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="55" t="n">
+      <c r="E7" s="34" t="n">
         <v>20</v>
       </c>
       <c r="F7" s="11" t="inlineStr">
@@ -6491,10 +6460,10 @@
           <t>Aeros Down Pillow (Regular)</t>
         </is>
       </c>
-      <c r="M7" s="54" t="n">
+      <c r="M7" s="33" t="n">
         <v>2.5</v>
       </c>
-      <c r="N7" s="55" t="n">
+      <c r="N7" s="34" t="n">
         <v>64.95</v>
       </c>
       <c r="O7" s="11" t="inlineStr">
@@ -6530,10 +6499,10 @@
           <t>Fillo Elite</t>
         </is>
       </c>
-      <c r="V7" s="54" t="n">
+      <c r="V7" s="33" t="n">
         <v>2.5</v>
       </c>
-      <c r="W7" s="55" t="n">
+      <c r="W7" s="34" t="n">
         <v>59.95</v>
       </c>
       <c r="X7" s="11" t="inlineStr">
@@ -6581,10 +6550,10 @@
           <t>Polycryo window-shrink-film sheet</t>
         </is>
       </c>
-      <c r="D8" s="54" t="n">
+      <c r="D8" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="E8" s="55" t="n">
+      <c r="E8" s="34" t="n">
         <v>13</v>
       </c>
       <c r="F8" s="11" t="inlineStr">
@@ -6620,10 +6589,10 @@
           <t>Tyvek HomeWrap sheet</t>
         </is>
       </c>
-      <c r="M8" s="54" t="n">
+      <c r="M8" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="N8" s="55" t="n">
+      <c r="N8" s="34" t="n">
         <v>22</v>
       </c>
       <c r="O8" s="11" t="inlineStr">
@@ -6659,10 +6628,10 @@
           <t>Matching branded tent footprint (polycro or DCF)</t>
         </is>
       </c>
-      <c r="V8" s="54" t="n">
+      <c r="V8" s="33" t="n">
         <v>3.5</v>
       </c>
-      <c r="W8" s="55" t="n">
+      <c r="W8" s="34" t="n">
         <v>59</v>
       </c>
       <c r="X8" s="11" t="inlineStr">
@@ -6710,10 +6679,10 @@
           <t>Ziploc freezer bags + a cheap nylon stuff sack (or reused packaging bags)</t>
         </is>
       </c>
-      <c r="D9" s="54" t="n">
+      <c r="D9" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="55" t="n">
+      <c r="E9" s="34" t="n">
         <v>12</v>
       </c>
       <c r="F9" s="11" t="inlineStr">
@@ -6749,10 +6718,10 @@
           <t>Ultra-Sil Dry Bag - Set of 3</t>
         </is>
       </c>
-      <c r="M9" s="54" t="n">
+      <c r="M9" s="33" t="n">
         <v>2.5</v>
       </c>
-      <c r="N9" s="55" t="n">
+      <c r="N9" s="34" t="n">
         <v>69.95</v>
       </c>
       <c r="O9" s="11" t="inlineStr">
@@ -6788,10 +6757,10 @@
           <t>DCF Stuff Sack (assorted sizes)</t>
         </is>
       </c>
-      <c r="V9" s="54" t="n">
+      <c r="V9" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="W9" s="55" t="n">
+      <c r="W9" s="34" t="n">
         <v>31</v>
       </c>
       <c r="X9" s="11" t="inlineStr">
@@ -6839,10 +6808,10 @@
           <t>Compactor/contractor trash bag (heavy-duty, unscented)</t>
         </is>
       </c>
-      <c r="D10" s="54" t="n">
+      <c r="D10" s="33" t="n">
         <v>1.4</v>
       </c>
-      <c r="E10" s="55" t="n">
+      <c r="E10" s="34" t="n">
         <v>10</v>
       </c>
       <c r="F10" s="11" t="inlineStr">
@@ -6878,10 +6847,10 @@
           <t>Nylofume Pack Liner Bag</t>
         </is>
       </c>
-      <c r="M10" s="54" t="n">
+      <c r="M10" s="33" t="n">
         <v>0.9</v>
       </c>
-      <c r="N10" s="55" t="n">
+      <c r="N10" s="34" t="n">
         <v>2.49</v>
       </c>
       <c r="O10" s="11" t="inlineStr">
@@ -6917,10 +6886,10 @@
           <t>Evac Lightweight Dry Bag (35L)</t>
         </is>
       </c>
-      <c r="V10" s="54" t="n">
+      <c r="V10" s="33" t="n">
         <v>3.5</v>
       </c>
-      <c r="W10" s="55" t="n">
+      <c r="W10" s="34" t="n">
         <v>44.95</v>
       </c>
       <c r="X10" s="11" t="inlineStr">
@@ -6968,10 +6937,10 @@
           <t>Amicus Stove Cookset Combo</t>
         </is>
       </c>
-      <c r="D11" s="54" t="n">
+      <c r="D11" s="33" t="n">
         <v>11.2</v>
       </c>
-      <c r="E11" s="55" t="n">
+      <c r="E11" s="34" t="n">
         <v>49.95</v>
       </c>
       <c r="F11" s="11" t="inlineStr">
@@ -7007,10 +6976,10 @@
           <t>WindMaster (4Flex)</t>
         </is>
       </c>
-      <c r="M11" s="54" t="n">
+      <c r="M11" s="33" t="n">
         <v>3.5</v>
       </c>
-      <c r="N11" s="55" t="n">
+      <c r="N11" s="34" t="n">
         <v>69.95</v>
       </c>
       <c r="O11" s="11" t="inlineStr">
@@ -7046,10 +7015,10 @@
           <t>Stash</t>
         </is>
       </c>
-      <c r="V11" s="54" t="n">
+      <c r="V11" s="33" t="n">
         <v>7.1</v>
       </c>
-      <c r="W11" s="55" t="n">
+      <c r="W11" s="34" t="n">
         <v>131</v>
       </c>
       <c r="X11" s="11" t="inlineStr">
@@ -7097,10 +7066,10 @@
           <t>A004-025001 Aluminum Sauce Pan, 1-Quart</t>
         </is>
       </c>
-      <c r="D12" s="54" t="n">
+      <c r="D12" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="E12" s="55" t="n">
+      <c r="E12" s="34" t="n">
         <v>12.99</v>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -7136,10 +7105,10 @@
           <t>750ml Titanium Pot with Bail Handle (POT-750-BH)</t>
         </is>
       </c>
-      <c r="M12" s="54" t="n">
+      <c r="M12" s="33" t="n">
         <v>4.1</v>
       </c>
-      <c r="N12" s="55" t="n">
+      <c r="N12" s="34" t="n">
         <v>30</v>
       </c>
       <c r="O12" s="11" t="inlineStr">
@@ -7175,10 +7144,10 @@
           <t>Trek 900 Titanium Cookset</t>
         </is>
       </c>
-      <c r="V12" s="54" t="n">
+      <c r="V12" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="W12" s="55" t="n">
+      <c r="W12" s="34" t="n">
         <v>54.95</v>
       </c>
       <c r="X12" s="11" t="inlineStr">
@@ -7226,10 +7195,10 @@
           <t>Butane/Propane Mix Fuel, 7.75oz (220g)</t>
         </is>
       </c>
-      <c r="D13" s="54" t="n">
+      <c r="D13" s="33" t="n">
         <v>7.75</v>
       </c>
-      <c r="E13" s="55" t="n">
+      <c r="E13" s="34" t="n">
         <v>5.97</v>
       </c>
       <c r="F13" s="11" t="inlineStr">
@@ -7265,10 +7234,10 @@
           <t>IsoPro 8oz/227g canister</t>
         </is>
       </c>
-      <c r="M13" s="54" t="n">
+      <c r="M13" s="33" t="n">
         <v>13.7</v>
       </c>
-      <c r="N13" s="55" t="n">
+      <c r="N13" s="34" t="n">
         <v>6.95</v>
       </c>
       <c r="O13" s="11" t="inlineStr">
@@ -7304,10 +7273,10 @@
           <t>IsoPro (same blend, cold-weather use case)</t>
         </is>
       </c>
-      <c r="V13" s="54" t="n">
+      <c r="V13" s="33" t="n">
         <v>7.6</v>
       </c>
-      <c r="W13" s="55" t="n">
+      <c r="W13" s="34" t="n">
         <v>5.95</v>
       </c>
       <c r="X13" s="11" t="inlineStr">
@@ -7355,10 +7324,10 @@
           <t>Titanium Spork</t>
         </is>
       </c>
-      <c r="D14" s="54" t="n">
+      <c r="D14" s="33" t="n">
         <v>0.6</v>
       </c>
-      <c r="E14" s="55" t="n">
+      <c r="E14" s="34" t="n">
         <v>9.949999999999999</v>
       </c>
       <c r="F14" s="11" t="inlineStr">
@@ -7394,10 +7363,10 @@
           <t>Frontier Ultralight Spoon - Long Handle</t>
         </is>
       </c>
-      <c r="M14" s="54" t="n">
+      <c r="M14" s="33" t="n">
         <v>0.6</v>
       </c>
-      <c r="N14" s="55" t="n">
+      <c r="N14" s="34" t="n">
         <v>10.95</v>
       </c>
       <c r="O14" s="11" t="inlineStr">
@@ -7433,10 +7402,10 @@
           <t>Titanium Spork</t>
         </is>
       </c>
-      <c r="V14" s="54" t="n">
+      <c r="V14" s="33" t="n">
         <v>0.6</v>
       </c>
-      <c r="W14" s="55" t="n">
+      <c r="W14" s="34" t="n">
         <v>9.949999999999999</v>
       </c>
       <c r="X14" s="11" t="inlineStr">
@@ -7484,10 +7453,10 @@
           <t>Squeeze (SP2129)</t>
         </is>
       </c>
-      <c r="D15" s="54" t="n">
+      <c r="D15" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="E15" s="55" t="n">
+      <c r="E15" s="34" t="n">
         <v>45.95</v>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -7523,10 +7492,10 @@
           <t>BeFree 1.0L</t>
         </is>
       </c>
-      <c r="M15" s="54" t="n">
+      <c r="M15" s="33" t="n">
         <v>2.3</v>
       </c>
-      <c r="N15" s="55" t="n">
+      <c r="N15" s="34" t="n">
         <v>52.95</v>
       </c>
       <c r="O15" s="11" t="inlineStr">
@@ -7562,10 +7531,10 @@
           <t>GeoPress</t>
         </is>
       </c>
-      <c r="V15" s="54" t="n">
+      <c r="V15" s="33" t="n">
         <v>15.9</v>
       </c>
-      <c r="W15" s="55" t="n">
+      <c r="W15" s="34" t="n">
         <v>99.95</v>
       </c>
       <c r="X15" s="11" t="inlineStr">
@@ -7613,10 +7582,10 @@
           <t>1L reused disposable bottle</t>
         </is>
       </c>
-      <c r="D16" s="54" t="n">
+      <c r="D16" s="33" t="n">
         <v>1.6</v>
       </c>
-      <c r="E16" s="55" t="n">
+      <c r="E16" s="34" t="n">
         <v>2.17</v>
       </c>
       <c r="F16" s="11" t="inlineStr">
@@ -7652,10 +7621,10 @@
           <t>Stow 1L collapsible bottle</t>
         </is>
       </c>
-      <c r="M16" s="54" t="n">
+      <c r="M16" s="33" t="n">
         <v>1.4</v>
       </c>
-      <c r="N16" s="55" t="n">
+      <c r="N16" s="34" t="n">
         <v>18</v>
       </c>
       <c r="O16" s="11" t="inlineStr">
@@ -7691,10 +7660,10 @@
           <t>Vecto 2L</t>
         </is>
       </c>
-      <c r="V16" s="54" t="n">
+      <c r="V16" s="33" t="n">
         <v>3.6</v>
       </c>
-      <c r="W16" s="55" t="n">
+      <c r="W16" s="34" t="n">
         <v>25</v>
       </c>
       <c r="X16" s="11" t="inlineStr">
@@ -7742,10 +7711,10 @@
           <t>Easy to Throw Bear Bag Hanging Kit (#371486)</t>
         </is>
       </c>
-      <c r="D17" s="54" t="n">
+      <c r="D17" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="E17" s="55" t="n">
+      <c r="E17" s="34" t="n">
         <v>27</v>
       </c>
       <c r="F17" s="11" t="inlineStr">
@@ -7781,10 +7750,10 @@
           <t>Major XL (with OPSak liner)</t>
         </is>
       </c>
-      <c r="M17" s="54" t="n">
+      <c r="M17" s="33" t="n">
         <v>10.8</v>
       </c>
-      <c r="N17" s="55" t="n">
+      <c r="N17" s="34" t="n">
         <v>149.95</v>
       </c>
       <c r="O17" s="11" t="inlineStr">
@@ -7820,10 +7789,10 @@
           <t>BV500</t>
         </is>
       </c>
-      <c r="V17" s="54" t="n">
+      <c r="V17" s="33" t="n">
         <v>41</v>
       </c>
-      <c r="W17" s="55" t="n">
+      <c r="W17" s="34" t="n">
         <v>99.95</v>
       </c>
       <c r="X17" s="11" t="inlineStr">
@@ -7871,10 +7840,10 @@
           <t>Tikkina</t>
         </is>
       </c>
-      <c r="D18" s="54" t="n">
+      <c r="D18" s="33" t="n">
         <v>2.9</v>
       </c>
-      <c r="E18" s="55" t="n">
+      <c r="E18" s="34" t="n">
         <v>19.95</v>
       </c>
       <c r="F18" s="11" t="inlineStr">
@@ -7910,10 +7879,10 @@
           <t>Spot 400</t>
         </is>
       </c>
-      <c r="M18" s="54" t="n">
+      <c r="M18" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="N18" s="55" t="n">
+      <c r="N18" s="34" t="n">
         <v>59.95</v>
       </c>
       <c r="O18" s="11" t="inlineStr">
@@ -7949,10 +7918,10 @@
           <t>NU25 (rechargeable)</t>
         </is>
       </c>
-      <c r="V18" s="54" t="n">
+      <c r="V18" s="33" t="n">
         <v>1.75</v>
       </c>
-      <c r="W18" s="55" t="n">
+      <c r="W18" s="34" t="n">
         <v>54.95</v>
       </c>
       <c r="X18" s="11" t="inlineStr">
@@ -8000,10 +7969,10 @@
           <t>Power Bank, 10,000mAh Portable Charger (PowerIQ, USB-C)</t>
         </is>
       </c>
-      <c r="D19" s="54" t="n">
+      <c r="D19" s="33" t="n">
         <v>6.3</v>
       </c>
-      <c r="E19" s="55" t="n">
+      <c r="E19" s="34" t="n">
         <v>21.99</v>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -8039,10 +8008,10 @@
           <t>NB10000 Gen 3</t>
         </is>
       </c>
-      <c r="M19" s="54" t="n">
+      <c r="M19" s="33" t="n">
         <v>5.1</v>
       </c>
-      <c r="N19" s="55" t="n">
+      <c r="N19" s="34" t="n">
         <v>64.95</v>
       </c>
       <c r="O19" s="11" t="inlineStr">
@@ -8078,10 +8047,10 @@
           <t>NB10000 Gen 4</t>
         </is>
       </c>
-      <c r="V19" s="54" t="n">
+      <c r="V19" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="W19" s="55" t="n">
+      <c r="W19" s="34" t="n">
         <v>83.95</v>
       </c>
       <c r="X19" s="11" t="inlineStr">
@@ -8129,10 +8098,10 @@
           <t>inReach Mini 2 (weekly rental)</t>
         </is>
       </c>
-      <c r="D20" s="54" t="n">
+      <c r="D20" s="33" t="n">
         <v>3.5</v>
       </c>
-      <c r="E20" s="55" t="n">
+      <c r="E20" s="34" t="n">
         <v>100</v>
       </c>
       <c r="F20" s="11" t="inlineStr">
@@ -8168,10 +8137,10 @@
           <t>Satellite Communicator</t>
         </is>
       </c>
-      <c r="M20" s="54" t="n">
+      <c r="M20" s="33" t="n">
         <v>5.4</v>
       </c>
-      <c r="N20" s="55" t="n">
+      <c r="N20" s="34" t="n">
         <v>199</v>
       </c>
       <c r="O20" s="11" t="inlineStr">
@@ -8207,10 +8176,10 @@
           <t>inReach Mini 2 (owned, Safety plan)</t>
         </is>
       </c>
-      <c r="V20" s="54" t="n">
+      <c r="V20" s="33" t="n">
         <v>3.5</v>
       </c>
-      <c r="W20" s="55" t="n">
+      <c r="W20" s="34" t="n">
         <v>349.99</v>
       </c>
       <c r="X20" s="11" t="inlineStr">
@@ -8258,10 +8227,10 @@
           <t>Free account + printed topo</t>
         </is>
       </c>
-      <c r="D21" s="54" t="n">
+      <c r="D21" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="55" t="n">
+      <c r="E21" s="34" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="11" t="inlineStr">
@@ -8297,10 +8266,10 @@
           <t>Premium subscription</t>
         </is>
       </c>
-      <c r="M21" s="54" t="n">
+      <c r="M21" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="N21" s="55" t="n">
+      <c r="N21" s="34" t="n">
         <v>39.99</v>
       </c>
       <c r="O21" s="11" t="inlineStr">
@@ -8336,10 +8305,10 @@
           <t>Regional trail guide (per-trail purchase)</t>
         </is>
       </c>
-      <c r="V21" s="54" t="n">
+      <c r="V21" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="W21" s="55" t="n">
+      <c r="W21" s="34" t="n">
         <v>14.99</v>
       </c>
       <c r="X21" s="11" t="inlineStr">
@@ -8387,10 +8356,10 @@
           <t>No.8 Carbon/Stainless folding knife</t>
         </is>
       </c>
-      <c r="D22" s="54" t="n">
+      <c r="D22" s="33" t="n">
         <v>1.6</v>
       </c>
-      <c r="E22" s="55" t="n">
+      <c r="E22" s="34" t="n">
         <v>22</v>
       </c>
       <c r="F22" s="11" t="inlineStr">
@@ -8426,10 +8395,10 @@
           <t>Wingman</t>
         </is>
       </c>
-      <c r="M22" s="54" t="n">
+      <c r="M22" s="33" t="n">
         <v>7.2</v>
       </c>
-      <c r="N22" s="55" t="n">
+      <c r="N22" s="34" t="n">
         <v>49.95</v>
       </c>
       <c r="O22" s="11" t="inlineStr">
@@ -8465,10 +8434,10 @@
           <t>Skeletool CX</t>
         </is>
       </c>
-      <c r="V22" s="54" t="n">
+      <c r="V22" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="W22" s="55" t="n">
+      <c r="W22" s="34" t="n">
         <v>99.95</v>
       </c>
       <c r="X22" s="11" t="inlineStr">
@@ -8516,10 +8485,10 @@
           <t>Build-your-own kit (gauze, tape, meds, moleskin, blister care)</t>
         </is>
       </c>
-      <c r="D23" s="54" t="n">
+      <c r="D23" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="E23" s="55" t="n">
+      <c r="E23" s="34" t="n">
         <v>22</v>
       </c>
       <c r="F23" s="11" t="inlineStr">
@@ -8555,10 +8524,10 @@
           <t>Ultralight/Watertight .7</t>
         </is>
       </c>
-      <c r="M23" s="54" t="n">
+      <c r="M23" s="33" t="n">
         <v>4.4</v>
       </c>
-      <c r="N23" s="55" t="n">
+      <c r="N23" s="34" t="n">
         <v>44.99</v>
       </c>
       <c r="O23" s="11" t="inlineStr">
@@ -8594,10 +8563,10 @@
           <t>Mountain Series Explorer</t>
         </is>
       </c>
-      <c r="V23" s="54" t="n">
+      <c r="V23" s="33" t="n">
         <v>16</v>
       </c>
-      <c r="W23" s="55" t="n">
+      <c r="W23" s="34" t="n">
         <v>86.48999999999999</v>
       </c>
       <c r="X23" s="11" t="inlineStr">
@@ -8645,10 +8614,10 @@
           <t>Backpackers Trowel</t>
         </is>
       </c>
-      <c r="D24" s="54" t="n">
+      <c r="D24" s="33" t="n">
         <v>1.5</v>
       </c>
-      <c r="E24" s="55" t="n">
+      <c r="E24" s="34" t="n">
         <v>8.75</v>
       </c>
       <c r="F24" s="11" t="inlineStr">
@@ -8684,10 +8653,10 @@
           <t>Cathole Trowel</t>
         </is>
       </c>
-      <c r="M24" s="54" t="n">
+      <c r="M24" s="33" t="n">
         <v>2.4</v>
       </c>
-      <c r="N24" s="55" t="n">
+      <c r="N24" s="34" t="n">
         <v>7.95</v>
       </c>
       <c r="O24" s="11" t="inlineStr">
@@ -8723,10 +8692,10 @@
           <t>The DirtSaw Deuce #2 Trowel</t>
         </is>
       </c>
-      <c r="V24" s="54" t="n">
+      <c r="V24" s="33" t="n">
         <v>0.6</v>
       </c>
-      <c r="W24" s="55" t="n">
+      <c r="W24" s="34" t="n">
         <v>21.95</v>
       </c>
       <c r="X24" s="11" t="inlineStr">
@@ -8774,10 +8743,10 @@
           <t>Travel-size toothbrush, toothpaste, TP, hand sanitizer</t>
         </is>
       </c>
-      <c r="D25" s="54" t="n">
+      <c r="D25" s="33" t="n">
         <v>3.5</v>
       </c>
-      <c r="E25" s="55" t="n">
+      <c r="E25" s="34" t="n">
         <v>3.94</v>
       </c>
       <c r="F25" s="11" t="inlineStr">
@@ -8813,10 +8782,10 @@
           <t>Small toiletry bag + biodegradable wipes</t>
         </is>
       </c>
-      <c r="M25" s="54" t="n">
+      <c r="M25" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="N25" s="55" t="n">
+      <c r="N25" s="34" t="n">
         <v>9</v>
       </c>
       <c r="O25" s="11" t="inlineStr">
@@ -8852,10 +8821,10 @@
           <t>Ultralight toiletry kit + pack towel wipes + sunscreen/lip balm travel set</t>
         </is>
       </c>
-      <c r="V25" s="54" t="n">
+      <c r="V25" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="W25" s="55" t="n">
+      <c r="W25" s="34" t="n">
         <v>15</v>
       </c>
       <c r="X25" s="11" t="inlineStr">
@@ -8903,10 +8872,10 @@
           <t>Aluminum adjustable trekking poles (pair)</t>
         </is>
       </c>
-      <c r="D26" s="54" t="n">
+      <c r="D26" s="33" t="n">
         <v>18</v>
       </c>
-      <c r="E26" s="55" t="n">
+      <c r="E26" s="34" t="n">
         <v>49.99</v>
       </c>
       <c r="F26" s="11" t="inlineStr">
@@ -8942,10 +8911,10 @@
           <t>Carbon Fiber Quick Lock (pair)</t>
         </is>
       </c>
-      <c r="M26" s="54" t="n">
+      <c r="M26" s="33" t="n">
         <v>8.1</v>
       </c>
-      <c r="N26" s="55" t="n">
+      <c r="N26" s="34" t="n">
         <v>64.98999999999999</v>
       </c>
       <c r="O26" s="11" t="inlineStr">
@@ -8981,10 +8950,10 @@
           <t>Distance Carbon Z (pair)</t>
         </is>
       </c>
-      <c r="V26" s="54" t="n">
+      <c r="V26" s="33" t="n">
         <v>10.9</v>
       </c>
-      <c r="W26" s="55" t="n">
+      <c r="W26" s="34" t="n">
         <v>219.95</v>
       </c>
       <c r="X26" s="11" t="inlineStr">
@@ -9032,10 +9001,10 @@
           <t>Cut piece of leftover closed-cell foam pad</t>
         </is>
       </c>
-      <c r="D27" s="54" t="n">
+      <c r="D27" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="E27" s="55" t="n">
+      <c r="E27" s="34" t="n">
         <v>0</v>
       </c>
       <c r="F27" s="11" t="inlineStr">
@@ -9071,10 +9040,10 @@
           <t>Z Seat</t>
         </is>
       </c>
-      <c r="M27" s="54" t="n">
+      <c r="M27" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="N27" s="55" t="n">
+      <c r="N27" s="34" t="n">
         <v>34.28</v>
       </c>
       <c r="O27" s="11" t="inlineStr">
@@ -9110,10 +9079,10 @@
           <t>1/8in Thinlight Foam Pad (full torso, multi-use)</t>
         </is>
       </c>
-      <c r="V27" s="54" t="n">
+      <c r="V27" s="33" t="n">
         <v>2.8</v>
       </c>
-      <c r="W27" s="55" t="n">
+      <c r="W27" s="34" t="n">
         <v>22.5</v>
       </c>
       <c r="X27" s="11" t="inlineStr">
@@ -9161,10 +9130,10 @@
           <t>Gabe Cloud Slide Sandals</t>
         </is>
       </c>
-      <c r="D28" s="54" t="n">
+      <c r="D28" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="E28" s="55" t="n">
+      <c r="E28" s="34" t="n">
         <v>19.99</v>
       </c>
       <c r="F28" s="11" t="inlineStr">
@@ -9200,10 +9169,10 @@
           <t>Classic Clog</t>
         </is>
       </c>
-      <c r="M28" s="54" t="n">
+      <c r="M28" s="33" t="n">
         <v>12</v>
       </c>
-      <c r="N28" s="55" t="n">
+      <c r="N28" s="34" t="n">
         <v>49.99</v>
       </c>
       <c r="O28" s="11" t="inlineStr">
@@ -9239,10 +9208,10 @@
           <t>Z-Trail EV Sandals</t>
         </is>
       </c>
-      <c r="V28" s="54" t="n">
+      <c r="V28" s="33" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="W28" s="55" t="n">
+      <c r="W28" s="34" t="n">
         <v>80</v>
       </c>
       <c r="X28" s="11" t="inlineStr">
@@ -9290,10 +9259,10 @@
           <t>Any old/thrifted trail running shoe (mesh upper, non-waterproof)</t>
         </is>
       </c>
-      <c r="D29" s="54" t="n">
+      <c r="D29" s="33" t="n">
         <v>24</v>
       </c>
-      <c r="E29" s="55" t="n">
+      <c r="E29" s="34" t="n">
         <v>0</v>
       </c>
       <c r="F29" s="11" t="inlineStr">
@@ -9329,10 +9298,10 @@
           <t>Moab 3</t>
         </is>
       </c>
-      <c r="M29" s="54" t="n">
+      <c r="M29" s="33" t="n">
         <v>33</v>
       </c>
-      <c r="N29" s="55" t="n">
+      <c r="N29" s="34" t="n">
         <v>100.93</v>
       </c>
       <c r="O29" s="11" t="inlineStr">
@@ -9368,10 +9337,10 @@
           <t>Lone Peak 9</t>
         </is>
       </c>
-      <c r="V29" s="54" t="n">
+      <c r="V29" s="33" t="n">
         <v>22.5</v>
       </c>
-      <c r="W29" s="55" t="n">
+      <c r="W29" s="34" t="n">
         <v>145</v>
       </c>
       <c r="X29" s="11" t="inlineStr">
@@ -9419,10 +9388,10 @@
           <t>Merino Wool Lightweight Hiking Crew (3-pack budget alt)</t>
         </is>
       </c>
-      <c r="D30" s="54" t="n">
+      <c r="D30" s="33" t="n">
         <v>2.5</v>
       </c>
-      <c r="E30" s="55" t="n">
+      <c r="E30" s="34" t="n">
         <v>8.83</v>
       </c>
       <c r="F30" s="11" t="inlineStr">
@@ -9458,10 +9427,10 @@
           <t>Hiker Micro Crew Midweight with Cushion</t>
         </is>
       </c>
-      <c r="M30" s="54" t="n">
+      <c r="M30" s="33" t="n">
         <v>2.6</v>
       </c>
-      <c r="N30" s="55" t="n">
+      <c r="N30" s="34" t="n">
         <v>25.95</v>
       </c>
       <c r="O30" s="11" t="inlineStr">
@@ -9497,10 +9466,10 @@
           <t>Waterproof All Weather Mid Length Sock</t>
         </is>
       </c>
-      <c r="V30" s="54" t="n">
+      <c r="V30" s="33" t="n">
         <v>3.2</v>
       </c>
-      <c r="W30" s="55" t="n">
+      <c r="W30" s="34" t="n">
         <v>55</v>
       </c>
       <c r="X30" s="11" t="inlineStr">
@@ -9548,10 +9517,10 @@
           <t>Watertight II Rain Jacket (Men's)</t>
         </is>
       </c>
-      <c r="D31" s="54" t="n">
+      <c r="D31" s="33" t="n">
         <v>12</v>
       </c>
-      <c r="E31" s="55" t="n">
+      <c r="E31" s="34" t="n">
         <v>70</v>
       </c>
       <c r="F31" s="11" t="inlineStr">
@@ -9587,10 +9556,10 @@
           <t>Rainier Rain Jacket</t>
         </is>
       </c>
-      <c r="M31" s="54" t="n">
+      <c r="M31" s="33" t="n">
         <v>12.5</v>
       </c>
-      <c r="N31" s="55" t="n">
+      <c r="N31" s="34" t="n">
         <v>99.95</v>
       </c>
       <c r="O31" s="11" t="inlineStr">
@@ -9626,10 +9595,10 @@
           <t>Helium Rain Jacket</t>
         </is>
       </c>
-      <c r="V31" s="54" t="n">
+      <c r="V31" s="33" t="n">
         <v>6.4</v>
       </c>
-      <c r="W31" s="55" t="n">
+      <c r="W31" s="34" t="n">
         <v>199</v>
       </c>
       <c r="X31" s="11" t="inlineStr">
@@ -9677,10 +9646,10 @@
           <t>MT100 Hooded Down Puffer Jacket</t>
         </is>
       </c>
-      <c r="D32" s="54" t="n">
+      <c r="D32" s="33" t="n">
         <v>10.6</v>
       </c>
-      <c r="E32" s="55" t="n">
+      <c r="E32" s="34" t="n">
         <v>80</v>
       </c>
       <c r="F32" s="11" t="inlineStr">
@@ -9716,10 +9685,10 @@
           <t>Nano Puff Jacket</t>
         </is>
       </c>
-      <c r="M32" s="54" t="n">
+      <c r="M32" s="33" t="n">
         <v>11.6</v>
       </c>
-      <c r="N32" s="55" t="n">
+      <c r="N32" s="34" t="n">
         <v>118.99</v>
       </c>
       <c r="O32" s="11" t="inlineStr">
@@ -9755,10 +9724,10 @@
           <t>Torrid APEX Jacket</t>
         </is>
       </c>
-      <c r="V32" s="54" t="n">
+      <c r="V32" s="33" t="n">
         <v>8.9</v>
       </c>
-      <c r="W32" s="55" t="n">
+      <c r="W32" s="34" t="n">
         <v>170</v>
       </c>
       <c r="X32" s="11" t="inlineStr">
@@ -9806,10 +9775,10 @@
           <t>MH100 Fleece</t>
         </is>
       </c>
-      <c r="D33" s="54" t="n">
+      <c r="D33" s="33" t="n">
         <v>12</v>
       </c>
-      <c r="E33" s="55" t="n">
+      <c r="E33" s="34" t="n">
         <v>25</v>
       </c>
       <c r="F33" s="11" t="inlineStr">
@@ -9845,10 +9814,10 @@
           <t>Alpha 90 Half-Zip Hoodie</t>
         </is>
       </c>
-      <c r="M33" s="54" t="n">
+      <c r="M33" s="33" t="n">
         <v>4.8</v>
       </c>
-      <c r="N33" s="55" t="n">
+      <c r="N33" s="34" t="n">
         <v>115</v>
       </c>
       <c r="O33" s="11" t="inlineStr">
@@ -9884,10 +9853,10 @@
           <t>R1 Air Hoody</t>
         </is>
       </c>
-      <c r="V33" s="54" t="n">
+      <c r="V33" s="33" t="n">
         <v>10.5</v>
       </c>
-      <c r="W33" s="55" t="n">
+      <c r="W33" s="34" t="n">
         <v>179</v>
       </c>
       <c r="X33" s="11" t="inlineStr">
@@ -9935,10 +9904,10 @@
           <t>Men's/Women's Long Sleeve Base Layer Set</t>
         </is>
       </c>
-      <c r="D34" s="54" t="n">
+      <c r="D34" s="33" t="n">
         <v>8</v>
       </c>
-      <c r="E34" s="55" t="n">
+      <c r="E34" s="34" t="n">
         <v>100</v>
       </c>
       <c r="F34" s="11" t="inlineStr">
@@ -9974,10 +9943,10 @@
           <t>Classic Thermal Merino Base Layer (top + bottom)</t>
         </is>
       </c>
-      <c r="M34" s="54" t="n">
+      <c r="M34" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="N34" s="55" t="n">
+      <c r="N34" s="34" t="n">
         <v>125</v>
       </c>
       <c r="O34" s="11" t="inlineStr">
@@ -10013,10 +9982,10 @@
           <t>200 Oasis (top + bottom)</t>
         </is>
       </c>
-      <c r="V34" s="54" t="n">
+      <c r="V34" s="33" t="n">
         <v>11</v>
       </c>
-      <c r="W34" s="55" t="n">
+      <c r="W34" s="34" t="n">
         <v>235</v>
       </c>
       <c r="X34" s="11" t="inlineStr">
@@ -10064,10 +10033,10 @@
           <t>Trailmade Pants</t>
         </is>
       </c>
-      <c r="D35" s="54" t="n">
+      <c r="D35" s="33" t="n">
         <v>11</v>
       </c>
-      <c r="E35" s="55" t="n">
+      <c r="E35" s="34" t="n">
         <v>80</v>
       </c>
       <c r="F35" s="11" t="inlineStr">
@@ -10103,10 +10072,10 @@
           <t>Ferrosi Pants</t>
         </is>
       </c>
-      <c r="M35" s="54" t="n">
+      <c r="M35" s="33" t="n">
         <v>11.4</v>
       </c>
-      <c r="N35" s="55" t="n">
+      <c r="N35" s="34" t="n">
         <v>110</v>
       </c>
       <c r="O35" s="11" t="inlineStr">
@@ -10142,10 +10111,10 @@
           <t>Stretch Zion Straight Pants (cargo version discontinued, replaced by current lineup)</t>
         </is>
       </c>
-      <c r="V35" s="54" t="n">
+      <c r="V35" s="33" t="n">
         <v>14</v>
       </c>
-      <c r="W35" s="55" t="n">
+      <c r="W35" s="34" t="n">
         <v>98</v>
       </c>
       <c r="X35" s="11" t="inlineStr">
@@ -10193,10 +10162,10 @@
           <t>Fleece-lined knit beanie</t>
         </is>
       </c>
-      <c r="D36" s="54" t="n">
+      <c r="D36" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="E36" s="55" t="n">
+      <c r="E36" s="34" t="n">
         <v>14.99</v>
       </c>
       <c r="F36" s="11" t="inlineStr">
@@ -10232,10 +10201,10 @@
           <t>Alpha Drifter Beanie</t>
         </is>
       </c>
-      <c r="M36" s="54" t="n">
+      <c r="M36" s="33" t="n">
         <v>0.7</v>
       </c>
-      <c r="N36" s="55" t="n">
+      <c r="N36" s="34" t="n">
         <v>38</v>
       </c>
       <c r="O36" s="11" t="inlineStr">
@@ -10271,10 +10240,10 @@
           <t>Merino 250 Reversible Cuffed Beanie</t>
         </is>
       </c>
-      <c r="V36" s="54" t="n">
+      <c r="V36" s="33" t="n">
         <v>2.1</v>
       </c>
-      <c r="W36" s="55" t="n">
+      <c r="W36" s="34" t="n">
         <v>35</v>
       </c>
       <c r="X36" s="11" t="inlineStr">
@@ -10322,10 +10291,10 @@
           <t>Wool Fleece-Liner Knit Gloves (3-pack)</t>
         </is>
       </c>
-      <c r="D37" s="54" t="n">
+      <c r="D37" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="E37" s="55" t="n">
+      <c r="E37" s="34" t="n">
         <v>12.99</v>
       </c>
       <c r="F37" s="11" t="inlineStr">
@@ -10361,10 +10330,10 @@
           <t>PL 400 Gloves</t>
         </is>
       </c>
-      <c r="M37" s="54" t="n">
+      <c r="M37" s="33" t="n">
         <v>2.3</v>
       </c>
-      <c r="N37" s="55" t="n">
+      <c r="N37" s="34" t="n">
         <v>35</v>
       </c>
       <c r="O37" s="11" t="inlineStr">
@@ -10400,10 +10369,10 @@
           <t>Merino/Possum Blend Gloves (touchscreen)</t>
         </is>
       </c>
-      <c r="V37" s="54" t="n">
+      <c r="V37" s="33" t="n">
         <v>1.5</v>
       </c>
-      <c r="W37" s="55" t="n">
+      <c r="W37" s="34" t="n">
         <v>40</v>
       </c>
       <c r="X37" s="11" t="inlineStr">
@@ -10451,10 +10420,10 @@
           <t>Mesh Safety Vest + Blaze Orange Insulated Beanie</t>
         </is>
       </c>
-      <c r="D38" s="54" t="n">
+      <c r="D38" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="E38" s="55" t="n">
+      <c r="E38" s="34" t="n">
         <v>16.96</v>
       </c>
       <c r="F38" s="11" t="inlineStr">
@@ -10490,10 +10459,10 @@
           <t>Blaze Orange Safety Vest</t>
         </is>
       </c>
-      <c r="M38" s="54" t="n">
+      <c r="M38" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="N38" s="55" t="n">
+      <c r="N38" s="34" t="n">
         <v>13.51</v>
       </c>
       <c r="O38" s="11" t="inlineStr">
@@ -10529,10 +10498,10 @@
           <t>Blaze Orange Hunting Vest &amp; Hat Combo</t>
         </is>
       </c>
-      <c r="V38" s="54" t="n">
+      <c r="V38" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="W38" s="55" t="n">
+      <c r="W38" s="34" t="n">
         <v>45</v>
       </c>
       <c r="X38" s="11" t="inlineStr">
@@ -10580,10 +10549,10 @@
           <t>Old sneakers or flip-flops already owned</t>
         </is>
       </c>
-      <c r="D39" s="54" t="n">
+      <c r="D39" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="E39" s="55" t="n">
+      <c r="E39" s="34" t="n">
         <v>0</v>
       </c>
       <c r="F39" s="11" t="inlineStr">
@@ -10619,10 +10588,10 @@
           <t>Classic Clog</t>
         </is>
       </c>
-      <c r="M39" s="54" t="n">
+      <c r="M39" s="33" t="n">
         <v>14</v>
       </c>
-      <c r="N39" s="55" t="n">
+      <c r="N39" s="34" t="n">
         <v>50</v>
       </c>
       <c r="O39" s="11" t="inlineStr">
@@ -10658,10 +10627,10 @@
           <t>Cairn Evo Adventure Sandals (current lineup; original Cairn Adventure Sandal discontinued)</t>
         </is>
       </c>
-      <c r="V39" s="54" t="n">
+      <c r="V39" s="33" t="n">
         <v>11</v>
       </c>
-      <c r="W39" s="55" t="n">
+      <c r="W39" s="34" t="n">
         <v>115</v>
       </c>
       <c r="X39" s="11" t="inlineStr">
@@ -10709,10 +10678,10 @@
           <t>Kenai Original</t>
         </is>
       </c>
-      <c r="D40" s="54" t="n">
+      <c r="D40" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="E40" s="55" t="n">
+      <c r="E40" s="34" t="n">
         <v>24.99</v>
       </c>
       <c r="F40" s="11" t="inlineStr">
@@ -10748,10 +10717,10 @@
           <t>Kenai Original</t>
         </is>
       </c>
-      <c r="M40" s="54" t="n">
+      <c r="M40" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="N40" s="55" t="n">
+      <c r="N40" s="34" t="n">
         <v>24.99</v>
       </c>
       <c r="O40" s="11" t="inlineStr">
@@ -10787,10 +10756,10 @@
           <t>Arctic Gauntlet Gloves for Cold Water Wading</t>
         </is>
       </c>
-      <c r="V40" s="54" t="n">
+      <c r="V40" s="33" t="n">
         <v>9</v>
       </c>
-      <c r="W40" s="55" t="n">
+      <c r="W40" s="34" t="n">
         <v>50</v>
       </c>
       <c r="X40" s="11" t="inlineStr">
@@ -10838,10 +10807,10 @@
           <t>3mm Knee-High Neoprene Sock</t>
         </is>
       </c>
-      <c r="D41" s="54" t="n">
+      <c r="D41" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="E41" s="55" t="n">
+      <c r="E41" s="34" t="n">
         <v>41.59</v>
       </c>
       <c r="F41" s="11" t="inlineStr">
@@ -10877,10 +10846,10 @@
           <t>3mm Neoprene Wading/Water Socks</t>
         </is>
       </c>
-      <c r="M41" s="54" t="n">
+      <c r="M41" s="33" t="n">
         <v>6.5</v>
       </c>
-      <c r="N41" s="55" t="n">
+      <c r="N41" s="34" t="n">
         <v>30.19</v>
       </c>
       <c r="O41" s="11" t="inlineStr">
@@ -10916,10 +10885,10 @@
           <t>I-Drain Neoprene Guard Socks, 3.5mm</t>
         </is>
       </c>
-      <c r="V41" s="54" t="n">
+      <c r="V41" s="33" t="n">
         <v>7</v>
       </c>
-      <c r="W41" s="55" t="n">
+      <c r="W41" s="34" t="n">
         <v>44.99</v>
       </c>
       <c r="X41" s="11" t="inlineStr">
@@ -10967,10 +10936,10 @@
           <t>No waders — neoprene socks + quick-dry pants only</t>
         </is>
       </c>
-      <c r="D42" s="54" t="n">
+      <c r="D42" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="E42" s="55" t="n">
+      <c r="E42" s="34" t="n">
         <v>0</v>
       </c>
       <c r="F42" s="11" t="inlineStr">
@@ -11006,10 +10975,10 @@
           <t>Canyon II Stockingfoot Hip Wader, Medium (needs separate wading shoe)</t>
         </is>
       </c>
-      <c r="M42" s="54" t="n">
+      <c r="M42" s="33" t="n">
         <v>20</v>
       </c>
-      <c r="N42" s="55" t="n">
+      <c r="N42" s="34" t="n">
         <v>98.29000000000001</v>
       </c>
       <c r="O42" s="11" t="inlineStr">
@@ -11045,10 +11014,10 @@
           <t>Tributary Stockingfoot Waders</t>
         </is>
       </c>
-      <c r="V42" s="54" t="n">
+      <c r="V42" s="33" t="n">
         <v>38</v>
       </c>
-      <c r="W42" s="55" t="n">
+      <c r="W42" s="34" t="n">
         <v>300</v>
       </c>
       <c r="X42" s="11" t="inlineStr">
@@ -11096,10 +11065,10 @@
           <t>Protective Knee Pads, Thick Sponge Anti-Slip Knee Sleeve</t>
         </is>
       </c>
-      <c r="D43" s="54" t="n">
+      <c r="D43" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="E43" s="55" t="n">
+      <c r="E43" s="34" t="n">
         <v>15.99</v>
       </c>
       <c r="F43" s="11" t="inlineStr">
@@ -11135,10 +11104,10 @@
           <t>Neoprene Strap-On Knee Pads (gardening/volleyball style)</t>
         </is>
       </c>
-      <c r="M43" s="54" t="n">
+      <c r="M43" s="33" t="n">
         <v>8</v>
       </c>
-      <c r="N43" s="55" t="n">
+      <c r="N43" s="34" t="n">
         <v>16</v>
       </c>
       <c r="O43" s="11" t="inlineStr">
@@ -11174,10 +11143,10 @@
           <t>Gel-Cushion Kneeling Pad with adjustable straps</t>
         </is>
       </c>
-      <c r="V43" s="54" t="n">
+      <c r="V43" s="33" t="n">
         <v>14</v>
       </c>
-      <c r="W43" s="55" t="n">
+      <c r="W43" s="34" t="n">
         <v>28</v>
       </c>
       <c r="X43" s="11" t="inlineStr">
@@ -11225,10 +11194,10 @@
           <t>BP-14 14" Black Plastic Gold Pan</t>
         </is>
       </c>
-      <c r="D44" s="54" t="n">
+      <c r="D44" s="33" t="n">
         <v>9</v>
       </c>
-      <c r="E44" s="55" t="n">
+      <c r="E44" s="34" t="n">
         <v>7.26</v>
       </c>
       <c r="F44" s="11" t="inlineStr">
@@ -11264,10 +11233,10 @@
           <t>14" Gravity Trap Gold Pan (green)</t>
         </is>
       </c>
-      <c r="M44" s="54" t="n">
+      <c r="M44" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="N44" s="55" t="n">
+      <c r="N44" s="34" t="n">
         <v>8.99</v>
       </c>
       <c r="O44" s="11" t="inlineStr">
@@ -11303,10 +11272,10 @@
           <t>15" Super Sluice Gold Pan (two-stage riffle pan)</t>
         </is>
       </c>
-      <c r="V44" s="54" t="n">
+      <c r="V44" s="33" t="n">
         <v>13</v>
       </c>
-      <c r="W44" s="55" t="n">
+      <c r="W44" s="34" t="n">
         <v>25</v>
       </c>
       <c r="X44" s="11" t="inlineStr">
@@ -11354,10 +11323,10 @@
           <t>1/2" Mesh Classifier</t>
         </is>
       </c>
-      <c r="D45" s="54" t="n">
+      <c r="D45" s="33" t="n">
         <v>16</v>
       </c>
-      <c r="E45" s="55" t="n">
+      <c r="E45" s="34" t="n">
         <v>25</v>
       </c>
       <c r="F45" s="11" t="inlineStr">
@@ -11393,10 +11362,10 @@
           <t>Stackable Classifier Set (1/2", 1/4", 1/8")</t>
         </is>
       </c>
-      <c r="M45" s="54" t="n">
+      <c r="M45" s="33" t="n">
         <v>30</v>
       </c>
-      <c r="N45" s="55" t="n">
+      <c r="N45" s="34" t="n">
         <v>75</v>
       </c>
       <c r="O45" s="11" t="inlineStr">
@@ -11432,10 +11401,10 @@
           <t>Stainless Mesh Classifier Set incl. 50-mesh fine screen</t>
         </is>
       </c>
-      <c r="V45" s="54" t="n">
+      <c r="V45" s="33" t="n">
         <v>34</v>
       </c>
-      <c r="W45" s="55" t="n">
+      <c r="W45" s="34" t="n">
         <v>65</v>
       </c>
       <c r="X45" s="11" t="inlineStr">
@@ -11483,10 +11452,10 @@
           <t>Plastic Snuffer Bottle</t>
         </is>
       </c>
-      <c r="D46" s="54" t="n">
+      <c r="D46" s="33" t="n">
         <v>1.5</v>
       </c>
-      <c r="E46" s="55" t="n">
+      <c r="E46" s="34" t="n">
         <v>4</v>
       </c>
       <c r="F46" s="11" t="inlineStr">
@@ -11522,10 +11491,10 @@
           <t>2-Pack Glass-Tip Snuffer Bottle with Tweezers</t>
         </is>
       </c>
-      <c r="M46" s="54" t="n">
+      <c r="M46" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="N46" s="55" t="n">
+      <c r="N46" s="34" t="n">
         <v>11.99</v>
       </c>
       <c r="O46" s="11" t="inlineStr">
@@ -11561,10 +11530,10 @@
           <t>Brass-Tip Snuffer Bottle Set</t>
         </is>
       </c>
-      <c r="V46" s="54" t="n">
+      <c r="V46" s="33" t="n">
         <v>2.5</v>
       </c>
-      <c r="W46" s="55" t="n">
+      <c r="W46" s="34" t="n">
         <v>13</v>
       </c>
       <c r="X46" s="11" t="inlineStr">
@@ -11612,10 +11581,10 @@
           <t>Hook and Pick Precision Crevice Tool Set, 6 Pieces</t>
         </is>
       </c>
-      <c r="D47" s="54" t="n">
+      <c r="D47" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="E47" s="55" t="n">
+      <c r="E47" s="34" t="n">
         <v>17.25</v>
       </c>
       <c r="F47" s="11" t="inlineStr">
@@ -11651,10 +11620,10 @@
           <t>Stainless Steel Crevice Tool Set with Magnet</t>
         </is>
       </c>
-      <c r="M47" s="54" t="n">
+      <c r="M47" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="N47" s="55" t="n">
+      <c r="N47" s="34" t="n">
         <v>59.95</v>
       </c>
       <c r="O47" s="11" t="inlineStr">
@@ -11690,10 +11659,10 @@
           <t>Branded Crevice Tool Kit</t>
         </is>
       </c>
-      <c r="V47" s="54" t="n">
+      <c r="V47" s="33" t="n">
         <v>8</v>
       </c>
-      <c r="W47" s="55" t="n">
+      <c r="W47" s="34" t="n">
         <v>25</v>
       </c>
       <c r="X47" s="11" t="inlineStr">
@@ -11741,10 +11710,10 @@
           <t>Plastic Snap-Cap Vials (5-pack)</t>
         </is>
       </c>
-      <c r="D48" s="54" t="n">
+      <c r="D48" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="E48" s="55" t="n">
+      <c r="E48" s="34" t="n">
         <v>5</v>
       </c>
       <c r="F48" s="11" t="inlineStr">
@@ -11780,10 +11749,10 @@
           <t>Glass Vials with Foam-Lined Screw Caps (12-pack)</t>
         </is>
       </c>
-      <c r="M48" s="54" t="n">
+      <c r="M48" s="33" t="n">
         <v>1.5</v>
       </c>
-      <c r="N48" s="55" t="n">
+      <c r="N48" s="34" t="n">
         <v>9.99</v>
       </c>
       <c r="O48" s="11" t="inlineStr">
@@ -11819,10 +11788,10 @@
           <t>Leak-Proof Glass Gold Vials with Measurement Markings</t>
         </is>
       </c>
-      <c r="V48" s="54" t="n">
+      <c r="V48" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="W48" s="55" t="n">
+      <c r="W48" s="34" t="n">
         <v>4</v>
       </c>
       <c r="X48" s="11" t="inlineStr">
@@ -11870,10 +11839,10 @@
           <t>10x Plastic Keychain Loupe</t>
         </is>
       </c>
-      <c r="D49" s="54" t="n">
+      <c r="D49" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="E49" s="55" t="n">
+      <c r="E49" s="34" t="n">
         <v>7.99</v>
       </c>
       <c r="F49" s="11" t="inlineStr">
@@ -11909,10 +11878,10 @@
           <t>30x60 Jeweler's Loupe with Built-In LED Light</t>
         </is>
       </c>
-      <c r="M49" s="54" t="n">
+      <c r="M49" s="33" t="n">
         <v>2.5</v>
       </c>
-      <c r="N49" s="55" t="n">
+      <c r="N49" s="34" t="n">
         <v>8.98</v>
       </c>
       <c r="O49" s="11" t="inlineStr">
@@ -11948,10 +11917,10 @@
           <t>10x Triplet Achromatic Loupe</t>
         </is>
       </c>
-      <c r="V49" s="54" t="n">
+      <c r="V49" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="W49" s="55" t="n">
+      <c r="W49" s="34" t="n">
         <v>20</v>
       </c>
       <c r="X49" s="11" t="inlineStr">
@@ -11999,10 +11968,10 @@
           <t>Folding Garden Trowel</t>
         </is>
       </c>
-      <c r="D50" s="54" t="n">
+      <c r="D50" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="E50" s="55" t="n">
+      <c r="E50" s="34" t="n">
         <v>6.28</v>
       </c>
       <c r="F50" s="11" t="inlineStr">
@@ -12038,10 +12007,10 @@
           <t>The Deuce of Spades UL Trowel</t>
         </is>
       </c>
-      <c r="M50" s="54" t="n">
+      <c r="M50" s="33" t="n">
         <v>0.6</v>
       </c>
-      <c r="N50" s="55" t="n">
+      <c r="N50" s="34" t="n">
         <v>20.95</v>
       </c>
       <c r="O50" s="11" t="inlineStr">
@@ -12077,10 +12046,10 @@
           <t>Full-Tang Stainless Prospecting Hand Shovel</t>
         </is>
       </c>
-      <c r="V50" s="54" t="n">
+      <c r="V50" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="W50" s="55" t="n">
+      <c r="W50" s="34" t="n">
         <v>28</v>
       </c>
       <c r="X50" s="11" t="inlineStr">
@@ -12128,10 +12097,10 @@
           <t>Plain 5-Gallon Bucket</t>
         </is>
       </c>
-      <c r="D51" s="54" t="n">
+      <c r="D51" s="33" t="n">
         <v>32</v>
       </c>
-      <c r="E51" s="55" t="n">
+      <c r="E51" s="34" t="n">
         <v>5</v>
       </c>
       <c r="F51" s="11" t="inlineStr">
@@ -12167,10 +12136,10 @@
           <t>5-Gallon Bucket with Built-In Classifier Lid</t>
         </is>
       </c>
-      <c r="M51" s="54" t="n">
+      <c r="M51" s="33" t="n">
         <v>40</v>
       </c>
-      <c r="N51" s="55" t="n">
+      <c r="N51" s="34" t="n">
         <v>28</v>
       </c>
       <c r="O51" s="11" t="inlineStr">
@@ -12206,10 +12175,10 @@
           <t>Bucket Riffle/Classifier Combo Kit</t>
         </is>
       </c>
-      <c r="V51" s="54" t="n">
+      <c r="V51" s="33" t="n">
         <v>48</v>
       </c>
-      <c r="W51" s="55" t="n">
+      <c r="W51" s="34" t="n">
         <v>45</v>
       </c>
       <c r="X51" s="11" t="inlineStr">
@@ -12257,10 +12226,10 @@
           <t>Estwing BP-14 pan + ASR 1/2" classifier + plastic snuffer + 2 vials</t>
         </is>
       </c>
-      <c r="D52" s="54" t="n">
+      <c r="D52" s="33" t="n">
         <v>30</v>
       </c>
-      <c r="E52" s="55" t="n">
+      <c r="E52" s="34" t="n">
         <v>7.26</v>
       </c>
       <c r="F52" s="11" t="inlineStr">
@@ -12296,10 +12265,10 @@
           <t>Compact Prospecting Kit (pan, 2 classifiers, magnet, magnifier, 3 snuffers, 3 vials) minus sluice</t>
         </is>
       </c>
-      <c r="M52" s="54" t="n">
+      <c r="M52" s="33" t="n">
         <v>38</v>
       </c>
-      <c r="N52" s="55" t="n">
+      <c r="N52" s="34" t="n">
         <v>40</v>
       </c>
       <c r="O52" s="11" t="inlineStr">
@@ -12335,10 +12304,10 @@
           <t>Curated kit: Garrett 14" Gravity Trap pan + stainless classifier set + stainless crevice tools + brass snuffer, packed in a dedicated mesh stuff sack</t>
         </is>
       </c>
-      <c r="V52" s="54" t="n">
+      <c r="V52" s="33" t="n">
         <v>52</v>
       </c>
-      <c r="W52" s="55" t="n">
+      <c r="W52" s="34" t="n">
         <v>69.98999999999999</v>
       </c>
       <c r="X52" s="11" t="inlineStr">
@@ -12386,10 +12355,10 @@
           <t>Trestles 30</t>
         </is>
       </c>
-      <c r="D53" s="54" t="n">
+      <c r="D53" s="33" t="n">
         <v>52</v>
       </c>
-      <c r="E53" s="55" t="n">
+      <c r="E53" s="34" t="n">
         <v>99.95</v>
       </c>
       <c r="F53" s="11" t="inlineStr">
@@ -12425,10 +12394,10 @@
           <t>Revelation 30 (stock, 850fp)</t>
         </is>
       </c>
-      <c r="M53" s="54" t="n">
+      <c r="M53" s="33" t="n">
         <v>19.8</v>
       </c>
-      <c r="N53" s="55" t="n">
+      <c r="N53" s="34" t="n">
         <v>365</v>
       </c>
       <c r="O53" s="11" t="inlineStr">
@@ -12464,10 +12433,10 @@
           <t>Flex 30</t>
         </is>
       </c>
-      <c r="V53" s="54" t="n">
+      <c r="V53" s="33" t="n">
         <v>20.3</v>
       </c>
-      <c r="W53" s="55" t="n">
+      <c r="W53" s="34" t="n">
         <v>365</v>
       </c>
       <c r="X53" s="11" t="inlineStr">
@@ -12665,7 +12634,7 @@
           <t>Rook 65 (men's) / Renn 65 (women's)</t>
         </is>
       </c>
-      <c r="F2" s="56" t="n">
+      <c r="F2" s="39" t="n">
         <v>66</v>
       </c>
       <c r="G2" s="38" t="inlineStr">
@@ -12673,7 +12642,7 @@
           <t>~4 lb 2 oz (66 oz) per Osprey specs; heavier than UL packs but has a real suspended mesh back panel and All Mighty Guarantee warranty</t>
         </is>
       </c>
-      <c r="H2" s="57" t="n">
+      <c r="H2" s="40" t="n">
         <v>205</v>
       </c>
       <c r="I2" s="41" t="inlineStr">
@@ -12758,7 +12727,7 @@
           <t>Flash 55</t>
         </is>
       </c>
-      <c r="F3" s="56" t="n">
+      <c r="F3" s="39" t="n">
         <v>45</v>
       </c>
       <c r="G3" s="38" t="inlineStr">
@@ -12766,7 +12735,7 @@
           <t>2 lb 13 oz (45 oz) men's medium per REI/Switchback Travel specs</t>
         </is>
       </c>
-      <c r="H3" s="57" t="n">
+      <c r="H3" s="40" t="n">
         <v>229</v>
       </c>
       <c r="I3" s="41" t="inlineStr">
@@ -12851,7 +12820,7 @@
           <t>Mariposa 60</t>
         </is>
       </c>
-      <c r="F4" s="56" t="n">
+      <c r="F4" s="39" t="n">
         <v>34.2</v>
       </c>
       <c r="G4" s="38" t="inlineStr">
@@ -12859,7 +12828,7 @@
           <t>2 lb 2.2 oz (34.2 oz) medium, straight hipbelt, per Gossamer Gear specs</t>
         </is>
       </c>
-      <c r="H4" s="57" t="n">
+      <c r="H4" s="40" t="n">
         <v>315</v>
       </c>
       <c r="I4" s="41" t="inlineStr">
@@ -12944,7 +12913,7 @@
           <t>Late Start 1P Tent</t>
         </is>
       </c>
-      <c r="F5" s="56" t="n">
+      <c r="F5" s="39" t="n">
         <v>57</v>
       </c>
       <c r="G5" s="38" t="inlineStr">
@@ -12952,7 +12921,7 @@
           <t>3 lb 9 oz (57 oz) minimum trail weight per REI spec</t>
         </is>
       </c>
-      <c r="H5" s="57" t="n">
+      <c r="H5" s="40" t="n">
         <v>149.95</v>
       </c>
       <c r="I5" s="41" t="inlineStr">
@@ -13037,7 +13006,7 @@
           <t>Elixir 1 Tent with Footprint</t>
         </is>
       </c>
-      <c r="F6" s="56" t="n">
+      <c r="F6" s="39" t="n">
         <v>65</v>
       </c>
       <c r="G6" s="38" t="inlineStr">
@@ -13045,7 +13014,7 @@
           <t>4 lb 1 oz (65 oz) minimum trail weight per REI spec</t>
         </is>
       </c>
-      <c r="H6" s="57" t="n">
+      <c r="H6" s="40" t="n">
         <v>289.95</v>
       </c>
       <c r="I6" s="41" t="inlineStr">
@@ -13130,7 +13099,7 @@
           <t>Dragonfly OSMO 1P Ultralight Backpacking Tent</t>
         </is>
       </c>
-      <c r="F7" s="56" t="n">
+      <c r="F7" s="39" t="n">
         <v>34</v>
       </c>
       <c r="G7" s="38" t="inlineStr">
@@ -13138,7 +13107,7 @@
           <t>~2 lb 2 oz (34 oz) minimum trail weight per NEMO/REI spec</t>
         </is>
       </c>
-      <c r="H7" s="57" t="n">
+      <c r="H7" s="40" t="n">
         <v>499.95</v>
       </c>
       <c r="I7" s="41" t="inlineStr">
@@ -13223,7 +13192,7 @@
           <t>Trestles Elite Eco 20 (or Kelty Cosmic 20 Synthetic)</t>
         </is>
       </c>
-      <c r="F8" s="56" t="n">
+      <c r="F8" s="39" t="n">
         <v>53</v>
       </c>
       <c r="G8" s="38" t="inlineStr">
@@ -13231,7 +13200,7 @@
           <t>Trestles 15 synthetic ~3.3 lb (53 oz) regular; Kelty Cosmic Synthetic 20 runs similar (~2.9-3.5 lb depending on source)</t>
         </is>
       </c>
-      <c r="H8" s="57" t="n">
+      <c r="H8" s="40" t="n">
         <v>179</v>
       </c>
       <c r="I8" s="41" t="inlineStr">
@@ -13316,7 +13285,7 @@
           <t>Revelation 20 (stock, 850fp)</t>
         </is>
       </c>
-      <c r="F9" s="56" t="n">
+      <c r="F9" s="39" t="n">
         <v>26</v>
       </c>
       <c r="G9" s="38" t="inlineStr">
@@ -13324,7 +13293,7 @@
           <t>Stock Revelation 20F, Regular/Regular ~26 oz with 850fp down (950fp version is lighter, ~20.9 oz)</t>
         </is>
       </c>
-      <c r="H9" s="57" t="n">
+      <c r="H9" s="40" t="n">
         <v>280</v>
       </c>
       <c r="I9" s="41" t="inlineStr">
@@ -13409,7 +13378,7 @@
           <t>Alsek 22</t>
         </is>
       </c>
-      <c r="F10" s="56" t="n">
+      <c r="F10" s="39" t="n">
         <v>25.5</v>
       </c>
       <c r="G10" s="38" t="inlineStr">
@@ -13417,7 +13386,7 @@
           <t>25.5 oz stated, range 20.9-27 oz by size; one tested Regular weighed 1 lb 7.3 oz per GearJunkie</t>
         </is>
       </c>
-      <c r="H10" s="57" t="n">
+      <c r="H10" s="40" t="n">
         <v>399</v>
       </c>
       <c r="I10" s="41" t="inlineStr">
@@ -13502,7 +13471,7 @@
           <t>Insulated Static V</t>
         </is>
       </c>
-      <c r="F11" s="56" t="n">
+      <c r="F11" s="39" t="n">
         <v>25</v>
       </c>
       <c r="G11" s="38" t="inlineStr">
@@ -13510,7 +13479,7 @@
           <t>Insulated Static V lists ~25 oz per Klymit specs (Lite version 19.6 oz has lower R-value, check spec before buying — need the full Insulated, not the Lite/Base, to clear R4)</t>
         </is>
       </c>
-      <c r="H11" s="57" t="n">
+      <c r="H11" s="40" t="n">
         <v>74.20999999999999</v>
       </c>
       <c r="I11" s="41" t="inlineStr">
@@ -13595,7 +13564,7 @@
           <t>Tensor All-Season Ultralight Insulated</t>
         </is>
       </c>
-      <c r="F12" s="56" t="n">
+      <c r="F12" s="39" t="n">
         <v>14.1</v>
       </c>
       <c r="G12" s="38" t="inlineStr">
@@ -13603,7 +13572,7 @@
           <t>14.1 oz regular per NEMO/REI specs</t>
         </is>
       </c>
-      <c r="H12" s="57" t="n">
+      <c r="H12" s="40" t="n">
         <v>199.95</v>
       </c>
       <c r="I12" s="41" t="inlineStr">
@@ -13688,7 +13657,7 @@
           <t>Tensor Extreme Conditions</t>
         </is>
       </c>
-      <c r="F13" s="56" t="n">
+      <c r="F13" s="39" t="n">
         <v>19</v>
       </c>
       <c r="G13" s="38" t="inlineStr">
@@ -13696,7 +13665,7 @@
           <t>~1 lb 3 oz (19 oz) per NEMO specs, R-value 8.5</t>
         </is>
       </c>
-      <c r="H13" s="57" t="n">
+      <c r="H13" s="40" t="n">
         <v>259.95</v>
       </c>
       <c r="I13" s="41" t="inlineStr">
@@ -13781,7 +13750,7 @@
           <t>Stuff sack filled with spare clothes (or generic inflatable pillow)</t>
         </is>
       </c>
-      <c r="F14" s="56" t="n">
+      <c r="F14" s="39" t="n">
         <v>2</v>
       </c>
       <c r="G14" s="38" t="inlineStr">
@@ -13789,7 +13758,7 @@
           <t>A stuff sack you're already carrying + a puffy/fleece stuffed inside is ~0 marginal oz; a generic $10 inflatable pillow runs 2-3 oz</t>
         </is>
       </c>
-      <c r="H14" s="57" t="n">
+      <c r="H14" s="40" t="n">
         <v>20</v>
       </c>
       <c r="I14" s="41" t="inlineStr">
@@ -13874,7 +13843,7 @@
           <t>Aeros Down Pillow (Regular)</t>
         </is>
       </c>
-      <c r="F15" s="56" t="n">
+      <c r="F15" s="39" t="n">
         <v>2.5</v>
       </c>
       <c r="G15" s="38" t="inlineStr">
@@ -13882,7 +13851,7 @@
           <t>~2.5 oz per Sea to Summit specs for the down-insulated Regular</t>
         </is>
       </c>
-      <c r="H15" s="57" t="n">
+      <c r="H15" s="40" t="n">
         <v>64.95</v>
       </c>
       <c r="I15" s="41" t="inlineStr">
@@ -13967,7 +13936,7 @@
           <t>Fillo Elite</t>
         </is>
       </c>
-      <c r="F16" s="56" t="n">
+      <c r="F16" s="39" t="n">
         <v>2.5</v>
       </c>
       <c r="G16" s="38" t="inlineStr">
@@ -13975,7 +13944,7 @@
           <t>~2.4-2.6 oz per NEMO specs</t>
         </is>
       </c>
-      <c r="H16" s="57" t="n">
+      <c r="H16" s="40" t="n">
         <v>59.95</v>
       </c>
       <c r="I16" s="41" t="inlineStr">
@@ -14060,7 +14029,7 @@
           <t>Polycryo window-shrink-film sheet</t>
         </is>
       </c>
-      <c r="F17" s="56" t="n">
+      <c r="F17" s="39" t="n">
         <v>2</v>
       </c>
       <c r="G17" s="38" t="inlineStr">
@@ -14068,7 +14037,7 @@
           <t>A cut sheet of polycryo/window film runs ~1-2 oz depending on tent footprint size</t>
         </is>
       </c>
-      <c r="H17" s="57" t="n">
+      <c r="H17" s="40" t="n">
         <v>13</v>
       </c>
       <c r="I17" s="41" t="inlineStr">
@@ -14153,7 +14122,7 @@
           <t>Tyvek HomeWrap sheet</t>
         </is>
       </c>
-      <c r="F18" s="56" t="n">
+      <c r="F18" s="39" t="n">
         <v>5</v>
       </c>
       <c r="G18" s="38" t="inlineStr">
@@ -14161,7 +14130,7 @@
           <t>~4-6 oz depending on footprint size (heavier than polycryo, more durable)</t>
         </is>
       </c>
-      <c r="H18" s="57" t="n">
+      <c r="H18" s="40" t="n">
         <v>22</v>
       </c>
       <c r="I18" s="41" t="inlineStr">
@@ -14246,7 +14215,7 @@
           <t>Matching branded tent footprint (polycro or DCF)</t>
         </is>
       </c>
-      <c r="F19" s="56" t="n">
+      <c r="F19" s="39" t="n">
         <v>3.5</v>
       </c>
       <c r="G19" s="38" t="inlineStr">
@@ -14254,7 +14223,7 @@
           <t>Manufacturer footprints for X-Mid/Duplex run ~2-5 oz depending on material and tent size</t>
         </is>
       </c>
-      <c r="H19" s="57" t="n">
+      <c r="H19" s="40" t="n">
         <v>59</v>
       </c>
       <c r="I19" s="41" t="inlineStr">
@@ -14339,7 +14308,7 @@
           <t>Ziploc freezer bags + a cheap nylon stuff sack (or reused packaging bags)</t>
         </is>
       </c>
-      <c r="F20" s="56" t="n">
+      <c r="F20" s="39" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="38" t="inlineStr">
@@ -14347,7 +14316,7 @@
           <t>A couple of gallon freezer bags + one $6 stuff sack run about 1 oz total</t>
         </is>
       </c>
-      <c r="H20" s="57" t="n">
+      <c r="H20" s="40" t="n">
         <v>12</v>
       </c>
       <c r="I20" s="41" t="inlineStr">
@@ -14432,7 +14401,7 @@
           <t>Ultra-Sil Dry Bag - Set of 3</t>
         </is>
       </c>
-      <c r="F21" s="56" t="n">
+      <c r="F21" s="39" t="n">
         <v>2.5</v>
       </c>
       <c r="G21" s="38" t="inlineStr">
@@ -14440,7 +14409,7 @@
           <t>~1-1.5 oz per bag depending on size; a useful 2-bag set (sleep system + electronics) runs ~2.5 oz combined</t>
         </is>
       </c>
-      <c r="H21" s="57" t="n">
+      <c r="H21" s="40" t="n">
         <v>69.95</v>
       </c>
       <c r="I21" s="41" t="inlineStr">
@@ -14525,7 +14494,7 @@
           <t>DCF Stuff Sack (assorted sizes)</t>
         </is>
       </c>
-      <c r="F22" s="56" t="n">
+      <c r="F22" s="39" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="38" t="inlineStr">
@@ -14533,7 +14502,7 @@
           <t>~0.5-1 oz per bag depending on size — DCF is lighter than silnylon at comparable volume</t>
         </is>
       </c>
-      <c r="H22" s="57" t="n">
+      <c r="H22" s="40" t="n">
         <v>31</v>
       </c>
       <c r="I22" s="41" t="inlineStr">
@@ -14618,7 +14587,7 @@
           <t>Compactor/contractor trash bag (heavy-duty, unscented)</t>
         </is>
       </c>
-      <c r="F23" s="56" t="n">
+      <c r="F23" s="39" t="n">
         <v>1.4</v>
       </c>
       <c r="G23" s="38" t="inlineStr">
@@ -14626,7 +14595,7 @@
           <t>18-gallon compactor bags run ~1.4 oz per 99Boulders/community measurements</t>
         </is>
       </c>
-      <c r="H23" s="57" t="n">
+      <c r="H23" s="40" t="n">
         <v>10</v>
       </c>
       <c r="I23" s="41" t="inlineStr">
@@ -14711,7 +14680,7 @@
           <t>Nylofume Pack Liner Bag</t>
         </is>
       </c>
-      <c r="F24" s="56" t="n">
+      <c r="F24" s="39" t="n">
         <v>0.9</v>
       </c>
       <c r="G24" s="38" t="inlineStr">
@@ -14719,7 +14688,7 @@
           <t>0.9 oz per bag per Litesmith/99Boulders specs</t>
         </is>
       </c>
-      <c r="H24" s="57" t="n">
+      <c r="H24" s="40" t="n">
         <v>2.49</v>
       </c>
       <c r="I24" s="41" t="inlineStr">
@@ -14804,7 +14773,7 @@
           <t>Evac Lightweight Dry Bag (35L)</t>
         </is>
       </c>
-      <c r="F25" s="56" t="n">
+      <c r="F25" s="39" t="n">
         <v>3.5</v>
       </c>
       <c r="G25" s="38" t="inlineStr">
@@ -14812,7 +14781,7 @@
           <t>~3.5 oz (100g) for the 35L/70L eVac-style liner per Sea to Summit specs</t>
         </is>
       </c>
-      <c r="H25" s="57" t="n">
+      <c r="H25" s="40" t="n">
         <v>44.95</v>
       </c>
       <c r="I25" s="41" t="inlineStr">
@@ -14897,7 +14866,7 @@
           <t>Amicus Stove Cookset Combo</t>
         </is>
       </c>
-      <c r="F26" s="56" t="n">
+      <c r="F26" s="39" t="n">
         <v>11.2</v>
       </c>
       <c r="G26" s="38" t="inlineStr">
@@ -14905,7 +14874,7 @@
           <t>REI spec 11.2oz for the stove + 0.6L aluminum pot/cup combo</t>
         </is>
       </c>
-      <c r="H26" s="57" t="n">
+      <c r="H26" s="40" t="n">
         <v>49.95</v>
       </c>
       <c r="I26" s="41" t="inlineStr">
@@ -14952,7 +14921,7 @@
         <v>5</v>
       </c>
       <c r="R26" s="37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S26" s="38" t="inlineStr">
         <is>
@@ -14990,7 +14959,7 @@
           <t>WindMaster (4Flex)</t>
         </is>
       </c>
-      <c r="F27" s="56" t="n">
+      <c r="F27" s="39" t="n">
         <v>3.5</v>
       </c>
       <c r="G27" s="38" t="inlineStr">
@@ -14998,7 +14967,7 @@
           <t>stove 2.5oz + 4Flex 4-arm pot stand ~1oz, per Soto spec, matches independent reviews</t>
         </is>
       </c>
-      <c r="H27" s="57" t="n">
+      <c r="H27" s="40" t="n">
         <v>69.95</v>
       </c>
       <c r="I27" s="41" t="inlineStr">
@@ -15045,7 +15014,7 @@
         <v>4</v>
       </c>
       <c r="R27" s="37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S27" s="38" t="inlineStr">
         <is>
@@ -15083,7 +15052,7 @@
           <t>Stash</t>
         </is>
       </c>
-      <c r="F28" s="56" t="n">
+      <c r="F28" s="39" t="n">
         <v>7.1</v>
       </c>
       <c r="G28" s="38" t="inlineStr">
@@ -15091,7 +15060,7 @@
           <t>full kit (stove + 0.8L pot + optional stabilizer), per Jetboil spec — matches Halfway Anywhere 2025 PCT survey listing</t>
         </is>
       </c>
-      <c r="H28" s="57" t="n">
+      <c r="H28" s="40" t="n">
         <v>131</v>
       </c>
       <c r="I28" s="41" t="inlineStr">
@@ -15138,7 +15107,7 @@
         <v>4</v>
       </c>
       <c r="R28" s="37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S28" s="38" t="inlineStr">
         <is>
@@ -15176,7 +15145,7 @@
           <t>A004-025001 Aluminum Sauce Pan, 1-Quart</t>
         </is>
       </c>
-      <c r="F29" s="56" t="n">
+      <c r="F29" s="39" t="n">
         <v>6</v>
       </c>
       <c r="G29" s="38" t="inlineStr">
@@ -15184,7 +15153,7 @@
           <t>typical stamped-aluminum camp pot weight; EST from category norms, not individually spec-verified this session; only 1qt capacity — buy two for group boiling of 6</t>
         </is>
       </c>
-      <c r="H29" s="57" t="n">
+      <c r="H29" s="40" t="n">
         <v>12.99</v>
       </c>
       <c r="I29" s="41" t="inlineStr">
@@ -15231,7 +15200,7 @@
         <v>5</v>
       </c>
       <c r="R29" s="37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S29" s="38" t="inlineStr">
         <is>
@@ -15269,7 +15238,7 @@
           <t>750ml Titanium Pot with Bail Handle (POT-750-BH)</t>
         </is>
       </c>
-      <c r="F30" s="56" t="n">
+      <c r="F30" s="39" t="n">
         <v>4.1</v>
       </c>
       <c r="G30" s="38" t="inlineStr">
@@ -15277,7 +15246,7 @@
           <t>TOAKS spec 4.1oz/116g, widely confirmed in reviews</t>
         </is>
       </c>
-      <c r="H30" s="57" t="n">
+      <c r="H30" s="40" t="n">
         <v>30</v>
       </c>
       <c r="I30" s="41" t="inlineStr">
@@ -15324,7 +15293,7 @@
         <v>4</v>
       </c>
       <c r="R30" s="37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S30" s="38" t="inlineStr">
         <is>
@@ -15362,7 +15331,7 @@
           <t>Trek 900 Titanium Cookset</t>
         </is>
       </c>
-      <c r="F31" s="56" t="n">
+      <c r="F31" s="39" t="n">
         <v>6</v>
       </c>
       <c r="G31" s="38" t="inlineStr">
@@ -15370,7 +15339,7 @@
           <t>REI spec 6oz/170g for the 2-piece cookset (900ml pot + pan/lid); swapped in for the Evernew pasta pot, which is discontinued/unavailable in the US as of 2026</t>
         </is>
       </c>
-      <c r="H31" s="57" t="n">
+      <c r="H31" s="40" t="n">
         <v>54.95</v>
       </c>
       <c r="I31" s="41" t="inlineStr">
@@ -15417,7 +15386,7 @@
         <v>3</v>
       </c>
       <c r="R31" s="37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S31" s="38" t="inlineStr">
         <is>
@@ -15455,7 +15424,7 @@
           <t>Butane/Propane Mix Fuel, 7.75oz (220g)</t>
         </is>
       </c>
-      <c r="F32" s="56" t="n">
+      <c r="F32" s="39" t="n">
         <v>7.75</v>
       </c>
       <c r="G32" s="38" t="inlineStr">
@@ -15463,7 +15432,7 @@
           <t>Walmart spec, 220g fuel canister</t>
         </is>
       </c>
-      <c r="H32" s="57" t="n">
+      <c r="H32" s="40" t="n">
         <v>5.97</v>
       </c>
       <c r="I32" s="41" t="inlineStr">
@@ -15510,7 +15479,7 @@
         <v>5</v>
       </c>
       <c r="R32" s="37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S32" s="38" t="inlineStr">
         <is>
@@ -15548,7 +15517,7 @@
           <t>IsoPro 8oz/227g canister</t>
         </is>
       </c>
-      <c r="F33" s="56" t="n">
+      <c r="F33" s="39" t="n">
         <v>13.7</v>
       </c>
       <c r="G33" s="38" t="inlineStr">
@@ -15556,7 +15525,7 @@
           <t>manufacturer spec, 227g fuel</t>
         </is>
       </c>
-      <c r="H33" s="57" t="n">
+      <c r="H33" s="40" t="n">
         <v>6.95</v>
       </c>
       <c r="I33" s="41" t="inlineStr">
@@ -15603,7 +15572,7 @@
         <v>5</v>
       </c>
       <c r="R33" s="37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S33" s="38" t="inlineStr">
         <is>
@@ -15641,7 +15610,7 @@
           <t>IsoPro (same blend, cold-weather use case)</t>
         </is>
       </c>
-      <c r="F34" s="56" t="n">
+      <c r="F34" s="39" t="n">
         <v>7.6</v>
       </c>
       <c r="G34" s="38" t="inlineStr">
@@ -15649,7 +15618,7 @@
           <t>4oz/113g canister spec</t>
         </is>
       </c>
-      <c r="H34" s="57" t="n">
+      <c r="H34" s="40" t="n">
         <v>5.95</v>
       </c>
       <c r="I34" s="41" t="inlineStr">
@@ -15696,7 +15665,7 @@
         <v>5</v>
       </c>
       <c r="R34" s="37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S34" s="38" t="inlineStr">
         <is>
@@ -15734,7 +15703,7 @@
           <t>Titanium Spork</t>
         </is>
       </c>
-      <c r="F35" s="56" t="n">
+      <c r="F35" s="39" t="n">
         <v>0.6</v>
       </c>
       <c r="G35" s="38" t="inlineStr">
@@ -15742,7 +15711,7 @@
           <t>typical spec for generic Ti sporks sold on Amazon</t>
         </is>
       </c>
-      <c r="H35" s="57" t="n">
+      <c r="H35" s="40" t="n">
         <v>9.949999999999999</v>
       </c>
       <c r="I35" s="41" t="inlineStr">
@@ -15827,7 +15796,7 @@
           <t>Frontier Ultralight Spoon - Long Handle</t>
         </is>
       </c>
-      <c r="F36" s="56" t="n">
+      <c r="F36" s="39" t="n">
         <v>0.6</v>
       </c>
       <c r="G36" s="38" t="inlineStr">
@@ -15835,7 +15804,7 @@
           <t>manufacturer spec 17g/0.6oz</t>
         </is>
       </c>
-      <c r="H36" s="57" t="n">
+      <c r="H36" s="40" t="n">
         <v>10.95</v>
       </c>
       <c r="I36" s="41" t="inlineStr">
@@ -15920,7 +15889,7 @@
           <t>Titanium Spork</t>
         </is>
       </c>
-      <c r="F37" s="56" t="n">
+      <c r="F37" s="39" t="n">
         <v>0.6</v>
       </c>
       <c r="G37" s="38" t="inlineStr">
@@ -15928,7 +15897,7 @@
           <t>manufacturer spec ~17g</t>
         </is>
       </c>
-      <c r="H37" s="57" t="n">
+      <c r="H37" s="40" t="n">
         <v>9.949999999999999</v>
       </c>
       <c r="I37" s="41" t="inlineStr">
@@ -16013,7 +15982,7 @@
           <t>Squeeze (SP2129)</t>
         </is>
       </c>
-      <c r="F38" s="56" t="n">
+      <c r="F38" s="39" t="n">
         <v>3</v>
       </c>
       <c r="G38" s="38" t="inlineStr">
@@ -16021,7 +15990,7 @@
           <t>Sawyer spec ~3oz for filter alone</t>
         </is>
       </c>
-      <c r="H38" s="57" t="n">
+      <c r="H38" s="40" t="n">
         <v>45.95</v>
       </c>
       <c r="I38" s="41" t="inlineStr">
@@ -16068,7 +16037,7 @@
         <v>4</v>
       </c>
       <c r="R38" s="37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S38" s="38" t="inlineStr">
         <is>
@@ -16106,7 +16075,7 @@
           <t>BeFree 1.0L</t>
         </is>
       </c>
-      <c r="F39" s="56" t="n">
+      <c r="F39" s="39" t="n">
         <v>2.3</v>
       </c>
       <c r="G39" s="38" t="inlineStr">
@@ -16114,7 +16083,7 @@
           <t>Katadyn spec 2.3oz filter+pouch</t>
         </is>
       </c>
-      <c r="H39" s="57" t="n">
+      <c r="H39" s="40" t="n">
         <v>52.95</v>
       </c>
       <c r="I39" s="41" t="inlineStr">
@@ -16161,7 +16130,7 @@
         <v>4</v>
       </c>
       <c r="R39" s="37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S39" s="38" t="inlineStr">
         <is>
@@ -16199,7 +16168,7 @@
           <t>GeoPress</t>
         </is>
       </c>
-      <c r="F40" s="56" t="n">
+      <c r="F40" s="39" t="n">
         <v>15.9</v>
       </c>
       <c r="G40" s="38" t="inlineStr">
@@ -16207,7 +16176,7 @@
           <t>manufacturer spec 15.9oz/450g — notably heavier than squeeze filters</t>
         </is>
       </c>
-      <c r="H40" s="57" t="n">
+      <c r="H40" s="40" t="n">
         <v>99.95</v>
       </c>
       <c r="I40" s="41" t="inlineStr">
@@ -16254,7 +16223,7 @@
         <v>5</v>
       </c>
       <c r="R40" s="37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S40" s="38" t="inlineStr">
         <is>
@@ -16292,7 +16261,7 @@
           <t>1L reused disposable bottle</t>
         </is>
       </c>
-      <c r="F41" s="56" t="n">
+      <c r="F41" s="39" t="n">
         <v>1.6</v>
       </c>
       <c r="G41" s="38" t="inlineStr">
@@ -16300,7 +16269,7 @@
           <t>empty bottle weight, widely cited in UL community measurements</t>
         </is>
       </c>
-      <c r="H41" s="57" t="n">
+      <c r="H41" s="40" t="n">
         <v>2.17</v>
       </c>
       <c r="I41" s="41" t="inlineStr">
@@ -16385,7 +16354,7 @@
           <t>Stow 1L collapsible bottle</t>
         </is>
       </c>
-      <c r="F42" s="56" t="n">
+      <c r="F42" s="39" t="n">
         <v>1.4</v>
       </c>
       <c r="G42" s="38" t="inlineStr">
@@ -16393,7 +16362,7 @@
           <t>manufacturer spec 1.4oz</t>
         </is>
       </c>
-      <c r="H42" s="57" t="n">
+      <c r="H42" s="40" t="n">
         <v>18</v>
       </c>
       <c r="I42" s="41" t="inlineStr">
@@ -16474,7 +16443,7 @@
           <t>Vecto 2L</t>
         </is>
       </c>
-      <c r="F43" s="56" t="n">
+      <c r="F43" s="39" t="n">
         <v>3.6</v>
       </c>
       <c r="G43" s="38" t="inlineStr">
@@ -16482,7 +16451,7 @@
           <t>manufacturer spec ~3.6oz for the 2L bag</t>
         </is>
       </c>
-      <c r="H43" s="57" t="n">
+      <c r="H43" s="40" t="n">
         <v>25</v>
       </c>
       <c r="I43" s="41" t="inlineStr">
@@ -16567,7 +16536,7 @@
           <t>Easy to Throw Bear Bag Hanging Kit (#371486)</t>
         </is>
       </c>
-      <c r="F44" s="56" t="n">
+      <c r="F44" s="39" t="n">
         <v>6</v>
       </c>
       <c r="G44" s="38" t="inlineStr">
@@ -16575,7 +16544,7 @@
           <t>typical DIY kit weight — 50ft of paracord/Zpacks cord + food sack; EST from common DIY builds</t>
         </is>
       </c>
-      <c r="H44" s="57" t="n">
+      <c r="H44" s="40" t="n">
         <v>27</v>
       </c>
       <c r="I44" s="41" t="inlineStr">
@@ -16622,7 +16591,7 @@
         <v>2</v>
       </c>
       <c r="R44" s="37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S44" s="38" t="inlineStr">
         <is>
@@ -16660,7 +16629,7 @@
           <t>Major XL (with OPSak liner)</t>
         </is>
       </c>
-      <c r="F45" s="56" t="n">
+      <c r="F45" s="39" t="n">
         <v>10.8</v>
       </c>
       <c r="G45" s="38" t="inlineStr">
@@ -16668,7 +16637,7 @@
           <t>Ursack Major ~7.8oz + OPSak liner ~1oz + typical XL upsizing; Ursack Major listed at 8.8oz in category roundups, XL slightly more</t>
         </is>
       </c>
-      <c r="H45" s="57" t="n">
+      <c r="H45" s="40" t="n">
         <v>149.95</v>
       </c>
       <c r="I45" s="41" t="inlineStr">
@@ -16715,7 +16684,7 @@
         <v>4</v>
       </c>
       <c r="R45" s="37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S45" s="38" t="inlineStr">
         <is>
@@ -16753,7 +16722,7 @@
           <t>BV500</t>
         </is>
       </c>
-      <c r="F46" s="56" t="n">
+      <c r="F46" s="39" t="n">
         <v>41</v>
       </c>
       <c r="G46" s="38" t="inlineStr">
@@ -16761,7 +16730,7 @@
           <t>manufacturer/retailer spec ~2lb 9oz (41oz)</t>
         </is>
       </c>
-      <c r="H46" s="57" t="n">
+      <c r="H46" s="40" t="n">
         <v>99.95</v>
       </c>
       <c r="I46" s="41" t="inlineStr">
@@ -16808,7 +16777,7 @@
         <v>4</v>
       </c>
       <c r="R46" s="37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S46" s="38" t="inlineStr">
         <is>
@@ -16846,7 +16815,7 @@
           <t>Tikkina</t>
         </is>
       </c>
-      <c r="F47" s="56" t="n">
+      <c r="F47" s="39" t="n">
         <v>2.9</v>
       </c>
       <c r="G47" s="38" t="inlineStr">
@@ -16854,7 +16823,7 @@
           <t>Petzl spec 82g/2.9oz including batteries</t>
         </is>
       </c>
-      <c r="H47" s="57" t="n">
+      <c r="H47" s="40" t="n">
         <v>19.95</v>
       </c>
       <c r="I47" s="41" t="inlineStr">
@@ -16935,7 +16904,7 @@
           <t>Spot 400</t>
         </is>
       </c>
-      <c r="F48" s="56" t="n">
+      <c r="F48" s="39" t="n">
         <v>3</v>
       </c>
       <c r="G48" s="38" t="inlineStr">
@@ -16943,7 +16912,7 @@
           <t>Black Diamond spec ~90g/3.2oz with batteries; commonly listed ~3oz</t>
         </is>
       </c>
-      <c r="H48" s="57" t="n">
+      <c r="H48" s="40" t="n">
         <v>59.95</v>
       </c>
       <c r="I48" s="41" t="inlineStr">
@@ -17028,7 +16997,7 @@
           <t>NU25 (rechargeable)</t>
         </is>
       </c>
-      <c r="F49" s="56" t="n">
+      <c r="F49" s="39" t="n">
         <v>1.75</v>
       </c>
       <c r="G49" s="38" t="inlineStr">
@@ -17036,7 +17005,7 @@
           <t>Nitecore spec ~48g/1.7oz — notably lighter than AAA headlamps since it's built-in rechargeable</t>
         </is>
       </c>
-      <c r="H49" s="57" t="n">
+      <c r="H49" s="40" t="n">
         <v>54.95</v>
       </c>
       <c r="I49" s="41" t="inlineStr">
@@ -17121,7 +17090,7 @@
           <t>Power Bank, 10,000mAh Portable Charger (PowerIQ, USB-C)</t>
         </is>
       </c>
-      <c r="F50" s="56" t="n">
+      <c r="F50" s="39" t="n">
         <v>6.3</v>
       </c>
       <c r="G50" s="38" t="inlineStr">
@@ -17129,7 +17098,7 @@
           <t>Anker spec ~180g/6.3oz</t>
         </is>
       </c>
-      <c r="H50" s="57" t="n">
+      <c r="H50" s="40" t="n">
         <v>21.99</v>
       </c>
       <c r="I50" s="41" t="inlineStr">
@@ -17210,7 +17179,7 @@
           <t>NB10000 Gen 3</t>
         </is>
       </c>
-      <c r="F51" s="56" t="n">
+      <c r="F51" s="39" t="n">
         <v>5.1</v>
       </c>
       <c r="G51" s="38" t="inlineStr">
@@ -17218,7 +17187,7 @@
           <t>Nitecore spec ~144g/5.1oz</t>
         </is>
       </c>
-      <c r="H51" s="57" t="n">
+      <c r="H51" s="40" t="n">
         <v>64.95</v>
       </c>
       <c r="I51" s="41" t="inlineStr">
@@ -17299,7 +17268,7 @@
           <t>NB10000 Gen 4</t>
         </is>
       </c>
-      <c r="F52" s="56" t="n">
+      <c r="F52" s="39" t="n">
         <v>5</v>
       </c>
       <c r="G52" s="38" t="inlineStr">
@@ -17307,7 +17276,7 @@
           <t>manufacturer press release claims 143g/5.0oz with improved IPX7 rating</t>
         </is>
       </c>
-      <c r="H52" s="57" t="n">
+      <c r="H52" s="40" t="n">
         <v>83.95</v>
       </c>
       <c r="I52" s="41" t="inlineStr">
@@ -17392,7 +17361,7 @@
           <t>inReach Mini 2 (weekly rental)</t>
         </is>
       </c>
-      <c r="F53" s="56" t="n">
+      <c r="F53" s="39" t="n">
         <v>3.5</v>
       </c>
       <c r="G53" s="38" t="inlineStr">
@@ -17400,7 +17369,7 @@
           <t>Garmin spec 3.5oz for the device itself; rental means no ownership weight/cost beyond the trip</t>
         </is>
       </c>
-      <c r="H53" s="57" t="n">
+      <c r="H53" s="40" t="n">
         <v>100</v>
       </c>
       <c r="I53" s="41" t="inlineStr">
@@ -17447,7 +17416,7 @@
         <v>4</v>
       </c>
       <c r="R53" s="37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S53" s="38" t="inlineStr">
         <is>
@@ -17485,7 +17454,7 @@
           <t>Satellite Communicator</t>
         </is>
       </c>
-      <c r="F54" s="56" t="n">
+      <c r="F54" s="39" t="n">
         <v>5.4</v>
       </c>
       <c r="G54" s="38" t="inlineStr">
@@ -17493,7 +17462,7 @@
           <t>ZOLEO manufacturer spec ~155g/5.4oz</t>
         </is>
       </c>
-      <c r="H54" s="57" t="n">
+      <c r="H54" s="40" t="n">
         <v>199</v>
       </c>
       <c r="I54" s="41" t="inlineStr">
@@ -17540,7 +17509,7 @@
         <v>4</v>
       </c>
       <c r="R54" s="37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S54" s="38" t="inlineStr">
         <is>
@@ -17578,7 +17547,7 @@
           <t>inReach Mini 2 (owned, Safety plan)</t>
         </is>
       </c>
-      <c r="F55" s="56" t="n">
+      <c r="F55" s="39" t="n">
         <v>3.5</v>
       </c>
       <c r="G55" s="38" t="inlineStr">
@@ -17586,7 +17555,7 @@
           <t>Garmin spec 3.5oz</t>
         </is>
       </c>
-      <c r="H55" s="57" t="n">
+      <c r="H55" s="40" t="n">
         <v>349.99</v>
       </c>
       <c r="I55" s="41" t="inlineStr">
@@ -17633,7 +17602,7 @@
         <v>4</v>
       </c>
       <c r="R55" s="37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S55" s="38" t="inlineStr">
         <is>
@@ -17671,7 +17640,7 @@
           <t>Free account + printed topo</t>
         </is>
       </c>
-      <c r="F56" s="56" t="n">
+      <c r="F56" s="39" t="n">
         <v>0</v>
       </c>
       <c r="G56" s="38" t="inlineStr">
@@ -17679,7 +17648,7 @@
           <t>n/a — software; printed map ~1oz on paper</t>
         </is>
       </c>
-      <c r="H56" s="57" t="n">
+      <c r="H56" s="40" t="n">
         <v>0</v>
       </c>
       <c r="I56" s="41" t="inlineStr">
@@ -17764,7 +17733,7 @@
           <t>Premium subscription</t>
         </is>
       </c>
-      <c r="F57" s="56" t="n">
+      <c r="F57" s="39" t="n">
         <v>0</v>
       </c>
       <c r="G57" s="38" t="inlineStr">
@@ -17772,7 +17741,7 @@
           <t>n/a — software</t>
         </is>
       </c>
-      <c r="H57" s="57" t="n">
+      <c r="H57" s="40" t="n">
         <v>39.99</v>
       </c>
       <c r="I57" s="41" t="inlineStr">
@@ -17857,7 +17826,7 @@
           <t>Regional trail guide (per-trail purchase)</t>
         </is>
       </c>
-      <c r="F58" s="56" t="n">
+      <c r="F58" s="39" t="n">
         <v>0</v>
       </c>
       <c r="G58" s="38" t="inlineStr">
@@ -17865,7 +17834,7 @@
           <t>n/a — software</t>
         </is>
       </c>
-      <c r="H58" s="57" t="n">
+      <c r="H58" s="40" t="n">
         <v>14.99</v>
       </c>
       <c r="I58" s="41" t="inlineStr">
@@ -17950,7 +17919,7 @@
           <t>No.8 Carbon/Stainless folding knife</t>
         </is>
       </c>
-      <c r="F59" s="56" t="n">
+      <c r="F59" s="39" t="n">
         <v>1.6</v>
       </c>
       <c r="G59" s="38" t="inlineStr">
@@ -17958,7 +17927,7 @@
           <t>Opinel spec ~45g/1.6oz for the No.8</t>
         </is>
       </c>
-      <c r="H59" s="57" t="n">
+      <c r="H59" s="40" t="n">
         <v>22</v>
       </c>
       <c r="I59" s="41" t="inlineStr">
@@ -18039,7 +18008,7 @@
           <t>Wingman</t>
         </is>
       </c>
-      <c r="F60" s="56" t="n">
+      <c r="F60" s="39" t="n">
         <v>7.2</v>
       </c>
       <c r="G60" s="38" t="inlineStr">
@@ -18047,7 +18016,7 @@
           <t>Leatherman spec 7.2oz/204g</t>
         </is>
       </c>
-      <c r="H60" s="57" t="n">
+      <c r="H60" s="40" t="n">
         <v>49.95</v>
       </c>
       <c r="I60" s="41" t="inlineStr">
@@ -18128,7 +18097,7 @@
           <t>Skeletool CX</t>
         </is>
       </c>
-      <c r="F61" s="56" t="n">
+      <c r="F61" s="39" t="n">
         <v>5</v>
       </c>
       <c r="G61" s="38" t="inlineStr">
@@ -18136,7 +18105,7 @@
           <t>Leatherman spec 5.0oz/142g</t>
         </is>
       </c>
-      <c r="H61" s="57" t="n">
+      <c r="H61" s="40" t="n">
         <v>99.95</v>
       </c>
       <c r="I61" s="41" t="inlineStr">
@@ -18217,7 +18186,7 @@
           <t>Build-your-own kit (gauze, tape, meds, moleskin, blister care)</t>
         </is>
       </c>
-      <c r="F62" s="56" t="n">
+      <c r="F62" s="39" t="n">
         <v>4</v>
       </c>
       <c r="G62" s="38" t="inlineStr">
@@ -18225,7 +18194,7 @@
           <t>EST — typical DIY minimal kit weight for group use; not individually itemized/weighed this session</t>
         </is>
       </c>
-      <c r="H62" s="57" t="n">
+      <c r="H62" s="40" t="n">
         <v>22</v>
       </c>
       <c r="I62" s="41" t="inlineStr">
@@ -18272,7 +18241,7 @@
         <v>2</v>
       </c>
       <c r="R62" s="37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S62" s="38" t="inlineStr">
         <is>
@@ -18310,7 +18279,7 @@
           <t>Ultralight/Watertight .7</t>
         </is>
       </c>
-      <c r="F63" s="56" t="n">
+      <c r="F63" s="39" t="n">
         <v>4.4</v>
       </c>
       <c r="G63" s="38" t="inlineStr">
@@ -18318,7 +18287,7 @@
           <t>AMK spec 4.4oz</t>
         </is>
       </c>
-      <c r="H63" s="57" t="n">
+      <c r="H63" s="40" t="n">
         <v>44.99</v>
       </c>
       <c r="I63" s="41" t="inlineStr">
@@ -18365,7 +18334,7 @@
         <v>4</v>
       </c>
       <c r="R63" s="37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S63" s="38" t="inlineStr">
         <is>
@@ -18403,7 +18372,7 @@
           <t>Mountain Series Explorer</t>
         </is>
       </c>
-      <c r="F64" s="56" t="n">
+      <c r="F64" s="39" t="n">
         <v>16</v>
       </c>
       <c r="G64" s="38" t="inlineStr">
@@ -18411,7 +18380,7 @@
           <t>AMK spec/listing; built for 4 people/7 days per AMK product description, oversized for 6/1-night but most complete</t>
         </is>
       </c>
-      <c r="H64" s="57" t="n">
+      <c r="H64" s="40" t="n">
         <v>86.48999999999999</v>
       </c>
       <c r="I64" s="41" t="inlineStr">
@@ -18458,7 +18427,7 @@
         <v>4</v>
       </c>
       <c r="R64" s="37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S64" s="38" t="inlineStr">
         <is>
@@ -18496,7 +18465,7 @@
           <t>Backpackers Trowel</t>
         </is>
       </c>
-      <c r="F65" s="56" t="n">
+      <c r="F65" s="39" t="n">
         <v>1.5</v>
       </c>
       <c r="G65" s="38" t="inlineStr">
@@ -18504,7 +18473,7 @@
           <t>typical plastic trowel weight ~1.5oz</t>
         </is>
       </c>
-      <c r="H65" s="57" t="n">
+      <c r="H65" s="40" t="n">
         <v>8.75</v>
       </c>
       <c r="I65" s="41" t="inlineStr">
@@ -18551,7 +18520,7 @@
         <v>5</v>
       </c>
       <c r="R65" s="37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S65" s="38" t="inlineStr">
         <is>
@@ -18589,7 +18558,7 @@
           <t>Cathole Trowel</t>
         </is>
       </c>
-      <c r="F66" s="56" t="n">
+      <c r="F66" s="39" t="n">
         <v>2.4</v>
       </c>
       <c r="G66" s="38" t="inlineStr">
@@ -18597,7 +18566,7 @@
           <t>manufacturer spec ~2.4oz</t>
         </is>
       </c>
-      <c r="H66" s="57" t="n">
+      <c r="H66" s="40" t="n">
         <v>7.95</v>
       </c>
       <c r="I66" s="41" t="inlineStr">
@@ -18644,7 +18613,7 @@
         <v>5</v>
       </c>
       <c r="R66" s="37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S66" s="38" t="inlineStr">
         <is>
@@ -18682,7 +18651,7 @@
           <t>The DirtSaw Deuce #2 Trowel</t>
         </is>
       </c>
-      <c r="F67" s="56" t="n">
+      <c r="F67" s="39" t="n">
         <v>0.6</v>
       </c>
       <c r="G67" s="38" t="inlineStr">
@@ -18690,7 +18659,7 @@
           <t>manufacturer spec ~17g/0.6oz for the #2 model</t>
         </is>
       </c>
-      <c r="H67" s="57" t="n">
+      <c r="H67" s="40" t="n">
         <v>21.95</v>
       </c>
       <c r="I67" s="41" t="inlineStr">
@@ -18737,7 +18706,7 @@
         <v>4</v>
       </c>
       <c r="R67" s="37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S67" s="38" t="inlineStr">
         <is>
@@ -18775,7 +18744,7 @@
           <t>Travel-size toothbrush, toothpaste, TP, hand sanitizer</t>
         </is>
       </c>
-      <c r="F68" s="56" t="n">
+      <c r="F68" s="39" t="n">
         <v>3.5</v>
       </c>
       <c r="G68" s="38" t="inlineStr">
@@ -18783,7 +18752,7 @@
           <t>small personal hygiene bag, EST from category norms</t>
         </is>
       </c>
-      <c r="H68" s="57" t="n">
+      <c r="H68" s="40" t="n">
         <v>3.94</v>
       </c>
       <c r="I68" s="41" t="inlineStr">
@@ -18864,7 +18833,7 @@
           <t>Small toiletry bag + biodegradable wipes</t>
         </is>
       </c>
-      <c r="F69" s="56" t="n">
+      <c r="F69" s="39" t="n">
         <v>4</v>
       </c>
       <c r="G69" s="38" t="inlineStr">
@@ -18872,7 +18841,7 @@
           <t>small personal hygiene bag with wipes, EST from category norms</t>
         </is>
       </c>
-      <c r="H69" s="57" t="n">
+      <c r="H69" s="40" t="n">
         <v>9</v>
       </c>
       <c r="I69" s="41" t="inlineStr">
@@ -18953,7 +18922,7 @@
           <t>Ultralight toiletry kit + pack towel wipes + sunscreen/lip balm travel set</t>
         </is>
       </c>
-      <c r="F70" s="56" t="n">
+      <c r="F70" s="39" t="n">
         <v>5</v>
       </c>
       <c r="G70" s="38" t="inlineStr">
@@ -18961,7 +18930,7 @@
           <t>fuller personal hygiene kit, EST from category norms</t>
         </is>
       </c>
-      <c r="H70" s="57" t="n">
+      <c r="H70" s="40" t="n">
         <v>15</v>
       </c>
       <c r="I70" s="41" t="inlineStr">
@@ -19042,7 +19011,7 @@
           <t>Aluminum adjustable trekking poles (pair)</t>
         </is>
       </c>
-      <c r="F71" s="56" t="n">
+      <c r="F71" s="39" t="n">
         <v>18</v>
       </c>
       <c r="G71" s="38" t="inlineStr">
@@ -19050,7 +19019,7 @@
           <t>typical aluminum adjustable pole pair weight per category comparisons; EST from category norms</t>
         </is>
       </c>
-      <c r="H71" s="57" t="n">
+      <c r="H71" s="40" t="n">
         <v>49.99</v>
       </c>
       <c r="I71" s="41" t="inlineStr">
@@ -19131,7 +19100,7 @@
           <t>Carbon Fiber Quick Lock (pair)</t>
         </is>
       </c>
-      <c r="F72" s="56" t="n">
+      <c r="F72" s="39" t="n">
         <v>8.1</v>
       </c>
       <c r="G72" s="38" t="inlineStr">
@@ -19139,7 +19108,7 @@
           <t>per CleverHiker/OutdoorGearLab testing, 8.1oz for the pair</t>
         </is>
       </c>
-      <c r="H72" s="57" t="n">
+      <c r="H72" s="40" t="n">
         <v>64.98999999999999</v>
       </c>
       <c r="I72" s="41" t="inlineStr">
@@ -19224,7 +19193,7 @@
           <t>Distance Carbon Z (pair)</t>
         </is>
       </c>
-      <c r="F73" s="56" t="n">
+      <c r="F73" s="39" t="n">
         <v>10.9</v>
       </c>
       <c r="G73" s="38" t="inlineStr">
@@ -19232,7 +19201,7 @@
           <t>Black Diamond spec ~10.9oz/310g per pair (folding Z-pole design)</t>
         </is>
       </c>
-      <c r="H73" s="57" t="n">
+      <c r="H73" s="40" t="n">
         <v>219.95</v>
       </c>
       <c r="I73" s="41" t="inlineStr">
@@ -19313,7 +19282,7 @@
           <t>Cut piece of leftover closed-cell foam pad</t>
         </is>
       </c>
-      <c r="F74" s="56" t="n">
+      <c r="F74" s="39" t="n">
         <v>1</v>
       </c>
       <c r="G74" s="38" t="inlineStr">
@@ -19321,7 +19290,7 @@
           <t>EST — small cut piece of CCF foam, typical DIY weight</t>
         </is>
       </c>
-      <c r="H74" s="57" t="n">
+      <c r="H74" s="40" t="n">
         <v>0</v>
       </c>
       <c r="I74" s="41" t="inlineStr">
@@ -19402,7 +19371,7 @@
           <t>Z Seat</t>
         </is>
       </c>
-      <c r="F75" s="56" t="n">
+      <c r="F75" s="39" t="n">
         <v>2</v>
       </c>
       <c r="G75" s="38" t="inlineStr">
@@ -19410,7 +19379,7 @@
           <t>Therm-a-Rest spec 2oz/56g</t>
         </is>
       </c>
-      <c r="H75" s="57" t="n">
+      <c r="H75" s="40" t="n">
         <v>34.28</v>
       </c>
       <c r="I75" s="41" t="inlineStr">
@@ -19495,7 +19464,7 @@
           <t>1/8in Thinlight Foam Pad (full torso, multi-use)</t>
         </is>
       </c>
-      <c r="F76" s="56" t="n">
+      <c r="F76" s="39" t="n">
         <v>2.8</v>
       </c>
       <c r="G76" s="38" t="inlineStr">
@@ -19503,7 +19472,7 @@
           <t>Gossamer Gear spec ~2.8oz for the torso-length piece</t>
         </is>
       </c>
-      <c r="H76" s="57" t="n">
+      <c r="H76" s="40" t="n">
         <v>22.5</v>
       </c>
       <c r="I76" s="41" t="inlineStr">
@@ -19588,7 +19557,7 @@
           <t>Gabe Cloud Slide Sandals</t>
         </is>
       </c>
-      <c r="F77" s="56" t="n">
+      <c r="F77" s="39" t="n">
         <v>6</v>
       </c>
       <c r="G77" s="38" t="inlineStr">
@@ -19596,7 +19565,7 @@
           <t>typical foam slide pair weight, EST from category norms</t>
         </is>
       </c>
-      <c r="H77" s="57" t="n">
+      <c r="H77" s="40" t="n">
         <v>19.99</v>
       </c>
       <c r="I77" s="41" t="inlineStr">
@@ -19681,7 +19650,7 @@
           <t>Classic Clog</t>
         </is>
       </c>
-      <c r="F78" s="56" t="n">
+      <c r="F78" s="39" t="n">
         <v>12</v>
       </c>
       <c r="G78" s="38" t="inlineStr">
@@ -19689,7 +19658,7 @@
           <t>typical Crocs Classic Clog pair weight per size, widely cited around 11-13oz</t>
         </is>
       </c>
-      <c r="H78" s="57" t="n">
+      <c r="H78" s="40" t="n">
         <v>49.99</v>
       </c>
       <c r="I78" s="41" t="inlineStr">
@@ -19770,7 +19739,7 @@
           <t>Z-Trail EV Sandals</t>
         </is>
       </c>
-      <c r="F79" s="56" t="n">
+      <c r="F79" s="39" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="G79" s="38" t="inlineStr">
@@ -19778,7 +19747,7 @@
           <t>Xero Shoes spec ~8.8oz per pair (size-dependent)</t>
         </is>
       </c>
-      <c r="H79" s="57" t="n">
+      <c r="H79" s="40" t="n">
         <v>80</v>
       </c>
       <c r="I79" s="41" t="inlineStr">
@@ -19859,7 +19828,7 @@
           <t>Any old/thrifted trail running shoe (mesh upper, non-waterproof)</t>
         </is>
       </c>
-      <c r="F80" s="56" t="n">
+      <c r="F80" s="39" t="n">
         <v>24</v>
       </c>
       <c r="G80" s="38" t="inlineStr">
@@ -19867,7 +19836,7 @@
           <t>varies, ~1.5 lb/pair typical trail runner</t>
         </is>
       </c>
-      <c r="H80" s="57" t="n">
+      <c r="H80" s="40" t="n">
         <v>0</v>
       </c>
       <c r="I80" s="41" t="inlineStr">
@@ -19952,7 +19921,7 @@
           <t>Moab 3</t>
         </is>
       </c>
-      <c r="F81" s="56" t="n">
+      <c r="F81" s="39" t="n">
         <v>33</v>
       </c>
       <c r="G81" s="38" t="inlineStr">
@@ -19960,7 +19929,7 @@
           <t>2 lb 1 oz/pair men's per Merrell spec</t>
         </is>
       </c>
-      <c r="H81" s="57" t="n">
+      <c r="H81" s="40" t="n">
         <v>100.93</v>
       </c>
       <c r="I81" s="41" t="inlineStr">
@@ -20045,7 +20014,7 @@
           <t>Lone Peak 9</t>
         </is>
       </c>
-      <c r="F82" s="56" t="n">
+      <c r="F82" s="39" t="n">
         <v>22.5</v>
       </c>
       <c r="G82" s="38" t="inlineStr">
@@ -20053,7 +20022,7 @@
           <t>1 lb 6.3 oz/pair men's per REI spec</t>
         </is>
       </c>
-      <c r="H82" s="57" t="n">
+      <c r="H82" s="40" t="n">
         <v>145</v>
       </c>
       <c r="I82" s="41" t="inlineStr">
@@ -20138,7 +20107,7 @@
           <t>Merino Wool Lightweight Hiking Crew (3-pack budget alt)</t>
         </is>
       </c>
-      <c r="F83" s="56" t="n">
+      <c r="F83" s="39" t="n">
         <v>2.5</v>
       </c>
       <c r="G83" s="38" t="inlineStr">
@@ -20146,7 +20115,7 @@
           <t>per pair, typical crew weight</t>
         </is>
       </c>
-      <c r="H83" s="57" t="n">
+      <c r="H83" s="40" t="n">
         <v>8.83</v>
       </c>
       <c r="I83" s="41" t="inlineStr">
@@ -20231,7 +20200,7 @@
           <t>Hiker Micro Crew Midweight with Cushion</t>
         </is>
       </c>
-      <c r="F84" s="56" t="n">
+      <c r="F84" s="39" t="n">
         <v>2.6</v>
       </c>
       <c r="G84" s="38" t="inlineStr">
@@ -20239,7 +20208,7 @@
           <t>per pair</t>
         </is>
       </c>
-      <c r="H84" s="57" t="n">
+      <c r="H84" s="40" t="n">
         <v>25.95</v>
       </c>
       <c r="I84" s="41" t="inlineStr">
@@ -20324,7 +20293,7 @@
           <t>Waterproof All Weather Mid Length Sock</t>
         </is>
       </c>
-      <c r="F85" s="56" t="n">
+      <c r="F85" s="39" t="n">
         <v>3.2</v>
       </c>
       <c r="G85" s="38" t="inlineStr">
@@ -20332,7 +20301,7 @@
           <t>per pair, waterproof membrane sock</t>
         </is>
       </c>
-      <c r="H85" s="57" t="n">
+      <c r="H85" s="40" t="n">
         <v>55</v>
       </c>
       <c r="I85" s="41" t="inlineStr">
@@ -20417,7 +20386,7 @@
           <t>Watertight II Rain Jacket (Men's)</t>
         </is>
       </c>
-      <c r="F86" s="56" t="n">
+      <c r="F86" s="39" t="n">
         <v>12</v>
       </c>
       <c r="G86" s="38" t="inlineStr">
@@ -20425,7 +20394,7 @@
           <t>typical packable Omni-Tech shell weight per Columbia/OGL testing</t>
         </is>
       </c>
-      <c r="H86" s="57" t="n">
+      <c r="H86" s="40" t="n">
         <v>70</v>
       </c>
       <c r="I86" s="41" t="inlineStr">
@@ -20510,7 +20479,7 @@
           <t>Rainier Rain Jacket</t>
         </is>
       </c>
-      <c r="F87" s="56" t="n">
+      <c r="F87" s="39" t="n">
         <v>12.5</v>
       </c>
       <c r="G87" s="38" t="inlineStr">
@@ -20518,7 +20487,7 @@
           <t>approx per REI listing, men's</t>
         </is>
       </c>
-      <c r="H87" s="57" t="n">
+      <c r="H87" s="40" t="n">
         <v>99.95</v>
       </c>
       <c r="I87" s="41" t="inlineStr">
@@ -20603,7 +20572,7 @@
           <t>Helium Rain Jacket</t>
         </is>
       </c>
-      <c r="F88" s="56" t="n">
+      <c r="F88" s="39" t="n">
         <v>6.4</v>
       </c>
       <c r="G88" s="38" t="inlineStr">
@@ -20611,7 +20580,7 @@
           <t>per OR spec, men's</t>
         </is>
       </c>
-      <c r="H88" s="57" t="n">
+      <c r="H88" s="40" t="n">
         <v>199</v>
       </c>
       <c r="I88" s="41" t="inlineStr">
@@ -20692,7 +20661,7 @@
           <t>MT100 Hooded Down Puffer Jacket</t>
         </is>
       </c>
-      <c r="F89" s="56" t="n">
+      <c r="F89" s="39" t="n">
         <v>10.6</v>
       </c>
       <c r="G89" s="38" t="inlineStr">
@@ -20700,7 +20669,7 @@
           <t>packable down jacket, per Decathlon/GearJunkie; rebranded from Forclaz to Simond</t>
         </is>
       </c>
-      <c r="H89" s="57" t="n">
+      <c r="H89" s="40" t="n">
         <v>80</v>
       </c>
       <c r="I89" s="41" t="inlineStr">
@@ -20785,7 +20754,7 @@
           <t>Nano Puff Jacket</t>
         </is>
       </c>
-      <c r="F90" s="56" t="n">
+      <c r="F90" s="39" t="n">
         <v>11.6</v>
       </c>
       <c r="G90" s="38" t="inlineStr">
@@ -20793,7 +20762,7 @@
           <t>per Patagonia spec, men's, synthetic PrimaLoft fill</t>
         </is>
       </c>
-      <c r="H90" s="57" t="n">
+      <c r="H90" s="40" t="n">
         <v>118.99</v>
       </c>
       <c r="I90" s="41" t="inlineStr">
@@ -20878,7 +20847,7 @@
           <t>Torrid APEX Jacket</t>
         </is>
       </c>
-      <c r="F91" s="56" t="n">
+      <c r="F91" s="39" t="n">
         <v>8.9</v>
       </c>
       <c r="G91" s="38" t="inlineStr">
@@ -20886,7 +20855,7 @@
           <t>per Adventure Alan review, synthetic APEX fill</t>
         </is>
       </c>
-      <c r="H91" s="57" t="n">
+      <c r="H91" s="40" t="n">
         <v>170</v>
       </c>
       <c r="I91" s="41" t="inlineStr">
@@ -20971,7 +20940,7 @@
           <t>MH100 Fleece</t>
         </is>
       </c>
-      <c r="F92" s="56" t="n">
+      <c r="F92" s="39" t="n">
         <v>12</v>
       </c>
       <c r="G92" s="38" t="inlineStr">
@@ -20979,7 +20948,7 @@
           <t>typical 100-weight fleece pullover</t>
         </is>
       </c>
-      <c r="H92" s="57" t="n">
+      <c r="H92" s="40" t="n">
         <v>25</v>
       </c>
       <c r="I92" s="41" t="inlineStr">
@@ -21064,7 +21033,7 @@
           <t>Alpha 90 Half-Zip Hoodie</t>
         </is>
       </c>
-      <c r="F93" s="56" t="n">
+      <c r="F93" s="39" t="n">
         <v>4.8</v>
       </c>
       <c r="G93" s="38" t="inlineStr">
@@ -21072,7 +21041,7 @@
           <t>Polartec Alpha Direct, sub-5oz per community reporting</t>
         </is>
       </c>
-      <c r="H93" s="57" t="n">
+      <c r="H93" s="40" t="n">
         <v>115</v>
       </c>
       <c r="I93" s="41" t="inlineStr">
@@ -21157,7 +21126,7 @@
           <t>R1 Air Hoody</t>
         </is>
       </c>
-      <c r="F94" s="56" t="n">
+      <c r="F94" s="39" t="n">
         <v>10.5</v>
       </c>
       <c r="G94" s="38" t="inlineStr">
@@ -21165,7 +21134,7 @@
           <t>per Patagonia spec</t>
         </is>
       </c>
-      <c r="H94" s="57" t="n">
+      <c r="H94" s="40" t="n">
         <v>179</v>
       </c>
       <c r="I94" s="41" t="inlineStr">
@@ -21246,7 +21215,7 @@
           <t>Men's/Women's Long Sleeve Base Layer Set</t>
         </is>
       </c>
-      <c r="F95" s="56" t="n">
+      <c r="F95" s="39" t="n">
         <v>8</v>
       </c>
       <c r="G95" s="38" t="inlineStr">
@@ -21254,7 +21223,7 @@
           <t>top+bottom combined, lightweight merino blend</t>
         </is>
       </c>
-      <c r="H95" s="57" t="n">
+      <c r="H95" s="40" t="n">
         <v>100</v>
       </c>
       <c r="I95" s="41" t="inlineStr">
@@ -21339,7 +21308,7 @@
           <t>Classic Thermal Merino Base Layer (top + bottom)</t>
         </is>
       </c>
-      <c r="F96" s="56" t="n">
+      <c r="F96" s="39" t="n">
         <v>10</v>
       </c>
       <c r="G96" s="38" t="inlineStr">
@@ -21347,7 +21316,7 @@
           <t>combined top+bottom, midweight merino</t>
         </is>
       </c>
-      <c r="H96" s="57" t="n">
+      <c r="H96" s="40" t="n">
         <v>125</v>
       </c>
       <c r="I96" s="41" t="inlineStr">
@@ -21428,7 +21397,7 @@
           <t>200 Oasis (top + bottom)</t>
         </is>
       </c>
-      <c r="F97" s="56" t="n">
+      <c r="F97" s="39" t="n">
         <v>11</v>
       </c>
       <c r="G97" s="38" t="inlineStr">
@@ -21436,7 +21405,7 @@
           <t>200gsm merino jersey, combined top+bottom</t>
         </is>
       </c>
-      <c r="H97" s="57" t="n">
+      <c r="H97" s="40" t="n">
         <v>235</v>
       </c>
       <c r="I97" s="41" t="inlineStr">
@@ -21517,7 +21486,7 @@
           <t>Trailmade Pants</t>
         </is>
       </c>
-      <c r="F98" s="56" t="n">
+      <c r="F98" s="39" t="n">
         <v>11</v>
       </c>
       <c r="G98" s="38" t="inlineStr">
@@ -21525,7 +21494,7 @@
           <t>per REI product listing</t>
         </is>
       </c>
-      <c r="H98" s="57" t="n">
+      <c r="H98" s="40" t="n">
         <v>80</v>
       </c>
       <c r="I98" s="41" t="inlineStr">
@@ -21610,7 +21579,7 @@
           <t>Ferrosi Pants</t>
         </is>
       </c>
-      <c r="F99" s="56" t="n">
+      <c r="F99" s="39" t="n">
         <v>11.4</v>
       </c>
       <c r="G99" s="38" t="inlineStr">
@@ -21618,7 +21587,7 @@
           <t>per OGL/Switchback testing</t>
         </is>
       </c>
-      <c r="H99" s="57" t="n">
+      <c r="H99" s="40" t="n">
         <v>110</v>
       </c>
       <c r="I99" s="41" t="inlineStr">
@@ -21703,7 +21672,7 @@
           <t>Stretch Zion Straight Pants (cargo version discontinued, replaced by current lineup)</t>
         </is>
       </c>
-      <c r="F100" s="56" t="n">
+      <c r="F100" s="39" t="n">
         <v>14</v>
       </c>
       <c r="G100" s="38" t="inlineStr">
@@ -21711,7 +21680,7 @@
           <t>per prAna spec, recycled nylon</t>
         </is>
       </c>
-      <c r="H100" s="57" t="n">
+      <c r="H100" s="40" t="n">
         <v>98</v>
       </c>
       <c r="I100" s="41" t="inlineStr">
@@ -21796,7 +21765,7 @@
           <t>Fleece-lined knit beanie</t>
         </is>
       </c>
-      <c r="F101" s="56" t="n">
+      <c r="F101" s="39" t="n">
         <v>2</v>
       </c>
       <c r="G101" s="38" t="inlineStr">
@@ -21804,7 +21773,7 @@
           <t>typical knit beanie</t>
         </is>
       </c>
-      <c r="H101" s="57" t="n">
+      <c r="H101" s="40" t="n">
         <v>14.99</v>
       </c>
       <c r="I101" s="41" t="inlineStr">
@@ -21885,7 +21854,7 @@
           <t>Alpha Drifter Beanie</t>
         </is>
       </c>
-      <c r="F102" s="56" t="n">
+      <c r="F102" s="39" t="n">
         <v>0.7</v>
       </c>
       <c r="G102" s="38" t="inlineStr">
@@ -21893,7 +21862,7 @@
           <t>Polartec Alpha Direct, sub-1oz per community reporting</t>
         </is>
       </c>
-      <c r="H102" s="57" t="n">
+      <c r="H102" s="40" t="n">
         <v>38</v>
       </c>
       <c r="I102" s="41" t="inlineStr">
@@ -21978,7 +21947,7 @@
           <t>Merino 250 Reversible Cuffed Beanie</t>
         </is>
       </c>
-      <c r="F103" s="56" t="n">
+      <c r="F103" s="39" t="n">
         <v>2.1</v>
       </c>
       <c r="G103" s="38" t="inlineStr">
@@ -21986,7 +21955,7 @@
           <t>per Smartwool spec</t>
         </is>
       </c>
-      <c r="H103" s="57" t="n">
+      <c r="H103" s="40" t="n">
         <v>35</v>
       </c>
       <c r="I103" s="41" t="inlineStr">
@@ -22071,7 +22040,7 @@
           <t>Wool Fleece-Liner Knit Gloves (3-pack)</t>
         </is>
       </c>
-      <c r="F104" s="56" t="n">
+      <c r="F104" s="39" t="n">
         <v>2</v>
       </c>
       <c r="G104" s="38" t="inlineStr">
@@ -22079,7 +22048,7 @@
           <t>typical knit glove pair; sold as a 3-pack for $12.99</t>
         </is>
       </c>
-      <c r="H104" s="57" t="n">
+      <c r="H104" s="40" t="n">
         <v>12.99</v>
       </c>
       <c r="I104" s="41" t="inlineStr">
@@ -22160,7 +22129,7 @@
           <t>PL 400 Gloves</t>
         </is>
       </c>
-      <c r="F105" s="56" t="n">
+      <c r="F105" s="39" t="n">
         <v>2.3</v>
       </c>
       <c r="G105" s="38" t="inlineStr">
@@ -22168,7 +22137,7 @@
           <t>per OR spec, fleece liner glove</t>
         </is>
       </c>
-      <c r="H105" s="57" t="n">
+      <c r="H105" s="40" t="n">
         <v>35</v>
       </c>
       <c r="I105" s="41" t="inlineStr">
@@ -22253,7 +22222,7 @@
           <t>Merino/Possum Blend Gloves (touchscreen)</t>
         </is>
       </c>
-      <c r="F106" s="56" t="n">
+      <c r="F106" s="39" t="n">
         <v>1.5</v>
       </c>
       <c r="G106" s="38" t="inlineStr">
@@ -22261,7 +22230,7 @@
           <t>per community reporting on brushtail possum/merino gloves</t>
         </is>
       </c>
-      <c r="H106" s="57" t="n">
+      <c r="H106" s="40" t="n">
         <v>40</v>
       </c>
       <c r="I106" s="41" t="inlineStr">
@@ -22342,7 +22311,7 @@
           <t>Mesh Safety Vest + Blaze Orange Insulated Beanie</t>
         </is>
       </c>
-      <c r="F107" s="56" t="n">
+      <c r="F107" s="39" t="n">
         <v>6</v>
       </c>
       <c r="G107" s="38" t="inlineStr">
@@ -22350,7 +22319,7 @@
           <t>vest ~4oz + beanie ~2oz combined estimate</t>
         </is>
       </c>
-      <c r="H107" s="57" t="n">
+      <c r="H107" s="40" t="n">
         <v>16.96</v>
       </c>
       <c r="I107" s="41" t="inlineStr">
@@ -22435,7 +22404,7 @@
           <t>Blaze Orange Safety Vest</t>
         </is>
       </c>
-      <c r="F108" s="56" t="n">
+      <c r="F108" s="39" t="n">
         <v>5</v>
       </c>
       <c r="G108" s="38" t="inlineStr">
@@ -22443,7 +22412,7 @@
           <t>per prior sourcing in project gear.md</t>
         </is>
       </c>
-      <c r="H108" s="57" t="n">
+      <c r="H108" s="40" t="n">
         <v>13.51</v>
       </c>
       <c r="I108" s="41" t="inlineStr">
@@ -22528,7 +22497,7 @@
           <t>Blaze Orange Hunting Vest &amp; Hat Combo</t>
         </is>
       </c>
-      <c r="F109" s="56" t="n">
+      <c r="F109" s="39" t="n">
         <v>10</v>
       </c>
       <c r="G109" s="38" t="inlineStr">
@@ -22536,7 +22505,7 @@
           <t>combo vest+hat, estimate based on similar products</t>
         </is>
       </c>
-      <c r="H109" s="57" t="n">
+      <c r="H109" s="40" t="n">
         <v>45</v>
       </c>
       <c r="I109" s="41" t="inlineStr">
@@ -22617,7 +22586,7 @@
           <t>Old sneakers or flip-flops already owned</t>
         </is>
       </c>
-      <c r="F110" s="56" t="n">
+      <c r="F110" s="39" t="n">
         <v>10</v>
       </c>
       <c r="G110" s="38" t="inlineStr">
@@ -22625,7 +22594,7 @@
           <t>varies</t>
         </is>
       </c>
-      <c r="H110" s="57" t="n">
+      <c r="H110" s="40" t="n">
         <v>0</v>
       </c>
       <c r="I110" s="41" t="inlineStr">
@@ -22710,7 +22679,7 @@
           <t>Classic Clog</t>
         </is>
       </c>
-      <c r="F111" s="56" t="n">
+      <c r="F111" s="39" t="n">
         <v>14</v>
       </c>
       <c r="G111" s="38" t="inlineStr">
@@ -22718,7 +22687,7 @@
           <t>per pair, per Bikepacking.com testing</t>
         </is>
       </c>
-      <c r="H111" s="57" t="n">
+      <c r="H111" s="40" t="n">
         <v>50</v>
       </c>
       <c r="I111" s="41" t="inlineStr">
@@ -22799,7 +22768,7 @@
           <t>Cairn Evo Adventure Sandals (current lineup; original Cairn Adventure Sandal discontinued)</t>
         </is>
       </c>
-      <c r="F112" s="56" t="n">
+      <c r="F112" s="39" t="n">
         <v>11</v>
       </c>
       <c r="G112" s="38" t="inlineStr">
@@ -22807,7 +22776,7 @@
           <t>per Bedrock Sandals spec, per pair</t>
         </is>
       </c>
-      <c r="H112" s="57" t="n">
+      <c r="H112" s="40" t="n">
         <v>115</v>
       </c>
       <c r="I112" s="41" t="inlineStr">
@@ -22888,7 +22857,7 @@
           <t>Kenai Original</t>
         </is>
       </c>
-      <c r="F113" s="56" t="n">
+      <c r="F113" s="39" t="n">
         <v>4</v>
       </c>
       <c r="G113" s="38" t="inlineStr">
@@ -22896,7 +22865,7 @@
           <t>per pair, 2mm neoprene glove</t>
         </is>
       </c>
-      <c r="H113" s="57" t="n">
+      <c r="H113" s="40" t="n">
         <v>24.99</v>
       </c>
       <c r="I113" s="41" t="inlineStr">
@@ -22981,7 +22950,7 @@
           <t>Kenai Original</t>
         </is>
       </c>
-      <c r="F114" s="56" t="n">
+      <c r="F114" s="39" t="n">
         <v>4</v>
       </c>
       <c r="G114" s="38" t="inlineStr">
@@ -22989,7 +22958,7 @@
           <t>per pair, 2mm neoprene glove</t>
         </is>
       </c>
-      <c r="H114" s="57" t="n">
+      <c r="H114" s="40" t="n">
         <v>24.99</v>
       </c>
       <c r="I114" s="41" t="inlineStr">
@@ -23074,7 +23043,7 @@
           <t>Arctic Gauntlet Gloves for Cold Water Wading</t>
         </is>
       </c>
-      <c r="F115" s="56" t="n">
+      <c r="F115" s="39" t="n">
         <v>9</v>
       </c>
       <c r="G115" s="38" t="inlineStr">
@@ -23082,7 +23051,7 @@
           <t>per pair, lined arm-length gauntlet, estimate</t>
         </is>
       </c>
-      <c r="H115" s="57" t="n">
+      <c r="H115" s="40" t="n">
         <v>50</v>
       </c>
       <c r="I115" s="41" t="inlineStr">
@@ -23163,7 +23132,7 @@
           <t>3mm Knee-High Neoprene Sock</t>
         </is>
       </c>
-      <c r="F116" s="56" t="n">
+      <c r="F116" s="39" t="n">
         <v>6</v>
       </c>
       <c r="G116" s="38" t="inlineStr">
@@ -23171,7 +23140,7 @@
           <t>per pair, per Walmart listing (verified live price)</t>
         </is>
       </c>
-      <c r="H116" s="57" t="n">
+      <c r="H116" s="40" t="n">
         <v>41.59</v>
       </c>
       <c r="I116" s="41" t="inlineStr">
@@ -23256,7 +23225,7 @@
           <t>3mm Neoprene Wading/Water Socks</t>
         </is>
       </c>
-      <c r="F117" s="56" t="n">
+      <c r="F117" s="39" t="n">
         <v>6.5</v>
       </c>
       <c r="G117" s="38" t="inlineStr">
@@ -23264,7 +23233,7 @@
           <t>per pair, typical 3mm dive/water sock (verified live price)</t>
         </is>
       </c>
-      <c r="H117" s="57" t="n">
+      <c r="H117" s="40" t="n">
         <v>30.19</v>
       </c>
       <c r="I117" s="41" t="inlineStr">
@@ -23349,7 +23318,7 @@
           <t>I-Drain Neoprene Guard Socks, 3.5mm</t>
         </is>
       </c>
-      <c r="F118" s="56" t="n">
+      <c r="F118" s="39" t="n">
         <v>7</v>
       </c>
       <c r="G118" s="38" t="inlineStr">
@@ -23357,7 +23326,7 @@
           <t>per pair, per Korkers spec</t>
         </is>
       </c>
-      <c r="H118" s="57" t="n">
+      <c r="H118" s="40" t="n">
         <v>44.99</v>
       </c>
       <c r="I118" s="41" t="inlineStr">
@@ -23438,7 +23407,7 @@
           <t>No waders — neoprene socks + quick-dry pants only</t>
         </is>
       </c>
-      <c r="F119" s="56" t="n">
+      <c r="F119" s="39" t="n">
         <v>0</v>
       </c>
       <c r="G119" s="38" t="inlineStr">
@@ -23446,7 +23415,7 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="H119" s="57" t="n">
+      <c r="H119" s="40" t="n">
         <v>0</v>
       </c>
       <c r="I119" s="41" t="inlineStr">
@@ -23531,7 +23500,7 @@
           <t>Canyon II Stockingfoot Hip Wader, Medium (needs separate wading shoe)</t>
         </is>
       </c>
-      <c r="F120" s="56" t="n">
+      <c r="F120" s="39" t="n">
         <v>20</v>
       </c>
       <c r="G120" s="38" t="inlineStr">
@@ -23539,7 +23508,7 @@
           <t>category estimate, no vendor spec published -- 4-ply nylon, no attached boot</t>
         </is>
       </c>
-      <c r="H120" s="57" t="n">
+      <c r="H120" s="40" t="n">
         <v>98.29000000000001</v>
       </c>
       <c r="I120" s="41" t="inlineStr">
@@ -23624,7 +23593,7 @@
           <t>Tributary Stockingfoot Waders</t>
         </is>
       </c>
-      <c r="F121" s="56" t="n">
+      <c r="F121" s="39" t="n">
         <v>38</v>
       </c>
       <c r="G121" s="38" t="inlineStr">
@@ -23632,7 +23601,7 @@
           <t>per Simms spec, breathable stockingfoot chest wader</t>
         </is>
       </c>
-      <c r="H121" s="57" t="n">
+      <c r="H121" s="40" t="n">
         <v>300</v>
       </c>
       <c r="I121" s="41" t="inlineStr">
@@ -23717,7 +23686,7 @@
           <t>Protective Knee Pads, Thick Sponge Anti-Slip Knee Sleeve</t>
         </is>
       </c>
-      <c r="F122" s="56" t="n">
+      <c r="F122" s="39" t="n">
         <v>6</v>
       </c>
       <c r="G122" s="38" t="inlineStr">
@@ -23725,7 +23694,7 @@
           <t>per pair, strap-on sleeve</t>
         </is>
       </c>
-      <c r="H122" s="57" t="n">
+      <c r="H122" s="40" t="n">
         <v>15.99</v>
       </c>
       <c r="I122" s="41" t="inlineStr">
@@ -23810,7 +23779,7 @@
           <t>Neoprene Strap-On Knee Pads (gardening/volleyball style)</t>
         </is>
       </c>
-      <c r="F123" s="56" t="n">
+      <c r="F123" s="39" t="n">
         <v>8</v>
       </c>
       <c r="G123" s="38" t="inlineStr">
@@ -23818,7 +23787,7 @@
           <t>per pair</t>
         </is>
       </c>
-      <c r="H123" s="57" t="n">
+      <c r="H123" s="40" t="n">
         <v>16</v>
       </c>
       <c r="I123" s="41" t="inlineStr">
@@ -23899,7 +23868,7 @@
           <t>Gel-Cushion Kneeling Pad with adjustable straps</t>
         </is>
       </c>
-      <c r="F124" s="56" t="n">
+      <c r="F124" s="39" t="n">
         <v>14</v>
       </c>
       <c r="G124" s="38" t="inlineStr">
@@ -23907,7 +23876,7 @@
           <t>per pair, gel-insert work knee pad</t>
         </is>
       </c>
-      <c r="H124" s="57" t="n">
+      <c r="H124" s="40" t="n">
         <v>28</v>
       </c>
       <c r="I124" s="41" t="inlineStr">
@@ -23988,7 +23957,7 @@
           <t>BP-14 14" Black Plastic Gold Pan</t>
         </is>
       </c>
-      <c r="F125" s="56" t="n">
+      <c r="F125" s="39" t="n">
         <v>9</v>
       </c>
       <c r="G125" s="38" t="inlineStr">
@@ -23996,7 +23965,7 @@
           <t>per Toolup listing (verified live price)</t>
         </is>
       </c>
-      <c r="H125" s="57" t="n">
+      <c r="H125" s="40" t="n">
         <v>7.26</v>
       </c>
       <c r="I125" s="41" t="inlineStr">
@@ -24043,7 +24012,7 @@
         <v>5</v>
       </c>
       <c r="R125" s="37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S125" s="38" t="inlineStr">
         <is>
@@ -24081,7 +24050,7 @@
           <t>14" Gravity Trap Gold Pan (green)</t>
         </is>
       </c>
-      <c r="F126" s="56" t="n">
+      <c r="F126" s="39" t="n">
         <v>10</v>
       </c>
       <c r="G126" s="38" t="inlineStr">
@@ -24089,7 +24058,7 @@
           <t>per Garrett product spec</t>
         </is>
       </c>
-      <c r="H126" s="57" t="n">
+      <c r="H126" s="40" t="n">
         <v>8.99</v>
       </c>
       <c r="I126" s="41" t="inlineStr">
@@ -24136,7 +24105,7 @@
         <v>5</v>
       </c>
       <c r="R126" s="37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S126" s="38" t="inlineStr">
         <is>
@@ -24174,7 +24143,7 @@
           <t>15" Super Sluice Gold Pan (two-stage riffle pan)</t>
         </is>
       </c>
-      <c r="F127" s="56" t="n">
+      <c r="F127" s="39" t="n">
         <v>13</v>
       </c>
       <c r="G127" s="38" t="inlineStr">
@@ -24182,7 +24151,7 @@
           <t>per Garrett/eBay listing</t>
         </is>
       </c>
-      <c r="H127" s="57" t="n">
+      <c r="H127" s="40" t="n">
         <v>25</v>
       </c>
       <c r="I127" s="41" t="inlineStr">
@@ -24229,7 +24198,7 @@
         <v>3</v>
       </c>
       <c r="R127" s="37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S127" s="38" t="inlineStr">
         <is>
@@ -24267,7 +24236,7 @@
           <t>1/2" Mesh Classifier</t>
         </is>
       </c>
-      <c r="F128" s="56" t="n">
+      <c r="F128" s="39" t="n">
         <v>16</v>
       </c>
       <c r="G128" s="38" t="inlineStr">
@@ -24275,7 +24244,7 @@
           <t>per prior project sourcing (ASR 1/4" model confirmed $28.99, 1/2" comparable)</t>
         </is>
       </c>
-      <c r="H128" s="57" t="n">
+      <c r="H128" s="40" t="n">
         <v>25</v>
       </c>
       <c r="I128" s="41" t="inlineStr">
@@ -24322,7 +24291,7 @@
         <v>5</v>
       </c>
       <c r="R128" s="37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S128" s="38" t="inlineStr">
         <is>
@@ -24360,7 +24329,7 @@
           <t>Stackable Classifier Set (1/2", 1/4", 1/8")</t>
         </is>
       </c>
-      <c r="F129" s="56" t="n">
+      <c r="F129" s="39" t="n">
         <v>30</v>
       </c>
       <c r="G129" s="38" t="inlineStr">
@@ -24368,7 +24337,7 @@
           <t>3-screen stacked set, estimate</t>
         </is>
       </c>
-      <c r="H129" s="57" t="n">
+      <c r="H129" s="40" t="n">
         <v>75</v>
       </c>
       <c r="I129" s="41" t="inlineStr">
@@ -24415,7 +24384,7 @@
         <v>4</v>
       </c>
       <c r="R129" s="37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S129" s="38" t="inlineStr">
         <is>
@@ -24453,7 +24422,7 @@
           <t>Stainless Mesh Classifier Set incl. 50-mesh fine screen</t>
         </is>
       </c>
-      <c r="F130" s="56" t="n">
+      <c r="F130" s="39" t="n">
         <v>34</v>
       </c>
       <c r="G130" s="38" t="inlineStr">
@@ -24461,7 +24430,7 @@
           <t>multi-screen stainless set, estimate</t>
         </is>
       </c>
-      <c r="H130" s="57" t="n">
+      <c r="H130" s="40" t="n">
         <v>65</v>
       </c>
       <c r="I130" s="41" t="inlineStr">
@@ -24546,7 +24515,7 @@
           <t>Plastic Snuffer Bottle</t>
         </is>
       </c>
-      <c r="F131" s="56" t="n">
+      <c r="F131" s="39" t="n">
         <v>1.5</v>
       </c>
       <c r="G131" s="38" t="inlineStr">
@@ -24554,7 +24523,7 @@
           <t>typical squeeze snuffer bottle</t>
         </is>
       </c>
-      <c r="H131" s="57" t="n">
+      <c r="H131" s="40" t="n">
         <v>4</v>
       </c>
       <c r="I131" s="41" t="inlineStr">
@@ -24601,7 +24570,7 @@
         <v>5</v>
       </c>
       <c r="R131" s="37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S131" s="38" t="inlineStr">
         <is>
@@ -24639,7 +24608,7 @@
           <t>2-Pack Glass-Tip Snuffer Bottle with Tweezers</t>
         </is>
       </c>
-      <c r="F132" s="56" t="n">
+      <c r="F132" s="39" t="n">
         <v>2</v>
       </c>
       <c r="G132" s="38" t="inlineStr">
@@ -24647,7 +24616,7 @@
           <t>per pair, bundled with tweezers</t>
         </is>
       </c>
-      <c r="H132" s="57" t="n">
+      <c r="H132" s="40" t="n">
         <v>11.99</v>
       </c>
       <c r="I132" s="41" t="inlineStr">
@@ -24694,7 +24663,7 @@
         <v>5</v>
       </c>
       <c r="R132" s="37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S132" s="38" t="inlineStr">
         <is>
@@ -24732,7 +24701,7 @@
           <t>Brass-Tip Snuffer Bottle Set</t>
         </is>
       </c>
-      <c r="F133" s="56" t="n">
+      <c r="F133" s="39" t="n">
         <v>2.5</v>
       </c>
       <c r="G133" s="38" t="inlineStr">
@@ -24740,7 +24709,7 @@
           <t>estimate, metal-tip snuffer</t>
         </is>
       </c>
-      <c r="H133" s="57" t="n">
+      <c r="H133" s="40" t="n">
         <v>13</v>
       </c>
       <c r="I133" s="41" t="inlineStr">
@@ -24787,7 +24756,7 @@
         <v>3</v>
       </c>
       <c r="R133" s="37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S133" s="38" t="inlineStr"/>
       <c r="T133">
@@ -24821,7 +24790,7 @@
           <t>Hook and Pick Precision Crevice Tool Set, 6 Pieces</t>
         </is>
       </c>
-      <c r="F134" s="56" t="n">
+      <c r="F134" s="39" t="n">
         <v>4</v>
       </c>
       <c r="G134" s="38" t="inlineStr">
@@ -24829,7 +24798,7 @@
           <t>per set</t>
         </is>
       </c>
-      <c r="H134" s="57" t="n">
+      <c r="H134" s="40" t="n">
         <v>17.25</v>
       </c>
       <c r="I134" s="41" t="inlineStr">
@@ -24876,7 +24845,7 @@
         <v>5</v>
       </c>
       <c r="R134" s="37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S134" s="38" t="inlineStr"/>
       <c r="T134">
@@ -24910,7 +24879,7 @@
           <t>Stainless Steel Crevice Tool Set with Magnet</t>
         </is>
       </c>
-      <c r="F135" s="56" t="n">
+      <c r="F135" s="39" t="n">
         <v>6</v>
       </c>
       <c r="G135" s="38" t="inlineStr">
@@ -24918,7 +24887,7 @@
           <t>per set</t>
         </is>
       </c>
-      <c r="H135" s="57" t="n">
+      <c r="H135" s="40" t="n">
         <v>59.95</v>
       </c>
       <c r="I135" s="41" t="inlineStr">
@@ -24965,7 +24934,7 @@
         <v>5</v>
       </c>
       <c r="R135" s="37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S135" s="38" t="inlineStr">
         <is>
@@ -25003,7 +24972,7 @@
           <t>Branded Crevice Tool Kit</t>
         </is>
       </c>
-      <c r="F136" s="56" t="n">
+      <c r="F136" s="39" t="n">
         <v>8</v>
       </c>
       <c r="G136" s="38" t="inlineStr">
@@ -25011,7 +24980,7 @@
           <t>per set, branded prospecting-tool kit</t>
         </is>
       </c>
-      <c r="H136" s="57" t="n">
+      <c r="H136" s="40" t="n">
         <v>25</v>
       </c>
       <c r="I136" s="41" t="inlineStr">
@@ -25058,7 +25027,7 @@
         <v>3</v>
       </c>
       <c r="R136" s="37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S136" s="38" t="inlineStr">
         <is>
@@ -25096,7 +25065,7 @@
           <t>Plastic Snap-Cap Vials (5-pack)</t>
         </is>
       </c>
-      <c r="F137" s="56" t="n">
+      <c r="F137" s="39" t="n">
         <v>1</v>
       </c>
       <c r="G137" s="38" t="inlineStr">
@@ -25104,7 +25073,7 @@
           <t>5-pack combined</t>
         </is>
       </c>
-      <c r="H137" s="57" t="n">
+      <c r="H137" s="40" t="n">
         <v>5</v>
       </c>
       <c r="I137" s="41" t="inlineStr">
@@ -25151,7 +25120,7 @@
         <v>5</v>
       </c>
       <c r="R137" s="37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S137" s="38" t="inlineStr"/>
       <c r="T137">
@@ -25185,7 +25154,7 @@
           <t>Glass Vials with Foam-Lined Screw Caps (12-pack)</t>
         </is>
       </c>
-      <c r="F138" s="56" t="n">
+      <c r="F138" s="39" t="n">
         <v>1.5</v>
       </c>
       <c r="G138" s="38" t="inlineStr">
@@ -25193,7 +25162,7 @@
           <t>price is for the 12-pack, not per vial</t>
         </is>
       </c>
-      <c r="H138" s="57" t="n">
+      <c r="H138" s="40" t="n">
         <v>9.99</v>
       </c>
       <c r="I138" s="41" t="inlineStr">
@@ -25240,7 +25209,7 @@
         <v>5</v>
       </c>
       <c r="R138" s="37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S138" s="38" t="inlineStr">
         <is>
@@ -25278,7 +25247,7 @@
           <t>Leak-Proof Glass Gold Vials with Measurement Markings</t>
         </is>
       </c>
-      <c r="F139" s="56" t="n">
+      <c r="F139" s="39" t="n">
         <v>2</v>
       </c>
       <c r="G139" s="38" t="inlineStr">
@@ -25286,7 +25255,7 @@
           <t>per vial</t>
         </is>
       </c>
-      <c r="H139" s="57" t="n">
+      <c r="H139" s="40" t="n">
         <v>4</v>
       </c>
       <c r="I139" s="41" t="inlineStr">
@@ -25333,7 +25302,7 @@
         <v>4</v>
       </c>
       <c r="R139" s="37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S139" s="38" t="inlineStr">
         <is>
@@ -25371,7 +25340,7 @@
           <t>10x Plastic Keychain Loupe</t>
         </is>
       </c>
-      <c r="F140" s="56" t="n">
+      <c r="F140" s="39" t="n">
         <v>1</v>
       </c>
       <c r="G140" s="38" t="inlineStr">
@@ -25379,7 +25348,7 @@
           <t>typical keychain loupe</t>
         </is>
       </c>
-      <c r="H140" s="57" t="n">
+      <c r="H140" s="40" t="n">
         <v>7.99</v>
       </c>
       <c r="I140" s="41" t="inlineStr">
@@ -25426,7 +25395,7 @@
         <v>5</v>
       </c>
       <c r="R140" s="37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S140" s="38" t="inlineStr">
         <is>
@@ -25464,7 +25433,7 @@
           <t>30x60 Jeweler's Loupe with Built-In LED Light</t>
         </is>
       </c>
-      <c r="F141" s="56" t="n">
+      <c r="F141" s="39" t="n">
         <v>2.5</v>
       </c>
       <c r="G141" s="38" t="inlineStr">
@@ -25472,7 +25441,7 @@
           <t>typical illuminated folding loupe</t>
         </is>
       </c>
-      <c r="H141" s="57" t="n">
+      <c r="H141" s="40" t="n">
         <v>8.98</v>
       </c>
       <c r="I141" s="41" t="inlineStr">
@@ -25519,7 +25488,7 @@
         <v>5</v>
       </c>
       <c r="R141" s="37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S141" s="38" t="inlineStr"/>
       <c r="T141">
@@ -25553,7 +25522,7 @@
           <t>10x Triplet Achromatic Loupe</t>
         </is>
       </c>
-      <c r="F142" s="56" t="n">
+      <c r="F142" s="39" t="n">
         <v>2</v>
       </c>
       <c r="G142" s="38" t="inlineStr">
@@ -25561,7 +25530,7 @@
           <t>typical premium triplet loupe</t>
         </is>
       </c>
-      <c r="H142" s="57" t="n">
+      <c r="H142" s="40" t="n">
         <v>20</v>
       </c>
       <c r="I142" s="41" t="inlineStr">
@@ -25608,7 +25577,7 @@
         <v>3</v>
       </c>
       <c r="R142" s="37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S142" s="38" t="inlineStr"/>
       <c r="T142">
@@ -25642,7 +25611,7 @@
           <t>Folding Garden Trowel</t>
         </is>
       </c>
-      <c r="F143" s="56" t="n">
+      <c r="F143" s="39" t="n">
         <v>6</v>
       </c>
       <c r="G143" s="38" t="inlineStr">
@@ -25650,7 +25619,7 @@
           <t>typical small garden trowel</t>
         </is>
       </c>
-      <c r="H143" s="57" t="n">
+      <c r="H143" s="40" t="n">
         <v>6.28</v>
       </c>
       <c r="I143" s="41" t="inlineStr">
@@ -25697,7 +25666,7 @@
         <v>5</v>
       </c>
       <c r="R143" s="37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S143" s="38" t="inlineStr">
         <is>
@@ -25735,7 +25704,7 @@
           <t>The Deuce of Spades UL Trowel</t>
         </is>
       </c>
-      <c r="F144" s="56" t="n">
+      <c r="F144" s="39" t="n">
         <v>0.6</v>
       </c>
       <c r="G144" s="38" t="inlineStr">
@@ -25743,7 +25712,7 @@
           <t>per TheTentLab spec, titanium</t>
         </is>
       </c>
-      <c r="H144" s="57" t="n">
+      <c r="H144" s="40" t="n">
         <v>20.95</v>
       </c>
       <c r="I144" s="41" t="inlineStr">
@@ -25790,7 +25759,7 @@
         <v>4</v>
       </c>
       <c r="R144" s="37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S144" s="38" t="inlineStr">
         <is>
@@ -25828,7 +25797,7 @@
           <t>Full-Tang Stainless Prospecting Hand Shovel</t>
         </is>
       </c>
-      <c r="F145" s="56" t="n">
+      <c r="F145" s="39" t="n">
         <v>10</v>
       </c>
       <c r="G145" s="38" t="inlineStr">
@@ -25836,7 +25805,7 @@
           <t>estimate, full-tang stainless prospecting trowel</t>
         </is>
       </c>
-      <c r="H145" s="57" t="n">
+      <c r="H145" s="40" t="n">
         <v>28</v>
       </c>
       <c r="I145" s="41" t="inlineStr">
@@ -25883,7 +25852,7 @@
         <v>3</v>
       </c>
       <c r="R145" s="37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S145" s="38" t="inlineStr"/>
       <c r="T145">
@@ -25917,7 +25886,7 @@
           <t>Plain 5-Gallon Bucket</t>
         </is>
       </c>
-      <c r="F146" s="56" t="n">
+      <c r="F146" s="39" t="n">
         <v>32</v>
       </c>
       <c r="G146" s="38" t="inlineStr">
@@ -25925,7 +25894,7 @@
           <t>empty bucket estimate</t>
         </is>
       </c>
-      <c r="H146" s="57" t="n">
+      <c r="H146" s="40" t="n">
         <v>5</v>
       </c>
       <c r="I146" s="41" t="inlineStr">
@@ -26010,7 +25979,7 @@
           <t>5-Gallon Bucket with Built-In Classifier Lid</t>
         </is>
       </c>
-      <c r="F147" s="56" t="n">
+      <c r="F147" s="39" t="n">
         <v>40</v>
       </c>
       <c r="G147" s="38" t="inlineStr">
@@ -26018,7 +25987,7 @@
           <t>bucket + mesh classifier lid, estimate</t>
         </is>
       </c>
-      <c r="H147" s="57" t="n">
+      <c r="H147" s="40" t="n">
         <v>28</v>
       </c>
       <c r="I147" s="41" t="inlineStr">
@@ -26099,7 +26068,7 @@
           <t>Bucket Riffle/Classifier Combo Kit</t>
         </is>
       </c>
-      <c r="F148" s="56" t="n">
+      <c r="F148" s="39" t="n">
         <v>48</v>
       </c>
       <c r="G148" s="38" t="inlineStr">
@@ -26107,7 +26076,7 @@
           <t>estimate, full combo kit</t>
         </is>
       </c>
-      <c r="H148" s="57" t="n">
+      <c r="H148" s="40" t="n">
         <v>45</v>
       </c>
       <c r="I148" s="41" t="inlineStr">
@@ -26188,7 +26157,7 @@
           <t>Estwing BP-14 pan + ASR 1/2" classifier + plastic snuffer + 2 vials</t>
         </is>
       </c>
-      <c r="F149" s="56" t="n">
+      <c r="F149" s="39" t="n">
         <v>30</v>
       </c>
       <c r="G149" s="38" t="inlineStr">
@@ -26196,7 +26165,7 @@
           <t>sum of budget-tier components above</t>
         </is>
       </c>
-      <c r="H149" s="57" t="n">
+      <c r="H149" s="40" t="n">
         <v>7.26</v>
       </c>
       <c r="I149" s="41" t="inlineStr">
@@ -26281,7 +26250,7 @@
           <t>Compact Prospecting Kit (pan, 2 classifiers, magnet, magnifier, 3 snuffers, 3 vials) minus sluice</t>
         </is>
       </c>
-      <c r="F150" s="56" t="n">
+      <c r="F150" s="39" t="n">
         <v>38</v>
       </c>
       <c r="G150" s="38" t="inlineStr">
@@ -26289,7 +26258,7 @@
           <t>per typical bundled-kit component list, sluice parts excluded/left home</t>
         </is>
       </c>
-      <c r="H150" s="57" t="n">
+      <c r="H150" s="40" t="n">
         <v>40</v>
       </c>
       <c r="I150" s="41" t="inlineStr">
@@ -26374,7 +26343,7 @@
           <t>Curated kit: Garrett 14" Gravity Trap pan + stainless classifier set + stainless crevice tools + brass snuffer, packed in a dedicated mesh stuff sack</t>
         </is>
       </c>
-      <c r="F151" s="56" t="n">
+      <c r="F151" s="39" t="n">
         <v>52</v>
       </c>
       <c r="G151" s="38" t="inlineStr">
@@ -26382,7 +26351,7 @@
           <t>sum of premium/value-tier components above plus ~2oz mesh sack</t>
         </is>
       </c>
-      <c r="H151" s="57" t="n">
+      <c r="H151" s="40" t="n">
         <v>69.98999999999999</v>
       </c>
       <c r="I151" s="41" t="inlineStr">
@@ -26467,7 +26436,7 @@
           <t>Trestles 30</t>
         </is>
       </c>
-      <c r="F152" s="56" t="n">
+      <c r="F152" s="39" t="n">
         <v>52</v>
       </c>
       <c r="G152" s="38" t="inlineStr">
@@ -26475,7 +26444,7 @@
           <t>Men's Reg listed 1450-1560g (~51-55oz) synthetic fill per REI spec</t>
         </is>
       </c>
-      <c r="H152" s="57" t="n">
+      <c r="H152" s="40" t="n">
         <v>99.95</v>
       </c>
       <c r="I152" s="41" t="inlineStr">
@@ -26560,7 +26529,7 @@
           <t>Revelation 30 (stock, 850fp)</t>
         </is>
       </c>
-      <c r="F153" s="56" t="n">
+      <c r="F153" s="39" t="n">
         <v>19.8</v>
       </c>
       <c r="G153" s="38" t="inlineStr">
@@ -26568,7 +26537,7 @@
           <t>Reg/Reg stock 850fp ~19.8oz per EE/retailer specs; all 30F+ quilts now include a draft collar</t>
         </is>
       </c>
-      <c r="H153" s="57" t="n">
+      <c r="H153" s="40" t="n">
         <v>365</v>
       </c>
       <c r="I153" s="41" t="inlineStr">
@@ -26653,7 +26622,7 @@
           <t>Flex 30</t>
         </is>
       </c>
-      <c r="F154" s="56" t="n">
+      <c r="F154" s="39" t="n">
         <v>20.3</v>
       </c>
       <c r="G154" s="38" t="inlineStr">
@@ -26661,7 +26630,7 @@
           <t>~575g (20.3oz) regular, 900fp water-resistant down, per Katabatic/retailer specs</t>
         </is>
       </c>
-      <c r="H154" s="57" t="n">
+      <c r="H154" s="40" t="n">
         <v>365</v>
       </c>
       <c r="I154" s="41" t="inlineStr">
@@ -26956,7 +26925,7 @@
       <c r="C2" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="46" t="n">
+      <c r="D2" s="13" t="n">
         <v>79.98999999999999</v>
       </c>
       <c r="E2" s="10" t="inlineStr"/>
@@ -26980,7 +26949,7 @@
       <c r="C3" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="D3" s="46" t="n">
+      <c r="D3" s="13" t="n">
         <v>36</v>
       </c>
       <c r="E3" s="10" t="inlineStr"/>
@@ -27004,7 +26973,7 @@
       <c r="C4" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="46" t="n">
+      <c r="D4" s="13" t="n">
         <v>40</v>
       </c>
       <c r="E4" s="10" t="inlineStr"/>
@@ -27028,7 +26997,7 @@
       <c r="C5" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="46" t="n">
+      <c r="D5" s="13" t="n">
         <v>130</v>
       </c>
       <c r="E5" s="10" t="inlineStr"/>
@@ -27052,7 +27021,7 @@
       <c r="C6" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="46" t="n">
+      <c r="D6" s="13" t="n">
         <v>34</v>
       </c>
       <c r="E6" s="10" t="inlineStr"/>
@@ -27076,7 +27045,7 @@
       <c r="C7" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="46" t="n">
+      <c r="D7" s="13" t="n">
         <v>15</v>
       </c>
       <c r="E7" s="10" t="inlineStr"/>
@@ -27100,7 +27069,7 @@
       <c r="C8" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="46" t="n">
+      <c r="D8" s="13" t="n">
         <v>40</v>
       </c>
       <c r="E8" s="10" t="inlineStr"/>
@@ -27124,7 +27093,7 @@
       <c r="C9" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="46" t="n">
+      <c r="D9" s="13" t="n">
         <v>80</v>
       </c>
       <c r="E9" s="10" t="inlineStr"/>
@@ -27148,7 +27117,7 @@
       <c r="C10" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="46" t="n">
+      <c r="D10" s="13" t="n">
         <v>40</v>
       </c>
       <c r="E10" s="10" t="inlineStr"/>
@@ -27172,7 +27141,7 @@
       <c r="C11" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="D11" s="46" t="n">
+      <c r="D11" s="13" t="n">
         <v>47</v>
       </c>
       <c r="E11" s="10" t="inlineStr"/>
@@ -27196,7 +27165,7 @@
       <c r="C12" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="D12" s="46" t="n">
+      <c r="D12" s="13" t="n">
         <v>54</v>
       </c>
       <c r="E12" s="10" t="inlineStr"/>
@@ -27220,7 +27189,7 @@
       <c r="C13" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="46" t="n">
+      <c r="D13" s="13" t="n">
         <v>50</v>
       </c>
       <c r="E13" s="10" t="inlineStr"/>
@@ -27244,7 +27213,7 @@
       <c r="C14" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="46" t="n">
+      <c r="D14" s="13" t="n">
         <v>15</v>
       </c>
       <c r="E14" s="10" t="inlineStr"/>
@@ -27268,7 +27237,7 @@
       <c r="C15" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="46" t="n">
+      <c r="D15" s="13" t="n">
         <v>76</v>
       </c>
       <c r="E15" s="10" t="inlineStr"/>
@@ -27292,7 +27261,7 @@
       <c r="C16" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="46" t="n">
+      <c r="D16" s="13" t="n">
         <v>55</v>
       </c>
       <c r="E16" s="10" t="inlineStr"/>
@@ -27316,7 +27285,7 @@
       <c r="C17" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="46" t="n">
+      <c r="D17" s="13" t="n">
         <v>10</v>
       </c>
       <c r="E17" s="10" t="inlineStr"/>
@@ -27340,7 +27309,7 @@
       <c r="C18" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="D18" s="46" t="n">
+      <c r="D18" s="13" t="n">
         <v>58</v>
       </c>
       <c r="E18" s="10" t="inlineStr"/>
@@ -27364,7 +27333,7 @@
       <c r="C19" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="46" t="n">
+      <c r="D19" s="13" t="n">
         <v>15</v>
       </c>
       <c r="E19" s="10" t="inlineStr"/>
@@ -27388,7 +27357,7 @@
       <c r="C20" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="D20" s="46" t="n">
+      <c r="D20" s="13" t="n">
         <v>24</v>
       </c>
       <c r="E20" s="10" t="inlineStr"/>
@@ -27412,7 +27381,7 @@
       <c r="C21" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="D21" s="46" t="n">
+      <c r="D21" s="13" t="n">
         <v>18</v>
       </c>
       <c r="E21" s="10" t="inlineStr"/>
@@ -27436,7 +27405,7 @@
       <c r="C22" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="46" t="n">
+      <c r="D22" s="13" t="n">
         <v>8</v>
       </c>
       <c r="E22" s="10" t="inlineStr"/>
@@ -27460,7 +27429,7 @@
       <c r="C23" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="46" t="n">
+      <c r="D23" s="13" t="n">
         <v>12</v>
       </c>
       <c r="E23" s="10" t="inlineStr"/>
@@ -27484,7 +27453,7 @@
       <c r="C24" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="46" t="n">
+      <c r="D24" s="13" t="n">
         <v>65</v>
       </c>
       <c r="E24" s="10" t="inlineStr"/>
@@ -27508,7 +27477,7 @@
       <c r="C25" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="46" t="n">
+      <c r="D25" s="13" t="n">
         <v>20</v>
       </c>
       <c r="E25" s="10" t="inlineStr"/>
@@ -27526,18 +27495,17 @@
         </is>
       </c>
       <c r="C26" s="42" t="n"/>
-      <c r="D26" s="48">
+      <c r="D26" s="16">
         <f>SUM(D2:D25)</f>
         <v/>
       </c>
       <c r="E26" s="42" t="n"/>
       <c r="F26" s="42" t="n"/>
     </row>
-    <row r="27"/>
     <row r="28">
       <c r="B28" s="43" t="inlineStr">
         <is>
-          <t>Rough total ~$800-870, or ~$135-145/person split 6 ways. Personal-only rows (chairs, vials, snuffers) are cheap enough to just buy 6 outright.</t>
+          <t>Rough total ~$800-870, or ~$160-175/person split 5 ways. Personal-only rows (chairs, vials, snuffers) are cheap enough to just buy 5 outright.</t>
         </is>
       </c>
     </row>
@@ -27586,7 +27554,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>

--- a/Gear_Picker.xlsx
+++ b/Gear_Picker.xlsx
@@ -16828,7 +16828,7 @@
       </c>
       <c r="I47" s="41" t="inlineStr">
         <is>
-          <t>https://www.petzl.com/US/en/Sport/headlamps/TIKKINA</t>
+          <t>https://www.petzl.com/US/en/Sport/Headlamps/TIKKINA</t>
         </is>
       </c>
       <c r="J47" s="38" t="inlineStr">
